--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B5F5DB-8C8E-4C0C-AFE8-2B7348DA38B5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FD68A2-623F-49E5-B3FD-9912C8A3561C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="86" spans="1:16" s="2" customFormat="1">
       <c r="A86" s="135" t="s">
-        <v>280</v>
+        <v>170</v>
       </c>
       <c r="B86" s="38" t="s">
         <v>281</v>

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FD68A2-623F-49E5-B3FD-9912C8A3561C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F126E1F7-4A47-4091-9F3B-A758DC04AEE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5902" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="762">
   <si>
     <t>DAFTAR PENDUDUK RT 06 - RW 14</t>
   </si>
@@ -832,9 +832,6 @@
     <t>B5-10</t>
   </si>
   <si>
-    <t>BEURANGONG</t>
-  </si>
-  <si>
     <t>B5-11</t>
   </si>
   <si>
@@ -2309,6 +2306,18 @@
   </si>
   <si>
     <t>RIFQIU ATTAUFIQI</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>ERNY NURLAENY</t>
+  </si>
+  <si>
+    <t>SOFIFAH NURFAHRANI</t>
+  </si>
+  <si>
+    <t>WIDURI NURSYAHRANI</t>
   </si>
 </sst>
 </file>
@@ -3871,10 +3880,10 @@
         <v>27</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O6" s="18" t="s">
         <v>30</v>
@@ -3922,10 +3931,10 @@
         <v>27</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O7" s="135" t="s">
         <v>36</v>
@@ -3969,10 +3978,10 @@
         <v>27</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O8" s="136"/>
       <c r="P8" s="19" t="s">
@@ -4014,10 +4023,10 @@
         <v>27</v>
       </c>
       <c r="M9" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N9" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O9" s="136"/>
       <c r="P9" s="19" t="s">
@@ -4062,7 +4071,7 @@
         <v>49</v>
       </c>
       <c r="N10" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O10" s="136"/>
       <c r="P10" s="19" t="s">
@@ -4104,10 +4113,10 @@
         <v>27</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O11" s="137"/>
       <c r="P11" s="19" t="s">
@@ -4153,10 +4162,10 @@
         <v>27</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N12" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O12" s="135" t="s">
         <v>30</v>
@@ -4200,10 +4209,10 @@
         <v>27</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O13" s="137"/>
       <c r="P13" s="46" t="s">
@@ -4274,7 +4283,7 @@
         <v>98</v>
       </c>
       <c r="N15" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O15" s="135" t="s">
         <v>30</v>
@@ -4287,7 +4296,7 @@
       <c r="A16" s="136"/>
       <c r="B16" s="29"/>
       <c r="C16" s="29" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>39</v>
@@ -4321,7 +4330,7 @@
         <v>98</v>
       </c>
       <c r="N16" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O16" s="136"/>
       <c r="P16" s="19" t="s">
@@ -4332,7 +4341,7 @@
       <c r="A17" s="136"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D17" s="31" t="s">
         <v>39</v>
@@ -4363,10 +4372,10 @@
         <v>27</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N17" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O17" s="136"/>
       <c r="P17" s="19" t="s">
@@ -4377,7 +4386,7 @@
       <c r="A18" s="136"/>
       <c r="B18" s="127"/>
       <c r="C18" s="127" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D18" s="116" t="s">
         <v>21</v>
@@ -4408,10 +4417,10 @@
         <v>27</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N18" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O18" s="136"/>
       <c r="P18" s="19" t="s">
@@ -4422,7 +4431,7 @@
       <c r="A19" s="137"/>
       <c r="B19" s="26"/>
       <c r="C19" s="134" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D19" s="116" t="s">
         <v>39</v>
@@ -4453,10 +4462,10 @@
         <v>27</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N19" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O19" s="137"/>
       <c r="P19" s="19" t="s">
@@ -4502,10 +4511,10 @@
         <v>27</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O20" s="135" t="s">
         <v>36</v>
@@ -4549,10 +4558,10 @@
         <v>27</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O21" s="136"/>
       <c r="P21" s="19" t="s">
@@ -4597,7 +4606,7 @@
         <v>68</v>
       </c>
       <c r="N22" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O22" s="136"/>
       <c r="P22" s="19" t="s">
@@ -4642,7 +4651,7 @@
         <v>49</v>
       </c>
       <c r="N23" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O23" s="137"/>
       <c r="P23" s="19" t="s">
@@ -4688,10 +4697,10 @@
         <v>27</v>
       </c>
       <c r="M24" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N24" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O24" s="135" t="s">
         <v>36</v>
@@ -4735,10 +4744,10 @@
         <v>27</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N25" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O25" s="136"/>
       <c r="P25" s="19" t="s">
@@ -4783,7 +4792,7 @@
         <v>49</v>
       </c>
       <c r="N26" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O26" s="136"/>
       <c r="P26" s="19" t="s">
@@ -4794,7 +4803,7 @@
       <c r="A27" s="137"/>
       <c r="B27" s="35"/>
       <c r="C27" s="35" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>21</v>
@@ -4825,10 +4834,10 @@
         <v>27</v>
       </c>
       <c r="M27" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N27" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O27" s="137"/>
       <c r="P27" s="19" t="s">
@@ -4874,10 +4883,10 @@
         <v>77</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N28" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O28" s="135" t="s">
         <v>36</v>
@@ -4921,10 +4930,10 @@
         <v>27</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N29" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O29" s="136"/>
       <c r="P29" s="19" t="s">
@@ -4969,7 +4978,7 @@
         <v>49</v>
       </c>
       <c r="N30" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O30" s="136"/>
       <c r="P30" s="19" t="s">
@@ -5014,7 +5023,7 @@
         <v>61</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O31" s="136"/>
       <c r="P31" s="19" t="s">
@@ -5059,7 +5068,7 @@
         <v>83</v>
       </c>
       <c r="N32" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O32" s="137"/>
       <c r="P32" s="19" t="s">
@@ -5105,10 +5114,10 @@
         <v>87</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N33" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O33" s="135" t="s">
         <v>36</v>
@@ -5152,10 +5161,10 @@
         <v>89</v>
       </c>
       <c r="M34" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N34" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O34" s="136"/>
       <c r="P34" s="19" t="s">
@@ -5200,7 +5209,7 @@
         <v>91</v>
       </c>
       <c r="N35" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O35" s="136"/>
       <c r="P35" s="19" t="s">
@@ -5245,7 +5254,7 @@
         <v>61</v>
       </c>
       <c r="N36" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O36" s="136"/>
       <c r="P36" s="19" t="s">
@@ -5287,10 +5296,10 @@
         <v>27</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N37" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O37" s="137"/>
       <c r="P37" s="19" t="s">
@@ -5302,10 +5311,10 @@
         <v>95</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>21</v>
@@ -5339,7 +5348,7 @@
         <v>98</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O38" s="135" t="s">
         <v>30</v>
@@ -5352,7 +5361,7 @@
       <c r="A39" s="136"/>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D39" s="31" t="s">
         <v>39</v>
@@ -5383,10 +5392,10 @@
         <v>27</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N39" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O39" s="136"/>
       <c r="P39" s="46" t="s">
@@ -5397,7 +5406,7 @@
       <c r="A40" s="136"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D40" s="31" t="s">
         <v>21</v>
@@ -5428,10 +5437,10 @@
         <v>27</v>
       </c>
       <c r="M40" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N40" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O40" s="136"/>
       <c r="P40" s="46" t="s">
@@ -5480,7 +5489,7 @@
         <v>105</v>
       </c>
       <c r="N41" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O41" s="135" t="s">
         <v>36</v>
@@ -5527,7 +5536,7 @@
         <v>105</v>
       </c>
       <c r="N42" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O42" s="136"/>
       <c r="P42" s="19" t="s">
@@ -5572,7 +5581,7 @@
         <v>61</v>
       </c>
       <c r="N43" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O43" s="136"/>
       <c r="P43" s="19" t="s">
@@ -5614,10 +5623,10 @@
         <v>27</v>
       </c>
       <c r="M44" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N44" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O44" s="137"/>
       <c r="P44" s="19" t="s">
@@ -5663,10 +5672,10 @@
         <v>112</v>
       </c>
       <c r="M45" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O45" s="135" t="s">
         <v>36</v>
@@ -5710,10 +5719,10 @@
         <v>27</v>
       </c>
       <c r="M46" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N46" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O46" s="136"/>
       <c r="P46" s="19" t="s">
@@ -5758,7 +5767,7 @@
         <v>49</v>
       </c>
       <c r="N47" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O47" s="136"/>
       <c r="P47" s="19" t="s">
@@ -5803,7 +5812,7 @@
         <v>61</v>
       </c>
       <c r="N48" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O48" s="137"/>
       <c r="P48" s="19" t="s">
@@ -5849,10 +5858,10 @@
         <v>27</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O49" s="135" t="s">
         <v>30</v>
@@ -5896,10 +5905,10 @@
         <v>27</v>
       </c>
       <c r="M50" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N50" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O50" s="136"/>
       <c r="P50" s="46" t="s">
@@ -5941,10 +5950,10 @@
         <v>27</v>
       </c>
       <c r="M51" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N51" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O51" s="136"/>
       <c r="P51" s="46" t="s">
@@ -5986,10 +5995,10 @@
         <v>27</v>
       </c>
       <c r="M52" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N52" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O52" s="136"/>
       <c r="P52" s="46" t="s">
@@ -6031,10 +6040,10 @@
         <v>27</v>
       </c>
       <c r="M53" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N53" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O53" s="137"/>
       <c r="P53" s="46" t="s">
@@ -6083,7 +6092,7 @@
         <v>126</v>
       </c>
       <c r="N54" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O54" s="135" t="s">
         <v>36</v>
@@ -6127,10 +6136,10 @@
         <v>27</v>
       </c>
       <c r="M55" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N55" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O55" s="136"/>
       <c r="P55" s="19" t="s">
@@ -6175,7 +6184,7 @@
         <v>91</v>
       </c>
       <c r="N56" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O56" s="136"/>
       <c r="P56" s="19" t="s">
@@ -6220,7 +6229,7 @@
         <v>61</v>
       </c>
       <c r="N57" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O57" s="137"/>
       <c r="P57" s="19" t="s">
@@ -6266,10 +6275,10 @@
         <v>112</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N58" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O58" s="135" t="s">
         <v>36</v>
@@ -6313,10 +6322,10 @@
         <v>112</v>
       </c>
       <c r="M59" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N59" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O59" s="136"/>
       <c r="P59" s="19" t="s">
@@ -6361,7 +6370,7 @@
         <v>91</v>
       </c>
       <c r="N60" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O60" s="136"/>
       <c r="P60" s="19" t="s">
@@ -6406,7 +6415,7 @@
         <v>61</v>
       </c>
       <c r="N61" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O61" s="136"/>
       <c r="P61" s="19" t="s">
@@ -6448,10 +6457,10 @@
         <v>112</v>
       </c>
       <c r="M62" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N62" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O62" s="137"/>
       <c r="P62" s="19" t="s">
@@ -6497,10 +6506,10 @@
         <v>27</v>
       </c>
       <c r="M63" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N63" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O63" s="135" t="s">
         <v>30</v>
@@ -6544,10 +6553,10 @@
         <v>27</v>
       </c>
       <c r="M64" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N64" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O64" s="136"/>
       <c r="P64" s="46" t="s">
@@ -6589,10 +6598,10 @@
         <v>27</v>
       </c>
       <c r="M65" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N65" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O65" s="136"/>
       <c r="P65" s="46" t="s">
@@ -6637,7 +6646,7 @@
         <v>68</v>
       </c>
       <c r="N66" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O66" s="136"/>
       <c r="P66" s="46" t="s">
@@ -6682,7 +6691,7 @@
         <v>61</v>
       </c>
       <c r="N67" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O67" s="137"/>
       <c r="P67" s="46" t="s">
@@ -6728,10 +6737,10 @@
         <v>27</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N68" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O68" s="135" t="s">
         <v>36</v>
@@ -6775,10 +6784,10 @@
         <v>27</v>
       </c>
       <c r="M69" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N69" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O69" s="136"/>
       <c r="P69" s="19" t="s">
@@ -6823,7 +6832,7 @@
         <v>91</v>
       </c>
       <c r="N70" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O70" s="136"/>
       <c r="P70" s="19" t="s">
@@ -6868,7 +6877,7 @@
         <v>61</v>
       </c>
       <c r="N71" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O71" s="137"/>
       <c r="P71" s="19" t="s">
@@ -6914,10 +6923,10 @@
         <v>27</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O72" s="135" t="s">
         <v>36</v>
@@ -6961,10 +6970,10 @@
         <v>27</v>
       </c>
       <c r="M73" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N73" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O73" s="136"/>
       <c r="P73" s="19" t="s">
@@ -7009,7 +7018,7 @@
         <v>49</v>
       </c>
       <c r="N74" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O74" s="136"/>
       <c r="P74" s="19" t="s">
@@ -7054,7 +7063,7 @@
         <v>61</v>
       </c>
       <c r="N75" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O75" s="137"/>
       <c r="P75" s="19" t="s">
@@ -7066,10 +7075,10 @@
         <v>154</v>
       </c>
       <c r="B76" s="93" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C76" s="93" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D76" s="24" t="s">
         <v>39</v>
@@ -7088,7 +7097,7 @@
         <v>69</v>
       </c>
       <c r="I76" s="25" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="J76" s="35" t="s">
         <v>25</v>
@@ -7100,10 +7109,10 @@
         <v>27</v>
       </c>
       <c r="M76" s="50" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N76" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O76" s="140" t="s">
         <v>30</v>
@@ -7116,7 +7125,7 @@
       <c r="A77" s="139"/>
       <c r="B77" s="94"/>
       <c r="C77" s="95" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D77" s="31" t="s">
         <v>21</v>
@@ -7147,10 +7156,10 @@
         <v>27</v>
       </c>
       <c r="M77" s="50" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N77" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O77" s="139"/>
       <c r="P77" s="46" t="s">
@@ -7196,10 +7205,10 @@
         <v>112</v>
       </c>
       <c r="M78" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N78" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O78" s="135" t="s">
         <v>36</v>
@@ -7243,10 +7252,10 @@
         <v>112</v>
       </c>
       <c r="M79" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N79" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O79" s="136"/>
       <c r="P79" s="19" t="s">
@@ -7291,7 +7300,7 @@
         <v>162</v>
       </c>
       <c r="N80" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O80" s="136"/>
       <c r="P80" s="19" t="s">
@@ -7333,10 +7342,10 @@
         <v>27</v>
       </c>
       <c r="M81" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N81" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O81" s="137"/>
       <c r="P81" s="19" t="s">
@@ -7382,10 +7391,10 @@
         <v>27</v>
       </c>
       <c r="M82" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N82" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O82" s="135" t="s">
         <v>36</v>
@@ -7429,10 +7438,10 @@
         <v>27</v>
       </c>
       <c r="M83" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N83" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O83" s="136"/>
       <c r="P83" s="19" t="s">
@@ -7474,10 +7483,10 @@
         <v>27</v>
       </c>
       <c r="M84" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N84" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O84" s="136"/>
       <c r="P84" s="19" t="s">
@@ -7522,7 +7531,7 @@
         <v>61</v>
       </c>
       <c r="N85" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O85" s="137"/>
       <c r="P85" s="19" t="s">
@@ -7534,10 +7543,10 @@
         <v>170</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D86" s="117" t="s">
         <v>21</v>
@@ -7571,7 +7580,7 @@
         <v>248</v>
       </c>
       <c r="N86" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O86" s="135" t="s">
         <v>30</v>
@@ -7584,7 +7593,7 @@
       <c r="A87" s="136"/>
       <c r="B87" s="29"/>
       <c r="C87" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D87" s="118" t="s">
         <v>39</v>
@@ -7593,7 +7602,7 @@
         <v>40</v>
       </c>
       <c r="F87" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G87" s="54">
         <v>30165</v>
@@ -7618,7 +7627,7 @@
         <v>248</v>
       </c>
       <c r="N87" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O87" s="136"/>
       <c r="P87" s="19" t="s">
@@ -7629,7 +7638,7 @@
       <c r="A88" s="136"/>
       <c r="B88" s="29"/>
       <c r="C88" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D88" s="118" t="s">
         <v>21</v>
@@ -7638,7 +7647,7 @@
         <v>44</v>
       </c>
       <c r="F88" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G88" s="54">
         <v>39711</v>
@@ -7663,7 +7672,7 @@
         <v>49</v>
       </c>
       <c r="N88" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O88" s="136"/>
       <c r="P88" s="19" t="s">
@@ -7674,7 +7683,7 @@
       <c r="A89" s="136"/>
       <c r="B89" s="29"/>
       <c r="C89" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D89" s="118" t="s">
         <v>21</v>
@@ -7708,7 +7717,7 @@
         <v>61</v>
       </c>
       <c r="N89" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O89" s="136"/>
       <c r="P89" s="19" t="s">
@@ -7719,7 +7728,7 @@
       <c r="A90" s="137"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D90" s="119" t="s">
         <v>21</v>
@@ -7750,10 +7759,10 @@
         <v>27</v>
       </c>
       <c r="M90" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N90" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O90" s="137"/>
       <c r="P90" s="19" t="s">
@@ -7765,10 +7774,10 @@
         <v>171</v>
       </c>
       <c r="B91" s="38" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D91" s="24" t="s">
         <v>21</v>
@@ -7799,10 +7808,10 @@
         <v>27</v>
       </c>
       <c r="M91" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N91" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O91" s="135" t="s">
         <v>30</v>
@@ -7815,7 +7824,7 @@
       <c r="A92" s="136"/>
       <c r="B92" s="29"/>
       <c r="C92" s="29" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D92" s="31" t="s">
         <v>39</v>
@@ -7846,10 +7855,10 @@
         <v>27</v>
       </c>
       <c r="M92" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N92" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O92" s="136"/>
       <c r="P92" s="46" t="s">
@@ -7860,7 +7869,7 @@
       <c r="A93" s="136"/>
       <c r="B93" s="91"/>
       <c r="C93" s="91" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D93" s="97" t="s">
         <v>39</v>
@@ -7891,10 +7900,10 @@
         <v>27</v>
       </c>
       <c r="M93" s="91" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N93" s="91" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O93" s="136"/>
       <c r="P93" s="46" t="s">
@@ -7940,10 +7949,10 @@
         <v>27</v>
       </c>
       <c r="M94" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N94" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O94" s="135" t="s">
         <v>36</v>
@@ -7987,10 +7996,10 @@
         <v>27</v>
       </c>
       <c r="M95" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N95" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O95" s="136"/>
       <c r="P95" s="19" t="s">
@@ -8032,10 +8041,10 @@
         <v>27</v>
       </c>
       <c r="M96" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N96" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O96" s="136"/>
       <c r="P96" s="19" t="s">
@@ -8080,7 +8089,7 @@
         <v>61</v>
       </c>
       <c r="N97" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O97" s="137"/>
       <c r="P97" s="19" t="s">
@@ -8126,10 +8135,10 @@
         <v>27</v>
       </c>
       <c r="M98" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N98" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O98" s="135" t="s">
         <v>30</v>
@@ -8173,10 +8182,10 @@
         <v>27</v>
       </c>
       <c r="M99" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N99" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O99" s="136"/>
       <c r="P99" s="19" t="s">
@@ -8218,10 +8227,10 @@
         <v>27</v>
       </c>
       <c r="M100" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N100" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O100" s="136"/>
       <c r="P100" s="19" t="s">
@@ -8267,10 +8276,10 @@
         <v>27</v>
       </c>
       <c r="M101" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N101" s="32" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O101" s="138" t="s">
         <v>36</v>
@@ -8317,7 +8326,7 @@
         <v>189</v>
       </c>
       <c r="N102" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O102" s="138"/>
       <c r="P102" s="19" t="s">
@@ -8359,10 +8368,10 @@
         <v>27</v>
       </c>
       <c r="M103" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N103" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O103" s="138"/>
       <c r="P103" s="19" t="s">
@@ -8404,10 +8413,10 @@
         <v>27</v>
       </c>
       <c r="M104" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N104" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O104" s="138"/>
       <c r="P104" s="19" t="s">
@@ -8452,7 +8461,7 @@
         <v>49</v>
       </c>
       <c r="N105" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O105" s="138"/>
       <c r="P105" s="19" t="s">
@@ -8497,7 +8506,7 @@
         <v>61</v>
       </c>
       <c r="N106" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O106" s="139"/>
       <c r="P106" s="19" t="s">
@@ -8543,10 +8552,10 @@
         <v>27</v>
       </c>
       <c r="M107" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N107" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O107" s="135" t="s">
         <v>36</v>
@@ -8590,10 +8599,10 @@
         <v>27</v>
       </c>
       <c r="M108" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N108" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O108" s="136"/>
       <c r="P108" s="19" t="s">
@@ -8635,10 +8644,10 @@
         <v>27</v>
       </c>
       <c r="M109" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N109" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O109" s="136"/>
       <c r="P109" s="19" t="s">
@@ -8683,7 +8692,7 @@
         <v>49</v>
       </c>
       <c r="N110" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O110" s="136"/>
       <c r="P110" s="19" t="s">
@@ -8728,7 +8737,7 @@
         <v>61</v>
       </c>
       <c r="N111" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O111" s="136"/>
       <c r="P111" s="19" t="s">
@@ -8773,7 +8782,7 @@
         <v>83</v>
       </c>
       <c r="N112" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O112" s="137"/>
       <c r="P112" s="19" t="s">
@@ -8822,7 +8831,7 @@
         <v>204</v>
       </c>
       <c r="N113" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O113" s="135" t="s">
         <v>36</v>
@@ -8869,7 +8878,7 @@
         <v>126</v>
       </c>
       <c r="N114" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O114" s="136"/>
       <c r="P114" s="19" t="s">
@@ -8914,7 +8923,7 @@
         <v>61</v>
       </c>
       <c r="N115" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O115" s="136"/>
       <c r="P115" s="19" t="s">
@@ -8959,7 +8968,7 @@
         <v>83</v>
       </c>
       <c r="N116" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O116" s="137"/>
       <c r="P116" s="19" t="s">
@@ -9005,10 +9014,10 @@
         <v>27</v>
       </c>
       <c r="M117" s="25" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N117" s="32" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O117" s="135" t="s">
         <v>30</v>
@@ -9052,10 +9061,10 @@
         <v>27</v>
       </c>
       <c r="M118" s="25" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N118" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O118" s="136"/>
       <c r="P118" s="46" t="s">
@@ -9100,7 +9109,7 @@
         <v>49</v>
       </c>
       <c r="N119" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O119" s="136"/>
       <c r="P119" s="46" t="s">
@@ -9142,10 +9151,10 @@
         <v>27</v>
       </c>
       <c r="M120" s="102" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N120" s="102" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O120" s="137"/>
       <c r="P120" s="46" t="s">
@@ -9191,10 +9200,10 @@
         <v>27</v>
       </c>
       <c r="M121" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N121" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O121" s="135" t="s">
         <v>36</v>
@@ -9238,10 +9247,10 @@
         <v>112</v>
       </c>
       <c r="M122" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N122" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O122" s="136"/>
       <c r="P122" s="19" t="s">
@@ -9286,7 +9295,7 @@
         <v>91</v>
       </c>
       <c r="N123" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O123" s="137"/>
       <c r="P123" s="19" t="s">
@@ -9332,10 +9341,10 @@
         <v>27</v>
       </c>
       <c r="M124" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N124" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O124" s="135" t="s">
         <v>36</v>
@@ -9379,10 +9388,10 @@
         <v>27</v>
       </c>
       <c r="M125" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N125" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O125" s="136"/>
       <c r="P125" s="19" t="s">
@@ -9427,7 +9436,7 @@
         <v>61</v>
       </c>
       <c r="N126" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O126" s="137"/>
       <c r="P126" s="19" t="s">
@@ -9436,13 +9445,13 @@
     </row>
     <row r="127" spans="1:16" s="2" customFormat="1">
       <c r="A127" s="135" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B127" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C127" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D127" s="119" t="s">
         <v>39</v>
@@ -9461,7 +9470,7 @@
         <v>33</v>
       </c>
       <c r="I127" s="26" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J127" s="35" t="s">
         <v>25</v>
@@ -9473,10 +9482,10 @@
         <v>27</v>
       </c>
       <c r="M127" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N127" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O127" s="135" t="s">
         <v>30</v>
@@ -9489,7 +9498,7 @@
       <c r="A128" s="136"/>
       <c r="B128" s="26"/>
       <c r="C128" s="26" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D128" s="117" t="s">
         <v>21</v>
@@ -9523,7 +9532,7 @@
         <v>49</v>
       </c>
       <c r="N128" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O128" s="136"/>
       <c r="P128" s="19" t="s">
@@ -9534,7 +9543,7 @@
       <c r="A129" s="137"/>
       <c r="B129" s="26"/>
       <c r="C129" s="26" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D129" s="97" t="s">
         <v>39</v>
@@ -9568,7 +9577,7 @@
         <v>61</v>
       </c>
       <c r="N129" s="32" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O129" s="137"/>
       <c r="P129" s="19" t="s">
@@ -9577,7 +9586,7 @@
     </row>
     <row r="130" spans="1:16" s="2" customFormat="1">
       <c r="A130" s="72" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B130" s="68"/>
       <c r="C130" s="68"/>
@@ -9636,10 +9645,10 @@
         <v>27</v>
       </c>
       <c r="M131" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N131" s="20" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O131" s="135" t="s">
         <v>30</v>
@@ -9683,10 +9692,10 @@
         <v>27</v>
       </c>
       <c r="M132" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N132" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O132" s="137"/>
       <c r="P132" s="19" t="s">
@@ -9698,10 +9707,10 @@
         <v>228</v>
       </c>
       <c r="B133" s="128" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C133" s="128" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D133" s="24" t="s">
         <v>21</v>
@@ -9735,7 +9744,7 @@
         <v>98</v>
       </c>
       <c r="N133" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O133" s="135" t="s">
         <v>30</v>
@@ -9748,7 +9757,7 @@
       <c r="A134" s="136"/>
       <c r="B134" s="29"/>
       <c r="C134" s="30" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D134" s="31" t="s">
         <v>39</v>
@@ -9779,10 +9788,10 @@
         <v>27</v>
       </c>
       <c r="M134" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N134" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O134" s="136"/>
       <c r="P134" s="19" t="s">
@@ -9793,7 +9802,7 @@
       <c r="A135" s="136"/>
       <c r="B135" s="91"/>
       <c r="C135" s="36" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D135" s="97" t="s">
         <v>39</v>
@@ -9824,10 +9833,10 @@
         <v>27</v>
       </c>
       <c r="M135" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N135" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O135" s="136"/>
       <c r="P135" s="19" t="s">
@@ -9838,7 +9847,7 @@
       <c r="A136" s="136"/>
       <c r="B136" s="91"/>
       <c r="C136" s="36" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D136" s="117" t="s">
         <v>21</v>
@@ -9872,7 +9881,7 @@
         <v>49</v>
       </c>
       <c r="N136" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O136" s="136"/>
       <c r="P136" s="19" t="s">
@@ -9883,7 +9892,7 @@
       <c r="A137" s="137"/>
       <c r="B137" s="35"/>
       <c r="C137" s="36" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D137" s="37" t="s">
         <v>21</v>
@@ -9914,10 +9923,10 @@
         <v>27</v>
       </c>
       <c r="M137" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N137" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O137" s="137"/>
       <c r="P137" s="19" t="s">
@@ -9926,13 +9935,13 @@
     </row>
     <row r="138" spans="1:16" s="2" customFormat="1">
       <c r="A138" s="120" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B138" s="150" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C138" s="150" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D138" s="123" t="s">
         <v>21</v>
@@ -9963,10 +9972,10 @@
         <v>27</v>
       </c>
       <c r="M138" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N138" s="126" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O138" s="120" t="s">
         <v>30</v>
@@ -9977,13 +9986,13 @@
     </row>
     <row r="139" spans="1:16" s="2" customFormat="1">
       <c r="A139" s="160" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B139" s="152" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C139" s="155" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D139" s="121" t="s">
         <v>21</v>
@@ -10014,10 +10023,10 @@
         <v>27</v>
       </c>
       <c r="M139" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N139" s="126" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O139" s="135" t="s">
         <v>30</v>
@@ -10030,7 +10039,7 @@
       <c r="A140" s="160"/>
       <c r="B140" s="153"/>
       <c r="C140" s="156" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D140" s="122" t="s">
         <v>39</v>
@@ -10061,10 +10070,10 @@
         <v>27</v>
       </c>
       <c r="M140" s="25" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N140" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O140" s="136"/>
       <c r="P140" s="46" t="s">
@@ -10075,7 +10084,7 @@
       <c r="A141" s="160"/>
       <c r="B141" s="154"/>
       <c r="C141" s="157" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D141" s="97" t="s">
         <v>39</v>
@@ -10084,7 +10093,7 @@
         <v>44</v>
       </c>
       <c r="F141" s="151" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G141" s="158">
         <v>45621</v>
@@ -10106,10 +10115,10 @@
         <v>27</v>
       </c>
       <c r="M141" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N141" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O141" s="137"/>
       <c r="P141" s="46" t="s">
@@ -10118,13 +10127,13 @@
     </row>
     <row r="142" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
       <c r="A142" s="116" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B142" s="127" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C142" s="127" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D142" s="117" t="s">
         <v>21</v>
@@ -10155,10 +10164,10 @@
         <v>27</v>
       </c>
       <c r="M142" s="25" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N142" s="20" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O142" s="136" t="s">
         <v>36</v>
@@ -10171,7 +10180,7 @@
       <c r="A143" s="116"/>
       <c r="B143" s="26"/>
       <c r="C143" s="134" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D143" s="118" t="s">
         <v>39</v>
@@ -10202,10 +10211,10 @@
         <v>27</v>
       </c>
       <c r="M143" s="25" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N143" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O143" s="136"/>
       <c r="P143" s="19" t="s">
@@ -10216,7 +10225,7 @@
       <c r="A144" s="116"/>
       <c r="B144" s="26"/>
       <c r="C144" s="134" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D144" s="97" t="s">
         <v>39</v>
@@ -10247,10 +10256,10 @@
         <v>27</v>
       </c>
       <c r="M144" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N144" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O144" s="136"/>
       <c r="P144" s="19" t="s">
@@ -10261,7 +10270,7 @@
       <c r="A145" s="116"/>
       <c r="B145" s="26"/>
       <c r="C145" s="134" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D145" s="117" t="s">
         <v>21</v>
@@ -10295,7 +10304,7 @@
         <v>98</v>
       </c>
       <c r="N145" s="126" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O145" s="136"/>
       <c r="P145" s="19" t="s">
@@ -10306,7 +10315,7 @@
       <c r="A146" s="116"/>
       <c r="B146" s="26"/>
       <c r="C146" s="134" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D146" s="118" t="s">
         <v>39</v>
@@ -10315,7 +10324,7 @@
         <v>40</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G146" s="124">
         <v>27706</v>
@@ -10340,7 +10349,7 @@
         <v>98</v>
       </c>
       <c r="N146" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O146" s="136"/>
       <c r="P146" s="19" t="s">
@@ -10351,7 +10360,7 @@
       <c r="A147" s="116"/>
       <c r="B147" s="26"/>
       <c r="C147" s="134" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D147" s="117" t="s">
         <v>21</v>
@@ -10382,10 +10391,10 @@
         <v>27</v>
       </c>
       <c r="M147" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N147" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O147" s="136"/>
       <c r="P147" s="19" t="s">
@@ -10396,7 +10405,7 @@
       <c r="A148" s="116"/>
       <c r="B148" s="26"/>
       <c r="C148" s="134" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D148" s="117" t="s">
         <v>21</v>
@@ -10430,7 +10439,7 @@
         <v>49</v>
       </c>
       <c r="N148" s="126" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O148" s="137"/>
       <c r="P148" s="19" t="s">
@@ -10476,10 +10485,10 @@
         <v>27</v>
       </c>
       <c r="M149" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N149" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O149" s="135" t="s">
         <v>36</v>
@@ -10526,7 +10535,7 @@
         <v>126</v>
       </c>
       <c r="N150" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O150" s="136"/>
       <c r="P150" s="19" t="s">
@@ -10571,7 +10580,7 @@
         <v>91</v>
       </c>
       <c r="N151" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O151" s="136"/>
       <c r="P151" s="19" t="s">
@@ -10657,10 +10666,10 @@
         <v>27</v>
       </c>
       <c r="M153" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N153" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O153" s="135" t="s">
         <v>36</v>
@@ -10704,10 +10713,10 @@
         <v>27</v>
       </c>
       <c r="M154" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N154" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O154" s="136"/>
       <c r="P154" s="19" t="s">
@@ -10752,7 +10761,7 @@
         <v>49</v>
       </c>
       <c r="N155" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O155" s="136"/>
       <c r="P155" s="19" t="s">
@@ -10797,7 +10806,7 @@
         <v>61</v>
       </c>
       <c r="N156" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O156" s="136"/>
       <c r="P156" s="19" t="s">
@@ -10839,10 +10848,10 @@
         <v>27</v>
       </c>
       <c r="M157" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N157" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O157" s="136"/>
       <c r="P157" s="19" t="s">
@@ -10884,10 +10893,10 @@
         <v>27</v>
       </c>
       <c r="M158" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N158" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O158" s="136"/>
       <c r="P158" s="19" t="s">
@@ -10924,10 +10933,10 @@
         <v>27</v>
       </c>
       <c r="M159" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N159" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O159" s="136"/>
       <c r="P159" s="19" t="s">
@@ -10969,10 +10978,10 @@
         <v>27</v>
       </c>
       <c r="M160" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N160" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O160" s="137"/>
       <c r="P160" s="19" t="s">
@@ -11021,7 +11030,7 @@
         <v>248</v>
       </c>
       <c r="N161" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O161" s="135" t="s">
         <v>36</v>
@@ -11068,7 +11077,7 @@
         <v>248</v>
       </c>
       <c r="N162" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O162" s="136"/>
       <c r="P162" s="19" t="s">
@@ -11082,7 +11091,7 @@
         <v>247</v>
       </c>
       <c r="D163" s="31" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E163" s="29" t="s">
         <v>44</v>
@@ -11113,7 +11122,7 @@
         <v>248</v>
       </c>
       <c r="N163" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O163" s="136"/>
       <c r="P163" s="19" t="s">
@@ -11127,7 +11136,7 @@
         <v>249</v>
       </c>
       <c r="D164" s="37" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E164" s="35" t="s">
         <v>44</v>
@@ -11155,10 +11164,10 @@
         <v>27</v>
       </c>
       <c r="M164" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N164" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O164" s="137"/>
       <c r="P164" s="19" t="s">
@@ -11170,10 +11179,10 @@
         <v>251</v>
       </c>
       <c r="B165" s="39" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C165" s="39" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D165" s="24" t="s">
         <v>21</v>
@@ -11204,10 +11213,10 @@
         <v>27</v>
       </c>
       <c r="M165" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N165" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O165" s="141" t="s">
         <v>36</v>
@@ -11220,7 +11229,7 @@
       <c r="A166" s="136"/>
       <c r="B166" s="29"/>
       <c r="C166" s="30" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D166" s="31" t="s">
         <v>39</v>
@@ -11229,7 +11238,7 @@
         <v>40</v>
       </c>
       <c r="F166" s="29" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G166" s="54">
         <v>35026</v>
@@ -11251,10 +11260,10 @@
         <v>27</v>
       </c>
       <c r="M166" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N166" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O166" s="141"/>
       <c r="P166" s="19" t="s">
@@ -11265,7 +11274,7 @@
       <c r="A167" s="137"/>
       <c r="B167" s="35"/>
       <c r="C167" s="36" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D167" s="37" t="s">
         <v>21</v>
@@ -11296,10 +11305,10 @@
         <v>27</v>
       </c>
       <c r="M167" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N167" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O167" s="141"/>
       <c r="P167" s="19" t="s">
@@ -11311,10 +11320,10 @@
         <v>252</v>
       </c>
       <c r="B168" s="99" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C168" s="99" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D168" s="24" t="s">
         <v>21</v>
@@ -11345,10 +11354,10 @@
         <v>27</v>
       </c>
       <c r="M168" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N168" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O168" s="135" t="s">
         <v>30</v>
@@ -11361,7 +11370,7 @@
       <c r="A169" s="138"/>
       <c r="B169" s="32"/>
       <c r="C169" s="106" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D169" s="31" t="s">
         <v>39</v>
@@ -11392,10 +11401,10 @@
         <v>27</v>
       </c>
       <c r="M169" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N169" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O169" s="137"/>
       <c r="P169" s="19" t="s">
@@ -11444,7 +11453,7 @@
         <v>126</v>
       </c>
       <c r="N170" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O170" s="135" t="s">
         <v>36</v>
@@ -11491,7 +11500,7 @@
         <v>126</v>
       </c>
       <c r="N171" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O171" s="136"/>
       <c r="P171" s="19" t="s">
@@ -11505,7 +11514,7 @@
         <v>262</v>
       </c>
       <c r="D172" s="31" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E172" s="29" t="s">
         <v>44</v>
@@ -11533,10 +11542,10 @@
         <v>27</v>
       </c>
       <c r="M172" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N172" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O172" s="136"/>
       <c r="P172" s="19" t="s">
@@ -11550,7 +11559,7 @@
         <v>263</v>
       </c>
       <c r="D173" s="37" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E173" s="35" t="s">
         <v>44</v>
@@ -11581,7 +11590,7 @@
         <v>61</v>
       </c>
       <c r="N173" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O173" s="136"/>
       <c r="P173" s="19" t="s">
@@ -11630,7 +11639,7 @@
         <v>98</v>
       </c>
       <c r="N174" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O174" s="136" t="s">
         <v>30</v>
@@ -11674,10 +11683,10 @@
         <v>27</v>
       </c>
       <c r="M175" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N175" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O175" s="136"/>
       <c r="P175" s="19" t="s">
@@ -11719,10 +11728,10 @@
         <v>27</v>
       </c>
       <c r="M176" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N176" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O176" s="136"/>
       <c r="P176" s="19" t="s">
@@ -11767,7 +11776,7 @@
         <v>61</v>
       </c>
       <c r="N177" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O177" s="137"/>
       <c r="P177" s="19" t="s">
@@ -11779,10 +11788,10 @@
         <v>265</v>
       </c>
       <c r="B178" s="93" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C178" s="93" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D178" s="24" t="s">
         <v>21</v>
@@ -11791,14 +11800,14 @@
         <v>22</v>
       </c>
       <c r="F178" s="102" t="s">
-        <v>266</v>
+        <v>23</v>
       </c>
       <c r="G178" s="57">
-        <v>31552</v>
+        <v>28945</v>
       </c>
       <c r="H178" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I178" s="25" t="s">
         <v>24</v>
@@ -11810,13 +11819,13 @@
         <v>26</v>
       </c>
       <c r="L178" s="101" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="M178" s="25" t="s">
         <v>248</v>
       </c>
       <c r="N178" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O178" s="140" t="s">
         <v>30</v>
@@ -11828,7 +11837,9 @@
     <row r="179" spans="1:16" s="84" customFormat="1">
       <c r="A179" s="138"/>
       <c r="B179" s="101"/>
-      <c r="C179" s="102"/>
+      <c r="C179" s="102" t="s">
+        <v>759</v>
+      </c>
       <c r="D179" s="31" t="s">
         <v>39</v>
       </c>
@@ -11839,11 +11850,11 @@
         <v>23</v>
       </c>
       <c r="G179" s="57">
-        <v>31765</v>
+        <v>30394</v>
       </c>
       <c r="H179" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I179" s="29" t="s">
         <v>24</v>
@@ -11861,7 +11872,7 @@
         <v>248</v>
       </c>
       <c r="N179" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O179" s="138"/>
       <c r="P179" s="19" t="s">
@@ -11871,7 +11882,9 @@
     <row r="180" spans="1:16" s="84" customFormat="1">
       <c r="A180" s="138"/>
       <c r="B180" s="101"/>
-      <c r="C180" s="102"/>
+      <c r="C180" s="102" t="s">
+        <v>760</v>
+      </c>
       <c r="D180" s="118" t="s">
         <v>39</v>
       </c>
@@ -11881,8 +11894,13 @@
       <c r="F180" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="G180" s="57"/>
-      <c r="H180" s="58"/>
+      <c r="G180" s="57">
+        <v>39765</v>
+      </c>
+      <c r="H180" s="58">
+        <f t="shared" ca="1" si="3"/>
+        <v>17</v>
+      </c>
       <c r="I180" s="35" t="s">
         <v>45</v>
       </c>
@@ -11899,7 +11917,7 @@
         <v>248</v>
       </c>
       <c r="N180" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O180" s="138"/>
       <c r="P180" s="19" t="s">
@@ -11909,7 +11927,9 @@
     <row r="181" spans="1:16" s="84" customFormat="1">
       <c r="A181" s="138"/>
       <c r="B181" s="101"/>
-      <c r="C181" s="102"/>
+      <c r="C181" s="102" t="s">
+        <v>761</v>
+      </c>
       <c r="D181" s="86" t="s">
         <v>39</v>
       </c>
@@ -11920,11 +11940,11 @@
         <v>23</v>
       </c>
       <c r="G181" s="57">
-        <v>37910</v>
+        <v>40275</v>
       </c>
       <c r="H181" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I181" s="35" t="s">
         <v>45</v>
@@ -11938,11 +11958,11 @@
       <c r="L181" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M181" s="25" t="s">
-        <v>248</v>
+      <c r="M181" s="29" t="s">
+        <v>91</v>
       </c>
       <c r="N181" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O181" s="139"/>
       <c r="P181" s="19" t="s">
@@ -11951,13 +11971,13 @@
     </row>
     <row r="182" spans="1:16" s="2" customFormat="1">
       <c r="A182" s="135" t="s">
+        <v>266</v>
+      </c>
+      <c r="B182" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="B182" s="38" t="s">
-        <v>268</v>
-      </c>
       <c r="C182" s="38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D182" s="24" t="s">
         <v>21</v>
@@ -11966,7 +11986,7 @@
         <v>22</v>
       </c>
       <c r="F182" s="25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G182" s="51">
         <v>29182</v>
@@ -11991,7 +12011,7 @@
         <v>126</v>
       </c>
       <c r="N182" s="19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O182" s="135" t="s">
         <v>36</v>
@@ -12004,7 +12024,7 @@
       <c r="A183" s="136"/>
       <c r="B183" s="29"/>
       <c r="C183" s="29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D183" s="31" t="s">
         <v>39</v>
@@ -12035,10 +12055,10 @@
         <v>27</v>
       </c>
       <c r="M183" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N183" s="19" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O183" s="136"/>
       <c r="P183" s="19" t="s">
@@ -12049,7 +12069,7 @@
       <c r="A184" s="136"/>
       <c r="B184" s="29"/>
       <c r="C184" s="29" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D184" s="31" t="s">
         <v>21</v>
@@ -12074,7 +12094,7 @@
         <v>25</v>
       </c>
       <c r="K184" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L184" s="31" t="s">
         <v>27</v>
@@ -12083,7 +12103,7 @@
         <v>49</v>
       </c>
       <c r="N184" s="19" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O184" s="136"/>
       <c r="P184" s="19" t="s">
@@ -12094,10 +12114,10 @@
       <c r="A185" s="137"/>
       <c r="B185" s="35"/>
       <c r="C185" s="35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D185" s="37" t="s">
-        <v>21</v>
+        <v>758</v>
       </c>
       <c r="E185" s="35" t="s">
         <v>44</v>
@@ -12128,7 +12148,7 @@
         <v>83</v>
       </c>
       <c r="N185" s="19" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O185" s="137"/>
       <c r="P185" s="19" t="s">
@@ -12137,13 +12157,13 @@
     </row>
     <row r="186" spans="1:16" s="2" customFormat="1">
       <c r="A186" s="135" t="s">
+        <v>273</v>
+      </c>
+      <c r="B186" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="B186" s="38" t="s">
-        <v>275</v>
-      </c>
       <c r="C186" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D186" s="24" t="s">
         <v>21</v>
@@ -12174,10 +12194,10 @@
         <v>27</v>
       </c>
       <c r="M186" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N186" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O186" s="135" t="s">
         <v>36</v>
@@ -12190,7 +12210,7 @@
       <c r="A187" s="136"/>
       <c r="B187" s="29"/>
       <c r="C187" s="29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D187" s="31" t="s">
         <v>39</v>
@@ -12221,10 +12241,10 @@
         <v>27</v>
       </c>
       <c r="M187" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N187" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O187" s="136"/>
       <c r="P187" s="19" t="s">
@@ -12235,7 +12255,7 @@
       <c r="A188" s="136"/>
       <c r="B188" s="29"/>
       <c r="C188" s="29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D188" s="31" t="s">
         <v>21</v>
@@ -12269,7 +12289,7 @@
         <v>91</v>
       </c>
       <c r="N188" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O188" s="136"/>
       <c r="P188" s="19" t="s">
@@ -12280,7 +12300,7 @@
       <c r="A189" s="136"/>
       <c r="B189" s="29"/>
       <c r="C189" s="29" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D189" s="31" t="s">
         <v>21</v>
@@ -12314,7 +12334,7 @@
         <v>49</v>
       </c>
       <c r="N189" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O189" s="136"/>
       <c r="P189" s="19" t="s">
@@ -12325,7 +12345,7 @@
       <c r="A190" s="137"/>
       <c r="B190" s="35"/>
       <c r="C190" s="35" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D190" s="37" t="s">
         <v>39</v>
@@ -12359,7 +12379,7 @@
         <v>61</v>
       </c>
       <c r="N190" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O190" s="137"/>
       <c r="P190" s="19" t="s">
@@ -12368,7 +12388,7 @@
     </row>
     <row r="191" spans="1:16" s="2" customFormat="1">
       <c r="A191" s="132" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B191" s="107"/>
       <c r="C191" s="107"/>
@@ -12390,7 +12410,7 @@
     </row>
     <row r="192" spans="1:16" s="2" customFormat="1">
       <c r="A192" s="132" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B192" s="107"/>
       <c r="C192" s="107"/>
@@ -12412,13 +12432,13 @@
     </row>
     <row r="193" spans="1:16" s="2" customFormat="1">
       <c r="A193" s="135" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B193" s="38" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C193" s="38" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D193" s="24" t="s">
         <v>21</v>
@@ -12427,7 +12447,7 @@
         <v>22</v>
       </c>
       <c r="F193" s="25" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G193" s="51">
         <v>28003</v>
@@ -12452,7 +12472,7 @@
         <v>204</v>
       </c>
       <c r="N193" s="19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O193" s="135" t="s">
         <v>30</v>
@@ -12465,7 +12485,7 @@
       <c r="A194" s="136"/>
       <c r="B194" s="29"/>
       <c r="C194" s="29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D194" s="31" t="s">
         <v>39</v>
@@ -12499,7 +12519,7 @@
         <v>248</v>
       </c>
       <c r="N194" s="19" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O194" s="136"/>
       <c r="P194" s="46" t="s">
@@ -12508,13 +12528,13 @@
     </row>
     <row r="195" spans="1:16" s="2" customFormat="1">
       <c r="A195" s="135" t="s">
+        <v>288</v>
+      </c>
+      <c r="B195" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="B195" s="38" t="s">
-        <v>290</v>
-      </c>
       <c r="C195" s="38" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D195" s="24" t="s">
         <v>21</v>
@@ -12523,7 +12543,7 @@
         <v>22</v>
       </c>
       <c r="F195" s="25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G195" s="51">
         <v>25422</v>
@@ -12545,10 +12565,10 @@
         <v>27</v>
       </c>
       <c r="M195" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N195" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O195" s="135" t="s">
         <v>36</v>
@@ -12561,7 +12581,7 @@
       <c r="A196" s="136"/>
       <c r="B196" s="29"/>
       <c r="C196" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D196" s="31" t="s">
         <v>39</v>
@@ -12570,7 +12590,7 @@
         <v>40</v>
       </c>
       <c r="F196" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G196" s="54">
         <v>26784</v>
@@ -12592,10 +12612,10 @@
         <v>112</v>
       </c>
       <c r="M196" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N196" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O196" s="136"/>
       <c r="P196" s="19" t="s">
@@ -12606,7 +12626,7 @@
       <c r="A197" s="136"/>
       <c r="B197" s="29"/>
       <c r="C197" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D197" s="31" t="s">
         <v>39</v>
@@ -12640,7 +12660,7 @@
         <v>68</v>
       </c>
       <c r="N197" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O197" s="136"/>
       <c r="P197" s="19" t="s">
@@ -12651,7 +12671,7 @@
       <c r="A198" s="137"/>
       <c r="B198" s="35"/>
       <c r="C198" s="35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D198" s="37" t="s">
         <v>39</v>
@@ -12685,7 +12705,7 @@
         <v>61</v>
       </c>
       <c r="N198" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O198" s="137"/>
       <c r="P198" s="19" t="s">
@@ -12694,13 +12714,13 @@
     </row>
     <row r="199" spans="1:16" s="2" customFormat="1">
       <c r="A199" s="116" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B199" s="127" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C199" s="127" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D199" s="117" t="s">
         <v>21</v>
@@ -12734,7 +12754,7 @@
         <v>98</v>
       </c>
       <c r="N199" s="26" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O199" s="135" t="s">
         <v>30</v>
@@ -12747,7 +12767,7 @@
       <c r="A200" s="116"/>
       <c r="B200" s="26"/>
       <c r="C200" s="26" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D200" s="118" t="s">
         <v>39</v>
@@ -12778,10 +12798,10 @@
         <v>27</v>
       </c>
       <c r="M200" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N200" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O200" s="136"/>
       <c r="P200" s="19" t="s">
@@ -12792,7 +12812,7 @@
       <c r="A201" s="116"/>
       <c r="B201" s="26"/>
       <c r="C201" s="26" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D201" s="118" t="s">
         <v>39</v>
@@ -12823,10 +12843,10 @@
         <v>27</v>
       </c>
       <c r="M201" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N201" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O201" s="136"/>
       <c r="P201" s="19" t="s">
@@ -12837,7 +12857,7 @@
       <c r="A202" s="116"/>
       <c r="B202" s="26"/>
       <c r="C202" s="26" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D202" s="119" t="s">
         <v>39</v>
@@ -12868,10 +12888,10 @@
         <v>27</v>
       </c>
       <c r="M202" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N202" s="26" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O202" s="137"/>
       <c r="P202" s="19" t="s">
@@ -12880,13 +12900,13 @@
     </row>
     <row r="203" spans="1:16" s="2" customFormat="1">
       <c r="A203" s="135" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B203" s="38" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C203" s="38" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D203" s="24" t="s">
         <v>21</v>
@@ -12917,10 +12937,10 @@
         <v>27</v>
       </c>
       <c r="M203" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N203" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O203" s="135" t="s">
         <v>30</v>
@@ -12933,7 +12953,7 @@
       <c r="A204" s="136"/>
       <c r="B204" s="29"/>
       <c r="C204" s="29" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D204" s="31" t="s">
         <v>39</v>
@@ -12942,7 +12962,7 @@
         <v>40</v>
       </c>
       <c r="F204" s="29" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G204" s="54">
         <v>20531</v>
@@ -12967,7 +12987,7 @@
         <v>155</v>
       </c>
       <c r="N204" s="29" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="O204" s="136"/>
       <c r="P204" s="46" t="s">
@@ -12976,13 +12996,13 @@
     </row>
     <row r="205" spans="1:16" s="2" customFormat="1">
       <c r="A205" s="135" t="s">
+        <v>301</v>
+      </c>
+      <c r="B205" s="38" t="s">
         <v>302</v>
       </c>
-      <c r="B205" s="38" t="s">
-        <v>303</v>
-      </c>
       <c r="C205" s="38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D205" s="24" t="s">
         <v>39</v>
@@ -13013,10 +13033,10 @@
         <v>27</v>
       </c>
       <c r="M205" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N205" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O205" s="135" t="s">
         <v>36</v>
@@ -13029,7 +13049,7 @@
       <c r="A206" s="136"/>
       <c r="B206" s="29"/>
       <c r="C206" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D206" s="31" t="s">
         <v>21</v>
@@ -13060,10 +13080,10 @@
         <v>27</v>
       </c>
       <c r="M206" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N206" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O206" s="136"/>
       <c r="P206" s="19" t="s">
@@ -13074,7 +13094,7 @@
       <c r="A207" s="137"/>
       <c r="B207" s="35"/>
       <c r="C207" s="35" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D207" s="37" t="s">
         <v>39</v>
@@ -13105,10 +13125,10 @@
         <v>27</v>
       </c>
       <c r="M207" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N207" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O207" s="137"/>
       <c r="P207" s="19" t="s">
@@ -13118,10 +13138,10 @@
     <row r="208" spans="1:16" s="2" customFormat="1">
       <c r="A208" s="87"/>
       <c r="B208" s="36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C208" s="36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D208" s="37" t="s">
         <v>39</v>
@@ -13155,7 +13175,7 @@
         <v>98</v>
       </c>
       <c r="N208" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O208" s="87" t="s">
         <v>36</v>
@@ -13166,13 +13186,13 @@
     </row>
     <row r="209" spans="1:16" s="2" customFormat="1">
       <c r="A209" s="135" t="s">
+        <v>306</v>
+      </c>
+      <c r="B209" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="B209" s="39" t="s">
-        <v>308</v>
-      </c>
       <c r="C209" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D209" s="24" t="s">
         <v>21</v>
@@ -13206,7 +13226,7 @@
         <v>204</v>
       </c>
       <c r="N209" s="29" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O209" s="135" t="s">
         <v>30</v>
@@ -13219,7 +13239,7 @@
       <c r="A210" s="136"/>
       <c r="B210" s="29"/>
       <c r="C210" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D210" s="37" t="s">
         <v>39</v>
@@ -13253,7 +13273,7 @@
         <v>155</v>
       </c>
       <c r="N210" s="29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O210" s="136"/>
       <c r="P210" s="46" t="s">
@@ -13264,7 +13284,7 @@
       <c r="A211" s="136"/>
       <c r="B211" s="29"/>
       <c r="C211" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D211" s="37" t="s">
         <v>39</v>
@@ -13295,10 +13315,10 @@
         <v>27</v>
       </c>
       <c r="M211" s="29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N211" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O211" s="136"/>
       <c r="P211" s="46" t="s">
@@ -13309,7 +13329,7 @@
       <c r="A212" s="136"/>
       <c r="B212" s="29"/>
       <c r="C212" s="30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D212" s="37" t="s">
         <v>39</v>
@@ -13340,10 +13360,10 @@
         <v>27</v>
       </c>
       <c r="M212" s="29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N212" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O212" s="136"/>
       <c r="P212" s="46" t="s">
@@ -13352,13 +13372,13 @@
     </row>
     <row r="213" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="140" t="s">
+        <v>314</v>
+      </c>
+      <c r="B213" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="B213" s="39" t="s">
-        <v>316</v>
-      </c>
       <c r="C213" s="39" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D213" s="24" t="s">
         <v>21</v>
@@ -13392,7 +13412,7 @@
         <v>98</v>
       </c>
       <c r="N213" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O213" s="135" t="s">
         <v>30</v>
@@ -13405,7 +13425,7 @@
       <c r="A214" s="138"/>
       <c r="B214" s="29"/>
       <c r="C214" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>39</v>
@@ -13436,10 +13456,10 @@
         <v>27</v>
       </c>
       <c r="M214" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N214" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O214" s="136"/>
       <c r="P214" s="19" t="s">
@@ -13450,7 +13470,7 @@
       <c r="A215" s="138"/>
       <c r="B215" s="29"/>
       <c r="C215" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D215" s="31" t="s">
         <v>21</v>
@@ -13481,10 +13501,10 @@
         <v>27</v>
       </c>
       <c r="M215" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N215" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O215" s="136"/>
       <c r="P215" s="19" t="s">
@@ -13495,7 +13515,7 @@
       <c r="A216" s="139"/>
       <c r="B216" s="35"/>
       <c r="C216" s="36" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D216" s="37" t="s">
         <v>21</v>
@@ -13529,20 +13549,20 @@
         <v>61</v>
       </c>
       <c r="N216" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O216" s="137"/>
       <c r="P216" s="19"/>
     </row>
     <row r="217" spans="1:16" s="2" customFormat="1">
       <c r="A217" s="135" t="s">
+        <v>320</v>
+      </c>
+      <c r="B217" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="B217" s="38" t="s">
-        <v>322</v>
-      </c>
       <c r="C217" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D217" s="24" t="s">
         <v>21</v>
@@ -13567,7 +13587,7 @@
         <v>25</v>
       </c>
       <c r="K217" s="25" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L217" s="24" t="s">
         <v>27</v>
@@ -13576,7 +13596,7 @@
         <v>204</v>
       </c>
       <c r="N217" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O217" s="135" t="s">
         <v>36</v>
@@ -13589,7 +13609,7 @@
       <c r="A218" s="136"/>
       <c r="B218" s="29"/>
       <c r="C218" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D218" s="31" t="s">
         <v>39</v>
@@ -13623,7 +13643,7 @@
         <v>204</v>
       </c>
       <c r="N218" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O218" s="136"/>
       <c r="P218" s="19" t="s">
@@ -13634,7 +13654,7 @@
       <c r="A219" s="136"/>
       <c r="B219" s="29"/>
       <c r="C219" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D219" s="31" t="s">
         <v>39</v>
@@ -13665,10 +13685,10 @@
         <v>27</v>
       </c>
       <c r="M219" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N219" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O219" s="136"/>
       <c r="P219" s="19" t="s">
@@ -13679,7 +13699,7 @@
       <c r="A220" s="137"/>
       <c r="B220" s="35"/>
       <c r="C220" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D220" s="37" t="s">
         <v>39</v>
@@ -13713,7 +13733,7 @@
         <v>98</v>
       </c>
       <c r="N220" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O220" s="137"/>
       <c r="P220" s="19" t="s">
@@ -13722,13 +13742,13 @@
     </row>
     <row r="221" spans="1:16" s="2" customFormat="1">
       <c r="A221" s="135" t="s">
+        <v>327</v>
+      </c>
+      <c r="B221" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="B221" s="38" t="s">
-        <v>329</v>
-      </c>
       <c r="C221" s="39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D221" s="24" t="s">
         <v>21</v>
@@ -13759,10 +13779,10 @@
         <v>27</v>
       </c>
       <c r="M221" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N221" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O221" s="135" t="s">
         <v>36</v>
@@ -13775,7 +13795,7 @@
       <c r="A222" s="136"/>
       <c r="B222" s="29"/>
       <c r="C222" s="30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D222" s="118" t="s">
         <v>39</v>
@@ -13806,10 +13826,10 @@
         <v>27</v>
       </c>
       <c r="M222" s="29" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N222" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O222" s="136"/>
       <c r="P222" s="46" t="s">
@@ -13820,7 +13840,7 @@
       <c r="A223" s="136"/>
       <c r="B223" s="29"/>
       <c r="C223" s="30" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D223" s="118" t="s">
         <v>39</v>
@@ -13851,10 +13871,10 @@
         <v>27</v>
       </c>
       <c r="M223" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N223" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O223" s="136"/>
       <c r="P223" s="46" t="s">
@@ -13865,7 +13885,7 @@
       <c r="A224" s="136"/>
       <c r="B224" s="29"/>
       <c r="C224" s="30" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D224" s="31" t="s">
         <v>21</v>
@@ -13896,10 +13916,10 @@
         <v>27</v>
       </c>
       <c r="M224" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N224" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O224" s="136"/>
       <c r="P224" s="46" t="s">
@@ -13908,7 +13928,7 @@
     </row>
     <row r="225" spans="1:253" s="2" customFormat="1">
       <c r="A225" s="88" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B225" s="107"/>
       <c r="C225" s="107"/>
@@ -13932,13 +13952,13 @@
     </row>
     <row r="226" spans="1:253" s="2" customFormat="1">
       <c r="A226" s="135" t="s">
+        <v>331</v>
+      </c>
+      <c r="B226" s="38" t="s">
         <v>332</v>
       </c>
-      <c r="B226" s="38" t="s">
-        <v>333</v>
-      </c>
       <c r="C226" s="38" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D226" s="24" t="s">
         <v>21</v>
@@ -13969,10 +13989,10 @@
         <v>27</v>
       </c>
       <c r="M226" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N226" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O226" s="135" t="s">
         <v>36</v>
@@ -13985,7 +14005,7 @@
       <c r="A227" s="136"/>
       <c r="B227" s="29"/>
       <c r="C227" s="29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D227" s="31" t="s">
         <v>39</v>
@@ -14016,10 +14036,10 @@
         <v>27</v>
       </c>
       <c r="M227" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N227" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O227" s="136"/>
       <c r="P227" s="19" t="s">
@@ -14030,7 +14050,7 @@
       <c r="A228" s="136"/>
       <c r="B228" s="35"/>
       <c r="C228" s="35" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D228" s="119" t="s">
         <v>21</v>
@@ -14064,7 +14084,7 @@
         <v>91</v>
       </c>
       <c r="N228" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O228" s="136"/>
       <c r="P228" s="19" t="s">
@@ -14075,7 +14095,7 @@
       <c r="A229" s="136"/>
       <c r="B229" s="29"/>
       <c r="C229" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D229" s="31" t="s">
         <v>21</v>
@@ -14109,7 +14129,7 @@
         <v>204</v>
       </c>
       <c r="N229" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O229" s="136"/>
       <c r="P229" s="19" t="s">
@@ -14120,7 +14140,7 @@
       <c r="A230" s="136"/>
       <c r="B230" s="91"/>
       <c r="C230" s="91" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D230" s="97" t="s">
         <v>39</v>
@@ -14154,7 +14174,7 @@
         <v>155</v>
       </c>
       <c r="N230" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O230" s="136"/>
       <c r="P230" s="19" t="s">
@@ -14163,13 +14183,13 @@
     </row>
     <row r="231" spans="1:253" s="2" customFormat="1">
       <c r="A231" s="141" t="s">
+        <v>336</v>
+      </c>
+      <c r="B231" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="B231" s="39" t="s">
-        <v>338</v>
-      </c>
       <c r="C231" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D231" s="24" t="s">
         <v>21</v>
@@ -14200,10 +14220,10 @@
         <v>27</v>
       </c>
       <c r="M231" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N231" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O231" s="141" t="s">
         <v>36</v>
@@ -14216,7 +14236,7 @@
       <c r="A232" s="141"/>
       <c r="B232" s="29"/>
       <c r="C232" s="30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D232" s="31" t="s">
         <v>39</v>
@@ -14247,10 +14267,10 @@
         <v>27</v>
       </c>
       <c r="M232" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N232" s="29" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O232" s="141"/>
       <c r="P232" s="46" t="s">
@@ -14261,7 +14281,7 @@
       <c r="A233" s="141"/>
       <c r="B233" s="29"/>
       <c r="C233" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D233" s="31" t="s">
         <v>21</v>
@@ -14295,7 +14315,7 @@
         <v>98</v>
       </c>
       <c r="N233" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O233" s="141"/>
       <c r="P233" s="46" t="s">
@@ -14306,7 +14326,7 @@
       <c r="A234" s="141"/>
       <c r="B234" s="29"/>
       <c r="C234" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D234" s="31" t="s">
         <v>39</v>
@@ -14340,7 +14360,7 @@
         <v>61</v>
       </c>
       <c r="N234" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O234" s="136"/>
       <c r="P234" s="46" t="s">
@@ -14351,7 +14371,7 @@
       <c r="A235" s="141"/>
       <c r="B235" s="29"/>
       <c r="C235" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D235" s="31" t="s">
         <v>21</v>
@@ -14385,7 +14405,7 @@
         <v>61</v>
       </c>
       <c r="N235" s="29" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="O235" s="136"/>
       <c r="P235" s="46" t="s">
@@ -14396,7 +14416,7 @@
       <c r="A236" s="141"/>
       <c r="B236" s="29"/>
       <c r="C236" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D236" s="31" t="s">
         <v>39</v>
@@ -14427,10 +14447,10 @@
         <v>27</v>
       </c>
       <c r="M236" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N236" s="29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="O236" s="136"/>
       <c r="P236" s="46" t="s">
@@ -14441,7 +14461,7 @@
       <c r="A237" s="141"/>
       <c r="B237" s="35"/>
       <c r="C237" s="36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D237" s="37" t="s">
         <v>39</v>
@@ -14475,7 +14495,7 @@
         <v>61</v>
       </c>
       <c r="N237" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O237" s="137"/>
       <c r="P237" s="46" t="s">
@@ -14498,7 +14518,7 @@
       </c>
       <c r="F239" s="114">
         <f>COUNTIF($D$6:$D$237,"l")</f>
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I239" s="3"/>
       <c r="J239" s="3"/>
@@ -14752,7 +14772,7 @@
       </c>
       <c r="F240" s="114">
         <f>COUNTIF($D$6:$D$237,"P")</f>
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I240" s="3"/>
       <c r="J240" s="3"/>
@@ -15466,7 +15486,7 @@
     </row>
     <row r="3" spans="1:20" s="1" customFormat="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -15495,10 +15515,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>346</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>347</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>4</v>
@@ -15543,10 +15563,10 @@
         <v>17</v>
       </c>
       <c r="S5" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="T5" s="7" t="s">
         <v>348</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="12" customHeight="1">
@@ -15639,10 +15659,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>350</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>351</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>20</v>
@@ -15689,7 +15709,7 @@
       </c>
       <c r="S8" s="46"/>
       <c r="T8" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15700,10 +15720,10 @@
         <v>32</v>
       </c>
       <c r="C9" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>353</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>354</v>
       </c>
       <c r="E9" s="23" t="s">
         <v>33</v>
@@ -15750,7 +15770,7 @@
       </c>
       <c r="S9" s="19"/>
       <c r="T9" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15759,10 +15779,10 @@
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" s="30" t="s">
@@ -15805,7 +15825,7 @@
       <c r="R10" s="26"/>
       <c r="S10" s="19"/>
       <c r="T10" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15814,10 +15834,10 @@
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="30" t="s">
@@ -15860,7 +15880,7 @@
       <c r="R11" s="26"/>
       <c r="S11" s="19"/>
       <c r="T11" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15869,10 +15889,10 @@
       </c>
       <c r="B12" s="26"/>
       <c r="C12" s="27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30" t="s">
@@ -15915,7 +15935,7 @@
       <c r="R12" s="26"/>
       <c r="S12" s="19"/>
       <c r="T12" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15924,10 +15944,10 @@
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="33" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E13" s="35"/>
       <c r="F13" s="36" t="s">
@@ -15970,7 +15990,7 @@
       <c r="R13" s="32"/>
       <c r="S13" s="19"/>
       <c r="T13" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15981,10 +16001,10 @@
         <v>54</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>360</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>361</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>55</v>
@@ -16031,7 +16051,7 @@
       </c>
       <c r="S14" s="19"/>
       <c r="T14" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16040,10 +16060,10 @@
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="36" t="s">
@@ -16086,7 +16106,7 @@
       <c r="R15" s="18"/>
       <c r="S15" s="19"/>
       <c r="T15" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16097,16 +16117,16 @@
         <v>57</v>
       </c>
       <c r="C16" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="E16" s="40" t="s">
-        <v>365</v>
-      </c>
       <c r="F16" s="40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G16" s="18" t="s">
         <v>21</v>
@@ -16147,7 +16167,7 @@
       </c>
       <c r="S16" s="19"/>
       <c r="T16" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16158,16 +16178,16 @@
         <v>59</v>
       </c>
       <c r="C17" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="39" t="s">
         <v>367</v>
       </c>
-      <c r="E17" s="39" t="s">
-        <v>368</v>
-      </c>
       <c r="F17" s="38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>21</v>
@@ -16176,7 +16196,7 @@
         <v>22</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J17" s="51">
         <v>30891</v>
@@ -16208,7 +16228,7 @@
       </c>
       <c r="S17" s="19"/>
       <c r="T17" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16217,14 +16237,14 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>39</v>
@@ -16263,7 +16283,7 @@
       <c r="R18" s="26"/>
       <c r="S18" s="19"/>
       <c r="T18" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16272,14 +16292,14 @@
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E19" s="35"/>
       <c r="F19" s="35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G19" s="37" t="s">
         <v>39</v>
@@ -16288,7 +16308,7 @@
         <v>44</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J19" s="57">
         <v>38784</v>
@@ -16318,7 +16338,7 @@
       <c r="R19" s="32"/>
       <c r="S19" s="19"/>
       <c r="T19" s="63" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16329,10 +16349,10 @@
         <v>64</v>
       </c>
       <c r="C20" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="D20" s="41" t="s">
         <v>374</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>375</v>
       </c>
       <c r="E20" s="38" t="s">
         <v>65</v>
@@ -16379,7 +16399,7 @@
       </c>
       <c r="S20" s="19"/>
       <c r="T20" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16388,10 +16408,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E21" s="29"/>
       <c r="F21" s="29" t="s">
@@ -16434,7 +16454,7 @@
       <c r="R21" s="26"/>
       <c r="S21" s="19"/>
       <c r="T21" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16443,10 +16463,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E22" s="29"/>
       <c r="F22" s="29" t="s">
@@ -16489,7 +16509,7 @@
       <c r="R22" s="26"/>
       <c r="S22" s="19"/>
       <c r="T22" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16498,10 +16518,10 @@
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="43" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E23" s="35"/>
       <c r="F23" s="35" t="s">
@@ -16544,7 +16564,7 @@
       <c r="R23" s="32"/>
       <c r="S23" s="19"/>
       <c r="T23" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16555,10 +16575,10 @@
         <v>70</v>
       </c>
       <c r="C24" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>379</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>380</v>
       </c>
       <c r="E24" s="38" t="s">
         <v>71</v>
@@ -16603,7 +16623,7 @@
       </c>
       <c r="S24" s="19"/>
       <c r="T24" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16612,10 +16632,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="27" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E25" s="29"/>
       <c r="F25" s="29" t="s">
@@ -16656,7 +16676,7 @@
       <c r="R25" s="32"/>
       <c r="S25" s="19"/>
       <c r="T25" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16665,10 +16685,10 @@
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="35" t="s">
@@ -16709,7 +16729,7 @@
       <c r="R26" s="18"/>
       <c r="S26" s="19"/>
       <c r="T26" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16720,10 +16740,10 @@
         <v>74</v>
       </c>
       <c r="C27" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" s="41" t="s">
         <v>383</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>384</v>
       </c>
       <c r="E27" s="38" t="s">
         <v>75</v>
@@ -16770,7 +16790,7 @@
       </c>
       <c r="S27" s="19"/>
       <c r="T27" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16779,10 +16799,10 @@
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E28" s="29"/>
       <c r="F28" s="29" t="s">
@@ -16825,7 +16845,7 @@
       <c r="R28" s="26"/>
       <c r="S28" s="19"/>
       <c r="T28" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16834,10 +16854,10 @@
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="29" t="s">
@@ -16880,7 +16900,7 @@
       <c r="R29" s="26"/>
       <c r="S29" s="19"/>
       <c r="T29" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16889,10 +16909,10 @@
       </c>
       <c r="B30" s="26"/>
       <c r="C30" s="42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E30" s="29"/>
       <c r="F30" s="29" t="s">
@@ -16935,7 +16955,7 @@
       <c r="R30" s="26"/>
       <c r="S30" s="19"/>
       <c r="T30" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16944,10 +16964,10 @@
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="43" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35" t="s">
@@ -16990,7 +17010,7 @@
       <c r="R31" s="32"/>
       <c r="S31" s="19"/>
       <c r="T31" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17001,10 +17021,10 @@
         <v>84</v>
       </c>
       <c r="C32" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" s="41" t="s">
         <v>389</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>390</v>
       </c>
       <c r="E32" s="38" t="s">
         <v>85</v>
@@ -17051,7 +17071,7 @@
       </c>
       <c r="S32" s="19"/>
       <c r="T32" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17060,10 +17080,10 @@
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="29" t="s">
@@ -17106,7 +17126,7 @@
       <c r="R33" s="26"/>
       <c r="S33" s="19"/>
       <c r="T33" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17115,10 +17135,10 @@
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E34" s="29"/>
       <c r="F34" s="29" t="s">
@@ -17161,7 +17181,7 @@
       <c r="R34" s="26"/>
       <c r="S34" s="19"/>
       <c r="T34" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17170,10 +17190,10 @@
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E35" s="29"/>
       <c r="F35" s="29" t="s">
@@ -17216,7 +17236,7 @@
       <c r="R35" s="26"/>
       <c r="S35" s="19"/>
       <c r="T35" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17225,10 +17245,10 @@
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="43" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E36" s="35"/>
       <c r="F36" s="35" t="s">
@@ -17271,7 +17291,7 @@
       <c r="R36" s="32"/>
       <c r="S36" s="19"/>
       <c r="T36" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17282,10 +17302,10 @@
         <v>95</v>
       </c>
       <c r="C37" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="D37" s="22" t="s">
         <v>395</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>396</v>
       </c>
       <c r="E37" s="38" t="s">
         <v>96</v>
@@ -17332,7 +17352,7 @@
       </c>
       <c r="S37" s="19"/>
       <c r="T37" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17341,10 +17361,10 @@
       </c>
       <c r="B38" s="26"/>
       <c r="C38" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E38" s="29"/>
       <c r="F38" s="29" t="s">
@@ -17387,7 +17407,7 @@
       <c r="R38" s="26"/>
       <c r="S38" s="19"/>
       <c r="T38" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17396,14 +17416,14 @@
       </c>
       <c r="B39" s="26"/>
       <c r="C39" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E39" s="29"/>
       <c r="F39" s="29" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G39" s="31" t="s">
         <v>21</v>
@@ -17442,7 +17462,7 @@
       <c r="R39" s="26"/>
       <c r="S39" s="19"/>
       <c r="T39" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17451,10 +17471,10 @@
       </c>
       <c r="B40" s="26"/>
       <c r="C40" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E40" s="29"/>
       <c r="F40" s="29" t="s">
@@ -17497,7 +17517,7 @@
       <c r="R40" s="26"/>
       <c r="S40" s="19"/>
       <c r="T40" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17506,14 +17526,14 @@
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E41" s="35"/>
       <c r="F41" s="35" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G41" s="37" t="s">
         <v>39</v>
@@ -17552,7 +17572,7 @@
       <c r="R41" s="32"/>
       <c r="S41" s="19"/>
       <c r="T41" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="42" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17563,10 +17583,10 @@
         <v>103</v>
       </c>
       <c r="C42" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="D42" s="41" t="s">
         <v>402</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>403</v>
       </c>
       <c r="E42" s="38" t="s">
         <v>104</v>
@@ -17613,7 +17633,7 @@
       </c>
       <c r="S42" s="19"/>
       <c r="T42" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17622,10 +17642,10 @@
       </c>
       <c r="B43" s="26"/>
       <c r="C43" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E43" s="29"/>
       <c r="F43" s="29" t="s">
@@ -17668,7 +17688,7 @@
       <c r="R43" s="26"/>
       <c r="S43" s="19"/>
       <c r="T43" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="44" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17677,10 +17697,10 @@
       </c>
       <c r="B44" s="26"/>
       <c r="C44" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E44" s="29"/>
       <c r="F44" s="29" t="s">
@@ -17723,7 +17743,7 @@
       <c r="R44" s="26"/>
       <c r="S44" s="19"/>
       <c r="T44" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="45" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17732,10 +17752,10 @@
       </c>
       <c r="B45" s="32"/>
       <c r="C45" s="43" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E45" s="35"/>
       <c r="F45" s="35" t="s">
@@ -17778,7 +17798,7 @@
       <c r="R45" s="32"/>
       <c r="S45" s="19"/>
       <c r="T45" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="46" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17789,10 +17809,10 @@
         <v>109</v>
       </c>
       <c r="C46" s="41" t="s">
+        <v>406</v>
+      </c>
+      <c r="D46" s="41" t="s">
         <v>407</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>408</v>
       </c>
       <c r="E46" s="38" t="s">
         <v>110</v>
@@ -17839,7 +17859,7 @@
       </c>
       <c r="S46" s="19"/>
       <c r="T46" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="47" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17848,10 +17868,10 @@
       </c>
       <c r="B47" s="26"/>
       <c r="C47" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E47" s="29"/>
       <c r="F47" s="29" t="s">
@@ -17894,7 +17914,7 @@
       <c r="R47" s="26"/>
       <c r="S47" s="19"/>
       <c r="T47" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17903,10 +17923,10 @@
       </c>
       <c r="B48" s="26"/>
       <c r="C48" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E48" s="29"/>
       <c r="F48" s="29" t="s">
@@ -17949,7 +17969,7 @@
       <c r="R48" s="26"/>
       <c r="S48" s="19"/>
       <c r="T48" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17958,10 +17978,10 @@
       </c>
       <c r="B49" s="32"/>
       <c r="C49" s="43" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E49" s="35"/>
       <c r="F49" s="35" t="s">
@@ -18004,7 +18024,7 @@
       <c r="R49" s="32"/>
       <c r="S49" s="19"/>
       <c r="T49" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18015,10 +18035,10 @@
         <v>116</v>
       </c>
       <c r="C50" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="D50" s="22" t="s">
         <v>412</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>413</v>
       </c>
       <c r="E50" s="38" t="s">
         <v>117</v>
@@ -18065,7 +18085,7 @@
       </c>
       <c r="S50" s="19"/>
       <c r="T50" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="51" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18074,10 +18094,10 @@
       </c>
       <c r="B51" s="26"/>
       <c r="C51" s="27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E51" s="29"/>
       <c r="F51" s="29" t="s">
@@ -18120,7 +18140,7 @@
       <c r="R51" s="26"/>
       <c r="S51" s="19"/>
       <c r="T51" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="52" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18129,10 +18149,10 @@
       </c>
       <c r="B52" s="26"/>
       <c r="C52" s="27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E52" s="29"/>
       <c r="F52" s="29" t="s">
@@ -18175,7 +18195,7 @@
       <c r="R52" s="26"/>
       <c r="S52" s="19"/>
       <c r="T52" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18184,10 +18204,10 @@
       </c>
       <c r="B53" s="26"/>
       <c r="C53" s="27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E53" s="29"/>
       <c r="F53" s="29" t="s">
@@ -18230,7 +18250,7 @@
       <c r="R53" s="26"/>
       <c r="S53" s="19"/>
       <c r="T53" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="54" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18239,7 +18259,7 @@
       </c>
       <c r="B54" s="32"/>
       <c r="C54" s="33" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D54" s="34" t="s">
         <v>172</v>
@@ -18285,7 +18305,7 @@
       <c r="R54" s="32"/>
       <c r="S54" s="19"/>
       <c r="T54" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="55" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18296,10 +18316,10 @@
         <v>123</v>
       </c>
       <c r="C55" s="41" t="s">
+        <v>416</v>
+      </c>
+      <c r="D55" s="41" t="s">
         <v>417</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>418</v>
       </c>
       <c r="E55" s="38" t="s">
         <v>124</v>
@@ -18346,7 +18366,7 @@
       </c>
       <c r="S55" s="19"/>
       <c r="T55" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="56" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18355,10 +18375,10 @@
       </c>
       <c r="B56" s="26"/>
       <c r="C56" s="42" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E56" s="29"/>
       <c r="F56" s="29" t="s">
@@ -18401,7 +18421,7 @@
       <c r="R56" s="26"/>
       <c r="S56" s="19"/>
       <c r="T56" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="57" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18410,10 +18430,10 @@
       </c>
       <c r="B57" s="26"/>
       <c r="C57" s="42" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D57" s="42" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E57" s="29"/>
       <c r="F57" s="29" t="s">
@@ -18456,7 +18476,7 @@
       <c r="R57" s="26"/>
       <c r="S57" s="19"/>
       <c r="T57" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18465,10 +18485,10 @@
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="43" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E58" s="35"/>
       <c r="F58" s="35" t="s">
@@ -18511,7 +18531,7 @@
       <c r="R58" s="32"/>
       <c r="S58" s="19"/>
       <c r="T58" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="59" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18522,10 +18542,10 @@
         <v>131</v>
       </c>
       <c r="C59" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="D59" s="41" t="s">
         <v>422</v>
-      </c>
-      <c r="D59" s="41" t="s">
-        <v>423</v>
       </c>
       <c r="E59" s="38" t="s">
         <v>132</v>
@@ -18572,7 +18592,7 @@
       </c>
       <c r="S59" s="19"/>
       <c r="T59" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="60" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18581,10 +18601,10 @@
       </c>
       <c r="B60" s="29"/>
       <c r="C60" s="42" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E60" s="29"/>
       <c r="F60" s="29" t="s">
@@ -18627,7 +18647,7 @@
       <c r="R60" s="26"/>
       <c r="S60" s="19"/>
       <c r="T60" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18636,10 +18656,10 @@
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="42" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D61" s="42" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E61" s="29"/>
       <c r="F61" s="29" t="s">
@@ -18682,7 +18702,7 @@
       <c r="R61" s="26"/>
       <c r="S61" s="19"/>
       <c r="T61" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18691,10 +18711,10 @@
       </c>
       <c r="B62" s="29"/>
       <c r="C62" s="42" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D62" s="42" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E62" s="29"/>
       <c r="F62" s="29" t="s">
@@ -18737,7 +18757,7 @@
       <c r="R62" s="26"/>
       <c r="S62" s="19"/>
       <c r="T62" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18746,10 +18766,10 @@
       </c>
       <c r="B63" s="35"/>
       <c r="C63" s="43" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D63" s="43" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E63" s="35"/>
       <c r="F63" s="35" t="s">
@@ -18792,7 +18812,7 @@
       <c r="R63" s="32"/>
       <c r="S63" s="19"/>
       <c r="T63" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="64" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18803,10 +18823,10 @@
         <v>138</v>
       </c>
       <c r="C64" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="D64" s="22" t="s">
         <v>428</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>429</v>
       </c>
       <c r="E64" s="38" t="s">
         <v>139</v>
@@ -18853,7 +18873,7 @@
       </c>
       <c r="S64" s="19"/>
       <c r="T64" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18862,10 +18882,10 @@
       </c>
       <c r="B65" s="26"/>
       <c r="C65" s="27" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E65" s="29"/>
       <c r="F65" s="29" t="s">
@@ -18908,7 +18928,7 @@
       <c r="R65" s="26"/>
       <c r="S65" s="19"/>
       <c r="T65" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="66" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18917,10 +18937,10 @@
       </c>
       <c r="B66" s="26"/>
       <c r="C66" s="27" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E66" s="29"/>
       <c r="F66" s="29" t="s">
@@ -18963,7 +18983,7 @@
       <c r="R66" s="26"/>
       <c r="S66" s="19"/>
       <c r="T66" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="67" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18972,10 +18992,10 @@
       </c>
       <c r="B67" s="26"/>
       <c r="C67" s="27" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E67" s="29"/>
       <c r="F67" s="29" t="s">
@@ -19018,7 +19038,7 @@
       <c r="R67" s="26"/>
       <c r="S67" s="19"/>
       <c r="T67" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19027,10 +19047,10 @@
       </c>
       <c r="B68" s="32"/>
       <c r="C68" s="33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D68" s="34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E68" s="35"/>
       <c r="F68" s="35" t="s">
@@ -19073,7 +19093,7 @@
       <c r="R68" s="32"/>
       <c r="S68" s="19"/>
       <c r="T68" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="69" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19084,10 +19104,10 @@
         <v>144</v>
       </c>
       <c r="C69" s="41" t="s">
+        <v>433</v>
+      </c>
+      <c r="D69" s="41" t="s">
         <v>434</v>
-      </c>
-      <c r="D69" s="41" t="s">
-        <v>435</v>
       </c>
       <c r="E69" s="38" t="s">
         <v>145</v>
@@ -19134,7 +19154,7 @@
       </c>
       <c r="S69" s="19"/>
       <c r="T69" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="70" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19143,10 +19163,10 @@
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="42" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E70" s="29"/>
       <c r="F70" s="29" t="s">
@@ -19189,7 +19209,7 @@
       <c r="R70" s="26"/>
       <c r="S70" s="19"/>
       <c r="T70" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="71" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19198,10 +19218,10 @@
       </c>
       <c r="B71" s="29"/>
       <c r="C71" s="42" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E71" s="29"/>
       <c r="F71" s="29" t="s">
@@ -19244,7 +19264,7 @@
       <c r="R71" s="26"/>
       <c r="S71" s="19"/>
       <c r="T71" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="72" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19253,10 +19273,10 @@
       </c>
       <c r="B72" s="35"/>
       <c r="C72" s="43" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D72" s="43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E72" s="35"/>
       <c r="F72" s="35" t="s">
@@ -19299,7 +19319,7 @@
       <c r="R72" s="32"/>
       <c r="S72" s="19"/>
       <c r="T72" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19310,10 +19330,10 @@
         <v>149</v>
       </c>
       <c r="C73" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="D73" s="41" t="s">
         <v>439</v>
-      </c>
-      <c r="D73" s="41" t="s">
-        <v>440</v>
       </c>
       <c r="E73" s="38" t="s">
         <v>150</v>
@@ -19360,7 +19380,7 @@
       </c>
       <c r="S73" s="19"/>
       <c r="T73" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19369,10 +19389,10 @@
       </c>
       <c r="B74" s="29"/>
       <c r="C74" s="42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E74" s="29"/>
       <c r="F74" s="29" t="s">
@@ -19415,7 +19435,7 @@
       <c r="R74" s="26"/>
       <c r="S74" s="19"/>
       <c r="T74" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="75" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19424,10 +19444,10 @@
       </c>
       <c r="B75" s="29"/>
       <c r="C75" s="42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D75" s="42" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E75" s="29"/>
       <c r="F75" s="29" t="s">
@@ -19470,7 +19490,7 @@
       <c r="R75" s="26"/>
       <c r="S75" s="19"/>
       <c r="T75" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19479,10 +19499,10 @@
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D76" s="43" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E76" s="35"/>
       <c r="F76" s="35" t="s">
@@ -19525,7 +19545,7 @@
       <c r="R76" s="32"/>
       <c r="S76" s="19"/>
       <c r="T76" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19588,10 +19608,10 @@
         <v>156</v>
       </c>
       <c r="C78" s="41" t="s">
+        <v>443</v>
+      </c>
+      <c r="D78" s="41" t="s">
         <v>444</v>
-      </c>
-      <c r="D78" s="41" t="s">
-        <v>445</v>
       </c>
       <c r="E78" s="38" t="s">
         <v>157</v>
@@ -19638,7 +19658,7 @@
       </c>
       <c r="S78" s="19"/>
       <c r="T78" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="79" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19647,10 +19667,10 @@
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="42" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D79" s="42" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E79" s="29"/>
       <c r="F79" s="29" t="s">
@@ -19693,7 +19713,7 @@
       <c r="R79" s="26"/>
       <c r="S79" s="19"/>
       <c r="T79" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="80" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19702,10 +19722,10 @@
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="42" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D80" s="42" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E80" s="29"/>
       <c r="F80" s="29" t="s">
@@ -19748,7 +19768,7 @@
       <c r="R80" s="26"/>
       <c r="S80" s="19"/>
       <c r="T80" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="81" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19757,10 +19777,10 @@
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="43" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D81" s="43" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E81" s="35"/>
       <c r="F81" s="35" t="s">
@@ -19803,7 +19823,7 @@
       <c r="R81" s="32"/>
       <c r="S81" s="19"/>
       <c r="T81" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="82" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19814,10 +19834,10 @@
         <v>164</v>
       </c>
       <c r="C82" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="D82" s="22" t="s">
         <v>449</v>
-      </c>
-      <c r="D82" s="22" t="s">
-        <v>450</v>
       </c>
       <c r="E82" s="38" t="s">
         <v>165</v>
@@ -19864,7 +19884,7 @@
       </c>
       <c r="S82" s="19"/>
       <c r="T82" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="83" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19873,10 +19893,10 @@
       </c>
       <c r="B83" s="29"/>
       <c r="C83" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E83" s="29"/>
       <c r="F83" s="29" t="s">
@@ -19919,7 +19939,7 @@
       <c r="R83" s="26"/>
       <c r="S83" s="19"/>
       <c r="T83" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19928,10 +19948,10 @@
       </c>
       <c r="B84" s="29"/>
       <c r="C84" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E84" s="29"/>
       <c r="F84" s="29" t="s">
@@ -19974,7 +19994,7 @@
       <c r="R84" s="26"/>
       <c r="S84" s="19"/>
       <c r="T84" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19983,10 +20003,10 @@
       </c>
       <c r="B85" s="35"/>
       <c r="C85" s="33" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D85" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E85" s="35"/>
       <c r="F85" s="35" t="s">
@@ -20029,7 +20049,7 @@
       <c r="R85" s="32"/>
       <c r="S85" s="19"/>
       <c r="T85" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20043,13 +20063,13 @@
         <v>172</v>
       </c>
       <c r="D86" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="E86" s="38" t="s">
         <v>454</v>
       </c>
-      <c r="E86" s="38" t="s">
-        <v>455</v>
-      </c>
       <c r="F86" s="38" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G86" s="24" t="s">
         <v>21</v>
@@ -20090,7 +20110,7 @@
       </c>
       <c r="S86" s="19"/>
       <c r="T86" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20102,11 +20122,11 @@
         <v>172</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E87" s="29"/>
       <c r="F87" s="29" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G87" s="31" t="s">
         <v>21</v>
@@ -20145,7 +20165,7 @@
       <c r="R87" s="26"/>
       <c r="S87" s="19"/>
       <c r="T87" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20157,11 +20177,11 @@
         <v>172</v>
       </c>
       <c r="D88" s="34" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E88" s="35"/>
       <c r="F88" s="35" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G88" s="37" t="s">
         <v>21</v>
@@ -20200,7 +20220,7 @@
       <c r="R88" s="32"/>
       <c r="S88" s="19"/>
       <c r="T88" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20211,16 +20231,16 @@
         <v>171</v>
       </c>
       <c r="C89" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="D89" s="22" t="s">
         <v>460</v>
       </c>
-      <c r="D89" s="22" t="s">
+      <c r="E89" s="38" t="s">
         <v>461</v>
       </c>
-      <c r="E89" s="38" t="s">
-        <v>462</v>
-      </c>
       <c r="F89" s="38" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G89" s="24" t="s">
         <v>21</v>
@@ -20261,7 +20281,7 @@
       </c>
       <c r="S89" s="19"/>
       <c r="T89" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20270,14 +20290,14 @@
       </c>
       <c r="B90" s="26"/>
       <c r="C90" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E90" s="29"/>
       <c r="F90" s="29" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G90" s="31" t="s">
         <v>39</v>
@@ -20316,7 +20336,7 @@
       <c r="R90" s="26"/>
       <c r="S90" s="19"/>
       <c r="T90" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20325,14 +20345,14 @@
       </c>
       <c r="B91" s="32"/>
       <c r="C91" s="33" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D91" s="34" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E91" s="35"/>
       <c r="F91" s="35" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G91" s="37" t="s">
         <v>21</v>
@@ -20371,7 +20391,7 @@
       <c r="R91" s="32"/>
       <c r="S91" s="19"/>
       <c r="T91" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20382,10 +20402,10 @@
         <v>176</v>
       </c>
       <c r="C92" s="41" t="s">
+        <v>466</v>
+      </c>
+      <c r="D92" s="41" t="s">
         <v>467</v>
-      </c>
-      <c r="D92" s="41" t="s">
-        <v>468</v>
       </c>
       <c r="E92" s="38" t="s">
         <v>177</v>
@@ -20432,7 +20452,7 @@
       </c>
       <c r="S92" s="19"/>
       <c r="T92" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20441,10 +20461,10 @@
       </c>
       <c r="B93" s="26"/>
       <c r="C93" s="42" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D93" s="42" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E93" s="29"/>
       <c r="F93" s="29" t="s">
@@ -20487,7 +20507,7 @@
       <c r="R93" s="26"/>
       <c r="S93" s="19"/>
       <c r="T93" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20496,10 +20516,10 @@
       </c>
       <c r="B94" s="26"/>
       <c r="C94" s="42" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D94" s="42" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E94" s="29"/>
       <c r="F94" s="29" t="s">
@@ -20542,7 +20562,7 @@
       <c r="R94" s="26"/>
       <c r="S94" s="19"/>
       <c r="T94" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20551,10 +20571,10 @@
       </c>
       <c r="B95" s="32"/>
       <c r="C95" s="43" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D95" s="43" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E95" s="35"/>
       <c r="F95" s="35" t="s">
@@ -20597,7 +20617,7 @@
       <c r="R95" s="32"/>
       <c r="S95" s="19"/>
       <c r="T95" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20608,10 +20628,10 @@
         <v>181</v>
       </c>
       <c r="C96" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="D96" s="22" t="s">
         <v>472</v>
-      </c>
-      <c r="D96" s="22" t="s">
-        <v>473</v>
       </c>
       <c r="E96" s="38" t="s">
         <v>182</v>
@@ -20658,7 +20678,7 @@
       </c>
       <c r="S96" s="19"/>
       <c r="T96" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20667,10 +20687,10 @@
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="27" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E97" s="29"/>
       <c r="F97" s="29" t="s">
@@ -20713,7 +20733,7 @@
       <c r="R97" s="26"/>
       <c r="S97" s="19"/>
       <c r="T97" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="98" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20722,10 +20742,10 @@
       </c>
       <c r="B98" s="19"/>
       <c r="C98" s="33" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E98" s="35"/>
       <c r="F98" s="35" t="s">
@@ -20768,7 +20788,7 @@
       <c r="R98" s="26"/>
       <c r="S98" s="19"/>
       <c r="T98" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="99" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20825,10 +20845,10 @@
         <v>194</v>
       </c>
       <c r="C100" s="41" t="s">
+        <v>475</v>
+      </c>
+      <c r="D100" s="41" t="s">
         <v>476</v>
-      </c>
-      <c r="D100" s="41" t="s">
-        <v>477</v>
       </c>
       <c r="E100" s="38" t="s">
         <v>195</v>
@@ -20875,7 +20895,7 @@
       </c>
       <c r="S100" s="19"/>
       <c r="T100" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="101" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20884,10 +20904,10 @@
       </c>
       <c r="B101" s="26"/>
       <c r="C101" s="42" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D101" s="42" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E101" s="29"/>
       <c r="F101" s="29" t="s">
@@ -20930,7 +20950,7 @@
       <c r="R101" s="20"/>
       <c r="S101" s="19"/>
       <c r="T101" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20939,10 +20959,10 @@
       </c>
       <c r="B102" s="26"/>
       <c r="C102" s="42" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D102" s="42" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E102" s="29"/>
       <c r="F102" s="29" t="s">
@@ -20985,7 +21005,7 @@
       <c r="R102" s="26"/>
       <c r="S102" s="19"/>
       <c r="T102" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20994,10 +21014,10 @@
       </c>
       <c r="B103" s="26"/>
       <c r="C103" s="42" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D103" s="42" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E103" s="29"/>
       <c r="F103" s="29" t="s">
@@ -21040,7 +21060,7 @@
       <c r="R103" s="26"/>
       <c r="S103" s="19"/>
       <c r="T103" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21049,10 +21069,10 @@
       </c>
       <c r="B104" s="26"/>
       <c r="C104" s="42" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D104" s="42" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E104" s="29"/>
       <c r="F104" s="29" t="s">
@@ -21095,7 +21115,7 @@
       <c r="R104" s="26"/>
       <c r="S104" s="19"/>
       <c r="T104" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21104,10 +21124,10 @@
       </c>
       <c r="B105" s="32"/>
       <c r="C105" s="43" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E105" s="35"/>
       <c r="F105" s="35" t="s">
@@ -21150,7 +21170,7 @@
       <c r="R105" s="32"/>
       <c r="S105" s="19"/>
       <c r="T105" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21161,10 +21181,10 @@
         <v>201</v>
       </c>
       <c r="C106" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="D106" s="22" t="s">
         <v>483</v>
-      </c>
-      <c r="D106" s="22" t="s">
-        <v>484</v>
       </c>
       <c r="E106" s="39" t="s">
         <v>202</v>
@@ -21211,7 +21231,7 @@
       </c>
       <c r="S106" s="19"/>
       <c r="T106" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21220,10 +21240,10 @@
       </c>
       <c r="B107" s="26"/>
       <c r="C107" s="27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D107" s="28" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E107" s="29"/>
       <c r="F107" s="30" t="s">
@@ -21266,7 +21286,7 @@
       <c r="R107" s="26"/>
       <c r="S107" s="19"/>
       <c r="T107" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21275,10 +21295,10 @@
       </c>
       <c r="B108" s="26"/>
       <c r="C108" s="27" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E108" s="29"/>
       <c r="F108" s="30" t="s">
@@ -21321,7 +21341,7 @@
       <c r="R108" s="26"/>
       <c r="S108" s="19"/>
       <c r="T108" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21330,10 +21350,10 @@
       </c>
       <c r="B109" s="32"/>
       <c r="C109" s="33" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E109" s="35"/>
       <c r="F109" s="36" t="s">
@@ -21376,7 +21396,7 @@
       <c r="R109" s="32"/>
       <c r="S109" s="19"/>
       <c r="T109" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="110" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21443,10 +21463,10 @@
         <v>213</v>
       </c>
       <c r="C111" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="D111" s="22" t="s">
         <v>488</v>
-      </c>
-      <c r="D111" s="22" t="s">
-        <v>489</v>
       </c>
       <c r="E111" s="38" t="s">
         <v>214</v>
@@ -21493,7 +21513,7 @@
       </c>
       <c r="S111" s="19"/>
       <c r="T111" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="112" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21502,10 +21522,10 @@
       </c>
       <c r="B112" s="26"/>
       <c r="C112" s="27" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D112" s="28" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E112" s="29"/>
       <c r="F112" s="30" t="s">
@@ -21548,7 +21568,7 @@
       <c r="R112" s="26"/>
       <c r="S112" s="19"/>
       <c r="T112" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="113" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21557,10 +21577,10 @@
       </c>
       <c r="B113" s="32"/>
       <c r="C113" s="33" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D113" s="34" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E113" s="35"/>
       <c r="F113" s="36" t="s">
@@ -21603,7 +21623,7 @@
       <c r="R113" s="32"/>
       <c r="S113" s="19"/>
       <c r="T113" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="114" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21614,10 +21634,10 @@
         <v>219</v>
       </c>
       <c r="C114" s="41" t="s">
+        <v>491</v>
+      </c>
+      <c r="D114" s="41" t="s">
         <v>492</v>
-      </c>
-      <c r="D114" s="41" t="s">
-        <v>493</v>
       </c>
       <c r="E114" s="38" t="s">
         <v>220</v>
@@ -21664,7 +21684,7 @@
       </c>
       <c r="S114" s="19"/>
       <c r="T114" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="115" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21673,10 +21693,10 @@
       </c>
       <c r="B115" s="26"/>
       <c r="C115" s="42" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D115" s="42" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E115" s="29"/>
       <c r="F115" s="29" t="s">
@@ -21719,7 +21739,7 @@
       <c r="R115" s="26"/>
       <c r="S115" s="19"/>
       <c r="T115" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="116" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21728,14 +21748,14 @@
       </c>
       <c r="B116" s="26"/>
       <c r="C116" s="42" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D116" s="42" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E116" s="29"/>
       <c r="F116" s="29" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G116" s="31" t="s">
         <v>21</v>
@@ -21774,7 +21794,7 @@
       <c r="R116" s="26"/>
       <c r="S116" s="19"/>
       <c r="T116" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21783,10 +21803,10 @@
       </c>
       <c r="B117" s="32"/>
       <c r="C117" s="43" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D117" s="43" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E117" s="35"/>
       <c r="F117" s="35" t="s">
@@ -21829,7 +21849,7 @@
       <c r="R117" s="32"/>
       <c r="S117" s="19"/>
       <c r="T117" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="118" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21837,19 +21857,19 @@
         <v>111</v>
       </c>
       <c r="B118" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="C118" s="21" t="s">
         <v>498</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="D118" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="D118" s="22" t="s">
+      <c r="E118" s="39" t="s">
         <v>500</v>
       </c>
-      <c r="E118" s="39" t="s">
-        <v>501</v>
-      </c>
       <c r="F118" s="39" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G118" s="24" t="s">
         <v>21</v>
@@ -21890,7 +21910,7 @@
       </c>
       <c r="S118" s="19"/>
       <c r="T118" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="119" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21899,14 +21919,14 @@
       </c>
       <c r="B119" s="26"/>
       <c r="C119" s="27" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E119" s="29"/>
       <c r="F119" s="30" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G119" s="31" t="s">
         <v>39</v>
@@ -21945,7 +21965,7 @@
       <c r="R119" s="26"/>
       <c r="S119" s="19"/>
       <c r="T119" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="120" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21954,14 +21974,14 @@
       </c>
       <c r="B120" s="32"/>
       <c r="C120" s="33" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D120" s="34" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E120" s="35"/>
       <c r="F120" s="36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G120" s="37" t="s">
         <v>39</v>
@@ -22000,7 +22020,7 @@
       <c r="R120" s="32"/>
       <c r="S120" s="19"/>
       <c r="T120" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22008,17 +22028,17 @@
         <v>114</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C121" s="21" t="s">
         <v>172</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E121" s="25"/>
       <c r="F121" s="59" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G121" s="24" t="s">
         <v>21</v>
@@ -22059,7 +22079,7 @@
       </c>
       <c r="S121" s="19"/>
       <c r="T121" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="122" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22071,11 +22091,11 @@
         <v>172</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E122" s="29"/>
       <c r="F122" s="30" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G122" s="31" t="s">
         <v>21</v>
@@ -22114,7 +22134,7 @@
       <c r="R122" s="26"/>
       <c r="S122" s="19"/>
       <c r="T122" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="123" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22126,11 +22146,11 @@
         <v>172</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E123" s="29"/>
       <c r="F123" s="30" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G123" s="31" t="s">
         <v>21</v>
@@ -22139,7 +22159,7 @@
         <v>172</v>
       </c>
       <c r="I123" s="29" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J123" s="54">
         <v>32181</v>
@@ -22169,7 +22189,7 @@
       <c r="R123" s="26"/>
       <c r="S123" s="19"/>
       <c r="T123" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="124" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22181,11 +22201,11 @@
         <v>172</v>
       </c>
       <c r="D124" s="34" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E124" s="35"/>
       <c r="F124" s="36" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G124" s="37" t="s">
         <v>21</v>
@@ -22224,7 +22244,7 @@
       <c r="R124" s="32"/>
       <c r="S124" s="19"/>
       <c r="T124" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="125" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22289,10 +22309,10 @@
         <v>228</v>
       </c>
       <c r="C126" s="21" t="s">
+        <v>515</v>
+      </c>
+      <c r="D126" s="22" t="s">
         <v>516</v>
-      </c>
-      <c r="D126" s="22" t="s">
-        <v>517</v>
       </c>
       <c r="E126" s="38" t="s">
         <v>229</v>
@@ -22339,7 +22359,7 @@
       </c>
       <c r="S126" s="19"/>
       <c r="T126" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="127" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22348,10 +22368,10 @@
       </c>
       <c r="B127" s="26"/>
       <c r="C127" s="27" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E127" s="29"/>
       <c r="F127" s="30" t="s">
@@ -22394,7 +22414,7 @@
       <c r="R127" s="26"/>
       <c r="S127" s="19"/>
       <c r="T127" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="128" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22403,10 +22423,10 @@
       </c>
       <c r="B128" s="32"/>
       <c r="C128" s="33" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D128" s="34" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E128" s="35"/>
       <c r="F128" s="36" t="s">
@@ -22449,7 +22469,7 @@
       <c r="R128" s="32"/>
       <c r="S128" s="19"/>
       <c r="T128" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="129" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22457,19 +22477,19 @@
         <v>122</v>
       </c>
       <c r="B129" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="C129" s="21" t="s">
         <v>520</v>
       </c>
-      <c r="C129" s="21" t="s">
+      <c r="D129" s="22" t="s">
         <v>521</v>
       </c>
-      <c r="D129" s="22" t="s">
+      <c r="E129" s="39" t="s">
         <v>522</v>
       </c>
-      <c r="E129" s="39" t="s">
-        <v>523</v>
-      </c>
       <c r="F129" s="39" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G129" s="24" t="s">
         <v>21</v>
@@ -22510,7 +22530,7 @@
       </c>
       <c r="S129" s="19"/>
       <c r="T129" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="130" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22519,14 +22539,14 @@
       </c>
       <c r="B130" s="26"/>
       <c r="C130" s="27" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D130" s="28" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E130" s="29"/>
       <c r="F130" s="30" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G130" s="31" t="s">
         <v>39</v>
@@ -22565,7 +22585,7 @@
       <c r="R130" s="26"/>
       <c r="S130" s="19"/>
       <c r="T130" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="131" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22574,14 +22594,14 @@
       </c>
       <c r="B131" s="26"/>
       <c r="C131" s="27" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D131" s="28" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E131" s="29"/>
       <c r="F131" s="30" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G131" s="31" t="s">
         <v>39</v>
@@ -22620,7 +22640,7 @@
       <c r="R131" s="26"/>
       <c r="S131" s="19"/>
       <c r="T131" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="132" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22629,14 +22649,14 @@
       </c>
       <c r="B132" s="32"/>
       <c r="C132" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E132" s="35"/>
       <c r="F132" s="36" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G132" s="37" t="s">
         <v>21</v>
@@ -22675,7 +22695,7 @@
       <c r="R132" s="32"/>
       <c r="S132" s="19"/>
       <c r="T132" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22683,19 +22703,19 @@
         <v>126</v>
       </c>
       <c r="B133" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="C133" s="22" t="s">
         <v>530</v>
       </c>
-      <c r="C133" s="22" t="s">
+      <c r="D133" s="22" t="s">
         <v>531</v>
       </c>
-      <c r="D133" s="22" t="s">
+      <c r="E133" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="E133" s="39" t="s">
-        <v>533</v>
-      </c>
       <c r="F133" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G133" s="24" t="s">
         <v>21</v>
@@ -22736,7 +22756,7 @@
       </c>
       <c r="S133" s="19"/>
       <c r="T133" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="134" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22745,14 +22765,14 @@
       </c>
       <c r="B134" s="29"/>
       <c r="C134" s="28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D134" s="28" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E134" s="29"/>
       <c r="F134" s="30" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G134" s="31" t="s">
         <v>39</v>
@@ -22791,7 +22811,7 @@
       <c r="R134" s="26"/>
       <c r="S134" s="19"/>
       <c r="T134" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="135" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22800,14 +22820,14 @@
       </c>
       <c r="B135" s="29"/>
       <c r="C135" s="28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D135" s="28" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E135" s="29"/>
       <c r="F135" s="30" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G135" s="31" t="s">
         <v>39</v>
@@ -22846,7 +22866,7 @@
       <c r="R135" s="26"/>
       <c r="S135" s="19"/>
       <c r="T135" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="136" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22855,14 +22875,14 @@
       </c>
       <c r="B136" s="29"/>
       <c r="C136" s="28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D136" s="28" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E136" s="29"/>
       <c r="F136" s="30" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G136" s="31" t="s">
         <v>21</v>
@@ -22901,7 +22921,7 @@
       <c r="R136" s="26"/>
       <c r="S136" s="19"/>
       <c r="T136" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="137" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22910,14 +22930,14 @@
       </c>
       <c r="B137" s="35"/>
       <c r="C137" s="34" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D137" s="34" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E137" s="35"/>
       <c r="F137" s="36" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G137" s="37" t="s">
         <v>39</v>
@@ -22956,7 +22976,7 @@
       <c r="R137" s="32"/>
       <c r="S137" s="19"/>
       <c r="T137" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="138" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22964,19 +22984,19 @@
         <v>131</v>
       </c>
       <c r="B138" s="20" t="s">
+        <v>541</v>
+      </c>
+      <c r="C138" s="22" t="s">
         <v>542</v>
       </c>
-      <c r="C138" s="22" t="s">
+      <c r="D138" s="22" t="s">
         <v>543</v>
       </c>
-      <c r="D138" s="22" t="s">
+      <c r="E138" s="39" t="s">
         <v>544</v>
       </c>
-      <c r="E138" s="39" t="s">
-        <v>545</v>
-      </c>
       <c r="F138" s="39" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G138" s="24" t="s">
         <v>39</v>
@@ -23017,7 +23037,7 @@
       </c>
       <c r="S138" s="19"/>
       <c r="T138" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23033,13 +23053,13 @@
       </c>
       <c r="E139" s="29"/>
       <c r="F139" s="30" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G139" s="31" t="s">
         <v>21</v>
       </c>
       <c r="H139" s="53" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I139" s="31" t="s">
         <v>172</v>
@@ -23071,7 +23091,7 @@
       <c r="R139" s="26"/>
       <c r="S139" s="19"/>
       <c r="T139" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="140" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23087,7 +23107,7 @@
       </c>
       <c r="E140" s="29"/>
       <c r="F140" s="30" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G140" s="31" t="s">
         <v>21</v>
@@ -23125,7 +23145,7 @@
       <c r="R140" s="26"/>
       <c r="S140" s="19"/>
       <c r="T140" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="141" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23141,7 +23161,7 @@
       </c>
       <c r="E141" s="35"/>
       <c r="F141" s="36" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G141" s="37" t="s">
         <v>39</v>
@@ -23179,7 +23199,7 @@
       <c r="R141" s="32"/>
       <c r="S141" s="19"/>
       <c r="T141" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="142" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23190,10 +23210,10 @@
         <v>233</v>
       </c>
       <c r="C142" s="41" t="s">
+        <v>549</v>
+      </c>
+      <c r="D142" s="41" t="s">
         <v>550</v>
-      </c>
-      <c r="D142" s="41" t="s">
-        <v>551</v>
       </c>
       <c r="E142" s="38" t="s">
         <v>234</v>
@@ -23240,7 +23260,7 @@
       </c>
       <c r="S142" s="19"/>
       <c r="T142" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="143" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23249,10 +23269,10 @@
       </c>
       <c r="B143" s="26"/>
       <c r="C143" s="42" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D143" s="42" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E143" s="29"/>
       <c r="F143" s="29" t="s">
@@ -23295,7 +23315,7 @@
       <c r="R143" s="26"/>
       <c r="S143" s="19"/>
       <c r="T143" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="144" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23304,10 +23324,10 @@
       </c>
       <c r="B144" s="26"/>
       <c r="C144" s="42" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D144" s="42" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E144" s="29"/>
       <c r="F144" s="29" t="s">
@@ -23350,7 +23370,7 @@
       <c r="R144" s="26"/>
       <c r="S144" s="19"/>
       <c r="T144" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="145" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23359,10 +23379,10 @@
       </c>
       <c r="B145" s="32"/>
       <c r="C145" s="43" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D145" s="43" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E145" s="35"/>
       <c r="F145" s="35" t="s">
@@ -23405,7 +23425,7 @@
       <c r="R145" s="26"/>
       <c r="S145" s="19"/>
       <c r="T145" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="146" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23472,10 +23492,10 @@
         <v>239</v>
       </c>
       <c r="C147" s="41" t="s">
+        <v>554</v>
+      </c>
+      <c r="D147" s="41" t="s">
         <v>555</v>
-      </c>
-      <c r="D147" s="41" t="s">
-        <v>556</v>
       </c>
       <c r="E147" s="38" t="s">
         <v>240</v>
@@ -23522,7 +23542,7 @@
       </c>
       <c r="S147" s="19"/>
       <c r="T147" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="148" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23531,10 +23551,10 @@
       </c>
       <c r="B148" s="26"/>
       <c r="C148" s="42" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D148" s="42" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E148" s="29"/>
       <c r="F148" s="29" t="s">
@@ -23577,7 +23597,7 @@
       <c r="R148" s="26"/>
       <c r="S148" s="19"/>
       <c r="T148" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="149" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23586,10 +23606,10 @@
       </c>
       <c r="B149" s="26"/>
       <c r="C149" s="42" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D149" s="42" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E149" s="29"/>
       <c r="F149" s="29" t="s">
@@ -23632,7 +23652,7 @@
       <c r="R149" s="26"/>
       <c r="S149" s="19"/>
       <c r="T149" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="150" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23641,10 +23661,10 @@
       </c>
       <c r="B150" s="32"/>
       <c r="C150" s="43" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D150" s="43" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E150" s="35"/>
       <c r="F150" s="35" t="s">
@@ -23687,7 +23707,7 @@
       <c r="R150" s="32"/>
       <c r="S150" s="19"/>
       <c r="T150" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="151" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23698,10 +23718,10 @@
         <v>244</v>
       </c>
       <c r="C151" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="D151" s="22" t="s">
         <v>560</v>
-      </c>
-      <c r="D151" s="22" t="s">
-        <v>561</v>
       </c>
       <c r="E151" s="39" t="s">
         <v>245</v>
@@ -23748,7 +23768,7 @@
       </c>
       <c r="S151" s="19"/>
       <c r="T151" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="152" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23757,10 +23777,10 @@
       </c>
       <c r="B152" s="26"/>
       <c r="C152" s="27" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D152" s="28" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E152" s="29"/>
       <c r="F152" s="30" t="s">
@@ -23803,7 +23823,7 @@
       <c r="R152" s="26"/>
       <c r="S152" s="19"/>
       <c r="T152" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="153" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23812,10 +23832,10 @@
       </c>
       <c r="B153" s="26"/>
       <c r="C153" s="27" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D153" s="28" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E153" s="29"/>
       <c r="F153" s="30" t="s">
@@ -23858,7 +23878,7 @@
       <c r="R153" s="26"/>
       <c r="S153" s="19"/>
       <c r="T153" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="154" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23867,10 +23887,10 @@
       </c>
       <c r="B154" s="32"/>
       <c r="C154" s="33" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D154" s="34" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E154" s="35"/>
       <c r="F154" s="36" t="s">
@@ -23913,7 +23933,7 @@
       <c r="R154" s="32"/>
       <c r="S154" s="19"/>
       <c r="T154" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="155" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23924,16 +23944,16 @@
         <v>251</v>
       </c>
       <c r="C155" s="21" t="s">
+        <v>564</v>
+      </c>
+      <c r="D155" s="22" t="s">
         <v>565</v>
       </c>
-      <c r="D155" s="22" t="s">
+      <c r="E155" s="39" t="s">
         <v>566</v>
       </c>
-      <c r="E155" s="39" t="s">
-        <v>567</v>
-      </c>
       <c r="F155" s="39" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G155" s="24" t="s">
         <v>21</v>
@@ -23974,7 +23994,7 @@
       </c>
       <c r="S155" s="19"/>
       <c r="T155" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23983,14 +24003,14 @@
       </c>
       <c r="B156" s="26"/>
       <c r="C156" s="27" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D156" s="28" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E156" s="29"/>
       <c r="F156" s="30" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G156" s="31" t="s">
         <v>39</v>
@@ -24029,7 +24049,7 @@
       <c r="R156" s="19"/>
       <c r="S156" s="19"/>
       <c r="T156" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="157" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24038,14 +24058,14 @@
       </c>
       <c r="B157" s="32"/>
       <c r="C157" s="33" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E157" s="35"/>
       <c r="F157" s="36" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G157" s="37" t="s">
         <v>39</v>
@@ -24084,7 +24104,7 @@
       <c r="R157" s="19"/>
       <c r="S157" s="19"/>
       <c r="T157" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="158" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24149,10 +24169,10 @@
         <v>257</v>
       </c>
       <c r="C159" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="D159" s="22" t="s">
         <v>572</v>
-      </c>
-      <c r="D159" s="22" t="s">
-        <v>573</v>
       </c>
       <c r="E159" s="39" t="s">
         <v>258</v>
@@ -24199,7 +24219,7 @@
       </c>
       <c r="S159" s="19"/>
       <c r="T159" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="160" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24208,10 +24228,10 @@
       </c>
       <c r="B160" s="26"/>
       <c r="C160" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D160" s="28" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E160" s="29"/>
       <c r="F160" s="30" t="s">
@@ -24254,7 +24274,7 @@
       <c r="R160" s="26"/>
       <c r="S160" s="19"/>
       <c r="T160" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="161" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24263,10 +24283,10 @@
       </c>
       <c r="B161" s="26"/>
       <c r="C161" s="27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D161" s="28" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E161" s="29"/>
       <c r="F161" s="30" t="s">
@@ -24309,7 +24329,7 @@
       <c r="R161" s="26"/>
       <c r="S161" s="19"/>
       <c r="T161" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="162" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24318,10 +24338,10 @@
       </c>
       <c r="B162" s="32"/>
       <c r="C162" s="33" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D162" s="34" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E162" s="35"/>
       <c r="F162" s="36" t="s">
@@ -24364,7 +24384,7 @@
       <c r="R162" s="26"/>
       <c r="S162" s="19"/>
       <c r="T162" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="163" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24480,19 +24500,19 @@
         <v>158</v>
       </c>
       <c r="B165" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C165" s="41" t="s">
+        <v>576</v>
+      </c>
+      <c r="D165" s="41" t="s">
+        <v>577</v>
+      </c>
+      <c r="E165" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="C165" s="41" t="s">
-        <v>577</v>
-      </c>
-      <c r="D165" s="41" t="s">
-        <v>578</v>
-      </c>
-      <c r="E165" s="38" t="s">
-        <v>268</v>
-      </c>
       <c r="F165" s="38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G165" s="24" t="s">
         <v>21</v>
@@ -24501,7 +24521,7 @@
         <v>22</v>
       </c>
       <c r="I165" s="25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J165" s="51">
         <v>29182</v>
@@ -24533,7 +24553,7 @@
       </c>
       <c r="S165" s="19"/>
       <c r="T165" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="166" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24542,14 +24562,14 @@
       </c>
       <c r="B166" s="26"/>
       <c r="C166" s="42" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D166" s="42" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E166" s="29"/>
       <c r="F166" s="29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G166" s="31" t="s">
         <v>39</v>
@@ -24588,7 +24608,7 @@
       <c r="R166" s="26"/>
       <c r="S166" s="19"/>
       <c r="T166" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24597,14 +24617,14 @@
       </c>
       <c r="B167" s="26"/>
       <c r="C167" s="42" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D167" s="42" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E167" s="29"/>
       <c r="F167" s="29" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G167" s="31" t="s">
         <v>21</v>
@@ -24629,7 +24649,7 @@
         <v>25</v>
       </c>
       <c r="N167" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O167" s="31" t="s">
         <v>27</v>
@@ -24643,7 +24663,7 @@
       <c r="R167" s="26"/>
       <c r="S167" s="19"/>
       <c r="T167" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="168" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24652,14 +24672,14 @@
       </c>
       <c r="B168" s="32"/>
       <c r="C168" s="43" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D168" s="43" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E168" s="35"/>
       <c r="F168" s="35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G168" s="37" t="s">
         <v>21</v>
@@ -24698,7 +24718,7 @@
       <c r="R168" s="32"/>
       <c r="S168" s="19"/>
       <c r="T168" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="169" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24706,19 +24726,19 @@
         <v>162</v>
       </c>
       <c r="B169" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="C169" s="41" t="s">
+        <v>581</v>
+      </c>
+      <c r="D169" s="41" t="s">
+        <v>582</v>
+      </c>
+      <c r="E169" s="38" t="s">
         <v>274</v>
       </c>
-      <c r="C169" s="41" t="s">
-        <v>582</v>
-      </c>
-      <c r="D169" s="41" t="s">
-        <v>583</v>
-      </c>
-      <c r="E169" s="38" t="s">
-        <v>275</v>
-      </c>
       <c r="F169" s="38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G169" s="24" t="s">
         <v>21</v>
@@ -24759,7 +24779,7 @@
       </c>
       <c r="S169" s="19"/>
       <c r="T169" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="170" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24768,14 +24788,14 @@
       </c>
       <c r="B170" s="26"/>
       <c r="C170" s="42" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D170" s="42" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E170" s="29"/>
       <c r="F170" s="29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G170" s="31" t="s">
         <v>39</v>
@@ -24814,7 +24834,7 @@
       <c r="R170" s="26"/>
       <c r="S170" s="19"/>
       <c r="T170" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="171" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24823,14 +24843,14 @@
       </c>
       <c r="B171" s="26"/>
       <c r="C171" s="42" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D171" s="42" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E171" s="29"/>
       <c r="F171" s="29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G171" s="31" t="s">
         <v>21</v>
@@ -24869,7 +24889,7 @@
       <c r="R171" s="26"/>
       <c r="S171" s="19"/>
       <c r="T171" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="172" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24878,14 +24898,14 @@
       </c>
       <c r="B172" s="26"/>
       <c r="C172" s="42" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D172" s="42" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E172" s="29"/>
       <c r="F172" s="29" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G172" s="31" t="s">
         <v>21</v>
@@ -24924,7 +24944,7 @@
       <c r="R172" s="26"/>
       <c r="S172" s="19"/>
       <c r="T172" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="173" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24933,14 +24953,14 @@
       </c>
       <c r="B173" s="32"/>
       <c r="C173" s="43" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D173" s="43" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E173" s="35"/>
       <c r="F173" s="35" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G173" s="37" t="s">
         <v>39</v>
@@ -24979,7 +24999,7 @@
       <c r="R173" s="32"/>
       <c r="S173" s="19"/>
       <c r="T173" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="174" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24987,19 +25007,19 @@
         <v>167</v>
       </c>
       <c r="B174" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C174" s="41" t="s">
+        <v>587</v>
+      </c>
+      <c r="D174" s="41" t="s">
+        <v>588</v>
+      </c>
+      <c r="E174" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="C174" s="41" t="s">
-        <v>588</v>
-      </c>
-      <c r="D174" s="41" t="s">
-        <v>589</v>
-      </c>
-      <c r="E174" s="38" t="s">
-        <v>281</v>
-      </c>
       <c r="F174" s="38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G174" s="24" t="s">
         <v>21</v>
@@ -25040,7 +25060,7 @@
       </c>
       <c r="S174" s="19"/>
       <c r="T174" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="175" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25049,14 +25069,14 @@
       </c>
       <c r="B175" s="26"/>
       <c r="C175" s="42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D175" s="42" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E175" s="29"/>
       <c r="F175" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G175" s="31" t="s">
         <v>39</v>
@@ -25065,7 +25085,7 @@
         <v>40</v>
       </c>
       <c r="I175" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J175" s="54">
         <v>30165</v>
@@ -25095,7 +25115,7 @@
       <c r="R175" s="26"/>
       <c r="S175" s="19"/>
       <c r="T175" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="176" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25104,14 +25124,14 @@
       </c>
       <c r="B176" s="26"/>
       <c r="C176" s="42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D176" s="42" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E176" s="29"/>
       <c r="F176" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G176" s="31" t="s">
         <v>21</v>
@@ -25120,7 +25140,7 @@
         <v>44</v>
       </c>
       <c r="I176" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J176" s="54">
         <v>39711</v>
@@ -25150,7 +25170,7 @@
       <c r="R176" s="26"/>
       <c r="S176" s="19"/>
       <c r="T176" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25159,14 +25179,14 @@
       </c>
       <c r="B177" s="26"/>
       <c r="C177" s="42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D177" s="42" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E177" s="29"/>
       <c r="F177" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G177" s="31" t="s">
         <v>21</v>
@@ -25205,7 +25225,7 @@
       <c r="R177" s="26"/>
       <c r="S177" s="19"/>
       <c r="T177" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="178" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25214,14 +25234,14 @@
       </c>
       <c r="B178" s="32"/>
       <c r="C178" s="43" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D178" s="43" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E178" s="35"/>
       <c r="F178" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G178" s="37" t="s">
         <v>21</v>
@@ -25252,7 +25272,7 @@
         <v>27</v>
       </c>
       <c r="P178" s="35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q178" s="35" t="s">
         <v>63</v>
@@ -25260,7 +25280,7 @@
       <c r="R178" s="32"/>
       <c r="S178" s="19"/>
       <c r="T178" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25268,19 +25288,19 @@
         <v>172</v>
       </c>
       <c r="B179" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C179" s="41" t="s">
+        <v>593</v>
+      </c>
+      <c r="D179" s="41" t="s">
         <v>594</v>
       </c>
-      <c r="D179" s="41" t="s">
+      <c r="E179" s="38" t="s">
         <v>595</v>
       </c>
-      <c r="E179" s="38" t="s">
-        <v>596</v>
-      </c>
       <c r="F179" s="38" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G179" s="24" t="s">
         <v>21</v>
@@ -25321,7 +25341,7 @@
       </c>
       <c r="S179" s="19"/>
       <c r="T179" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="180" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25330,14 +25350,14 @@
       </c>
       <c r="B180" s="26"/>
       <c r="C180" s="42" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D180" s="42" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E180" s="29"/>
       <c r="F180" s="29" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G180" s="31" t="s">
         <v>39</v>
@@ -25376,7 +25396,7 @@
       <c r="R180" s="26"/>
       <c r="S180" s="19"/>
       <c r="T180" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25385,14 +25405,14 @@
       </c>
       <c r="B181" s="26"/>
       <c r="C181" s="42" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D181" s="42" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E181" s="29"/>
       <c r="F181" s="29" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G181" s="31" t="s">
         <v>21</v>
@@ -25431,7 +25451,7 @@
       <c r="R181" s="26"/>
       <c r="S181" s="19"/>
       <c r="T181" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25440,14 +25460,14 @@
       </c>
       <c r="B182" s="26"/>
       <c r="C182" s="42" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D182" s="42" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E182" s="29"/>
       <c r="F182" s="73" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G182" s="31" t="s">
         <v>21</v>
@@ -25486,7 +25506,7 @@
       <c r="R182" s="26"/>
       <c r="S182" s="19"/>
       <c r="T182" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25495,14 +25515,14 @@
       </c>
       <c r="B183" s="26"/>
       <c r="C183" s="42" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D183" s="42" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E183" s="29"/>
       <c r="F183" s="29" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G183" s="31" t="s">
         <v>21</v>
@@ -25541,7 +25561,7 @@
       <c r="R183" s="26"/>
       <c r="S183" s="19"/>
       <c r="T183" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25550,14 +25570,14 @@
       </c>
       <c r="B184" s="32"/>
       <c r="C184" s="43" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D184" s="43" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E184" s="35"/>
       <c r="F184" s="35" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G184" s="37" t="s">
         <v>39</v>
@@ -25588,7 +25608,7 @@
         <v>27</v>
       </c>
       <c r="P184" s="35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q184" s="19" t="s">
         <v>63</v>
@@ -25596,7 +25616,7 @@
       <c r="R184" s="32"/>
       <c r="S184" s="19"/>
       <c r="T184" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="185" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25604,7 +25624,7 @@
         <v>178</v>
       </c>
       <c r="B185" s="20" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C185" s="74" t="s">
         <v>172</v>
@@ -25613,10 +25633,10 @@
         <v>172</v>
       </c>
       <c r="E185" s="75" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F185" s="75" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G185" s="18" t="s">
         <v>21</v>
@@ -25653,7 +25673,7 @@
       </c>
       <c r="S185" s="19"/>
       <c r="T185" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25669,7 +25689,7 @@
       </c>
       <c r="E186" s="19"/>
       <c r="F186" s="76" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G186" s="18" t="s">
         <v>39</v>
@@ -25678,7 +25698,7 @@
         <v>40</v>
       </c>
       <c r="I186" s="19" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J186" s="48">
         <v>30633</v>
@@ -25706,7 +25726,7 @@
       <c r="R186" s="26"/>
       <c r="S186" s="19"/>
       <c r="T186" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="187" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25722,7 +25742,7 @@
       </c>
       <c r="E187" s="19"/>
       <c r="F187" s="76" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G187" s="18" t="s">
         <v>21</v>
@@ -25731,7 +25751,7 @@
         <v>44</v>
       </c>
       <c r="I187" s="19" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J187" s="48">
         <v>37428</v>
@@ -25757,7 +25777,7 @@
       <c r="R187" s="26"/>
       <c r="S187" s="19"/>
       <c r="T187" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="188" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25773,7 +25793,7 @@
       </c>
       <c r="E188" s="19"/>
       <c r="F188" s="76" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G188" s="18" t="s">
         <v>21</v>
@@ -25782,7 +25802,7 @@
         <v>44</v>
       </c>
       <c r="I188" s="19" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J188" s="48">
         <v>38512</v>
@@ -25808,7 +25828,7 @@
       <c r="R188" s="26"/>
       <c r="S188" s="19"/>
       <c r="T188" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="189" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25824,7 +25844,7 @@
       </c>
       <c r="E189" s="19"/>
       <c r="F189" s="76" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G189" s="18" t="s">
         <v>39</v>
@@ -25833,7 +25853,7 @@
         <v>44</v>
       </c>
       <c r="I189" s="19" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="J189" s="48">
         <v>40102</v>
@@ -25859,7 +25879,7 @@
       <c r="R189" s="26"/>
       <c r="S189" s="19"/>
       <c r="T189" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="190" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25875,7 +25895,7 @@
       </c>
       <c r="E190" s="19"/>
       <c r="F190" s="76" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G190" s="18" t="s">
         <v>21</v>
@@ -25884,7 +25904,7 @@
         <v>44</v>
       </c>
       <c r="I190" s="19" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J190" s="48">
         <v>40230</v>
@@ -25910,7 +25930,7 @@
       <c r="R190" s="26"/>
       <c r="S190" s="19"/>
       <c r="T190" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="191" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25926,7 +25946,7 @@
       </c>
       <c r="E191" s="19"/>
       <c r="F191" s="76" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G191" s="18" t="s">
         <v>39</v>
@@ -25935,7 +25955,7 @@
         <v>44</v>
       </c>
       <c r="I191" s="19" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J191" s="48">
         <v>41570</v>
@@ -25961,7 +25981,7 @@
       <c r="R191" s="26"/>
       <c r="S191" s="19"/>
       <c r="T191" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="192" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25977,7 +25997,7 @@
       </c>
       <c r="E192" s="19"/>
       <c r="F192" s="76" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G192" s="18" t="s">
         <v>39</v>
@@ -25986,7 +26006,7 @@
         <v>44</v>
       </c>
       <c r="I192" s="19" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J192" s="48">
         <v>43126</v>
@@ -26008,7 +26028,7 @@
         <v>27</v>
       </c>
       <c r="P192" s="35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q192" s="19" t="s">
         <v>63</v>
@@ -26016,7 +26036,7 @@
       <c r="R192" s="26"/>
       <c r="S192" s="19"/>
       <c r="T192" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="193" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26032,7 +26052,7 @@
       </c>
       <c r="E193" s="19"/>
       <c r="F193" s="76" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G193" s="18" t="s">
         <v>39</v>
@@ -26041,7 +26061,7 @@
         <v>44</v>
       </c>
       <c r="I193" s="19" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J193" s="48">
         <v>44241</v>
@@ -26063,7 +26083,7 @@
         <v>27</v>
       </c>
       <c r="P193" s="35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q193" s="19" t="s">
         <v>63</v>
@@ -26071,7 +26091,7 @@
       <c r="R193" s="32"/>
       <c r="S193" s="19"/>
       <c r="T193" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="194" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26079,19 +26099,19 @@
         <v>187</v>
       </c>
       <c r="B194" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="C194" s="41" t="s">
+        <v>620</v>
+      </c>
+      <c r="D194" s="41" t="s">
+        <v>621</v>
+      </c>
+      <c r="E194" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="C194" s="41" t="s">
-        <v>621</v>
-      </c>
-      <c r="D194" s="41" t="s">
-        <v>622</v>
-      </c>
-      <c r="E194" s="38" t="s">
-        <v>290</v>
-      </c>
       <c r="F194" s="38" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G194" s="24" t="s">
         <v>21</v>
@@ -26100,7 +26120,7 @@
         <v>22</v>
       </c>
       <c r="I194" s="25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J194" s="51">
         <v>25422</v>
@@ -26132,7 +26152,7 @@
       </c>
       <c r="S194" s="19"/>
       <c r="T194" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="195" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26141,14 +26161,14 @@
       </c>
       <c r="B195" s="26"/>
       <c r="C195" s="42" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D195" s="42" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E195" s="29"/>
       <c r="F195" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G195" s="31" t="s">
         <v>39</v>
@@ -26157,7 +26177,7 @@
         <v>40</v>
       </c>
       <c r="I195" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J195" s="54">
         <v>26784</v>
@@ -26187,7 +26207,7 @@
       <c r="R195" s="26"/>
       <c r="S195" s="19"/>
       <c r="T195" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="196" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26196,14 +26216,14 @@
       </c>
       <c r="B196" s="26"/>
       <c r="C196" s="42" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D196" s="42" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E196" s="29"/>
       <c r="F196" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G196" s="31" t="s">
         <v>39</v>
@@ -26242,7 +26262,7 @@
       <c r="R196" s="26"/>
       <c r="S196" s="19"/>
       <c r="T196" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="197" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26251,14 +26271,14 @@
       </c>
       <c r="B197" s="32"/>
       <c r="C197" s="43" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D197" s="43" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E197" s="35"/>
       <c r="F197" s="35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G197" s="37" t="s">
         <v>39</v>
@@ -26297,7 +26317,7 @@
       <c r="R197" s="32"/>
       <c r="S197" s="19"/>
       <c r="T197" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="198" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26305,19 +26325,19 @@
         <v>191</v>
       </c>
       <c r="B198" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="C198" s="21" t="s">
         <v>626</v>
       </c>
-      <c r="C198" s="21" t="s">
+      <c r="D198" s="22" t="s">
         <v>627</v>
       </c>
-      <c r="D198" s="22" t="s">
+      <c r="E198" s="39" t="s">
         <v>628</v>
       </c>
-      <c r="E198" s="39" t="s">
-        <v>629</v>
-      </c>
       <c r="F198" s="39" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G198" s="24" t="s">
         <v>21</v>
@@ -26326,7 +26346,7 @@
         <v>22</v>
       </c>
       <c r="I198" s="25" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J198" s="51">
         <v>16132</v>
@@ -26351,14 +26371,14 @@
         <v>34</v>
       </c>
       <c r="Q198" s="19" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R198" s="20" t="s">
         <v>30</v>
       </c>
       <c r="S198" s="19"/>
       <c r="T198" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="199" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26367,14 +26387,14 @@
       </c>
       <c r="B199" s="26"/>
       <c r="C199" s="27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D199" s="28" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E199" s="29"/>
       <c r="F199" s="29" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G199" s="31" t="s">
         <v>39</v>
@@ -26413,7 +26433,7 @@
       <c r="R199" s="26"/>
       <c r="S199" s="19"/>
       <c r="T199" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="200" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26422,14 +26442,14 @@
       </c>
       <c r="B200" s="26"/>
       <c r="C200" s="27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D200" s="28" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E200" s="29"/>
       <c r="F200" s="29" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G200" s="31" t="s">
         <v>21</v>
@@ -26468,7 +26488,7 @@
       <c r="R200" s="26"/>
       <c r="S200" s="19"/>
       <c r="T200" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="201" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26477,14 +26497,14 @@
       </c>
       <c r="B201" s="26"/>
       <c r="C201" s="27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D201" s="28" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E201" s="29"/>
       <c r="F201" s="29" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G201" s="31" t="s">
         <v>21</v>
@@ -26523,7 +26543,7 @@
       <c r="R201" s="26"/>
       <c r="S201" s="19"/>
       <c r="T201" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="202" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26532,14 +26552,14 @@
       </c>
       <c r="B202" s="26"/>
       <c r="C202" s="27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D202" s="28" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E202" s="29"/>
       <c r="F202" s="29" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G202" s="31" t="s">
         <v>21</v>
@@ -26578,7 +26598,7 @@
       <c r="R202" s="26"/>
       <c r="S202" s="19"/>
       <c r="T202" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="203" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26587,14 +26607,14 @@
       </c>
       <c r="B203" s="32"/>
       <c r="C203" s="33" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D203" s="34" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E203" s="35"/>
       <c r="F203" s="35" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G203" s="37" t="s">
         <v>39</v>
@@ -26633,7 +26653,7 @@
       <c r="R203" s="32"/>
       <c r="S203" s="19"/>
       <c r="T203" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="204" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26641,19 +26661,19 @@
         <v>197</v>
       </c>
       <c r="B204" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="C204" s="21" t="s">
+        <v>641</v>
+      </c>
+      <c r="D204" s="22" t="s">
+        <v>642</v>
+      </c>
+      <c r="E204" s="38" t="s">
         <v>296</v>
       </c>
-      <c r="C204" s="21" t="s">
-        <v>642</v>
-      </c>
-      <c r="D204" s="22" t="s">
-        <v>643</v>
-      </c>
-      <c r="E204" s="38" t="s">
-        <v>297</v>
-      </c>
       <c r="F204" s="38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G204" s="24" t="s">
         <v>21</v>
@@ -26687,14 +26707,14 @@
         <v>34</v>
       </c>
       <c r="Q204" s="25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R204" s="20" t="s">
         <v>30</v>
       </c>
       <c r="S204" s="19"/>
       <c r="T204" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="205" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26703,14 +26723,14 @@
       </c>
       <c r="B205" s="26"/>
       <c r="C205" s="27" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D205" s="28" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E205" s="29"/>
       <c r="F205" s="29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G205" s="31" t="s">
         <v>39</v>
@@ -26749,7 +26769,7 @@
       <c r="R205" s="26"/>
       <c r="S205" s="19"/>
       <c r="T205" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="206" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26758,14 +26778,14 @@
       </c>
       <c r="B206" s="26"/>
       <c r="C206" s="27" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D206" s="28" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E206" s="29"/>
       <c r="F206" s="29" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G206" s="31" t="s">
         <v>39</v>
@@ -26804,7 +26824,7 @@
       <c r="R206" s="26"/>
       <c r="S206" s="19"/>
       <c r="T206" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="207" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26813,14 +26833,14 @@
       </c>
       <c r="B207" s="32"/>
       <c r="C207" s="33" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D207" s="34" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E207" s="35"/>
       <c r="F207" s="35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G207" s="37" t="s">
         <v>21</v>
@@ -26859,7 +26879,7 @@
       <c r="R207" s="32"/>
       <c r="S207" s="19"/>
       <c r="T207" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="208" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26867,19 +26887,19 @@
         <v>201</v>
       </c>
       <c r="B208" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="C208" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="D208" s="22" t="s">
+        <v>647</v>
+      </c>
+      <c r="E208" s="38" t="s">
         <v>302</v>
       </c>
-      <c r="C208" s="21" t="s">
-        <v>647</v>
-      </c>
-      <c r="D208" s="22" t="s">
-        <v>648</v>
-      </c>
-      <c r="E208" s="38" t="s">
-        <v>303</v>
-      </c>
       <c r="F208" s="38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G208" s="24" t="s">
         <v>39</v>
@@ -26920,7 +26940,7 @@
       </c>
       <c r="S208" s="19"/>
       <c r="T208" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="209" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26929,14 +26949,14 @@
       </c>
       <c r="B209" s="26"/>
       <c r="C209" s="27" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D209" s="28" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E209" s="29"/>
       <c r="F209" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G209" s="31" t="s">
         <v>21</v>
@@ -26975,7 +26995,7 @@
       <c r="R209" s="26"/>
       <c r="S209" s="19"/>
       <c r="T209" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="210" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26984,14 +27004,14 @@
       </c>
       <c r="B210" s="32"/>
       <c r="C210" s="33" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D210" s="34" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E210" s="35"/>
       <c r="F210" s="35" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G210" s="37" t="s">
         <v>39</v>
@@ -27030,7 +27050,7 @@
       <c r="R210" s="32"/>
       <c r="S210" s="19"/>
       <c r="T210" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="211" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27038,19 +27058,19 @@
         <v>204</v>
       </c>
       <c r="B211" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="C211" s="21" t="s">
         <v>651</v>
       </c>
-      <c r="C211" s="21" t="s">
+      <c r="D211" s="22" t="s">
         <v>652</v>
       </c>
-      <c r="D211" s="22" t="s">
+      <c r="E211" s="39" t="s">
         <v>653</v>
       </c>
-      <c r="E211" s="39" t="s">
-        <v>654</v>
-      </c>
       <c r="F211" s="39" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G211" s="24" t="s">
         <v>21</v>
@@ -27084,14 +27104,14 @@
         <v>34</v>
       </c>
       <c r="Q211" s="25" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R211" s="20" t="s">
         <v>36</v>
       </c>
       <c r="S211" s="19"/>
       <c r="T211" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="212" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27100,14 +27120,14 @@
       </c>
       <c r="B212" s="32"/>
       <c r="C212" s="33" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D212" s="34" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E212" s="35"/>
       <c r="F212" s="36" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G212" s="37" t="s">
         <v>39</v>
@@ -27146,7 +27166,7 @@
       <c r="R212" s="32"/>
       <c r="S212" s="19"/>
       <c r="T212" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="213" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27154,19 +27174,19 @@
         <v>206</v>
       </c>
       <c r="B213" s="20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C213" s="21" t="s">
+        <v>655</v>
+      </c>
+      <c r="D213" s="22" t="s">
         <v>656</v>
       </c>
-      <c r="D213" s="22" t="s">
-        <v>657</v>
-      </c>
       <c r="E213" s="39" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F213" s="59" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G213" s="24" t="s">
         <v>21</v>
@@ -27207,7 +27227,7 @@
       </c>
       <c r="S213" s="19"/>
       <c r="T213" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="214" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27216,14 +27236,14 @@
       </c>
       <c r="B214" s="26"/>
       <c r="C214" s="27" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D214" s="28" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E214" s="29"/>
       <c r="F214" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G214" s="31" t="s">
         <v>39</v>
@@ -27262,7 +27282,7 @@
       <c r="R214" s="26"/>
       <c r="S214" s="19"/>
       <c r="T214" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="215" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27271,14 +27291,14 @@
       </c>
       <c r="B215" s="26"/>
       <c r="C215" s="27" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D215" s="28" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E215" s="29"/>
       <c r="F215" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G215" s="31" t="s">
         <v>21</v>
@@ -27317,7 +27337,7 @@
       <c r="R215" s="26"/>
       <c r="S215" s="19"/>
       <c r="T215" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="216" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27326,14 +27346,14 @@
       </c>
       <c r="B216" s="26"/>
       <c r="C216" s="27" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D216" s="28" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E216" s="29"/>
       <c r="F216" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G216" s="31" t="s">
         <v>39</v>
@@ -27372,7 +27392,7 @@
       <c r="R216" s="26"/>
       <c r="S216" s="19"/>
       <c r="T216" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="217" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27381,14 +27401,14 @@
       </c>
       <c r="B217" s="32"/>
       <c r="C217" s="33" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D217" s="34" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E217" s="35"/>
       <c r="F217" s="36" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G217" s="37" t="s">
         <v>21</v>
@@ -27427,7 +27447,7 @@
       <c r="R217" s="32"/>
       <c r="S217" s="19"/>
       <c r="T217" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="218" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27435,7 +27455,7 @@
         <v>211</v>
       </c>
       <c r="B218" s="64" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C218" s="78"/>
       <c r="D218" s="79"/>
@@ -27467,19 +27487,19 @@
         <v>212</v>
       </c>
       <c r="B219" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="C219" s="41" t="s">
+        <v>661</v>
+      </c>
+      <c r="D219" s="41" t="s">
+        <v>662</v>
+      </c>
+      <c r="E219" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="C219" s="41" t="s">
-        <v>662</v>
-      </c>
-      <c r="D219" s="41" t="s">
-        <v>663</v>
-      </c>
-      <c r="E219" s="38" t="s">
-        <v>322</v>
-      </c>
       <c r="F219" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G219" s="24" t="s">
         <v>21</v>
@@ -27504,7 +27524,7 @@
         <v>25</v>
       </c>
       <c r="N219" s="25" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O219" s="24" t="s">
         <v>27</v>
@@ -27520,7 +27540,7 @@
       </c>
       <c r="S219" s="19"/>
       <c r="T219" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="220" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27529,14 +27549,14 @@
       </c>
       <c r="B220" s="26"/>
       <c r="C220" s="42" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D220" s="42" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E220" s="29"/>
       <c r="F220" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G220" s="31" t="s">
         <v>39</v>
@@ -27570,12 +27590,12 @@
         <v>204</v>
       </c>
       <c r="Q220" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R220" s="26"/>
       <c r="S220" s="19"/>
       <c r="T220" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="221" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27584,14 +27604,14 @@
       </c>
       <c r="B221" s="26"/>
       <c r="C221" s="42" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D221" s="42" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E221" s="29"/>
       <c r="F221" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G221" s="31" t="s">
         <v>39</v>
@@ -27630,7 +27650,7 @@
       <c r="R221" s="26"/>
       <c r="S221" s="19"/>
       <c r="T221" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="222" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27639,14 +27659,14 @@
       </c>
       <c r="B222" s="32"/>
       <c r="C222" s="33" t="s">
+        <v>665</v>
+      </c>
+      <c r="D222" s="34" t="s">
         <v>666</v>
-      </c>
-      <c r="D222" s="34" t="s">
-        <v>667</v>
       </c>
       <c r="E222" s="35"/>
       <c r="F222" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G222" s="37" t="s">
         <v>39</v>
@@ -27685,7 +27705,7 @@
       <c r="R222" s="32"/>
       <c r="S222" s="19"/>
       <c r="T222" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="223" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27693,19 +27713,19 @@
         <v>216</v>
       </c>
       <c r="B223" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="C223" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="D223" s="22" t="s">
+        <v>668</v>
+      </c>
+      <c r="E223" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="C223" s="21" t="s">
-        <v>668</v>
-      </c>
-      <c r="D223" s="22" t="s">
-        <v>669</v>
-      </c>
-      <c r="E223" s="38" t="s">
-        <v>329</v>
-      </c>
       <c r="F223" s="39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G223" s="24" t="s">
         <v>21</v>
@@ -27746,7 +27766,7 @@
       </c>
       <c r="S223" s="19"/>
       <c r="T223" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="224" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27755,14 +27775,14 @@
       </c>
       <c r="B224" s="26"/>
       <c r="C224" s="27" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E224" s="29"/>
       <c r="F224" s="30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G224" s="31" t="s">
         <v>39</v>
@@ -27801,7 +27821,7 @@
       <c r="R224" s="26"/>
       <c r="S224" s="19"/>
       <c r="T224" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="225" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27810,14 +27830,14 @@
       </c>
       <c r="B225" s="32"/>
       <c r="C225" s="33" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D225" s="34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E225" s="35"/>
       <c r="F225" s="36" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G225" s="37" t="s">
         <v>39</v>
@@ -27856,7 +27876,7 @@
       <c r="R225" s="32"/>
       <c r="S225" s="19"/>
       <c r="T225" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="226" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27864,19 +27884,19 @@
         <v>219</v>
       </c>
       <c r="B226" s="20" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C226" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="D226" s="22" t="s">
         <v>673</v>
       </c>
-      <c r="D226" s="22" t="s">
+      <c r="E226" s="38" t="s">
         <v>674</v>
       </c>
-      <c r="E226" s="38" t="s">
-        <v>675</v>
-      </c>
       <c r="F226" s="38" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G226" s="24" t="s">
         <v>21</v>
@@ -27917,7 +27937,7 @@
       </c>
       <c r="S226" s="19"/>
       <c r="T226" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="227" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27926,14 +27946,14 @@
       </c>
       <c r="B227" s="26"/>
       <c r="C227" s="27" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D227" s="28" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E227" s="29"/>
       <c r="F227" s="29" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G227" s="31" t="s">
         <v>21</v>
@@ -27972,7 +27992,7 @@
       <c r="R227" s="26"/>
       <c r="S227" s="19"/>
       <c r="T227" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="228" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27981,14 +28001,14 @@
       </c>
       <c r="B228" s="26"/>
       <c r="C228" s="27" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D228" s="28" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E228" s="29"/>
       <c r="F228" s="29" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G228" s="31" t="s">
         <v>39</v>
@@ -28027,7 +28047,7 @@
       <c r="R228" s="26"/>
       <c r="S228" s="19"/>
       <c r="T228" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="229" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28036,14 +28056,14 @@
       </c>
       <c r="B229" s="32"/>
       <c r="C229" s="33" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D229" s="34" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E229" s="35"/>
       <c r="F229" s="35" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G229" s="37" t="s">
         <v>21</v>
@@ -28082,7 +28102,7 @@
       <c r="R229" s="32"/>
       <c r="S229" s="19"/>
       <c r="T229" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="230" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28090,19 +28110,19 @@
         <v>223</v>
       </c>
       <c r="B230" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="C230" s="21" t="s">
+        <v>681</v>
+      </c>
+      <c r="D230" s="22" t="s">
+        <v>682</v>
+      </c>
+      <c r="E230" s="38" t="s">
         <v>332</v>
       </c>
-      <c r="C230" s="21" t="s">
-        <v>682</v>
-      </c>
-      <c r="D230" s="22" t="s">
-        <v>683</v>
-      </c>
-      <c r="E230" s="38" t="s">
-        <v>333</v>
-      </c>
       <c r="F230" s="38" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G230" s="24" t="s">
         <v>21</v>
@@ -28143,7 +28163,7 @@
       </c>
       <c r="S230" s="19"/>
       <c r="T230" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="231" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28152,14 +28172,14 @@
       </c>
       <c r="B231" s="26"/>
       <c r="C231" s="27" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D231" s="28" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E231" s="29"/>
       <c r="F231" s="29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G231" s="31" t="s">
         <v>39</v>
@@ -28198,7 +28218,7 @@
       <c r="R231" s="26"/>
       <c r="S231" s="19"/>
       <c r="T231" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="232" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28207,14 +28227,14 @@
       </c>
       <c r="B232" s="26"/>
       <c r="C232" s="27" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D232" s="28" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E232" s="29"/>
       <c r="F232" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G232" s="31" t="s">
         <v>21</v>
@@ -28253,7 +28273,7 @@
       <c r="R232" s="26"/>
       <c r="S232" s="19"/>
       <c r="T232" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="233" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28262,14 +28282,14 @@
       </c>
       <c r="B233" s="32"/>
       <c r="C233" s="33" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D233" s="34" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E233" s="35"/>
       <c r="F233" s="35" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G233" s="37" t="s">
         <v>21</v>
@@ -28308,7 +28328,7 @@
       <c r="R233" s="32"/>
       <c r="S233" s="19"/>
       <c r="T233" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="234" spans="1:20" s="2" customFormat="1">
@@ -28316,19 +28336,19 @@
         <v>227</v>
       </c>
       <c r="B234" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="C234" s="21" t="s">
+        <v>686</v>
+      </c>
+      <c r="D234" s="22" t="s">
+        <v>687</v>
+      </c>
+      <c r="E234" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="C234" s="21" t="s">
-        <v>687</v>
-      </c>
-      <c r="D234" s="22" t="s">
-        <v>688</v>
-      </c>
-      <c r="E234" s="39" t="s">
-        <v>338</v>
-      </c>
       <c r="F234" s="39" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G234" s="24" t="s">
         <v>21</v>
@@ -28369,7 +28389,7 @@
       </c>
       <c r="S234" s="19"/>
       <c r="T234" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="235" spans="1:20" s="2" customFormat="1">
@@ -28378,14 +28398,14 @@
       </c>
       <c r="B235" s="19"/>
       <c r="C235" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D235" s="28" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E235" s="29"/>
       <c r="F235" s="30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G235" s="31" t="s">
         <v>39</v>
@@ -28424,7 +28444,7 @@
       <c r="R235" s="19"/>
       <c r="S235" s="19"/>
       <c r="T235" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="236" spans="1:20" s="2" customFormat="1">
@@ -28433,14 +28453,14 @@
       </c>
       <c r="B236" s="19"/>
       <c r="C236" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D236" s="28" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E236" s="29"/>
       <c r="F236" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G236" s="31" t="s">
         <v>21</v>
@@ -28479,7 +28499,7 @@
       <c r="R236" s="19"/>
       <c r="S236" s="19"/>
       <c r="T236" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="237" spans="1:20" s="2" customFormat="1">
@@ -28488,14 +28508,14 @@
       </c>
       <c r="B237" s="19"/>
       <c r="C237" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D237" s="28" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E237" s="29"/>
       <c r="F237" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G237" s="31" t="s">
         <v>39</v>
@@ -28534,7 +28554,7 @@
       <c r="R237" s="26"/>
       <c r="S237" s="19"/>
       <c r="T237" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="238" spans="1:20" s="2" customFormat="1">
@@ -28543,14 +28563,14 @@
       </c>
       <c r="B238" s="19"/>
       <c r="C238" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D238" s="28" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E238" s="29"/>
       <c r="F238" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G238" s="31" t="s">
         <v>21</v>
@@ -28589,7 +28609,7 @@
       <c r="R238" s="26"/>
       <c r="S238" s="19"/>
       <c r="T238" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="239" spans="1:20" s="2" customFormat="1">
@@ -28598,14 +28618,14 @@
       </c>
       <c r="B239" s="19"/>
       <c r="C239" s="27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D239" s="28" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E239" s="29"/>
       <c r="F239" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G239" s="31" t="s">
         <v>39</v>
@@ -28644,7 +28664,7 @@
       <c r="R239" s="26"/>
       <c r="S239" s="19"/>
       <c r="T239" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="240" spans="1:20" s="2" customFormat="1">
@@ -28656,11 +28676,11 @@
         <v>172</v>
       </c>
       <c r="D240" s="34" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E240" s="35"/>
       <c r="F240" s="36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G240" s="37" t="s">
         <v>39</v>
@@ -28699,7 +28719,7 @@
       <c r="R240" s="32"/>
       <c r="S240" s="19"/>
       <c r="T240" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="242" spans="6:6">

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F126E1F7-4A47-4091-9F3B-A758DC04AEE2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278AEA1F-1469-4841-8E65-50224DB6C176}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4023,10 +4023,10 @@
         <v>27</v>
       </c>
       <c r="M9" s="29" t="s">
-        <v>721</v>
+        <v>155</v>
       </c>
       <c r="N9" s="29" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="O9" s="136"/>
       <c r="P9" s="19" t="s">
@@ -4068,7 +4068,7 @@
         <v>27</v>
       </c>
       <c r="M10" s="29" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="N10" s="29" t="s">
         <v>742</v>
@@ -4603,10 +4603,10 @@
         <v>27</v>
       </c>
       <c r="M22" s="29" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="N22" s="29" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="O22" s="136"/>
       <c r="P22" s="19" t="s">
@@ -4647,8 +4647,8 @@
       <c r="L23" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M23" s="35" t="s">
-        <v>49</v>
+      <c r="M23" s="29" t="s">
+        <v>91</v>
       </c>
       <c r="N23" s="35" t="s">
         <v>742</v>
@@ -5206,10 +5206,10 @@
         <v>27</v>
       </c>
       <c r="M35" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="N35" s="29" t="s">
-        <v>742</v>
+        <v>155</v>
+      </c>
+      <c r="N35" s="25" t="s">
+        <v>739</v>
       </c>
       <c r="O35" s="136"/>
       <c r="P35" s="19" t="s">
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="M36" s="29" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="N36" s="29" t="s">
         <v>742</v>
@@ -5295,8 +5295,8 @@
       <c r="L37" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M37" s="35" t="s">
-        <v>720</v>
+      <c r="M37" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="N37" s="35" t="s">
         <v>732</v>
@@ -5437,7 +5437,7 @@
         <v>27</v>
       </c>
       <c r="M40" s="29" t="s">
-        <v>720</v>
+        <v>91</v>
       </c>
       <c r="N40" s="29" t="s">
         <v>732</v>
@@ -5764,7 +5764,7 @@
         <v>27</v>
       </c>
       <c r="M47" s="29" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="N47" s="29" t="s">
         <v>742</v>
@@ -5808,8 +5808,8 @@
       <c r="L48" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M48" s="35" t="s">
-        <v>61</v>
+      <c r="M48" s="29" t="s">
+        <v>49</v>
       </c>
       <c r="N48" s="35" t="s">
         <v>742</v>
@@ -6180,8 +6180,8 @@
       <c r="L56" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M56" s="29" t="s">
-        <v>91</v>
+      <c r="M56" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="N56" s="29" t="s">
         <v>742</v>
@@ -6225,8 +6225,8 @@
       <c r="L57" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M57" s="35" t="s">
-        <v>61</v>
+      <c r="M57" s="29" t="s">
+        <v>91</v>
       </c>
       <c r="N57" s="35" t="s">
         <v>742</v>
@@ -6366,11 +6366,11 @@
       <c r="L60" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="M60" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="N60" s="29" t="s">
-        <v>742</v>
+      <c r="M60" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="N60" s="91" t="s">
+        <v>732</v>
       </c>
       <c r="O60" s="136"/>
       <c r="P60" s="19" t="s">
@@ -6411,8 +6411,8 @@
       <c r="L61" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M61" s="29" t="s">
-        <v>61</v>
+      <c r="M61" s="91" t="s">
+        <v>732</v>
       </c>
       <c r="N61" s="29" t="s">
         <v>742</v>
@@ -6829,10 +6829,10 @@
         <v>27</v>
       </c>
       <c r="M70" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="N70" s="29" t="s">
-        <v>742</v>
+        <v>155</v>
+      </c>
+      <c r="N70" s="91" t="s">
+        <v>732</v>
       </c>
       <c r="O70" s="136"/>
       <c r="P70" s="19" t="s">
@@ -6873,8 +6873,8 @@
       <c r="L71" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M71" s="35" t="s">
-        <v>61</v>
+      <c r="M71" s="29" t="s">
+        <v>49</v>
       </c>
       <c r="N71" s="35" t="s">
         <v>742</v>

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278AEA1F-1469-4841-8E65-50224DB6C176}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECB4ECE-18E5-4976-AC03-9737BF982073}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="761">
   <si>
     <t>DAFTAR PENDUDUK RT 06 - RW 14</t>
   </si>
@@ -968,9 +968,6 @@
   </si>
   <si>
     <t>ARSYLA  ROMEESA PUTRI HIDAYAT</t>
-  </si>
-  <si>
-    <t>TK</t>
   </si>
   <si>
     <t>KANZIA AMBERLY ALFHATUNISA HIDAYAT</t>
@@ -3880,10 +3877,10 @@
         <v>27</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O6" s="18" t="s">
         <v>30</v>
@@ -3931,10 +3928,10 @@
         <v>27</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O7" s="135" t="s">
         <v>36</v>
@@ -3978,10 +3975,10 @@
         <v>27</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O8" s="136"/>
       <c r="P8" s="19" t="s">
@@ -4026,7 +4023,7 @@
         <v>155</v>
       </c>
       <c r="N9" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O9" s="136"/>
       <c r="P9" s="19" t="s">
@@ -4071,7 +4068,7 @@
         <v>91</v>
       </c>
       <c r="N10" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O10" s="136"/>
       <c r="P10" s="19" t="s">
@@ -4113,10 +4110,10 @@
         <v>27</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O11" s="137"/>
       <c r="P11" s="19" t="s">
@@ -4162,10 +4159,10 @@
         <v>27</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N12" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O12" s="135" t="s">
         <v>30</v>
@@ -4209,10 +4206,10 @@
         <v>27</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O13" s="137"/>
       <c r="P13" s="46" t="s">
@@ -4283,7 +4280,7 @@
         <v>98</v>
       </c>
       <c r="N15" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O15" s="135" t="s">
         <v>30</v>
@@ -4296,7 +4293,7 @@
       <c r="A16" s="136"/>
       <c r="B16" s="29"/>
       <c r="C16" s="29" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>39</v>
@@ -4330,7 +4327,7 @@
         <v>98</v>
       </c>
       <c r="N16" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O16" s="136"/>
       <c r="P16" s="19" t="s">
@@ -4341,7 +4338,7 @@
       <c r="A17" s="136"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D17" s="31" t="s">
         <v>39</v>
@@ -4372,10 +4369,10 @@
         <v>27</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N17" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O17" s="136"/>
       <c r="P17" s="19" t="s">
@@ -4386,7 +4383,7 @@
       <c r="A18" s="136"/>
       <c r="B18" s="127"/>
       <c r="C18" s="127" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D18" s="116" t="s">
         <v>21</v>
@@ -4417,10 +4414,10 @@
         <v>27</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N18" s="35" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O18" s="136"/>
       <c r="P18" s="19" t="s">
@@ -4431,7 +4428,7 @@
       <c r="A19" s="137"/>
       <c r="B19" s="26"/>
       <c r="C19" s="134" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D19" s="116" t="s">
         <v>39</v>
@@ -4462,10 +4459,10 @@
         <v>27</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N19" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O19" s="137"/>
       <c r="P19" s="19" t="s">
@@ -4511,10 +4508,10 @@
         <v>27</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O20" s="135" t="s">
         <v>36</v>
@@ -4558,10 +4555,10 @@
         <v>27</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O21" s="136"/>
       <c r="P21" s="19" t="s">
@@ -4606,7 +4603,7 @@
         <v>155</v>
       </c>
       <c r="N22" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O22" s="136"/>
       <c r="P22" s="19" t="s">
@@ -4651,7 +4648,7 @@
         <v>91</v>
       </c>
       <c r="N23" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O23" s="137"/>
       <c r="P23" s="19" t="s">
@@ -4697,10 +4694,10 @@
         <v>27</v>
       </c>
       <c r="M24" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N24" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O24" s="135" t="s">
         <v>36</v>
@@ -4744,10 +4741,10 @@
         <v>27</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N25" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O25" s="136"/>
       <c r="P25" s="19" t="s">
@@ -4792,7 +4789,7 @@
         <v>49</v>
       </c>
       <c r="N26" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O26" s="136"/>
       <c r="P26" s="19" t="s">
@@ -4803,7 +4800,7 @@
       <c r="A27" s="137"/>
       <c r="B27" s="35"/>
       <c r="C27" s="35" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>21</v>
@@ -4834,10 +4831,10 @@
         <v>27</v>
       </c>
       <c r="M27" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N27" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O27" s="137"/>
       <c r="P27" s="19" t="s">
@@ -4883,10 +4880,10 @@
         <v>77</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N28" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O28" s="135" t="s">
         <v>36</v>
@@ -4930,10 +4927,10 @@
         <v>27</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N29" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O29" s="136"/>
       <c r="P29" s="19" t="s">
@@ -4978,7 +4975,7 @@
         <v>49</v>
       </c>
       <c r="N30" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O30" s="136"/>
       <c r="P30" s="19" t="s">
@@ -5023,7 +5020,7 @@
         <v>61</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O31" s="136"/>
       <c r="P31" s="19" t="s">
@@ -5068,7 +5065,7 @@
         <v>83</v>
       </c>
       <c r="N32" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O32" s="137"/>
       <c r="P32" s="19" t="s">
@@ -5114,10 +5111,10 @@
         <v>87</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N33" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O33" s="135" t="s">
         <v>36</v>
@@ -5161,10 +5158,10 @@
         <v>89</v>
       </c>
       <c r="M34" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N34" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O34" s="136"/>
       <c r="P34" s="19" t="s">
@@ -5209,7 +5206,7 @@
         <v>155</v>
       </c>
       <c r="N35" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O35" s="136"/>
       <c r="P35" s="19" t="s">
@@ -5254,7 +5251,7 @@
         <v>91</v>
       </c>
       <c r="N36" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O36" s="136"/>
       <c r="P36" s="19" t="s">
@@ -5299,7 +5296,7 @@
         <v>61</v>
       </c>
       <c r="N37" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O37" s="137"/>
       <c r="P37" s="19" t="s">
@@ -5311,10 +5308,10 @@
         <v>95</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>21</v>
@@ -5348,7 +5345,7 @@
         <v>98</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O38" s="135" t="s">
         <v>30</v>
@@ -5361,7 +5358,7 @@
       <c r="A39" s="136"/>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D39" s="31" t="s">
         <v>39</v>
@@ -5392,10 +5389,10 @@
         <v>27</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N39" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O39" s="136"/>
       <c r="P39" s="46" t="s">
@@ -5406,7 +5403,7 @@
       <c r="A40" s="136"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D40" s="31" t="s">
         <v>21</v>
@@ -5440,7 +5437,7 @@
         <v>91</v>
       </c>
       <c r="N40" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O40" s="136"/>
       <c r="P40" s="46" t="s">
@@ -5485,11 +5482,11 @@
       <c r="L41" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="M41" s="25" t="s">
-        <v>105</v>
+      <c r="M41" s="29" t="s">
+        <v>155</v>
       </c>
       <c r="N41" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O41" s="135" t="s">
         <v>36</v>
@@ -5533,10 +5530,10 @@
         <v>27</v>
       </c>
       <c r="M42" s="29" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="N42" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O42" s="136"/>
       <c r="P42" s="19" t="s">
@@ -5581,7 +5578,7 @@
         <v>61</v>
       </c>
       <c r="N43" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O43" s="136"/>
       <c r="P43" s="19" t="s">
@@ -5623,10 +5620,10 @@
         <v>27</v>
       </c>
       <c r="M44" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N44" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O44" s="137"/>
       <c r="P44" s="19" t="s">
@@ -5672,10 +5669,10 @@
         <v>112</v>
       </c>
       <c r="M45" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O45" s="135" t="s">
         <v>36</v>
@@ -5719,10 +5716,10 @@
         <v>27</v>
       </c>
       <c r="M46" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N46" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O46" s="136"/>
       <c r="P46" s="19" t="s">
@@ -5767,7 +5764,7 @@
         <v>91</v>
       </c>
       <c r="N47" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O47" s="136"/>
       <c r="P47" s="19" t="s">
@@ -5812,7 +5809,7 @@
         <v>49</v>
       </c>
       <c r="N48" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O48" s="137"/>
       <c r="P48" s="19" t="s">
@@ -5858,10 +5855,10 @@
         <v>27</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O49" s="135" t="s">
         <v>30</v>
@@ -5905,10 +5902,10 @@
         <v>27</v>
       </c>
       <c r="M50" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N50" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O50" s="136"/>
       <c r="P50" s="46" t="s">
@@ -5950,10 +5947,10 @@
         <v>27</v>
       </c>
       <c r="M51" s="29" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N51" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O51" s="136"/>
       <c r="P51" s="46" t="s">
@@ -5995,10 +5992,10 @@
         <v>27</v>
       </c>
       <c r="M52" s="29" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N52" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O52" s="136"/>
       <c r="P52" s="46" t="s">
@@ -6040,10 +6037,10 @@
         <v>27</v>
       </c>
       <c r="M53" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N53" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O53" s="137"/>
       <c r="P53" s="46" t="s">
@@ -6092,7 +6089,7 @@
         <v>126</v>
       </c>
       <c r="N54" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O54" s="135" t="s">
         <v>36</v>
@@ -6136,10 +6133,10 @@
         <v>27</v>
       </c>
       <c r="M55" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N55" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O55" s="136"/>
       <c r="P55" s="19" t="s">
@@ -6184,7 +6181,7 @@
         <v>204</v>
       </c>
       <c r="N56" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O56" s="136"/>
       <c r="P56" s="19" t="s">
@@ -6229,7 +6226,7 @@
         <v>91</v>
       </c>
       <c r="N57" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O57" s="137"/>
       <c r="P57" s="19" t="s">
@@ -6275,10 +6272,10 @@
         <v>112</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N58" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O58" s="135" t="s">
         <v>36</v>
@@ -6322,10 +6319,10 @@
         <v>112</v>
       </c>
       <c r="M59" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N59" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O59" s="136"/>
       <c r="P59" s="19" t="s">
@@ -6370,7 +6367,7 @@
         <v>204</v>
       </c>
       <c r="N60" s="91" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O60" s="136"/>
       <c r="P60" s="19" t="s">
@@ -6412,10 +6409,10 @@
         <v>27</v>
       </c>
       <c r="M61" s="91" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="N61" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O61" s="136"/>
       <c r="P61" s="19" t="s">
@@ -6457,10 +6454,10 @@
         <v>112</v>
       </c>
       <c r="M62" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N62" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O62" s="137"/>
       <c r="P62" s="19" t="s">
@@ -6506,10 +6503,10 @@
         <v>27</v>
       </c>
       <c r="M63" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N63" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O63" s="135" t="s">
         <v>30</v>
@@ -6553,10 +6550,10 @@
         <v>27</v>
       </c>
       <c r="M64" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N64" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O64" s="136"/>
       <c r="P64" s="46" t="s">
@@ -6598,10 +6595,10 @@
         <v>27</v>
       </c>
       <c r="M65" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N65" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O65" s="136"/>
       <c r="P65" s="46" t="s">
@@ -6643,10 +6640,10 @@
         <v>27</v>
       </c>
       <c r="M66" s="29" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="N66" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O66" s="136"/>
       <c r="P66" s="46" t="s">
@@ -6691,7 +6688,7 @@
         <v>61</v>
       </c>
       <c r="N67" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O67" s="137"/>
       <c r="P67" s="46" t="s">
@@ -6737,10 +6734,10 @@
         <v>27</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N68" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O68" s="135" t="s">
         <v>36</v>
@@ -6784,10 +6781,10 @@
         <v>27</v>
       </c>
       <c r="M69" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N69" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O69" s="136"/>
       <c r="P69" s="19" t="s">
@@ -6832,7 +6829,7 @@
         <v>155</v>
       </c>
       <c r="N70" s="91" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O70" s="136"/>
       <c r="P70" s="19" t="s">
@@ -6877,7 +6874,7 @@
         <v>49</v>
       </c>
       <c r="N71" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O71" s="137"/>
       <c r="P71" s="19" t="s">
@@ -6923,10 +6920,10 @@
         <v>27</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O72" s="135" t="s">
         <v>36</v>
@@ -6970,10 +6967,10 @@
         <v>27</v>
       </c>
       <c r="M73" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N73" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O73" s="136"/>
       <c r="P73" s="19" t="s">
@@ -7018,7 +7015,7 @@
         <v>49</v>
       </c>
       <c r="N74" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O74" s="136"/>
       <c r="P74" s="19" t="s">
@@ -7063,7 +7060,7 @@
         <v>61</v>
       </c>
       <c r="N75" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O75" s="137"/>
       <c r="P75" s="19" t="s">
@@ -7075,10 +7072,10 @@
         <v>154</v>
       </c>
       <c r="B76" s="93" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C76" s="93" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D76" s="24" t="s">
         <v>39</v>
@@ -7097,7 +7094,7 @@
         <v>69</v>
       </c>
       <c r="I76" s="25" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="J76" s="35" t="s">
         <v>25</v>
@@ -7109,10 +7106,10 @@
         <v>27</v>
       </c>
       <c r="M76" s="50" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N76" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O76" s="140" t="s">
         <v>30</v>
@@ -7125,7 +7122,7 @@
       <c r="A77" s="139"/>
       <c r="B77" s="94"/>
       <c r="C77" s="95" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D77" s="31" t="s">
         <v>21</v>
@@ -7156,10 +7153,10 @@
         <v>27</v>
       </c>
       <c r="M77" s="50" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N77" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O77" s="139"/>
       <c r="P77" s="46" t="s">
@@ -7205,10 +7202,10 @@
         <v>112</v>
       </c>
       <c r="M78" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N78" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O78" s="135" t="s">
         <v>36</v>
@@ -7252,10 +7249,10 @@
         <v>112</v>
       </c>
       <c r="M79" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N79" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O79" s="136"/>
       <c r="P79" s="19" t="s">
@@ -7300,7 +7297,7 @@
         <v>162</v>
       </c>
       <c r="N80" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O80" s="136"/>
       <c r="P80" s="19" t="s">
@@ -7342,10 +7339,10 @@
         <v>27</v>
       </c>
       <c r="M81" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N81" s="35" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O81" s="137"/>
       <c r="P81" s="19" t="s">
@@ -7391,10 +7388,10 @@
         <v>27</v>
       </c>
       <c r="M82" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N82" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O82" s="135" t="s">
         <v>36</v>
@@ -7438,10 +7435,10 @@
         <v>27</v>
       </c>
       <c r="M83" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N83" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O83" s="136"/>
       <c r="P83" s="19" t="s">
@@ -7483,10 +7480,10 @@
         <v>27</v>
       </c>
       <c r="M84" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N84" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O84" s="136"/>
       <c r="P84" s="19" t="s">
@@ -7531,7 +7528,7 @@
         <v>61</v>
       </c>
       <c r="N85" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O85" s="137"/>
       <c r="P85" s="19" t="s">
@@ -7580,7 +7577,7 @@
         <v>248</v>
       </c>
       <c r="N86" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O86" s="135" t="s">
         <v>30</v>
@@ -7627,7 +7624,7 @@
         <v>248</v>
       </c>
       <c r="N87" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O87" s="136"/>
       <c r="P87" s="19" t="s">
@@ -7672,7 +7669,7 @@
         <v>49</v>
       </c>
       <c r="N88" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O88" s="136"/>
       <c r="P88" s="19" t="s">
@@ -7717,7 +7714,7 @@
         <v>61</v>
       </c>
       <c r="N89" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O89" s="136"/>
       <c r="P89" s="19" t="s">
@@ -7759,10 +7756,10 @@
         <v>27</v>
       </c>
       <c r="M90" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N90" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O90" s="137"/>
       <c r="P90" s="19" t="s">
@@ -7774,10 +7771,10 @@
         <v>171</v>
       </c>
       <c r="B91" s="38" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D91" s="24" t="s">
         <v>21</v>
@@ -7808,10 +7805,10 @@
         <v>27</v>
       </c>
       <c r="M91" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N91" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O91" s="135" t="s">
         <v>30</v>
@@ -7824,7 +7821,7 @@
       <c r="A92" s="136"/>
       <c r="B92" s="29"/>
       <c r="C92" s="29" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D92" s="31" t="s">
         <v>39</v>
@@ -7855,10 +7852,10 @@
         <v>27</v>
       </c>
       <c r="M92" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N92" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O92" s="136"/>
       <c r="P92" s="46" t="s">
@@ -7869,7 +7866,7 @@
       <c r="A93" s="136"/>
       <c r="B93" s="91"/>
       <c r="C93" s="91" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D93" s="97" t="s">
         <v>39</v>
@@ -7900,10 +7897,10 @@
         <v>27</v>
       </c>
       <c r="M93" s="91" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N93" s="91" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O93" s="136"/>
       <c r="P93" s="46" t="s">
@@ -7949,10 +7946,10 @@
         <v>27</v>
       </c>
       <c r="M94" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N94" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O94" s="135" t="s">
         <v>36</v>
@@ -7996,10 +7993,10 @@
         <v>27</v>
       </c>
       <c r="M95" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N95" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O95" s="136"/>
       <c r="P95" s="19" t="s">
@@ -8041,10 +8038,10 @@
         <v>27</v>
       </c>
       <c r="M96" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N96" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O96" s="136"/>
       <c r="P96" s="19" t="s">
@@ -8089,7 +8086,7 @@
         <v>61</v>
       </c>
       <c r="N97" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O97" s="137"/>
       <c r="P97" s="19" t="s">
@@ -8135,10 +8132,10 @@
         <v>27</v>
       </c>
       <c r="M98" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N98" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O98" s="135" t="s">
         <v>30</v>
@@ -8182,10 +8179,10 @@
         <v>27</v>
       </c>
       <c r="M99" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N99" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O99" s="136"/>
       <c r="P99" s="19" t="s">
@@ -8227,10 +8224,10 @@
         <v>27</v>
       </c>
       <c r="M100" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N100" s="35" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O100" s="136"/>
       <c r="P100" s="19" t="s">
@@ -8276,10 +8273,10 @@
         <v>27</v>
       </c>
       <c r="M101" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N101" s="32" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O101" s="138" t="s">
         <v>36</v>
@@ -8326,7 +8323,7 @@
         <v>189</v>
       </c>
       <c r="N102" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O102" s="138"/>
       <c r="P102" s="19" t="s">
@@ -8368,10 +8365,10 @@
         <v>27</v>
       </c>
       <c r="M103" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N103" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O103" s="138"/>
       <c r="P103" s="19" t="s">
@@ -8413,10 +8410,10 @@
         <v>27</v>
       </c>
       <c r="M104" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N104" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O104" s="138"/>
       <c r="P104" s="19" t="s">
@@ -8461,7 +8458,7 @@
         <v>49</v>
       </c>
       <c r="N105" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O105" s="138"/>
       <c r="P105" s="19" t="s">
@@ -8506,7 +8503,7 @@
         <v>61</v>
       </c>
       <c r="N106" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O106" s="139"/>
       <c r="P106" s="19" t="s">
@@ -8552,10 +8549,10 @@
         <v>27</v>
       </c>
       <c r="M107" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N107" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O107" s="135" t="s">
         <v>36</v>
@@ -8599,10 +8596,10 @@
         <v>27</v>
       </c>
       <c r="M108" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N108" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O108" s="136"/>
       <c r="P108" s="19" t="s">
@@ -8644,10 +8641,10 @@
         <v>27</v>
       </c>
       <c r="M109" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N109" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O109" s="136"/>
       <c r="P109" s="19" t="s">
@@ -8692,7 +8689,7 @@
         <v>49</v>
       </c>
       <c r="N110" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O110" s="136"/>
       <c r="P110" s="19" t="s">
@@ -8737,7 +8734,7 @@
         <v>61</v>
       </c>
       <c r="N111" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O111" s="136"/>
       <c r="P111" s="19" t="s">
@@ -8782,7 +8779,7 @@
         <v>83</v>
       </c>
       <c r="N112" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O112" s="137"/>
       <c r="P112" s="19" t="s">
@@ -8831,7 +8828,7 @@
         <v>204</v>
       </c>
       <c r="N113" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O113" s="135" t="s">
         <v>36</v>
@@ -8875,10 +8872,10 @@
         <v>112</v>
       </c>
       <c r="M114" s="29" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="N114" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O114" s="136"/>
       <c r="P114" s="19" t="s">
@@ -8920,10 +8917,10 @@
         <v>112</v>
       </c>
       <c r="M115" s="29" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="N115" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O115" s="136"/>
       <c r="P115" s="19" t="s">
@@ -8964,11 +8961,11 @@
       <c r="L116" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M116" s="35" t="s">
-        <v>83</v>
+      <c r="M116" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="N116" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O116" s="137"/>
       <c r="P116" s="19" t="s">
@@ -9014,10 +9011,10 @@
         <v>27</v>
       </c>
       <c r="M117" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N117" s="32" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O117" s="135" t="s">
         <v>30</v>
@@ -9061,10 +9058,10 @@
         <v>27</v>
       </c>
       <c r="M118" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N118" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O118" s="136"/>
       <c r="P118" s="46" t="s">
@@ -9109,7 +9106,7 @@
         <v>49</v>
       </c>
       <c r="N119" s="32" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O119" s="136"/>
       <c r="P119" s="46" t="s">
@@ -9151,10 +9148,10 @@
         <v>27</v>
       </c>
       <c r="M120" s="102" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N120" s="102" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O120" s="137"/>
       <c r="P120" s="46" t="s">
@@ -9200,10 +9197,10 @@
         <v>27</v>
       </c>
       <c r="M121" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N121" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O121" s="135" t="s">
         <v>36</v>
@@ -9247,10 +9244,10 @@
         <v>112</v>
       </c>
       <c r="M122" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N122" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O122" s="136"/>
       <c r="P122" s="19" t="s">
@@ -9295,7 +9292,7 @@
         <v>91</v>
       </c>
       <c r="N123" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O123" s="137"/>
       <c r="P123" s="19" t="s">
@@ -9341,10 +9338,10 @@
         <v>27</v>
       </c>
       <c r="M124" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N124" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O124" s="135" t="s">
         <v>36</v>
@@ -9388,10 +9385,10 @@
         <v>27</v>
       </c>
       <c r="M125" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N125" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O125" s="136"/>
       <c r="P125" s="19" t="s">
@@ -9436,7 +9433,7 @@
         <v>61</v>
       </c>
       <c r="N126" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O126" s="137"/>
       <c r="P126" s="19" t="s">
@@ -9445,13 +9442,13 @@
     </row>
     <row r="127" spans="1:16" s="2" customFormat="1">
       <c r="A127" s="135" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B127" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C127" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D127" s="119" t="s">
         <v>39</v>
@@ -9470,7 +9467,7 @@
         <v>33</v>
       </c>
       <c r="I127" s="26" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="J127" s="35" t="s">
         <v>25</v>
@@ -9482,10 +9479,10 @@
         <v>27</v>
       </c>
       <c r="M127" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N127" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O127" s="135" t="s">
         <v>30</v>
@@ -9498,7 +9495,7 @@
       <c r="A128" s="136"/>
       <c r="B128" s="26"/>
       <c r="C128" s="26" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D128" s="117" t="s">
         <v>21</v>
@@ -9532,7 +9529,7 @@
         <v>49</v>
       </c>
       <c r="N128" s="32" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O128" s="136"/>
       <c r="P128" s="19" t="s">
@@ -9543,7 +9540,7 @@
       <c r="A129" s="137"/>
       <c r="B129" s="26"/>
       <c r="C129" s="26" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D129" s="97" t="s">
         <v>39</v>
@@ -9577,7 +9574,7 @@
         <v>61</v>
       </c>
       <c r="N129" s="32" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O129" s="137"/>
       <c r="P129" s="19" t="s">
@@ -9586,7 +9583,7 @@
     </row>
     <row r="130" spans="1:16" s="2" customFormat="1">
       <c r="A130" s="72" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B130" s="68"/>
       <c r="C130" s="68"/>
@@ -9645,10 +9642,10 @@
         <v>27</v>
       </c>
       <c r="M131" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N131" s="20" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O131" s="135" t="s">
         <v>30</v>
@@ -9692,10 +9689,10 @@
         <v>27</v>
       </c>
       <c r="M132" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N132" s="35" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O132" s="137"/>
       <c r="P132" s="19" t="s">
@@ -9707,10 +9704,10 @@
         <v>228</v>
       </c>
       <c r="B133" s="128" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C133" s="128" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D133" s="24" t="s">
         <v>21</v>
@@ -9744,7 +9741,7 @@
         <v>98</v>
       </c>
       <c r="N133" s="35" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O133" s="135" t="s">
         <v>30</v>
@@ -9757,7 +9754,7 @@
       <c r="A134" s="136"/>
       <c r="B134" s="29"/>
       <c r="C134" s="30" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D134" s="31" t="s">
         <v>39</v>
@@ -9788,10 +9785,10 @@
         <v>27</v>
       </c>
       <c r="M134" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N134" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O134" s="136"/>
       <c r="P134" s="19" t="s">
@@ -9802,7 +9799,7 @@
       <c r="A135" s="136"/>
       <c r="B135" s="91"/>
       <c r="C135" s="36" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D135" s="97" t="s">
         <v>39</v>
@@ -9833,10 +9830,10 @@
         <v>27</v>
       </c>
       <c r="M135" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N135" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O135" s="136"/>
       <c r="P135" s="19" t="s">
@@ -9847,7 +9844,7 @@
       <c r="A136" s="136"/>
       <c r="B136" s="91"/>
       <c r="C136" s="36" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D136" s="117" t="s">
         <v>21</v>
@@ -9881,7 +9878,7 @@
         <v>49</v>
       </c>
       <c r="N136" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O136" s="136"/>
       <c r="P136" s="19" t="s">
@@ -9892,7 +9889,7 @@
       <c r="A137" s="137"/>
       <c r="B137" s="35"/>
       <c r="C137" s="36" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D137" s="37" t="s">
         <v>21</v>
@@ -9923,10 +9920,10 @@
         <v>27</v>
       </c>
       <c r="M137" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N137" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O137" s="137"/>
       <c r="P137" s="19" t="s">
@@ -9935,13 +9932,13 @@
     </row>
     <row r="138" spans="1:16" s="2" customFormat="1">
       <c r="A138" s="120" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B138" s="150" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C138" s="150" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D138" s="123" t="s">
         <v>21</v>
@@ -9972,10 +9969,10 @@
         <v>27</v>
       </c>
       <c r="M138" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N138" s="126" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O138" s="120" t="s">
         <v>30</v>
@@ -9986,13 +9983,13 @@
     </row>
     <row r="139" spans="1:16" s="2" customFormat="1">
       <c r="A139" s="160" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B139" s="152" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C139" s="155" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D139" s="121" t="s">
         <v>21</v>
@@ -10023,10 +10020,10 @@
         <v>27</v>
       </c>
       <c r="M139" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N139" s="126" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O139" s="135" t="s">
         <v>30</v>
@@ -10039,7 +10036,7 @@
       <c r="A140" s="160"/>
       <c r="B140" s="153"/>
       <c r="C140" s="156" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D140" s="122" t="s">
         <v>39</v>
@@ -10070,10 +10067,10 @@
         <v>27</v>
       </c>
       <c r="M140" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N140" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O140" s="136"/>
       <c r="P140" s="46" t="s">
@@ -10084,7 +10081,7 @@
       <c r="A141" s="160"/>
       <c r="B141" s="154"/>
       <c r="C141" s="157" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D141" s="97" t="s">
         <v>39</v>
@@ -10093,7 +10090,7 @@
         <v>44</v>
       </c>
       <c r="F141" s="151" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G141" s="158">
         <v>45621</v>
@@ -10115,10 +10112,10 @@
         <v>27</v>
       </c>
       <c r="M141" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N141" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O141" s="137"/>
       <c r="P141" s="46" t="s">
@@ -10127,13 +10124,13 @@
     </row>
     <row r="142" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
       <c r="A142" s="116" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B142" s="127" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C142" s="127" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D142" s="117" t="s">
         <v>21</v>
@@ -10164,10 +10161,10 @@
         <v>27</v>
       </c>
       <c r="M142" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N142" s="20" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O142" s="136" t="s">
         <v>36</v>
@@ -10180,7 +10177,7 @@
       <c r="A143" s="116"/>
       <c r="B143" s="26"/>
       <c r="C143" s="134" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D143" s="118" t="s">
         <v>39</v>
@@ -10211,10 +10208,10 @@
         <v>27</v>
       </c>
       <c r="M143" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N143" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O143" s="136"/>
       <c r="P143" s="19" t="s">
@@ -10225,7 +10222,7 @@
       <c r="A144" s="116"/>
       <c r="B144" s="26"/>
       <c r="C144" s="134" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D144" s="97" t="s">
         <v>39</v>
@@ -10256,10 +10253,10 @@
         <v>27</v>
       </c>
       <c r="M144" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N144" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O144" s="136"/>
       <c r="P144" s="19" t="s">
@@ -10270,7 +10267,7 @@
       <c r="A145" s="116"/>
       <c r="B145" s="26"/>
       <c r="C145" s="134" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D145" s="117" t="s">
         <v>21</v>
@@ -10304,7 +10301,7 @@
         <v>98</v>
       </c>
       <c r="N145" s="126" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O145" s="136"/>
       <c r="P145" s="19" t="s">
@@ -10315,7 +10312,7 @@
       <c r="A146" s="116"/>
       <c r="B146" s="26"/>
       <c r="C146" s="134" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D146" s="118" t="s">
         <v>39</v>
@@ -10324,7 +10321,7 @@
         <v>40</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G146" s="124">
         <v>27706</v>
@@ -10349,7 +10346,7 @@
         <v>98</v>
       </c>
       <c r="N146" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O146" s="136"/>
       <c r="P146" s="19" t="s">
@@ -10360,7 +10357,7 @@
       <c r="A147" s="116"/>
       <c r="B147" s="26"/>
       <c r="C147" s="134" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D147" s="117" t="s">
         <v>21</v>
@@ -10391,10 +10388,10 @@
         <v>27</v>
       </c>
       <c r="M147" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N147" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O147" s="136"/>
       <c r="P147" s="19" t="s">
@@ -10405,7 +10402,7 @@
       <c r="A148" s="116"/>
       <c r="B148" s="26"/>
       <c r="C148" s="134" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D148" s="117" t="s">
         <v>21</v>
@@ -10439,7 +10436,7 @@
         <v>49</v>
       </c>
       <c r="N148" s="126" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O148" s="137"/>
       <c r="P148" s="19" t="s">
@@ -10485,10 +10482,10 @@
         <v>27</v>
       </c>
       <c r="M149" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N149" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O149" s="135" t="s">
         <v>36</v>
@@ -10535,7 +10532,7 @@
         <v>126</v>
       </c>
       <c r="N150" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O150" s="136"/>
       <c r="P150" s="19" t="s">
@@ -10580,7 +10577,7 @@
         <v>91</v>
       </c>
       <c r="N151" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O151" s="136"/>
       <c r="P151" s="19" t="s">
@@ -10666,10 +10663,10 @@
         <v>27</v>
       </c>
       <c r="M153" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N153" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O153" s="135" t="s">
         <v>36</v>
@@ -10713,10 +10710,10 @@
         <v>27</v>
       </c>
       <c r="M154" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N154" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O154" s="136"/>
       <c r="P154" s="19" t="s">
@@ -10761,7 +10758,7 @@
         <v>49</v>
       </c>
       <c r="N155" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O155" s="136"/>
       <c r="P155" s="19" t="s">
@@ -10806,7 +10803,7 @@
         <v>61</v>
       </c>
       <c r="N156" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O156" s="136"/>
       <c r="P156" s="19" t="s">
@@ -10848,10 +10845,10 @@
         <v>27</v>
       </c>
       <c r="M157" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N157" s="35" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O157" s="136"/>
       <c r="P157" s="19" t="s">
@@ -10893,10 +10890,10 @@
         <v>27</v>
       </c>
       <c r="M158" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N158" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O158" s="136"/>
       <c r="P158" s="19" t="s">
@@ -10933,10 +10930,10 @@
         <v>27</v>
       </c>
       <c r="M159" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N159" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O159" s="136"/>
       <c r="P159" s="19" t="s">
@@ -10978,10 +10975,10 @@
         <v>27</v>
       </c>
       <c r="M160" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N160" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O160" s="137"/>
       <c r="P160" s="19" t="s">
@@ -11030,7 +11027,7 @@
         <v>248</v>
       </c>
       <c r="N161" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O161" s="135" t="s">
         <v>36</v>
@@ -11077,7 +11074,7 @@
         <v>248</v>
       </c>
       <c r="N162" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O162" s="136"/>
       <c r="P162" s="19" t="s">
@@ -11122,7 +11119,7 @@
         <v>248</v>
       </c>
       <c r="N163" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O163" s="136"/>
       <c r="P163" s="19" t="s">
@@ -11164,10 +11161,10 @@
         <v>27</v>
       </c>
       <c r="M164" s="35" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="N164" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O164" s="137"/>
       <c r="P164" s="19" t="s">
@@ -11179,10 +11176,10 @@
         <v>251</v>
       </c>
       <c r="B165" s="39" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C165" s="39" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D165" s="24" t="s">
         <v>21</v>
@@ -11213,10 +11210,10 @@
         <v>27</v>
       </c>
       <c r="M165" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N165" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O165" s="141" t="s">
         <v>36</v>
@@ -11229,7 +11226,7 @@
       <c r="A166" s="136"/>
       <c r="B166" s="29"/>
       <c r="C166" s="30" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D166" s="31" t="s">
         <v>39</v>
@@ -11238,7 +11235,7 @@
         <v>40</v>
       </c>
       <c r="F166" s="29" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G166" s="54">
         <v>35026</v>
@@ -11260,10 +11257,10 @@
         <v>27</v>
       </c>
       <c r="M166" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N166" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O166" s="141"/>
       <c r="P166" s="19" t="s">
@@ -11274,7 +11271,7 @@
       <c r="A167" s="137"/>
       <c r="B167" s="35"/>
       <c r="C167" s="36" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D167" s="37" t="s">
         <v>21</v>
@@ -11305,10 +11302,10 @@
         <v>27</v>
       </c>
       <c r="M167" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N167" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O167" s="141"/>
       <c r="P167" s="19" t="s">
@@ -11320,10 +11317,10 @@
         <v>252</v>
       </c>
       <c r="B168" s="99" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C168" s="99" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D168" s="24" t="s">
         <v>21</v>
@@ -11354,10 +11351,10 @@
         <v>27</v>
       </c>
       <c r="M168" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N168" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O168" s="135" t="s">
         <v>30</v>
@@ -11370,7 +11367,7 @@
       <c r="A169" s="138"/>
       <c r="B169" s="32"/>
       <c r="C169" s="106" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D169" s="31" t="s">
         <v>39</v>
@@ -11401,10 +11398,10 @@
         <v>27</v>
       </c>
       <c r="M169" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N169" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O169" s="137"/>
       <c r="P169" s="19" t="s">
@@ -11453,7 +11450,7 @@
         <v>126</v>
       </c>
       <c r="N170" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O170" s="135" t="s">
         <v>36</v>
@@ -11500,7 +11497,7 @@
         <v>126</v>
       </c>
       <c r="N171" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O171" s="136"/>
       <c r="P171" s="19" t="s">
@@ -11542,10 +11539,10 @@
         <v>27</v>
       </c>
       <c r="M172" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N172" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O172" s="136"/>
       <c r="P172" s="19" t="s">
@@ -11590,7 +11587,7 @@
         <v>61</v>
       </c>
       <c r="N173" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O173" s="136"/>
       <c r="P173" s="19" t="s">
@@ -11639,7 +11636,7 @@
         <v>98</v>
       </c>
       <c r="N174" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O174" s="136" t="s">
         <v>30</v>
@@ -11683,10 +11680,10 @@
         <v>27</v>
       </c>
       <c r="M175" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N175" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O175" s="136"/>
       <c r="P175" s="19" t="s">
@@ -11728,10 +11725,10 @@
         <v>27</v>
       </c>
       <c r="M176" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N176" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O176" s="136"/>
       <c r="P176" s="19" t="s">
@@ -11776,7 +11773,7 @@
         <v>61</v>
       </c>
       <c r="N177" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O177" s="137"/>
       <c r="P177" s="19" t="s">
@@ -11788,10 +11785,10 @@
         <v>265</v>
       </c>
       <c r="B178" s="93" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C178" s="93" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D178" s="24" t="s">
         <v>21</v>
@@ -11825,7 +11822,7 @@
         <v>248</v>
       </c>
       <c r="N178" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O178" s="140" t="s">
         <v>30</v>
@@ -11838,7 +11835,7 @@
       <c r="A179" s="138"/>
       <c r="B179" s="101"/>
       <c r="C179" s="102" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D179" s="31" t="s">
         <v>39</v>
@@ -11872,7 +11869,7 @@
         <v>248</v>
       </c>
       <c r="N179" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O179" s="138"/>
       <c r="P179" s="19" t="s">
@@ -11883,7 +11880,7 @@
       <c r="A180" s="138"/>
       <c r="B180" s="101"/>
       <c r="C180" s="102" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D180" s="118" t="s">
         <v>39</v>
@@ -11917,7 +11914,7 @@
         <v>248</v>
       </c>
       <c r="N180" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O180" s="138"/>
       <c r="P180" s="19" t="s">
@@ -11928,7 +11925,7 @@
       <c r="A181" s="138"/>
       <c r="B181" s="101"/>
       <c r="C181" s="102" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D181" s="86" t="s">
         <v>39</v>
@@ -11962,7 +11959,7 @@
         <v>91</v>
       </c>
       <c r="N181" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O181" s="139"/>
       <c r="P181" s="19" t="s">
@@ -12008,10 +12005,10 @@
         <v>112</v>
       </c>
       <c r="M182" s="25" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="N182" s="19" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O182" s="135" t="s">
         <v>36</v>
@@ -12055,10 +12052,10 @@
         <v>27</v>
       </c>
       <c r="M183" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N183" s="19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O183" s="136"/>
       <c r="P183" s="19" t="s">
@@ -12103,7 +12100,7 @@
         <v>49</v>
       </c>
       <c r="N184" s="19" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O184" s="136"/>
       <c r="P184" s="19" t="s">
@@ -12117,7 +12114,7 @@
         <v>272</v>
       </c>
       <c r="D185" s="37" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E185" s="35" t="s">
         <v>44</v>
@@ -12148,7 +12145,7 @@
         <v>83</v>
       </c>
       <c r="N185" s="19" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O185" s="137"/>
       <c r="P185" s="19" t="s">
@@ -12194,10 +12191,10 @@
         <v>27</v>
       </c>
       <c r="M186" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N186" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O186" s="135" t="s">
         <v>36</v>
@@ -12241,10 +12238,10 @@
         <v>27</v>
       </c>
       <c r="M187" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N187" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O187" s="136"/>
       <c r="P187" s="19" t="s">
@@ -12289,7 +12286,7 @@
         <v>91</v>
       </c>
       <c r="N188" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O188" s="136"/>
       <c r="P188" s="19" t="s">
@@ -12334,7 +12331,7 @@
         <v>49</v>
       </c>
       <c r="N189" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O189" s="136"/>
       <c r="P189" s="19" t="s">
@@ -12379,7 +12376,7 @@
         <v>61</v>
       </c>
       <c r="N190" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O190" s="137"/>
       <c r="P190" s="19" t="s">
@@ -12432,13 +12429,13 @@
     </row>
     <row r="193" spans="1:16" s="2" customFormat="1">
       <c r="A193" s="135" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B193" s="38" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C193" s="38" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D193" s="24" t="s">
         <v>21</v>
@@ -12447,7 +12444,7 @@
         <v>22</v>
       </c>
       <c r="F193" s="25" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G193" s="51">
         <v>28003</v>
@@ -12472,7 +12469,7 @@
         <v>204</v>
       </c>
       <c r="N193" s="19" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O193" s="135" t="s">
         <v>30</v>
@@ -12485,7 +12482,7 @@
       <c r="A194" s="136"/>
       <c r="B194" s="29"/>
       <c r="C194" s="29" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D194" s="31" t="s">
         <v>39</v>
@@ -12519,7 +12516,7 @@
         <v>248</v>
       </c>
       <c r="N194" s="19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O194" s="136"/>
       <c r="P194" s="46" t="s">
@@ -12565,10 +12562,10 @@
         <v>27</v>
       </c>
       <c r="M195" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N195" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O195" s="135" t="s">
         <v>36</v>
@@ -12612,10 +12609,10 @@
         <v>112</v>
       </c>
       <c r="M196" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N196" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O196" s="136"/>
       <c r="P196" s="19" t="s">
@@ -12657,10 +12654,10 @@
         <v>27</v>
       </c>
       <c r="M197" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="N197" s="29" t="s">
-        <v>742</v>
+        <v>155</v>
+      </c>
+      <c r="N197" s="35" t="s">
+        <v>731</v>
       </c>
       <c r="O197" s="136"/>
       <c r="P197" s="19" t="s">
@@ -12701,11 +12698,11 @@
       <c r="L198" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M198" s="35" t="s">
-        <v>61</v>
+      <c r="M198" s="29" t="s">
+        <v>720</v>
       </c>
       <c r="N198" s="35" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="O198" s="137"/>
       <c r="P198" s="19" t="s">
@@ -12714,13 +12711,13 @@
     </row>
     <row r="199" spans="1:16" s="2" customFormat="1">
       <c r="A199" s="116" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B199" s="127" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C199" s="127" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D199" s="117" t="s">
         <v>21</v>
@@ -12754,7 +12751,7 @@
         <v>98</v>
       </c>
       <c r="N199" s="26" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O199" s="135" t="s">
         <v>30</v>
@@ -12767,7 +12764,7 @@
       <c r="A200" s="116"/>
       <c r="B200" s="26"/>
       <c r="C200" s="26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D200" s="118" t="s">
         <v>39</v>
@@ -12798,10 +12795,10 @@
         <v>27</v>
       </c>
       <c r="M200" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N200" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O200" s="136"/>
       <c r="P200" s="19" t="s">
@@ -12812,7 +12809,7 @@
       <c r="A201" s="116"/>
       <c r="B201" s="26"/>
       <c r="C201" s="26" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D201" s="118" t="s">
         <v>39</v>
@@ -12843,10 +12840,10 @@
         <v>27</v>
       </c>
       <c r="M201" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N201" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O201" s="136"/>
       <c r="P201" s="19" t="s">
@@ -12857,7 +12854,7 @@
       <c r="A202" s="116"/>
       <c r="B202" s="26"/>
       <c r="C202" s="26" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D202" s="119" t="s">
         <v>39</v>
@@ -12888,10 +12885,10 @@
         <v>27</v>
       </c>
       <c r="M202" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N202" s="26" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O202" s="137"/>
       <c r="P202" s="19" t="s">
@@ -12903,10 +12900,10 @@
         <v>295</v>
       </c>
       <c r="B203" s="38" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C203" s="38" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D203" s="24" t="s">
         <v>21</v>
@@ -12937,10 +12934,10 @@
         <v>27</v>
       </c>
       <c r="M203" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N203" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O203" s="135" t="s">
         <v>30</v>
@@ -12953,7 +12950,7 @@
       <c r="A204" s="136"/>
       <c r="B204" s="29"/>
       <c r="C204" s="29" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D204" s="31" t="s">
         <v>39</v>
@@ -12962,7 +12959,7 @@
         <v>40</v>
       </c>
       <c r="F204" s="29" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G204" s="54">
         <v>20531</v>
@@ -12987,7 +12984,7 @@
         <v>155</v>
       </c>
       <c r="N204" s="29" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="O204" s="136"/>
       <c r="P204" s="46" t="s">
@@ -13033,10 +13030,10 @@
         <v>27</v>
       </c>
       <c r="M205" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N205" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O205" s="135" t="s">
         <v>36</v>
@@ -13080,10 +13077,10 @@
         <v>27</v>
       </c>
       <c r="M206" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N206" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O206" s="136"/>
       <c r="P206" s="19" t="s">
@@ -13125,10 +13122,10 @@
         <v>27</v>
       </c>
       <c r="M207" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N207" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O207" s="137"/>
       <c r="P207" s="19" t="s">
@@ -13175,7 +13172,7 @@
         <v>98</v>
       </c>
       <c r="N208" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O208" s="87" t="s">
         <v>36</v>
@@ -13314,11 +13311,11 @@
       <c r="L211" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="M211" s="29" t="s">
-        <v>312</v>
+      <c r="M211" s="35" t="s">
+        <v>61</v>
       </c>
       <c r="N211" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O211" s="136"/>
       <c r="P211" s="46" t="s">
@@ -13329,7 +13326,7 @@
       <c r="A212" s="136"/>
       <c r="B212" s="29"/>
       <c r="C212" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D212" s="37" t="s">
         <v>39</v>
@@ -13359,11 +13356,11 @@
       <c r="L212" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="M212" s="29" t="s">
-        <v>312</v>
+      <c r="M212" s="35" t="s">
+        <v>61</v>
       </c>
       <c r="N212" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O212" s="136"/>
       <c r="P212" s="46" t="s">
@@ -13372,13 +13369,13 @@
     </row>
     <row r="213" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A213" s="140" t="s">
+        <v>313</v>
+      </c>
+      <c r="B213" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="B213" s="39" t="s">
-        <v>315</v>
-      </c>
       <c r="C213" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D213" s="24" t="s">
         <v>21</v>
@@ -13412,7 +13409,7 @@
         <v>98</v>
       </c>
       <c r="N213" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O213" s="135" t="s">
         <v>30</v>
@@ -13425,7 +13422,7 @@
       <c r="A214" s="138"/>
       <c r="B214" s="29"/>
       <c r="C214" s="30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>39</v>
@@ -13456,10 +13453,10 @@
         <v>27</v>
       </c>
       <c r="M214" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N214" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O214" s="136"/>
       <c r="P214" s="19" t="s">
@@ -13470,7 +13467,7 @@
       <c r="A215" s="138"/>
       <c r="B215" s="29"/>
       <c r="C215" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D215" s="31" t="s">
         <v>21</v>
@@ -13501,10 +13498,10 @@
         <v>27</v>
       </c>
       <c r="M215" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N215" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O215" s="136"/>
       <c r="P215" s="19" t="s">
@@ -13515,7 +13512,7 @@
       <c r="A216" s="139"/>
       <c r="B216" s="35"/>
       <c r="C216" s="36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D216" s="37" t="s">
         <v>21</v>
@@ -13549,20 +13546,20 @@
         <v>61</v>
       </c>
       <c r="N216" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O216" s="137"/>
       <c r="P216" s="19"/>
     </row>
     <row r="217" spans="1:16" s="2" customFormat="1">
       <c r="A217" s="135" t="s">
+        <v>319</v>
+      </c>
+      <c r="B217" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="B217" s="38" t="s">
-        <v>321</v>
-      </c>
       <c r="C217" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D217" s="24" t="s">
         <v>21</v>
@@ -13587,7 +13584,7 @@
         <v>25</v>
       </c>
       <c r="K217" s="25" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L217" s="24" t="s">
         <v>27</v>
@@ -13596,7 +13593,7 @@
         <v>204</v>
       </c>
       <c r="N217" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O217" s="135" t="s">
         <v>36</v>
@@ -13609,7 +13606,7 @@
       <c r="A218" s="136"/>
       <c r="B218" s="29"/>
       <c r="C218" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D218" s="31" t="s">
         <v>39</v>
@@ -13643,7 +13640,7 @@
         <v>204</v>
       </c>
       <c r="N218" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O218" s="136"/>
       <c r="P218" s="19" t="s">
@@ -13654,7 +13651,7 @@
       <c r="A219" s="136"/>
       <c r="B219" s="29"/>
       <c r="C219" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D219" s="31" t="s">
         <v>39</v>
@@ -13685,10 +13682,10 @@
         <v>27</v>
       </c>
       <c r="M219" s="29" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N219" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O219" s="136"/>
       <c r="P219" s="19" t="s">
@@ -13699,7 +13696,7 @@
       <c r="A220" s="137"/>
       <c r="B220" s="35"/>
       <c r="C220" s="36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D220" s="37" t="s">
         <v>39</v>
@@ -13733,7 +13730,7 @@
         <v>98</v>
       </c>
       <c r="N220" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O220" s="137"/>
       <c r="P220" s="19" t="s">
@@ -13742,13 +13739,13 @@
     </row>
     <row r="221" spans="1:16" s="2" customFormat="1">
       <c r="A221" s="135" t="s">
+        <v>326</v>
+      </c>
+      <c r="B221" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="B221" s="38" t="s">
-        <v>328</v>
-      </c>
       <c r="C221" s="39" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D221" s="24" t="s">
         <v>21</v>
@@ -13779,10 +13776,10 @@
         <v>27</v>
       </c>
       <c r="M221" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N221" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O221" s="135" t="s">
         <v>36</v>
@@ -13795,7 +13792,7 @@
       <c r="A222" s="136"/>
       <c r="B222" s="29"/>
       <c r="C222" s="30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D222" s="118" t="s">
         <v>39</v>
@@ -13826,10 +13823,10 @@
         <v>27</v>
       </c>
       <c r="M222" s="29" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N222" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O222" s="136"/>
       <c r="P222" s="46" t="s">
@@ -13840,7 +13837,7 @@
       <c r="A223" s="136"/>
       <c r="B223" s="29"/>
       <c r="C223" s="30" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D223" s="118" t="s">
         <v>39</v>
@@ -13871,10 +13868,10 @@
         <v>27</v>
       </c>
       <c r="M223" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N223" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O223" s="136"/>
       <c r="P223" s="46" t="s">
@@ -13885,7 +13882,7 @@
       <c r="A224" s="136"/>
       <c r="B224" s="29"/>
       <c r="C224" s="30" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D224" s="31" t="s">
         <v>21</v>
@@ -13916,10 +13913,10 @@
         <v>27</v>
       </c>
       <c r="M224" s="29" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N224" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O224" s="136"/>
       <c r="P224" s="46" t="s">
@@ -13928,7 +13925,7 @@
     </row>
     <row r="225" spans="1:253" s="2" customFormat="1">
       <c r="A225" s="88" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B225" s="107"/>
       <c r="C225" s="107"/>
@@ -13952,13 +13949,13 @@
     </row>
     <row r="226" spans="1:253" s="2" customFormat="1">
       <c r="A226" s="135" t="s">
+        <v>330</v>
+      </c>
+      <c r="B226" s="38" t="s">
         <v>331</v>
       </c>
-      <c r="B226" s="38" t="s">
-        <v>332</v>
-      </c>
       <c r="C226" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D226" s="24" t="s">
         <v>21</v>
@@ -13989,10 +13986,10 @@
         <v>27</v>
       </c>
       <c r="M226" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N226" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O226" s="135" t="s">
         <v>36</v>
@@ -14005,7 +14002,7 @@
       <c r="A227" s="136"/>
       <c r="B227" s="29"/>
       <c r="C227" s="29" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D227" s="31" t="s">
         <v>39</v>
@@ -14036,10 +14033,10 @@
         <v>27</v>
       </c>
       <c r="M227" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N227" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O227" s="136"/>
       <c r="P227" s="19" t="s">
@@ -14050,7 +14047,7 @@
       <c r="A228" s="136"/>
       <c r="B228" s="35"/>
       <c r="C228" s="35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D228" s="119" t="s">
         <v>21</v>
@@ -14084,7 +14081,7 @@
         <v>91</v>
       </c>
       <c r="N228" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O228" s="136"/>
       <c r="P228" s="19" t="s">
@@ -14095,7 +14092,7 @@
       <c r="A229" s="136"/>
       <c r="B229" s="29"/>
       <c r="C229" s="29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D229" s="31" t="s">
         <v>21</v>
@@ -14129,7 +14126,7 @@
         <v>204</v>
       </c>
       <c r="N229" s="29" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="O229" s="136"/>
       <c r="P229" s="19" t="s">
@@ -14140,7 +14137,7 @@
       <c r="A230" s="136"/>
       <c r="B230" s="91"/>
       <c r="C230" s="91" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D230" s="97" t="s">
         <v>39</v>
@@ -14174,7 +14171,7 @@
         <v>155</v>
       </c>
       <c r="N230" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O230" s="136"/>
       <c r="P230" s="19" t="s">
@@ -14183,13 +14180,13 @@
     </row>
     <row r="231" spans="1:253" s="2" customFormat="1">
       <c r="A231" s="141" t="s">
+        <v>335</v>
+      </c>
+      <c r="B231" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="B231" s="39" t="s">
-        <v>337</v>
-      </c>
       <c r="C231" s="39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D231" s="24" t="s">
         <v>21</v>
@@ -14220,10 +14217,10 @@
         <v>27</v>
       </c>
       <c r="M231" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N231" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O231" s="141" t="s">
         <v>36</v>
@@ -14236,7 +14233,7 @@
       <c r="A232" s="141"/>
       <c r="B232" s="29"/>
       <c r="C232" s="30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D232" s="31" t="s">
         <v>39</v>
@@ -14267,10 +14264,10 @@
         <v>27</v>
       </c>
       <c r="M232" s="29" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N232" s="29" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O232" s="141"/>
       <c r="P232" s="46" t="s">
@@ -14281,7 +14278,7 @@
       <c r="A233" s="141"/>
       <c r="B233" s="29"/>
       <c r="C233" s="30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D233" s="31" t="s">
         <v>21</v>
@@ -14315,7 +14312,7 @@
         <v>98</v>
       </c>
       <c r="N233" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O233" s="141"/>
       <c r="P233" s="46" t="s">
@@ -14326,7 +14323,7 @@
       <c r="A234" s="141"/>
       <c r="B234" s="29"/>
       <c r="C234" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D234" s="31" t="s">
         <v>39</v>
@@ -14360,7 +14357,7 @@
         <v>61</v>
       </c>
       <c r="N234" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O234" s="136"/>
       <c r="P234" s="46" t="s">
@@ -14371,7 +14368,7 @@
       <c r="A235" s="141"/>
       <c r="B235" s="29"/>
       <c r="C235" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D235" s="31" t="s">
         <v>21</v>
@@ -14405,7 +14402,7 @@
         <v>61</v>
       </c>
       <c r="N235" s="29" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O235" s="136"/>
       <c r="P235" s="46" t="s">
@@ -14416,7 +14413,7 @@
       <c r="A236" s="141"/>
       <c r="B236" s="29"/>
       <c r="C236" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D236" s="31" t="s">
         <v>39</v>
@@ -14447,10 +14444,10 @@
         <v>27</v>
       </c>
       <c r="M236" s="29" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N236" s="29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O236" s="136"/>
       <c r="P236" s="46" t="s">
@@ -14461,7 +14458,7 @@
       <c r="A237" s="141"/>
       <c r="B237" s="35"/>
       <c r="C237" s="36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D237" s="37" t="s">
         <v>39</v>
@@ -14495,7 +14492,7 @@
         <v>61</v>
       </c>
       <c r="N237" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O237" s="137"/>
       <c r="P237" s="46" t="s">
@@ -15486,7 +15483,7 @@
     </row>
     <row r="3" spans="1:20" s="1" customFormat="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -15515,10 +15512,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>346</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>4</v>
@@ -15563,10 +15560,10 @@
         <v>17</v>
       </c>
       <c r="S5" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="T5" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="12" customHeight="1">
@@ -15659,10 +15656,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>349</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>350</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>20</v>
@@ -15709,7 +15706,7 @@
       </c>
       <c r="S8" s="46"/>
       <c r="T8" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15720,10 +15717,10 @@
         <v>32</v>
       </c>
       <c r="C9" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>352</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>353</v>
       </c>
       <c r="E9" s="23" t="s">
         <v>33</v>
@@ -15770,7 +15767,7 @@
       </c>
       <c r="S9" s="19"/>
       <c r="T9" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15779,10 +15776,10 @@
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E10" s="29"/>
       <c r="F10" s="30" t="s">
@@ -15825,7 +15822,7 @@
       <c r="R10" s="26"/>
       <c r="S10" s="19"/>
       <c r="T10" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15834,10 +15831,10 @@
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="30" t="s">
@@ -15880,7 +15877,7 @@
       <c r="R11" s="26"/>
       <c r="S11" s="19"/>
       <c r="T11" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15889,10 +15886,10 @@
       </c>
       <c r="B12" s="26"/>
       <c r="C12" s="27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="30" t="s">
@@ -15935,7 +15932,7 @@
       <c r="R12" s="26"/>
       <c r="S12" s="19"/>
       <c r="T12" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -15944,10 +15941,10 @@
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="33" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E13" s="35"/>
       <c r="F13" s="36" t="s">
@@ -15990,7 +15987,7 @@
       <c r="R13" s="32"/>
       <c r="S13" s="19"/>
       <c r="T13" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16001,10 +15998,10 @@
         <v>54</v>
       </c>
       <c r="C14" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>359</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>360</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>55</v>
@@ -16051,7 +16048,7 @@
       </c>
       <c r="S14" s="19"/>
       <c r="T14" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16060,10 +16057,10 @@
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="33" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="36" t="s">
@@ -16106,7 +16103,7 @@
       <c r="R15" s="18"/>
       <c r="S15" s="19"/>
       <c r="T15" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16117,16 +16114,16 @@
         <v>57</v>
       </c>
       <c r="C16" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="E16" s="40" t="s">
-        <v>364</v>
-      </c>
       <c r="F16" s="40" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G16" s="18" t="s">
         <v>21</v>
@@ -16167,7 +16164,7 @@
       </c>
       <c r="S16" s="19"/>
       <c r="T16" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16178,16 +16175,16 @@
         <v>59</v>
       </c>
       <c r="C17" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>365</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="E17" s="39" t="s">
         <v>366</v>
       </c>
-      <c r="E17" s="39" t="s">
-        <v>367</v>
-      </c>
       <c r="F17" s="38" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>21</v>
@@ -16196,7 +16193,7 @@
         <v>22</v>
       </c>
       <c r="I17" s="59" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J17" s="51">
         <v>30891</v>
@@ -16228,7 +16225,7 @@
       </c>
       <c r="S17" s="19"/>
       <c r="T17" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16237,14 +16234,14 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>39</v>
@@ -16283,7 +16280,7 @@
       <c r="R18" s="26"/>
       <c r="S18" s="19"/>
       <c r="T18" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16292,14 +16289,14 @@
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="33" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E19" s="35"/>
       <c r="F19" s="35" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G19" s="37" t="s">
         <v>39</v>
@@ -16308,7 +16305,7 @@
         <v>44</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J19" s="57">
         <v>38784</v>
@@ -16338,7 +16335,7 @@
       <c r="R19" s="32"/>
       <c r="S19" s="19"/>
       <c r="T19" s="63" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16349,10 +16346,10 @@
         <v>64</v>
       </c>
       <c r="C20" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="D20" s="41" t="s">
         <v>373</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>374</v>
       </c>
       <c r="E20" s="38" t="s">
         <v>65</v>
@@ -16399,7 +16396,7 @@
       </c>
       <c r="S20" s="19"/>
       <c r="T20" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16408,10 +16405,10 @@
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E21" s="29"/>
       <c r="F21" s="29" t="s">
@@ -16454,7 +16451,7 @@
       <c r="R21" s="26"/>
       <c r="S21" s="19"/>
       <c r="T21" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16463,10 +16460,10 @@
       </c>
       <c r="B22" s="26"/>
       <c r="C22" s="42" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E22" s="29"/>
       <c r="F22" s="29" t="s">
@@ -16509,7 +16506,7 @@
       <c r="R22" s="26"/>
       <c r="S22" s="19"/>
       <c r="T22" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16518,10 +16515,10 @@
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="43" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E23" s="35"/>
       <c r="F23" s="35" t="s">
@@ -16564,7 +16561,7 @@
       <c r="R23" s="32"/>
       <c r="S23" s="19"/>
       <c r="T23" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16575,10 +16572,10 @@
         <v>70</v>
       </c>
       <c r="C24" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>378</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>379</v>
       </c>
       <c r="E24" s="38" t="s">
         <v>71</v>
@@ -16623,7 +16620,7 @@
       </c>
       <c r="S24" s="19"/>
       <c r="T24" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16632,10 +16629,10 @@
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E25" s="29"/>
       <c r="F25" s="29" t="s">
@@ -16676,7 +16673,7 @@
       <c r="R25" s="32"/>
       <c r="S25" s="19"/>
       <c r="T25" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16685,10 +16682,10 @@
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="35" t="s">
@@ -16729,7 +16726,7 @@
       <c r="R26" s="18"/>
       <c r="S26" s="19"/>
       <c r="T26" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="27" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16740,10 +16737,10 @@
         <v>74</v>
       </c>
       <c r="C27" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="D27" s="41" t="s">
         <v>382</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>383</v>
       </c>
       <c r="E27" s="38" t="s">
         <v>75</v>
@@ -16790,7 +16787,7 @@
       </c>
       <c r="S27" s="19"/>
       <c r="T27" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="28" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16799,10 +16796,10 @@
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E28" s="29"/>
       <c r="F28" s="29" t="s">
@@ -16845,7 +16842,7 @@
       <c r="R28" s="26"/>
       <c r="S28" s="19"/>
       <c r="T28" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="29" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16854,10 +16851,10 @@
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="29" t="s">
@@ -16900,7 +16897,7 @@
       <c r="R29" s="26"/>
       <c r="S29" s="19"/>
       <c r="T29" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16909,10 +16906,10 @@
       </c>
       <c r="B30" s="26"/>
       <c r="C30" s="42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E30" s="29"/>
       <c r="F30" s="29" t="s">
@@ -16955,7 +16952,7 @@
       <c r="R30" s="26"/>
       <c r="S30" s="19"/>
       <c r="T30" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -16964,10 +16961,10 @@
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="43" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35" t="s">
@@ -17010,7 +17007,7 @@
       <c r="R31" s="32"/>
       <c r="S31" s="19"/>
       <c r="T31" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17021,10 +17018,10 @@
         <v>84</v>
       </c>
       <c r="C32" s="41" t="s">
+        <v>387</v>
+      </c>
+      <c r="D32" s="41" t="s">
         <v>388</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>389</v>
       </c>
       <c r="E32" s="38" t="s">
         <v>85</v>
@@ -17071,7 +17068,7 @@
       </c>
       <c r="S32" s="19"/>
       <c r="T32" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17080,10 +17077,10 @@
       </c>
       <c r="B33" s="26"/>
       <c r="C33" s="42" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="29" t="s">
@@ -17126,7 +17123,7 @@
       <c r="R33" s="26"/>
       <c r="S33" s="19"/>
       <c r="T33" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17135,10 +17132,10 @@
       </c>
       <c r="B34" s="26"/>
       <c r="C34" s="42" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E34" s="29"/>
       <c r="F34" s="29" t="s">
@@ -17181,7 +17178,7 @@
       <c r="R34" s="26"/>
       <c r="S34" s="19"/>
       <c r="T34" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17190,10 +17187,10 @@
       </c>
       <c r="B35" s="26"/>
       <c r="C35" s="42" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E35" s="29"/>
       <c r="F35" s="29" t="s">
@@ -17236,7 +17233,7 @@
       <c r="R35" s="26"/>
       <c r="S35" s="19"/>
       <c r="T35" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17245,10 +17242,10 @@
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="43" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D36" s="43" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E36" s="35"/>
       <c r="F36" s="35" t="s">
@@ -17291,7 +17288,7 @@
       <c r="R36" s="32"/>
       <c r="S36" s="19"/>
       <c r="T36" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17302,10 +17299,10 @@
         <v>95</v>
       </c>
       <c r="C37" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="D37" s="22" t="s">
         <v>394</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>395</v>
       </c>
       <c r="E37" s="38" t="s">
         <v>96</v>
@@ -17352,7 +17349,7 @@
       </c>
       <c r="S37" s="19"/>
       <c r="T37" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17361,10 +17358,10 @@
       </c>
       <c r="B38" s="26"/>
       <c r="C38" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E38" s="29"/>
       <c r="F38" s="29" t="s">
@@ -17407,7 +17404,7 @@
       <c r="R38" s="26"/>
       <c r="S38" s="19"/>
       <c r="T38" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17416,14 +17413,14 @@
       </c>
       <c r="B39" s="26"/>
       <c r="C39" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E39" s="29"/>
       <c r="F39" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G39" s="31" t="s">
         <v>21</v>
@@ -17462,7 +17459,7 @@
       <c r="R39" s="26"/>
       <c r="S39" s="19"/>
       <c r="T39" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17471,10 +17468,10 @@
       </c>
       <c r="B40" s="26"/>
       <c r="C40" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E40" s="29"/>
       <c r="F40" s="29" t="s">
@@ -17517,7 +17514,7 @@
       <c r="R40" s="26"/>
       <c r="S40" s="19"/>
       <c r="T40" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17526,14 +17523,14 @@
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="33" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E41" s="35"/>
       <c r="F41" s="35" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G41" s="37" t="s">
         <v>39</v>
@@ -17572,7 +17569,7 @@
       <c r="R41" s="32"/>
       <c r="S41" s="19"/>
       <c r="T41" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17583,10 +17580,10 @@
         <v>103</v>
       </c>
       <c r="C42" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="D42" s="41" t="s">
         <v>401</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>402</v>
       </c>
       <c r="E42" s="38" t="s">
         <v>104</v>
@@ -17633,7 +17630,7 @@
       </c>
       <c r="S42" s="19"/>
       <c r="T42" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17642,10 +17639,10 @@
       </c>
       <c r="B43" s="26"/>
       <c r="C43" s="42" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E43" s="29"/>
       <c r="F43" s="29" t="s">
@@ -17688,7 +17685,7 @@
       <c r="R43" s="26"/>
       <c r="S43" s="19"/>
       <c r="T43" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17697,10 +17694,10 @@
       </c>
       <c r="B44" s="26"/>
       <c r="C44" s="42" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E44" s="29"/>
       <c r="F44" s="29" t="s">
@@ -17743,7 +17740,7 @@
       <c r="R44" s="26"/>
       <c r="S44" s="19"/>
       <c r="T44" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17752,10 +17749,10 @@
       </c>
       <c r="B45" s="32"/>
       <c r="C45" s="43" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E45" s="35"/>
       <c r="F45" s="35" t="s">
@@ -17798,7 +17795,7 @@
       <c r="R45" s="32"/>
       <c r="S45" s="19"/>
       <c r="T45" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17809,10 +17806,10 @@
         <v>109</v>
       </c>
       <c r="C46" s="41" t="s">
+        <v>405</v>
+      </c>
+      <c r="D46" s="41" t="s">
         <v>406</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>407</v>
       </c>
       <c r="E46" s="38" t="s">
         <v>110</v>
@@ -17859,7 +17856,7 @@
       </c>
       <c r="S46" s="19"/>
       <c r="T46" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17868,10 +17865,10 @@
       </c>
       <c r="B47" s="26"/>
       <c r="C47" s="42" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E47" s="29"/>
       <c r="F47" s="29" t="s">
@@ -17914,7 +17911,7 @@
       <c r="R47" s="26"/>
       <c r="S47" s="19"/>
       <c r="T47" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17923,10 +17920,10 @@
       </c>
       <c r="B48" s="26"/>
       <c r="C48" s="42" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E48" s="29"/>
       <c r="F48" s="29" t="s">
@@ -17969,7 +17966,7 @@
       <c r="R48" s="26"/>
       <c r="S48" s="19"/>
       <c r="T48" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -17978,10 +17975,10 @@
       </c>
       <c r="B49" s="32"/>
       <c r="C49" s="43" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E49" s="35"/>
       <c r="F49" s="35" t="s">
@@ -18024,7 +18021,7 @@
       <c r="R49" s="32"/>
       <c r="S49" s="19"/>
       <c r="T49" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18035,10 +18032,10 @@
         <v>116</v>
       </c>
       <c r="C50" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="D50" s="22" t="s">
         <v>411</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>412</v>
       </c>
       <c r="E50" s="38" t="s">
         <v>117</v>
@@ -18085,7 +18082,7 @@
       </c>
       <c r="S50" s="19"/>
       <c r="T50" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18094,10 +18091,10 @@
       </c>
       <c r="B51" s="26"/>
       <c r="C51" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E51" s="29"/>
       <c r="F51" s="29" t="s">
@@ -18140,7 +18137,7 @@
       <c r="R51" s="26"/>
       <c r="S51" s="19"/>
       <c r="T51" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18149,10 +18146,10 @@
       </c>
       <c r="B52" s="26"/>
       <c r="C52" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E52" s="29"/>
       <c r="F52" s="29" t="s">
@@ -18195,7 +18192,7 @@
       <c r="R52" s="26"/>
       <c r="S52" s="19"/>
       <c r="T52" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18204,10 +18201,10 @@
       </c>
       <c r="B53" s="26"/>
       <c r="C53" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E53" s="29"/>
       <c r="F53" s="29" t="s">
@@ -18250,7 +18247,7 @@
       <c r="R53" s="26"/>
       <c r="S53" s="19"/>
       <c r="T53" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="54" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18259,7 +18256,7 @@
       </c>
       <c r="B54" s="32"/>
       <c r="C54" s="33" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D54" s="34" t="s">
         <v>172</v>
@@ -18305,7 +18302,7 @@
       <c r="R54" s="32"/>
       <c r="S54" s="19"/>
       <c r="T54" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="55" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18316,10 +18313,10 @@
         <v>123</v>
       </c>
       <c r="C55" s="41" t="s">
+        <v>415</v>
+      </c>
+      <c r="D55" s="41" t="s">
         <v>416</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>417</v>
       </c>
       <c r="E55" s="38" t="s">
         <v>124</v>
@@ -18366,7 +18363,7 @@
       </c>
       <c r="S55" s="19"/>
       <c r="T55" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18375,10 +18372,10 @@
       </c>
       <c r="B56" s="26"/>
       <c r="C56" s="42" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E56" s="29"/>
       <c r="F56" s="29" t="s">
@@ -18421,7 +18418,7 @@
       <c r="R56" s="26"/>
       <c r="S56" s="19"/>
       <c r="T56" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18430,10 +18427,10 @@
       </c>
       <c r="B57" s="26"/>
       <c r="C57" s="42" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D57" s="42" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E57" s="29"/>
       <c r="F57" s="29" t="s">
@@ -18476,7 +18473,7 @@
       <c r="R57" s="26"/>
       <c r="S57" s="19"/>
       <c r="T57" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18485,10 +18482,10 @@
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="43" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D58" s="43" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E58" s="35"/>
       <c r="F58" s="35" t="s">
@@ -18531,7 +18528,7 @@
       <c r="R58" s="32"/>
       <c r="S58" s="19"/>
       <c r="T58" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18542,10 +18539,10 @@
         <v>131</v>
       </c>
       <c r="C59" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="D59" s="41" t="s">
         <v>421</v>
-      </c>
-      <c r="D59" s="41" t="s">
-        <v>422</v>
       </c>
       <c r="E59" s="38" t="s">
         <v>132</v>
@@ -18592,7 +18589,7 @@
       </c>
       <c r="S59" s="19"/>
       <c r="T59" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18601,10 +18598,10 @@
       </c>
       <c r="B60" s="29"/>
       <c r="C60" s="42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E60" s="29"/>
       <c r="F60" s="29" t="s">
@@ -18647,7 +18644,7 @@
       <c r="R60" s="26"/>
       <c r="S60" s="19"/>
       <c r="T60" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18656,10 +18653,10 @@
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D61" s="42" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E61" s="29"/>
       <c r="F61" s="29" t="s">
@@ -18702,7 +18699,7 @@
       <c r="R61" s="26"/>
       <c r="S61" s="19"/>
       <c r="T61" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18711,10 +18708,10 @@
       </c>
       <c r="B62" s="29"/>
       <c r="C62" s="42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D62" s="42" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E62" s="29"/>
       <c r="F62" s="29" t="s">
@@ -18757,7 +18754,7 @@
       <c r="R62" s="26"/>
       <c r="S62" s="19"/>
       <c r="T62" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18766,10 +18763,10 @@
       </c>
       <c r="B63" s="35"/>
       <c r="C63" s="43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D63" s="43" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E63" s="35"/>
       <c r="F63" s="35" t="s">
@@ -18812,7 +18809,7 @@
       <c r="R63" s="32"/>
       <c r="S63" s="19"/>
       <c r="T63" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="64" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18823,10 +18820,10 @@
         <v>138</v>
       </c>
       <c r="C64" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="D64" s="22" t="s">
         <v>427</v>
-      </c>
-      <c r="D64" s="22" t="s">
-        <v>428</v>
       </c>
       <c r="E64" s="38" t="s">
         <v>139</v>
@@ -18873,7 +18870,7 @@
       </c>
       <c r="S64" s="19"/>
       <c r="T64" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18882,10 +18879,10 @@
       </c>
       <c r="B65" s="26"/>
       <c r="C65" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E65" s="29"/>
       <c r="F65" s="29" t="s">
@@ -18928,7 +18925,7 @@
       <c r="R65" s="26"/>
       <c r="S65" s="19"/>
       <c r="T65" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18937,10 +18934,10 @@
       </c>
       <c r="B66" s="26"/>
       <c r="C66" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E66" s="29"/>
       <c r="F66" s="29" t="s">
@@ -18983,7 +18980,7 @@
       <c r="R66" s="26"/>
       <c r="S66" s="19"/>
       <c r="T66" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="67" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -18992,10 +18989,10 @@
       </c>
       <c r="B67" s="26"/>
       <c r="C67" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E67" s="29"/>
       <c r="F67" s="29" t="s">
@@ -19038,7 +19035,7 @@
       <c r="R67" s="26"/>
       <c r="S67" s="19"/>
       <c r="T67" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19047,10 +19044,10 @@
       </c>
       <c r="B68" s="32"/>
       <c r="C68" s="33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D68" s="34" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E68" s="35"/>
       <c r="F68" s="35" t="s">
@@ -19093,7 +19090,7 @@
       <c r="R68" s="32"/>
       <c r="S68" s="19"/>
       <c r="T68" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19104,10 +19101,10 @@
         <v>144</v>
       </c>
       <c r="C69" s="41" t="s">
+        <v>432</v>
+      </c>
+      <c r="D69" s="41" t="s">
         <v>433</v>
-      </c>
-      <c r="D69" s="41" t="s">
-        <v>434</v>
       </c>
       <c r="E69" s="38" t="s">
         <v>145</v>
@@ -19154,7 +19151,7 @@
       </c>
       <c r="S69" s="19"/>
       <c r="T69" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="70" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19163,10 +19160,10 @@
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="42" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E70" s="29"/>
       <c r="F70" s="29" t="s">
@@ -19209,7 +19206,7 @@
       <c r="R70" s="26"/>
       <c r="S70" s="19"/>
       <c r="T70" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="71" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19218,10 +19215,10 @@
       </c>
       <c r="B71" s="29"/>
       <c r="C71" s="42" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D71" s="42" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E71" s="29"/>
       <c r="F71" s="29" t="s">
@@ -19264,7 +19261,7 @@
       <c r="R71" s="26"/>
       <c r="S71" s="19"/>
       <c r="T71" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19273,10 +19270,10 @@
       </c>
       <c r="B72" s="35"/>
       <c r="C72" s="43" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D72" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E72" s="35"/>
       <c r="F72" s="35" t="s">
@@ -19319,7 +19316,7 @@
       <c r="R72" s="32"/>
       <c r="S72" s="19"/>
       <c r="T72" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="73" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19330,10 +19327,10 @@
         <v>149</v>
       </c>
       <c r="C73" s="41" t="s">
+        <v>437</v>
+      </c>
+      <c r="D73" s="41" t="s">
         <v>438</v>
-      </c>
-      <c r="D73" s="41" t="s">
-        <v>439</v>
       </c>
       <c r="E73" s="38" t="s">
         <v>150</v>
@@ -19380,7 +19377,7 @@
       </c>
       <c r="S73" s="19"/>
       <c r="T73" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="74" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19389,10 +19386,10 @@
       </c>
       <c r="B74" s="29"/>
       <c r="C74" s="42" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E74" s="29"/>
       <c r="F74" s="29" t="s">
@@ -19435,7 +19432,7 @@
       <c r="R74" s="26"/>
       <c r="S74" s="19"/>
       <c r="T74" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19444,10 +19441,10 @@
       </c>
       <c r="B75" s="29"/>
       <c r="C75" s="42" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D75" s="42" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E75" s="29"/>
       <c r="F75" s="29" t="s">
@@ -19490,7 +19487,7 @@
       <c r="R75" s="26"/>
       <c r="S75" s="19"/>
       <c r="T75" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19499,10 +19496,10 @@
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D76" s="43" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E76" s="35"/>
       <c r="F76" s="35" t="s">
@@ -19545,7 +19542,7 @@
       <c r="R76" s="32"/>
       <c r="S76" s="19"/>
       <c r="T76" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19608,10 +19605,10 @@
         <v>156</v>
       </c>
       <c r="C78" s="41" t="s">
+        <v>442</v>
+      </c>
+      <c r="D78" s="41" t="s">
         <v>443</v>
-      </c>
-      <c r="D78" s="41" t="s">
-        <v>444</v>
       </c>
       <c r="E78" s="38" t="s">
         <v>157</v>
@@ -19658,7 +19655,7 @@
       </c>
       <c r="S78" s="19"/>
       <c r="T78" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="79" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19667,10 +19664,10 @@
       </c>
       <c r="B79" s="26"/>
       <c r="C79" s="42" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D79" s="42" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E79" s="29"/>
       <c r="F79" s="29" t="s">
@@ -19713,7 +19710,7 @@
       <c r="R79" s="26"/>
       <c r="S79" s="19"/>
       <c r="T79" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="80" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19722,10 +19719,10 @@
       </c>
       <c r="B80" s="26"/>
       <c r="C80" s="42" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D80" s="42" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E80" s="29"/>
       <c r="F80" s="29" t="s">
@@ -19768,7 +19765,7 @@
       <c r="R80" s="26"/>
       <c r="S80" s="19"/>
       <c r="T80" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="81" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19777,10 +19774,10 @@
       </c>
       <c r="B81" s="32"/>
       <c r="C81" s="43" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D81" s="43" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E81" s="35"/>
       <c r="F81" s="35" t="s">
@@ -19823,7 +19820,7 @@
       <c r="R81" s="32"/>
       <c r="S81" s="19"/>
       <c r="T81" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="82" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19834,10 +19831,10 @@
         <v>164</v>
       </c>
       <c r="C82" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="D82" s="22" t="s">
         <v>448</v>
-      </c>
-      <c r="D82" s="22" t="s">
-        <v>449</v>
       </c>
       <c r="E82" s="38" t="s">
         <v>165</v>
@@ -19884,7 +19881,7 @@
       </c>
       <c r="S82" s="19"/>
       <c r="T82" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19893,10 +19890,10 @@
       </c>
       <c r="B83" s="29"/>
       <c r="C83" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E83" s="29"/>
       <c r="F83" s="29" t="s">
@@ -19939,7 +19936,7 @@
       <c r="R83" s="26"/>
       <c r="S83" s="19"/>
       <c r="T83" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -19948,10 +19945,10 @@
       </c>
       <c r="B84" s="29"/>
       <c r="C84" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E84" s="29"/>
       <c r="F84" s="29" t="s">
@@ -19994,7 +19991,7 @@
       <c r="R84" s="26"/>
       <c r="S84" s="19"/>
       <c r="T84" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20003,10 +20000,10 @@
       </c>
       <c r="B85" s="35"/>
       <c r="C85" s="33" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D85" s="34" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E85" s="35"/>
       <c r="F85" s="35" t="s">
@@ -20049,7 +20046,7 @@
       <c r="R85" s="32"/>
       <c r="S85" s="19"/>
       <c r="T85" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="86" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20063,13 +20060,13 @@
         <v>172</v>
       </c>
       <c r="D86" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="E86" s="38" t="s">
         <v>453</v>
       </c>
-      <c r="E86" s="38" t="s">
-        <v>454</v>
-      </c>
       <c r="F86" s="38" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G86" s="24" t="s">
         <v>21</v>
@@ -20110,7 +20107,7 @@
       </c>
       <c r="S86" s="19"/>
       <c r="T86" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20122,11 +20119,11 @@
         <v>172</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E87" s="29"/>
       <c r="F87" s="29" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G87" s="31" t="s">
         <v>21</v>
@@ -20165,7 +20162,7 @@
       <c r="R87" s="26"/>
       <c r="S87" s="19"/>
       <c r="T87" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20177,11 +20174,11 @@
         <v>172</v>
       </c>
       <c r="D88" s="34" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E88" s="35"/>
       <c r="F88" s="35" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G88" s="37" t="s">
         <v>21</v>
@@ -20220,7 +20217,7 @@
       <c r="R88" s="32"/>
       <c r="S88" s="19"/>
       <c r="T88" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20231,16 +20228,16 @@
         <v>171</v>
       </c>
       <c r="C89" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="D89" s="22" t="s">
         <v>459</v>
       </c>
-      <c r="D89" s="22" t="s">
+      <c r="E89" s="38" t="s">
         <v>460</v>
       </c>
-      <c r="E89" s="38" t="s">
-        <v>461</v>
-      </c>
       <c r="F89" s="38" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G89" s="24" t="s">
         <v>21</v>
@@ -20281,7 +20278,7 @@
       </c>
       <c r="S89" s="19"/>
       <c r="T89" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20290,14 +20287,14 @@
       </c>
       <c r="B90" s="26"/>
       <c r="C90" s="27" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E90" s="29"/>
       <c r="F90" s="29" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G90" s="31" t="s">
         <v>39</v>
@@ -20336,7 +20333,7 @@
       <c r="R90" s="26"/>
       <c r="S90" s="19"/>
       <c r="T90" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20345,14 +20342,14 @@
       </c>
       <c r="B91" s="32"/>
       <c r="C91" s="33" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D91" s="34" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E91" s="35"/>
       <c r="F91" s="35" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G91" s="37" t="s">
         <v>21</v>
@@ -20391,7 +20388,7 @@
       <c r="R91" s="32"/>
       <c r="S91" s="19"/>
       <c r="T91" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20402,10 +20399,10 @@
         <v>176</v>
       </c>
       <c r="C92" s="41" t="s">
+        <v>465</v>
+      </c>
+      <c r="D92" s="41" t="s">
         <v>466</v>
-      </c>
-      <c r="D92" s="41" t="s">
-        <v>467</v>
       </c>
       <c r="E92" s="38" t="s">
         <v>177</v>
@@ -20452,7 +20449,7 @@
       </c>
       <c r="S92" s="19"/>
       <c r="T92" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20461,10 +20458,10 @@
       </c>
       <c r="B93" s="26"/>
       <c r="C93" s="42" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D93" s="42" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E93" s="29"/>
       <c r="F93" s="29" t="s">
@@ -20507,7 +20504,7 @@
       <c r="R93" s="26"/>
       <c r="S93" s="19"/>
       <c r="T93" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20516,10 +20513,10 @@
       </c>
       <c r="B94" s="26"/>
       <c r="C94" s="42" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D94" s="42" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E94" s="29"/>
       <c r="F94" s="29" t="s">
@@ -20562,7 +20559,7 @@
       <c r="R94" s="26"/>
       <c r="S94" s="19"/>
       <c r="T94" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20571,10 +20568,10 @@
       </c>
       <c r="B95" s="32"/>
       <c r="C95" s="43" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D95" s="43" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E95" s="35"/>
       <c r="F95" s="35" t="s">
@@ -20617,7 +20614,7 @@
       <c r="R95" s="32"/>
       <c r="S95" s="19"/>
       <c r="T95" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20628,10 +20625,10 @@
         <v>181</v>
       </c>
       <c r="C96" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="D96" s="22" t="s">
         <v>471</v>
-      </c>
-      <c r="D96" s="22" t="s">
-        <v>472</v>
       </c>
       <c r="E96" s="38" t="s">
         <v>182</v>
@@ -20678,7 +20675,7 @@
       </c>
       <c r="S96" s="19"/>
       <c r="T96" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20687,10 +20684,10 @@
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="27" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E97" s="29"/>
       <c r="F97" s="29" t="s">
@@ -20733,7 +20730,7 @@
       <c r="R97" s="26"/>
       <c r="S97" s="19"/>
       <c r="T97" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="98" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20742,10 +20739,10 @@
       </c>
       <c r="B98" s="19"/>
       <c r="C98" s="33" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E98" s="35"/>
       <c r="F98" s="35" t="s">
@@ -20788,7 +20785,7 @@
       <c r="R98" s="26"/>
       <c r="S98" s="19"/>
       <c r="T98" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="99" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20845,10 +20842,10 @@
         <v>194</v>
       </c>
       <c r="C100" s="41" t="s">
+        <v>474</v>
+      </c>
+      <c r="D100" s="41" t="s">
         <v>475</v>
-      </c>
-      <c r="D100" s="41" t="s">
-        <v>476</v>
       </c>
       <c r="E100" s="38" t="s">
         <v>195</v>
@@ -20895,7 +20892,7 @@
       </c>
       <c r="S100" s="19"/>
       <c r="T100" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="101" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20904,10 +20901,10 @@
       </c>
       <c r="B101" s="26"/>
       <c r="C101" s="42" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D101" s="42" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E101" s="29"/>
       <c r="F101" s="29" t="s">
@@ -20950,7 +20947,7 @@
       <c r="R101" s="20"/>
       <c r="S101" s="19"/>
       <c r="T101" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="102" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -20959,10 +20956,10 @@
       </c>
       <c r="B102" s="26"/>
       <c r="C102" s="42" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D102" s="42" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E102" s="29"/>
       <c r="F102" s="29" t="s">
@@ -21005,7 +21002,7 @@
       <c r="R102" s="26"/>
       <c r="S102" s="19"/>
       <c r="T102" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21014,10 +21011,10 @@
       </c>
       <c r="B103" s="26"/>
       <c r="C103" s="42" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D103" s="42" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E103" s="29"/>
       <c r="F103" s="29" t="s">
@@ -21060,7 +21057,7 @@
       <c r="R103" s="26"/>
       <c r="S103" s="19"/>
       <c r="T103" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21069,10 +21066,10 @@
       </c>
       <c r="B104" s="26"/>
       <c r="C104" s="42" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D104" s="42" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E104" s="29"/>
       <c r="F104" s="29" t="s">
@@ -21115,7 +21112,7 @@
       <c r="R104" s="26"/>
       <c r="S104" s="19"/>
       <c r="T104" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="105" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21124,10 +21121,10 @@
       </c>
       <c r="B105" s="32"/>
       <c r="C105" s="43" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D105" s="43" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E105" s="35"/>
       <c r="F105" s="35" t="s">
@@ -21170,7 +21167,7 @@
       <c r="R105" s="32"/>
       <c r="S105" s="19"/>
       <c r="T105" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21181,10 +21178,10 @@
         <v>201</v>
       </c>
       <c r="C106" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="D106" s="22" t="s">
         <v>482</v>
-      </c>
-      <c r="D106" s="22" t="s">
-        <v>483</v>
       </c>
       <c r="E106" s="39" t="s">
         <v>202</v>
@@ -21231,7 +21228,7 @@
       </c>
       <c r="S106" s="19"/>
       <c r="T106" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21240,10 +21237,10 @@
       </c>
       <c r="B107" s="26"/>
       <c r="C107" s="27" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D107" s="28" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E107" s="29"/>
       <c r="F107" s="30" t="s">
@@ -21286,7 +21283,7 @@
       <c r="R107" s="26"/>
       <c r="S107" s="19"/>
       <c r="T107" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21295,10 +21292,10 @@
       </c>
       <c r="B108" s="26"/>
       <c r="C108" s="27" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E108" s="29"/>
       <c r="F108" s="30" t="s">
@@ -21341,7 +21338,7 @@
       <c r="R108" s="26"/>
       <c r="S108" s="19"/>
       <c r="T108" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="109" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21350,10 +21347,10 @@
       </c>
       <c r="B109" s="32"/>
       <c r="C109" s="33" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D109" s="34" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E109" s="35"/>
       <c r="F109" s="36" t="s">
@@ -21396,7 +21393,7 @@
       <c r="R109" s="32"/>
       <c r="S109" s="19"/>
       <c r="T109" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="110" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21463,10 +21460,10 @@
         <v>213</v>
       </c>
       <c r="C111" s="21" t="s">
+        <v>486</v>
+      </c>
+      <c r="D111" s="22" t="s">
         <v>487</v>
-      </c>
-      <c r="D111" s="22" t="s">
-        <v>488</v>
       </c>
       <c r="E111" s="38" t="s">
         <v>214</v>
@@ -21513,7 +21510,7 @@
       </c>
       <c r="S111" s="19"/>
       <c r="T111" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="112" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21522,10 +21519,10 @@
       </c>
       <c r="B112" s="26"/>
       <c r="C112" s="27" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D112" s="28" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E112" s="29"/>
       <c r="F112" s="30" t="s">
@@ -21568,7 +21565,7 @@
       <c r="R112" s="26"/>
       <c r="S112" s="19"/>
       <c r="T112" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="113" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21577,10 +21574,10 @@
       </c>
       <c r="B113" s="32"/>
       <c r="C113" s="33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D113" s="34" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E113" s="35"/>
       <c r="F113" s="36" t="s">
@@ -21623,7 +21620,7 @@
       <c r="R113" s="32"/>
       <c r="S113" s="19"/>
       <c r="T113" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="114" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21634,10 +21631,10 @@
         <v>219</v>
       </c>
       <c r="C114" s="41" t="s">
+        <v>490</v>
+      </c>
+      <c r="D114" s="41" t="s">
         <v>491</v>
-      </c>
-      <c r="D114" s="41" t="s">
-        <v>492</v>
       </c>
       <c r="E114" s="38" t="s">
         <v>220</v>
@@ -21684,7 +21681,7 @@
       </c>
       <c r="S114" s="19"/>
       <c r="T114" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="115" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21693,10 +21690,10 @@
       </c>
       <c r="B115" s="26"/>
       <c r="C115" s="42" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D115" s="42" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E115" s="29"/>
       <c r="F115" s="29" t="s">
@@ -21739,7 +21736,7 @@
       <c r="R115" s="26"/>
       <c r="S115" s="19"/>
       <c r="T115" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="116" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21748,14 +21745,14 @@
       </c>
       <c r="B116" s="26"/>
       <c r="C116" s="42" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D116" s="42" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E116" s="29"/>
       <c r="F116" s="29" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G116" s="31" t="s">
         <v>21</v>
@@ -21794,7 +21791,7 @@
       <c r="R116" s="26"/>
       <c r="S116" s="19"/>
       <c r="T116" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="117" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21803,10 +21800,10 @@
       </c>
       <c r="B117" s="32"/>
       <c r="C117" s="43" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D117" s="43" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E117" s="35"/>
       <c r="F117" s="35" t="s">
@@ -21849,7 +21846,7 @@
       <c r="R117" s="32"/>
       <c r="S117" s="19"/>
       <c r="T117" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="118" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21857,19 +21854,19 @@
         <v>111</v>
       </c>
       <c r="B118" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="C118" s="21" t="s">
         <v>497</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="D118" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="D118" s="22" t="s">
+      <c r="E118" s="39" t="s">
         <v>499</v>
       </c>
-      <c r="E118" s="39" t="s">
-        <v>500</v>
-      </c>
       <c r="F118" s="39" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G118" s="24" t="s">
         <v>21</v>
@@ -21910,7 +21907,7 @@
       </c>
       <c r="S118" s="19"/>
       <c r="T118" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="119" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21919,14 +21916,14 @@
       </c>
       <c r="B119" s="26"/>
       <c r="C119" s="27" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E119" s="29"/>
       <c r="F119" s="30" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G119" s="31" t="s">
         <v>39</v>
@@ -21965,7 +21962,7 @@
       <c r="R119" s="26"/>
       <c r="S119" s="19"/>
       <c r="T119" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="120" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -21974,14 +21971,14 @@
       </c>
       <c r="B120" s="32"/>
       <c r="C120" s="33" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D120" s="34" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E120" s="35"/>
       <c r="F120" s="36" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G120" s="37" t="s">
         <v>39</v>
@@ -22020,7 +22017,7 @@
       <c r="R120" s="32"/>
       <c r="S120" s="19"/>
       <c r="T120" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="121" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22028,17 +22025,17 @@
         <v>114</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C121" s="21" t="s">
         <v>172</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E121" s="25"/>
       <c r="F121" s="59" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G121" s="24" t="s">
         <v>21</v>
@@ -22079,7 +22076,7 @@
       </c>
       <c r="S121" s="19"/>
       <c r="T121" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="122" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22091,11 +22088,11 @@
         <v>172</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E122" s="29"/>
       <c r="F122" s="30" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G122" s="31" t="s">
         <v>21</v>
@@ -22134,7 +22131,7 @@
       <c r="R122" s="26"/>
       <c r="S122" s="19"/>
       <c r="T122" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="123" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22146,11 +22143,11 @@
         <v>172</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E123" s="29"/>
       <c r="F123" s="30" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G123" s="31" t="s">
         <v>21</v>
@@ -22159,7 +22156,7 @@
         <v>172</v>
       </c>
       <c r="I123" s="29" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J123" s="54">
         <v>32181</v>
@@ -22189,7 +22186,7 @@
       <c r="R123" s="26"/>
       <c r="S123" s="19"/>
       <c r="T123" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="124" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22201,11 +22198,11 @@
         <v>172</v>
       </c>
       <c r="D124" s="34" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E124" s="35"/>
       <c r="F124" s="36" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G124" s="37" t="s">
         <v>21</v>
@@ -22244,7 +22241,7 @@
       <c r="R124" s="32"/>
       <c r="S124" s="19"/>
       <c r="T124" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="125" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22309,10 +22306,10 @@
         <v>228</v>
       </c>
       <c r="C126" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="D126" s="22" t="s">
         <v>515</v>
-      </c>
-      <c r="D126" s="22" t="s">
-        <v>516</v>
       </c>
       <c r="E126" s="38" t="s">
         <v>229</v>
@@ -22359,7 +22356,7 @@
       </c>
       <c r="S126" s="19"/>
       <c r="T126" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="127" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22368,10 +22365,10 @@
       </c>
       <c r="B127" s="26"/>
       <c r="C127" s="27" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E127" s="29"/>
       <c r="F127" s="30" t="s">
@@ -22414,7 +22411,7 @@
       <c r="R127" s="26"/>
       <c r="S127" s="19"/>
       <c r="T127" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="128" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22423,10 +22420,10 @@
       </c>
       <c r="B128" s="32"/>
       <c r="C128" s="33" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D128" s="34" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E128" s="35"/>
       <c r="F128" s="36" t="s">
@@ -22469,7 +22466,7 @@
       <c r="R128" s="32"/>
       <c r="S128" s="19"/>
       <c r="T128" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22477,19 +22474,19 @@
         <v>122</v>
       </c>
       <c r="B129" s="20" t="s">
+        <v>518</v>
+      </c>
+      <c r="C129" s="21" t="s">
         <v>519</v>
       </c>
-      <c r="C129" s="21" t="s">
+      <c r="D129" s="22" t="s">
         <v>520</v>
       </c>
-      <c r="D129" s="22" t="s">
+      <c r="E129" s="39" t="s">
         <v>521</v>
       </c>
-      <c r="E129" s="39" t="s">
-        <v>522</v>
-      </c>
       <c r="F129" s="39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G129" s="24" t="s">
         <v>21</v>
@@ -22530,7 +22527,7 @@
       </c>
       <c r="S129" s="19"/>
       <c r="T129" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="130" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22539,14 +22536,14 @@
       </c>
       <c r="B130" s="26"/>
       <c r="C130" s="27" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D130" s="28" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E130" s="29"/>
       <c r="F130" s="30" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G130" s="31" t="s">
         <v>39</v>
@@ -22585,7 +22582,7 @@
       <c r="R130" s="26"/>
       <c r="S130" s="19"/>
       <c r="T130" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="131" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22594,14 +22591,14 @@
       </c>
       <c r="B131" s="26"/>
       <c r="C131" s="27" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D131" s="28" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E131" s="29"/>
       <c r="F131" s="30" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G131" s="31" t="s">
         <v>39</v>
@@ -22640,7 +22637,7 @@
       <c r="R131" s="26"/>
       <c r="S131" s="19"/>
       <c r="T131" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="132" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22649,14 +22646,14 @@
       </c>
       <c r="B132" s="32"/>
       <c r="C132" s="33" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D132" s="34" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E132" s="35"/>
       <c r="F132" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G132" s="37" t="s">
         <v>21</v>
@@ -22695,7 +22692,7 @@
       <c r="R132" s="32"/>
       <c r="S132" s="19"/>
       <c r="T132" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="133" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22703,19 +22700,19 @@
         <v>126</v>
       </c>
       <c r="B133" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="C133" s="22" t="s">
         <v>529</v>
       </c>
-      <c r="C133" s="22" t="s">
+      <c r="D133" s="22" t="s">
         <v>530</v>
       </c>
-      <c r="D133" s="22" t="s">
+      <c r="E133" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="E133" s="39" t="s">
-        <v>532</v>
-      </c>
       <c r="F133" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G133" s="24" t="s">
         <v>21</v>
@@ -22756,7 +22753,7 @@
       </c>
       <c r="S133" s="19"/>
       <c r="T133" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="134" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22765,14 +22762,14 @@
       </c>
       <c r="B134" s="29"/>
       <c r="C134" s="28" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D134" s="28" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E134" s="29"/>
       <c r="F134" s="30" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G134" s="31" t="s">
         <v>39</v>
@@ -22811,7 +22808,7 @@
       <c r="R134" s="26"/>
       <c r="S134" s="19"/>
       <c r="T134" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="135" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22820,14 +22817,14 @@
       </c>
       <c r="B135" s="29"/>
       <c r="C135" s="28" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D135" s="28" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E135" s="29"/>
       <c r="F135" s="30" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G135" s="31" t="s">
         <v>39</v>
@@ -22866,7 +22863,7 @@
       <c r="R135" s="26"/>
       <c r="S135" s="19"/>
       <c r="T135" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="136" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22875,14 +22872,14 @@
       </c>
       <c r="B136" s="29"/>
       <c r="C136" s="28" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D136" s="28" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E136" s="29"/>
       <c r="F136" s="30" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G136" s="31" t="s">
         <v>21</v>
@@ -22921,7 +22918,7 @@
       <c r="R136" s="26"/>
       <c r="S136" s="19"/>
       <c r="T136" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="137" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22930,14 +22927,14 @@
       </c>
       <c r="B137" s="35"/>
       <c r="C137" s="34" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D137" s="34" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E137" s="35"/>
       <c r="F137" s="36" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G137" s="37" t="s">
         <v>39</v>
@@ -22976,7 +22973,7 @@
       <c r="R137" s="32"/>
       <c r="S137" s="19"/>
       <c r="T137" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="138" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -22984,19 +22981,19 @@
         <v>131</v>
       </c>
       <c r="B138" s="20" t="s">
+        <v>540</v>
+      </c>
+      <c r="C138" s="22" t="s">
         <v>541</v>
       </c>
-      <c r="C138" s="22" t="s">
+      <c r="D138" s="22" t="s">
         <v>542</v>
       </c>
-      <c r="D138" s="22" t="s">
+      <c r="E138" s="39" t="s">
         <v>543</v>
       </c>
-      <c r="E138" s="39" t="s">
-        <v>544</v>
-      </c>
       <c r="F138" s="39" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G138" s="24" t="s">
         <v>39</v>
@@ -23037,7 +23034,7 @@
       </c>
       <c r="S138" s="19"/>
       <c r="T138" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="139" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23053,13 +23050,13 @@
       </c>
       <c r="E139" s="29"/>
       <c r="F139" s="30" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G139" s="31" t="s">
         <v>21</v>
       </c>
       <c r="H139" s="53" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I139" s="31" t="s">
         <v>172</v>
@@ -23091,7 +23088,7 @@
       <c r="R139" s="26"/>
       <c r="S139" s="19"/>
       <c r="T139" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="140" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23107,7 +23104,7 @@
       </c>
       <c r="E140" s="29"/>
       <c r="F140" s="30" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G140" s="31" t="s">
         <v>21</v>
@@ -23145,7 +23142,7 @@
       <c r="R140" s="26"/>
       <c r="S140" s="19"/>
       <c r="T140" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="141" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23161,7 +23158,7 @@
       </c>
       <c r="E141" s="35"/>
       <c r="F141" s="36" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G141" s="37" t="s">
         <v>39</v>
@@ -23199,7 +23196,7 @@
       <c r="R141" s="32"/>
       <c r="S141" s="19"/>
       <c r="T141" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="142" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23210,10 +23207,10 @@
         <v>233</v>
       </c>
       <c r="C142" s="41" t="s">
+        <v>548</v>
+      </c>
+      <c r="D142" s="41" t="s">
         <v>549</v>
-      </c>
-      <c r="D142" s="41" t="s">
-        <v>550</v>
       </c>
       <c r="E142" s="38" t="s">
         <v>234</v>
@@ -23260,7 +23257,7 @@
       </c>
       <c r="S142" s="19"/>
       <c r="T142" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="143" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23269,10 +23266,10 @@
       </c>
       <c r="B143" s="26"/>
       <c r="C143" s="42" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D143" s="42" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E143" s="29"/>
       <c r="F143" s="29" t="s">
@@ -23315,7 +23312,7 @@
       <c r="R143" s="26"/>
       <c r="S143" s="19"/>
       <c r="T143" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="144" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23324,10 +23321,10 @@
       </c>
       <c r="B144" s="26"/>
       <c r="C144" s="42" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D144" s="42" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E144" s="29"/>
       <c r="F144" s="29" t="s">
@@ -23370,7 +23367,7 @@
       <c r="R144" s="26"/>
       <c r="S144" s="19"/>
       <c r="T144" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="145" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23379,10 +23376,10 @@
       </c>
       <c r="B145" s="32"/>
       <c r="C145" s="43" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D145" s="43" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E145" s="35"/>
       <c r="F145" s="35" t="s">
@@ -23425,7 +23422,7 @@
       <c r="R145" s="26"/>
       <c r="S145" s="19"/>
       <c r="T145" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="146" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23492,10 +23489,10 @@
         <v>239</v>
       </c>
       <c r="C147" s="41" t="s">
+        <v>553</v>
+      </c>
+      <c r="D147" s="41" t="s">
         <v>554</v>
-      </c>
-      <c r="D147" s="41" t="s">
-        <v>555</v>
       </c>
       <c r="E147" s="38" t="s">
         <v>240</v>
@@ -23542,7 +23539,7 @@
       </c>
       <c r="S147" s="19"/>
       <c r="T147" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="148" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23551,10 +23548,10 @@
       </c>
       <c r="B148" s="26"/>
       <c r="C148" s="42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D148" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E148" s="29"/>
       <c r="F148" s="29" t="s">
@@ -23597,7 +23594,7 @@
       <c r="R148" s="26"/>
       <c r="S148" s="19"/>
       <c r="T148" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="149" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23606,10 +23603,10 @@
       </c>
       <c r="B149" s="26"/>
       <c r="C149" s="42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D149" s="42" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E149" s="29"/>
       <c r="F149" s="29" t="s">
@@ -23652,7 +23649,7 @@
       <c r="R149" s="26"/>
       <c r="S149" s="19"/>
       <c r="T149" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="150" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23661,10 +23658,10 @@
       </c>
       <c r="B150" s="32"/>
       <c r="C150" s="43" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D150" s="43" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E150" s="35"/>
       <c r="F150" s="35" t="s">
@@ -23707,7 +23704,7 @@
       <c r="R150" s="32"/>
       <c r="S150" s="19"/>
       <c r="T150" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="151" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23718,10 +23715,10 @@
         <v>244</v>
       </c>
       <c r="C151" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="D151" s="22" t="s">
         <v>559</v>
-      </c>
-      <c r="D151" s="22" t="s">
-        <v>560</v>
       </c>
       <c r="E151" s="39" t="s">
         <v>245</v>
@@ -23768,7 +23765,7 @@
       </c>
       <c r="S151" s="19"/>
       <c r="T151" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="152" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23777,10 +23774,10 @@
       </c>
       <c r="B152" s="26"/>
       <c r="C152" s="27" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D152" s="28" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E152" s="29"/>
       <c r="F152" s="30" t="s">
@@ -23823,7 +23820,7 @@
       <c r="R152" s="26"/>
       <c r="S152" s="19"/>
       <c r="T152" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="153" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23832,10 +23829,10 @@
       </c>
       <c r="B153" s="26"/>
       <c r="C153" s="27" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D153" s="28" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E153" s="29"/>
       <c r="F153" s="30" t="s">
@@ -23878,7 +23875,7 @@
       <c r="R153" s="26"/>
       <c r="S153" s="19"/>
       <c r="T153" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="154" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23887,10 +23884,10 @@
       </c>
       <c r="B154" s="32"/>
       <c r="C154" s="33" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D154" s="34" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E154" s="35"/>
       <c r="F154" s="36" t="s">
@@ -23933,7 +23930,7 @@
       <c r="R154" s="32"/>
       <c r="S154" s="19"/>
       <c r="T154" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="155" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -23944,16 +23941,16 @@
         <v>251</v>
       </c>
       <c r="C155" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="D155" s="22" t="s">
         <v>564</v>
       </c>
-      <c r="D155" s="22" t="s">
+      <c r="E155" s="39" t="s">
         <v>565</v>
       </c>
-      <c r="E155" s="39" t="s">
-        <v>566</v>
-      </c>
       <c r="F155" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G155" s="24" t="s">
         <v>21</v>
@@ -23994,7 +23991,7 @@
       </c>
       <c r="S155" s="19"/>
       <c r="T155" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24003,14 +24000,14 @@
       </c>
       <c r="B156" s="26"/>
       <c r="C156" s="27" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D156" s="28" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E156" s="29"/>
       <c r="F156" s="30" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G156" s="31" t="s">
         <v>39</v>
@@ -24049,7 +24046,7 @@
       <c r="R156" s="19"/>
       <c r="S156" s="19"/>
       <c r="T156" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24058,14 +24055,14 @@
       </c>
       <c r="B157" s="32"/>
       <c r="C157" s="33" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E157" s="35"/>
       <c r="F157" s="36" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G157" s="37" t="s">
         <v>39</v>
@@ -24104,7 +24101,7 @@
       <c r="R157" s="19"/>
       <c r="S157" s="19"/>
       <c r="T157" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24169,10 +24166,10 @@
         <v>257</v>
       </c>
       <c r="C159" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="D159" s="22" t="s">
         <v>571</v>
-      </c>
-      <c r="D159" s="22" t="s">
-        <v>572</v>
       </c>
       <c r="E159" s="39" t="s">
         <v>258</v>
@@ -24219,7 +24216,7 @@
       </c>
       <c r="S159" s="19"/>
       <c r="T159" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="160" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24228,10 +24225,10 @@
       </c>
       <c r="B160" s="26"/>
       <c r="C160" s="27" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D160" s="28" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E160" s="29"/>
       <c r="F160" s="30" t="s">
@@ -24274,7 +24271,7 @@
       <c r="R160" s="26"/>
       <c r="S160" s="19"/>
       <c r="T160" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="161" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24283,10 +24280,10 @@
       </c>
       <c r="B161" s="26"/>
       <c r="C161" s="27" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D161" s="28" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E161" s="29"/>
       <c r="F161" s="30" t="s">
@@ -24329,7 +24326,7 @@
       <c r="R161" s="26"/>
       <c r="S161" s="19"/>
       <c r="T161" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="162" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24338,10 +24335,10 @@
       </c>
       <c r="B162" s="32"/>
       <c r="C162" s="33" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D162" s="34" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E162" s="35"/>
       <c r="F162" s="36" t="s">
@@ -24384,7 +24381,7 @@
       <c r="R162" s="26"/>
       <c r="S162" s="19"/>
       <c r="T162" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="163" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24503,10 +24500,10 @@
         <v>266</v>
       </c>
       <c r="C165" s="41" t="s">
+        <v>575</v>
+      </c>
+      <c r="D165" s="41" t="s">
         <v>576</v>
-      </c>
-      <c r="D165" s="41" t="s">
-        <v>577</v>
       </c>
       <c r="E165" s="38" t="s">
         <v>267</v>
@@ -24553,7 +24550,7 @@
       </c>
       <c r="S165" s="19"/>
       <c r="T165" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="166" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24562,10 +24559,10 @@
       </c>
       <c r="B166" s="26"/>
       <c r="C166" s="42" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D166" s="42" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E166" s="29"/>
       <c r="F166" s="29" t="s">
@@ -24608,7 +24605,7 @@
       <c r="R166" s="26"/>
       <c r="S166" s="19"/>
       <c r="T166" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="167" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24617,10 +24614,10 @@
       </c>
       <c r="B167" s="26"/>
       <c r="C167" s="42" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D167" s="42" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E167" s="29"/>
       <c r="F167" s="29" t="s">
@@ -24663,7 +24660,7 @@
       <c r="R167" s="26"/>
       <c r="S167" s="19"/>
       <c r="T167" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="168" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24672,10 +24669,10 @@
       </c>
       <c r="B168" s="32"/>
       <c r="C168" s="43" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D168" s="43" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E168" s="35"/>
       <c r="F168" s="35" t="s">
@@ -24718,7 +24715,7 @@
       <c r="R168" s="32"/>
       <c r="S168" s="19"/>
       <c r="T168" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="169" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24729,10 +24726,10 @@
         <v>273</v>
       </c>
       <c r="C169" s="41" t="s">
+        <v>580</v>
+      </c>
+      <c r="D169" s="41" t="s">
         <v>581</v>
-      </c>
-      <c r="D169" s="41" t="s">
-        <v>582</v>
       </c>
       <c r="E169" s="38" t="s">
         <v>274</v>
@@ -24779,7 +24776,7 @@
       </c>
       <c r="S169" s="19"/>
       <c r="T169" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="170" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24788,10 +24785,10 @@
       </c>
       <c r="B170" s="26"/>
       <c r="C170" s="42" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D170" s="42" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E170" s="29"/>
       <c r="F170" s="29" t="s">
@@ -24834,7 +24831,7 @@
       <c r="R170" s="26"/>
       <c r="S170" s="19"/>
       <c r="T170" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="171" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24843,10 +24840,10 @@
       </c>
       <c r="B171" s="26"/>
       <c r="C171" s="42" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D171" s="42" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E171" s="29"/>
       <c r="F171" s="29" t="s">
@@ -24889,7 +24886,7 @@
       <c r="R171" s="26"/>
       <c r="S171" s="19"/>
       <c r="T171" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="172" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24898,10 +24895,10 @@
       </c>
       <c r="B172" s="26"/>
       <c r="C172" s="42" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D172" s="42" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E172" s="29"/>
       <c r="F172" s="29" t="s">
@@ -24944,7 +24941,7 @@
       <c r="R172" s="26"/>
       <c r="S172" s="19"/>
       <c r="T172" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="173" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -24953,10 +24950,10 @@
       </c>
       <c r="B173" s="32"/>
       <c r="C173" s="43" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D173" s="43" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E173" s="35"/>
       <c r="F173" s="35" t="s">
@@ -24999,7 +24996,7 @@
       <c r="R173" s="32"/>
       <c r="S173" s="19"/>
       <c r="T173" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="174" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25010,10 +25007,10 @@
         <v>279</v>
       </c>
       <c r="C174" s="41" t="s">
+        <v>586</v>
+      </c>
+      <c r="D174" s="41" t="s">
         <v>587</v>
-      </c>
-      <c r="D174" s="41" t="s">
-        <v>588</v>
       </c>
       <c r="E174" s="38" t="s">
         <v>280</v>
@@ -25060,7 +25057,7 @@
       </c>
       <c r="S174" s="19"/>
       <c r="T174" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="175" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25069,10 +25066,10 @@
       </c>
       <c r="B175" s="26"/>
       <c r="C175" s="42" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D175" s="42" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E175" s="29"/>
       <c r="F175" s="29" t="s">
@@ -25115,7 +25112,7 @@
       <c r="R175" s="26"/>
       <c r="S175" s="19"/>
       <c r="T175" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="176" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25124,10 +25121,10 @@
       </c>
       <c r="B176" s="26"/>
       <c r="C176" s="42" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D176" s="42" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E176" s="29"/>
       <c r="F176" s="29" t="s">
@@ -25170,7 +25167,7 @@
       <c r="R176" s="26"/>
       <c r="S176" s="19"/>
       <c r="T176" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="177" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25179,10 +25176,10 @@
       </c>
       <c r="B177" s="26"/>
       <c r="C177" s="42" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D177" s="42" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E177" s="29"/>
       <c r="F177" s="29" t="s">
@@ -25225,7 +25222,7 @@
       <c r="R177" s="26"/>
       <c r="S177" s="19"/>
       <c r="T177" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="178" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25234,10 +25231,10 @@
       </c>
       <c r="B178" s="32"/>
       <c r="C178" s="43" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D178" s="43" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E178" s="35"/>
       <c r="F178" s="35" t="s">
@@ -25280,7 +25277,7 @@
       <c r="R178" s="32"/>
       <c r="S178" s="19"/>
       <c r="T178" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="179" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25291,16 +25288,16 @@
         <v>287</v>
       </c>
       <c r="C179" s="41" t="s">
+        <v>592</v>
+      </c>
+      <c r="D179" s="41" t="s">
         <v>593</v>
       </c>
-      <c r="D179" s="41" t="s">
+      <c r="E179" s="38" t="s">
         <v>594</v>
       </c>
-      <c r="E179" s="38" t="s">
-        <v>595</v>
-      </c>
       <c r="F179" s="38" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G179" s="24" t="s">
         <v>21</v>
@@ -25341,7 +25338,7 @@
       </c>
       <c r="S179" s="19"/>
       <c r="T179" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="180" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25350,14 +25347,14 @@
       </c>
       <c r="B180" s="26"/>
       <c r="C180" s="42" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D180" s="42" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E180" s="29"/>
       <c r="F180" s="29" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G180" s="31" t="s">
         <v>39</v>
@@ -25396,7 +25393,7 @@
       <c r="R180" s="26"/>
       <c r="S180" s="19"/>
       <c r="T180" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="181" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25405,14 +25402,14 @@
       </c>
       <c r="B181" s="26"/>
       <c r="C181" s="42" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D181" s="42" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E181" s="29"/>
       <c r="F181" s="29" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G181" s="31" t="s">
         <v>21</v>
@@ -25451,7 +25448,7 @@
       <c r="R181" s="26"/>
       <c r="S181" s="19"/>
       <c r="T181" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="182" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25460,14 +25457,14 @@
       </c>
       <c r="B182" s="26"/>
       <c r="C182" s="42" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D182" s="42" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E182" s="29"/>
       <c r="F182" s="73" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G182" s="31" t="s">
         <v>21</v>
@@ -25506,7 +25503,7 @@
       <c r="R182" s="26"/>
       <c r="S182" s="19"/>
       <c r="T182" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="183" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25515,14 +25512,14 @@
       </c>
       <c r="B183" s="26"/>
       <c r="C183" s="42" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D183" s="42" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E183" s="29"/>
       <c r="F183" s="29" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G183" s="31" t="s">
         <v>21</v>
@@ -25561,7 +25558,7 @@
       <c r="R183" s="26"/>
       <c r="S183" s="19"/>
       <c r="T183" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="184" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25570,14 +25567,14 @@
       </c>
       <c r="B184" s="32"/>
       <c r="C184" s="43" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D184" s="43" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E184" s="35"/>
       <c r="F184" s="35" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G184" s="37" t="s">
         <v>39</v>
@@ -25616,7 +25613,7 @@
       <c r="R184" s="32"/>
       <c r="S184" s="19"/>
       <c r="T184" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="185" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25624,7 +25621,7 @@
         <v>178</v>
       </c>
       <c r="B185" s="20" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C185" s="74" t="s">
         <v>172</v>
@@ -25633,10 +25630,10 @@
         <v>172</v>
       </c>
       <c r="E185" s="75" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F185" s="75" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G185" s="18" t="s">
         <v>21</v>
@@ -25673,7 +25670,7 @@
       </c>
       <c r="S185" s="19"/>
       <c r="T185" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="186" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25689,7 +25686,7 @@
       </c>
       <c r="E186" s="19"/>
       <c r="F186" s="76" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G186" s="18" t="s">
         <v>39</v>
@@ -25698,7 +25695,7 @@
         <v>40</v>
       </c>
       <c r="I186" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J186" s="48">
         <v>30633</v>
@@ -25726,7 +25723,7 @@
       <c r="R186" s="26"/>
       <c r="S186" s="19"/>
       <c r="T186" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="187" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25742,7 +25739,7 @@
       </c>
       <c r="E187" s="19"/>
       <c r="F187" s="76" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G187" s="18" t="s">
         <v>21</v>
@@ -25751,7 +25748,7 @@
         <v>44</v>
       </c>
       <c r="I187" s="19" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J187" s="48">
         <v>37428</v>
@@ -25777,7 +25774,7 @@
       <c r="R187" s="26"/>
       <c r="S187" s="19"/>
       <c r="T187" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="188" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25793,7 +25790,7 @@
       </c>
       <c r="E188" s="19"/>
       <c r="F188" s="76" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G188" s="18" t="s">
         <v>21</v>
@@ -25802,7 +25799,7 @@
         <v>44</v>
       </c>
       <c r="I188" s="19" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J188" s="48">
         <v>38512</v>
@@ -25828,7 +25825,7 @@
       <c r="R188" s="26"/>
       <c r="S188" s="19"/>
       <c r="T188" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="189" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25844,7 +25841,7 @@
       </c>
       <c r="E189" s="19"/>
       <c r="F189" s="76" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G189" s="18" t="s">
         <v>39</v>
@@ -25853,7 +25850,7 @@
         <v>44</v>
       </c>
       <c r="I189" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J189" s="48">
         <v>40102</v>
@@ -25879,7 +25876,7 @@
       <c r="R189" s="26"/>
       <c r="S189" s="19"/>
       <c r="T189" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="190" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25895,7 +25892,7 @@
       </c>
       <c r="E190" s="19"/>
       <c r="F190" s="76" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G190" s="18" t="s">
         <v>21</v>
@@ -25904,7 +25901,7 @@
         <v>44</v>
       </c>
       <c r="I190" s="19" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="J190" s="48">
         <v>40230</v>
@@ -25930,7 +25927,7 @@
       <c r="R190" s="26"/>
       <c r="S190" s="19"/>
       <c r="T190" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="191" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25946,7 +25943,7 @@
       </c>
       <c r="E191" s="19"/>
       <c r="F191" s="76" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G191" s="18" t="s">
         <v>39</v>
@@ -25955,7 +25952,7 @@
         <v>44</v>
       </c>
       <c r="I191" s="19" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J191" s="48">
         <v>41570</v>
@@ -25981,7 +25978,7 @@
       <c r="R191" s="26"/>
       <c r="S191" s="19"/>
       <c r="T191" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="192" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -25997,7 +25994,7 @@
       </c>
       <c r="E192" s="19"/>
       <c r="F192" s="76" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G192" s="18" t="s">
         <v>39</v>
@@ -26006,7 +26003,7 @@
         <v>44</v>
       </c>
       <c r="I192" s="19" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J192" s="48">
         <v>43126</v>
@@ -26036,7 +26033,7 @@
       <c r="R192" s="26"/>
       <c r="S192" s="19"/>
       <c r="T192" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="193" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26052,7 +26049,7 @@
       </c>
       <c r="E193" s="19"/>
       <c r="F193" s="76" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G193" s="18" t="s">
         <v>39</v>
@@ -26061,7 +26058,7 @@
         <v>44</v>
       </c>
       <c r="I193" s="19" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J193" s="48">
         <v>44241</v>
@@ -26091,7 +26088,7 @@
       <c r="R193" s="32"/>
       <c r="S193" s="19"/>
       <c r="T193" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="194" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26102,10 +26099,10 @@
         <v>288</v>
       </c>
       <c r="C194" s="41" t="s">
+        <v>619</v>
+      </c>
+      <c r="D194" s="41" t="s">
         <v>620</v>
-      </c>
-      <c r="D194" s="41" t="s">
-        <v>621</v>
       </c>
       <c r="E194" s="38" t="s">
         <v>289</v>
@@ -26152,7 +26149,7 @@
       </c>
       <c r="S194" s="19"/>
       <c r="T194" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="195" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26161,10 +26158,10 @@
       </c>
       <c r="B195" s="26"/>
       <c r="C195" s="42" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D195" s="42" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E195" s="29"/>
       <c r="F195" s="29" t="s">
@@ -26207,7 +26204,7 @@
       <c r="R195" s="26"/>
       <c r="S195" s="19"/>
       <c r="T195" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="196" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26216,10 +26213,10 @@
       </c>
       <c r="B196" s="26"/>
       <c r="C196" s="42" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D196" s="42" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E196" s="29"/>
       <c r="F196" s="29" t="s">
@@ -26262,7 +26259,7 @@
       <c r="R196" s="26"/>
       <c r="S196" s="19"/>
       <c r="T196" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="197" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26271,10 +26268,10 @@
       </c>
       <c r="B197" s="32"/>
       <c r="C197" s="43" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D197" s="43" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E197" s="35"/>
       <c r="F197" s="35" t="s">
@@ -26317,7 +26314,7 @@
       <c r="R197" s="32"/>
       <c r="S197" s="19"/>
       <c r="T197" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="198" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26325,19 +26322,19 @@
         <v>191</v>
       </c>
       <c r="B198" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="C198" s="21" t="s">
         <v>625</v>
       </c>
-      <c r="C198" s="21" t="s">
+      <c r="D198" s="22" t="s">
         <v>626</v>
       </c>
-      <c r="D198" s="22" t="s">
+      <c r="E198" s="39" t="s">
         <v>627</v>
       </c>
-      <c r="E198" s="39" t="s">
-        <v>628</v>
-      </c>
       <c r="F198" s="39" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G198" s="24" t="s">
         <v>21</v>
@@ -26346,7 +26343,7 @@
         <v>22</v>
       </c>
       <c r="I198" s="25" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J198" s="51">
         <v>16132</v>
@@ -26371,14 +26368,14 @@
         <v>34</v>
       </c>
       <c r="Q198" s="19" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="R198" s="20" t="s">
         <v>30</v>
       </c>
       <c r="S198" s="19"/>
       <c r="T198" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="199" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26387,14 +26384,14 @@
       </c>
       <c r="B199" s="26"/>
       <c r="C199" s="27" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D199" s="28" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E199" s="29"/>
       <c r="F199" s="29" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G199" s="31" t="s">
         <v>39</v>
@@ -26433,7 +26430,7 @@
       <c r="R199" s="26"/>
       <c r="S199" s="19"/>
       <c r="T199" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="200" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26442,14 +26439,14 @@
       </c>
       <c r="B200" s="26"/>
       <c r="C200" s="27" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D200" s="28" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E200" s="29"/>
       <c r="F200" s="29" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G200" s="31" t="s">
         <v>21</v>
@@ -26488,7 +26485,7 @@
       <c r="R200" s="26"/>
       <c r="S200" s="19"/>
       <c r="T200" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="201" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26497,14 +26494,14 @@
       </c>
       <c r="B201" s="26"/>
       <c r="C201" s="27" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D201" s="28" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E201" s="29"/>
       <c r="F201" s="29" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G201" s="31" t="s">
         <v>21</v>
@@ -26543,7 +26540,7 @@
       <c r="R201" s="26"/>
       <c r="S201" s="19"/>
       <c r="T201" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="202" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26552,14 +26549,14 @@
       </c>
       <c r="B202" s="26"/>
       <c r="C202" s="27" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D202" s="28" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E202" s="29"/>
       <c r="F202" s="29" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G202" s="31" t="s">
         <v>21</v>
@@ -26598,7 +26595,7 @@
       <c r="R202" s="26"/>
       <c r="S202" s="19"/>
       <c r="T202" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="203" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26607,14 +26604,14 @@
       </c>
       <c r="B203" s="32"/>
       <c r="C203" s="33" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D203" s="34" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E203" s="35"/>
       <c r="F203" s="35" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G203" s="37" t="s">
         <v>39</v>
@@ -26653,7 +26650,7 @@
       <c r="R203" s="32"/>
       <c r="S203" s="19"/>
       <c r="T203" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="204" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26664,10 +26661,10 @@
         <v>295</v>
       </c>
       <c r="C204" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="D204" s="22" t="s">
         <v>641</v>
-      </c>
-      <c r="D204" s="22" t="s">
-        <v>642</v>
       </c>
       <c r="E204" s="38" t="s">
         <v>296</v>
@@ -26714,7 +26711,7 @@
       </c>
       <c r="S204" s="19"/>
       <c r="T204" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="205" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26723,10 +26720,10 @@
       </c>
       <c r="B205" s="26"/>
       <c r="C205" s="27" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D205" s="28" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E205" s="29"/>
       <c r="F205" s="29" t="s">
@@ -26769,7 +26766,7 @@
       <c r="R205" s="26"/>
       <c r="S205" s="19"/>
       <c r="T205" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="206" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26778,10 +26775,10 @@
       </c>
       <c r="B206" s="26"/>
       <c r="C206" s="27" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D206" s="28" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E206" s="29"/>
       <c r="F206" s="29" t="s">
@@ -26824,7 +26821,7 @@
       <c r="R206" s="26"/>
       <c r="S206" s="19"/>
       <c r="T206" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="207" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26833,10 +26830,10 @@
       </c>
       <c r="B207" s="32"/>
       <c r="C207" s="33" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D207" s="34" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E207" s="35"/>
       <c r="F207" s="35" t="s">
@@ -26879,7 +26876,7 @@
       <c r="R207" s="32"/>
       <c r="S207" s="19"/>
       <c r="T207" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="208" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26890,10 +26887,10 @@
         <v>301</v>
       </c>
       <c r="C208" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="D208" s="22" t="s">
         <v>646</v>
-      </c>
-      <c r="D208" s="22" t="s">
-        <v>647</v>
       </c>
       <c r="E208" s="38" t="s">
         <v>302</v>
@@ -26940,7 +26937,7 @@
       </c>
       <c r="S208" s="19"/>
       <c r="T208" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="209" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -26949,10 +26946,10 @@
       </c>
       <c r="B209" s="26"/>
       <c r="C209" s="27" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D209" s="28" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E209" s="29"/>
       <c r="F209" s="29" t="s">
@@ -26995,7 +26992,7 @@
       <c r="R209" s="26"/>
       <c r="S209" s="19"/>
       <c r="T209" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="210" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27004,10 +27001,10 @@
       </c>
       <c r="B210" s="32"/>
       <c r="C210" s="33" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D210" s="34" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E210" s="35"/>
       <c r="F210" s="35" t="s">
@@ -27050,7 +27047,7 @@
       <c r="R210" s="32"/>
       <c r="S210" s="19"/>
       <c r="T210" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="211" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27058,19 +27055,19 @@
         <v>204</v>
       </c>
       <c r="B211" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="C211" s="21" t="s">
         <v>650</v>
       </c>
-      <c r="C211" s="21" t="s">
+      <c r="D211" s="22" t="s">
         <v>651</v>
       </c>
-      <c r="D211" s="22" t="s">
+      <c r="E211" s="39" t="s">
         <v>652</v>
       </c>
-      <c r="E211" s="39" t="s">
-        <v>653</v>
-      </c>
       <c r="F211" s="39" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G211" s="24" t="s">
         <v>21</v>
@@ -27104,14 +27101,14 @@
         <v>34</v>
       </c>
       <c r="Q211" s="25" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="R211" s="20" t="s">
         <v>36</v>
       </c>
       <c r="S211" s="19"/>
       <c r="T211" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="212" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27120,10 +27117,10 @@
       </c>
       <c r="B212" s="32"/>
       <c r="C212" s="33" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D212" s="34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E212" s="35"/>
       <c r="F212" s="36" t="s">
@@ -27166,7 +27163,7 @@
       <c r="R212" s="32"/>
       <c r="S212" s="19"/>
       <c r="T212" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="213" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27177,16 +27174,16 @@
         <v>306</v>
       </c>
       <c r="C213" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="D213" s="22" t="s">
         <v>655</v>
       </c>
-      <c r="D213" s="22" t="s">
-        <v>656</v>
-      </c>
       <c r="E213" s="39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F213" s="59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G213" s="24" t="s">
         <v>21</v>
@@ -27227,7 +27224,7 @@
       </c>
       <c r="S213" s="19"/>
       <c r="T213" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="214" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27236,14 +27233,14 @@
       </c>
       <c r="B214" s="26"/>
       <c r="C214" s="27" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D214" s="28" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E214" s="29"/>
       <c r="F214" s="30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G214" s="31" t="s">
         <v>39</v>
@@ -27282,7 +27279,7 @@
       <c r="R214" s="26"/>
       <c r="S214" s="19"/>
       <c r="T214" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="215" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27291,14 +27288,14 @@
       </c>
       <c r="B215" s="26"/>
       <c r="C215" s="27" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D215" s="28" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E215" s="29"/>
       <c r="F215" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G215" s="31" t="s">
         <v>21</v>
@@ -27337,7 +27334,7 @@
       <c r="R215" s="26"/>
       <c r="S215" s="19"/>
       <c r="T215" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="216" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27346,14 +27343,14 @@
       </c>
       <c r="B216" s="26"/>
       <c r="C216" s="27" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D216" s="28" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E216" s="29"/>
       <c r="F216" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G216" s="31" t="s">
         <v>39</v>
@@ -27392,7 +27389,7 @@
       <c r="R216" s="26"/>
       <c r="S216" s="19"/>
       <c r="T216" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="217" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27401,14 +27398,14 @@
       </c>
       <c r="B217" s="32"/>
       <c r="C217" s="33" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D217" s="34" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E217" s="35"/>
       <c r="F217" s="36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G217" s="37" t="s">
         <v>21</v>
@@ -27447,7 +27444,7 @@
       <c r="R217" s="32"/>
       <c r="S217" s="19"/>
       <c r="T217" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="218" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27455,7 +27452,7 @@
         <v>211</v>
       </c>
       <c r="B218" s="64" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C218" s="78"/>
       <c r="D218" s="79"/>
@@ -27487,19 +27484,19 @@
         <v>212</v>
       </c>
       <c r="B219" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="C219" s="41" t="s">
+        <v>660</v>
+      </c>
+      <c r="D219" s="41" t="s">
+        <v>661</v>
+      </c>
+      <c r="E219" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="C219" s="41" t="s">
-        <v>661</v>
-      </c>
-      <c r="D219" s="41" t="s">
-        <v>662</v>
-      </c>
-      <c r="E219" s="38" t="s">
-        <v>321</v>
-      </c>
       <c r="F219" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G219" s="24" t="s">
         <v>21</v>
@@ -27524,7 +27521,7 @@
         <v>25</v>
       </c>
       <c r="N219" s="25" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O219" s="24" t="s">
         <v>27</v>
@@ -27540,7 +27537,7 @@
       </c>
       <c r="S219" s="19"/>
       <c r="T219" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="220" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27549,14 +27546,14 @@
       </c>
       <c r="B220" s="26"/>
       <c r="C220" s="42" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D220" s="42" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E220" s="29"/>
       <c r="F220" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G220" s="31" t="s">
         <v>39</v>
@@ -27590,12 +27587,12 @@
         <v>204</v>
       </c>
       <c r="Q220" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R220" s="26"/>
       <c r="S220" s="19"/>
       <c r="T220" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="221" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27604,14 +27601,14 @@
       </c>
       <c r="B221" s="26"/>
       <c r="C221" s="42" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D221" s="42" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E221" s="29"/>
       <c r="F221" s="29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G221" s="31" t="s">
         <v>39</v>
@@ -27650,7 +27647,7 @@
       <c r="R221" s="26"/>
       <c r="S221" s="19"/>
       <c r="T221" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="222" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27659,14 +27656,14 @@
       </c>
       <c r="B222" s="32"/>
       <c r="C222" s="33" t="s">
+        <v>664</v>
+      </c>
+      <c r="D222" s="34" t="s">
         <v>665</v>
-      </c>
-      <c r="D222" s="34" t="s">
-        <v>666</v>
       </c>
       <c r="E222" s="35"/>
       <c r="F222" s="36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G222" s="37" t="s">
         <v>39</v>
@@ -27705,7 +27702,7 @@
       <c r="R222" s="32"/>
       <c r="S222" s="19"/>
       <c r="T222" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="223" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27713,19 +27710,19 @@
         <v>216</v>
       </c>
       <c r="B223" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="C223" s="21" t="s">
+        <v>666</v>
+      </c>
+      <c r="D223" s="22" t="s">
+        <v>667</v>
+      </c>
+      <c r="E223" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="C223" s="21" t="s">
-        <v>667</v>
-      </c>
-      <c r="D223" s="22" t="s">
-        <v>668</v>
-      </c>
-      <c r="E223" s="38" t="s">
-        <v>328</v>
-      </c>
       <c r="F223" s="39" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G223" s="24" t="s">
         <v>21</v>
@@ -27766,7 +27763,7 @@
       </c>
       <c r="S223" s="19"/>
       <c r="T223" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="224" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27775,14 +27772,14 @@
       </c>
       <c r="B224" s="26"/>
       <c r="C224" s="27" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D224" s="28" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E224" s="29"/>
       <c r="F224" s="30" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G224" s="31" t="s">
         <v>39</v>
@@ -27821,7 +27818,7 @@
       <c r="R224" s="26"/>
       <c r="S224" s="19"/>
       <c r="T224" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="225" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27830,14 +27827,14 @@
       </c>
       <c r="B225" s="32"/>
       <c r="C225" s="33" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D225" s="34" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E225" s="35"/>
       <c r="F225" s="36" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G225" s="37" t="s">
         <v>39</v>
@@ -27876,7 +27873,7 @@
       <c r="R225" s="32"/>
       <c r="S225" s="19"/>
       <c r="T225" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="226" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27884,19 +27881,19 @@
         <v>219</v>
       </c>
       <c r="B226" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C226" s="21" t="s">
+        <v>671</v>
+      </c>
+      <c r="D226" s="22" t="s">
         <v>672</v>
       </c>
-      <c r="D226" s="22" t="s">
+      <c r="E226" s="38" t="s">
         <v>673</v>
       </c>
-      <c r="E226" s="38" t="s">
-        <v>674</v>
-      </c>
       <c r="F226" s="38" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G226" s="24" t="s">
         <v>21</v>
@@ -27937,7 +27934,7 @@
       </c>
       <c r="S226" s="19"/>
       <c r="T226" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="227" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -27946,14 +27943,14 @@
       </c>
       <c r="B227" s="26"/>
       <c r="C227" s="27" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D227" s="28" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E227" s="29"/>
       <c r="F227" s="29" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G227" s="31" t="s">
         <v>21</v>
@@ -27992,7 +27989,7 @@
       <c r="R227" s="26"/>
       <c r="S227" s="19"/>
       <c r="T227" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="228" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28001,14 +27998,14 @@
       </c>
       <c r="B228" s="26"/>
       <c r="C228" s="27" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D228" s="28" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E228" s="29"/>
       <c r="F228" s="29" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G228" s="31" t="s">
         <v>39</v>
@@ -28047,7 +28044,7 @@
       <c r="R228" s="26"/>
       <c r="S228" s="19"/>
       <c r="T228" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="229" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28056,14 +28053,14 @@
       </c>
       <c r="B229" s="32"/>
       <c r="C229" s="33" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D229" s="34" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E229" s="35"/>
       <c r="F229" s="35" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G229" s="37" t="s">
         <v>21</v>
@@ -28102,7 +28099,7 @@
       <c r="R229" s="32"/>
       <c r="S229" s="19"/>
       <c r="T229" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="230" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28110,19 +28107,19 @@
         <v>223</v>
       </c>
       <c r="B230" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="C230" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="D230" s="22" t="s">
+        <v>681</v>
+      </c>
+      <c r="E230" s="38" t="s">
         <v>331</v>
       </c>
-      <c r="C230" s="21" t="s">
-        <v>681</v>
-      </c>
-      <c r="D230" s="22" t="s">
-        <v>682</v>
-      </c>
-      <c r="E230" s="38" t="s">
-        <v>332</v>
-      </c>
       <c r="F230" s="38" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G230" s="24" t="s">
         <v>21</v>
@@ -28163,7 +28160,7 @@
       </c>
       <c r="S230" s="19"/>
       <c r="T230" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="231" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28172,14 +28169,14 @@
       </c>
       <c r="B231" s="26"/>
       <c r="C231" s="27" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D231" s="28" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E231" s="29"/>
       <c r="F231" s="29" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G231" s="31" t="s">
         <v>39</v>
@@ -28218,7 +28215,7 @@
       <c r="R231" s="26"/>
       <c r="S231" s="19"/>
       <c r="T231" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="232" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28227,14 +28224,14 @@
       </c>
       <c r="B232" s="26"/>
       <c r="C232" s="27" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D232" s="28" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E232" s="29"/>
       <c r="F232" s="29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G232" s="31" t="s">
         <v>21</v>
@@ -28273,7 +28270,7 @@
       <c r="R232" s="26"/>
       <c r="S232" s="19"/>
       <c r="T232" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" spans="1:20" s="2" customFormat="1" ht="12" customHeight="1">
@@ -28282,14 +28279,14 @@
       </c>
       <c r="B233" s="32"/>
       <c r="C233" s="33" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D233" s="34" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E233" s="35"/>
       <c r="F233" s="35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G233" s="37" t="s">
         <v>21</v>
@@ -28328,7 +28325,7 @@
       <c r="R233" s="32"/>
       <c r="S233" s="19"/>
       <c r="T233" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="234" spans="1:20" s="2" customFormat="1">
@@ -28336,19 +28333,19 @@
         <v>227</v>
       </c>
       <c r="B234" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="C234" s="21" t="s">
+        <v>685</v>
+      </c>
+      <c r="D234" s="22" t="s">
+        <v>686</v>
+      </c>
+      <c r="E234" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="C234" s="21" t="s">
-        <v>686</v>
-      </c>
-      <c r="D234" s="22" t="s">
-        <v>687</v>
-      </c>
-      <c r="E234" s="39" t="s">
-        <v>337</v>
-      </c>
       <c r="F234" s="39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G234" s="24" t="s">
         <v>21</v>
@@ -28389,7 +28386,7 @@
       </c>
       <c r="S234" s="19"/>
       <c r="T234" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="235" spans="1:20" s="2" customFormat="1">
@@ -28398,14 +28395,14 @@
       </c>
       <c r="B235" s="19"/>
       <c r="C235" s="27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D235" s="28" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E235" s="29"/>
       <c r="F235" s="30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G235" s="31" t="s">
         <v>39</v>
@@ -28444,7 +28441,7 @@
       <c r="R235" s="19"/>
       <c r="S235" s="19"/>
       <c r="T235" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="236" spans="1:20" s="2" customFormat="1">
@@ -28453,14 +28450,14 @@
       </c>
       <c r="B236" s="19"/>
       <c r="C236" s="27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D236" s="28" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E236" s="29"/>
       <c r="F236" s="30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G236" s="31" t="s">
         <v>21</v>
@@ -28499,7 +28496,7 @@
       <c r="R236" s="19"/>
       <c r="S236" s="19"/>
       <c r="T236" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="237" spans="1:20" s="2" customFormat="1">
@@ -28508,14 +28505,14 @@
       </c>
       <c r="B237" s="19"/>
       <c r="C237" s="27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D237" s="28" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E237" s="29"/>
       <c r="F237" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G237" s="31" t="s">
         <v>39</v>
@@ -28554,7 +28551,7 @@
       <c r="R237" s="26"/>
       <c r="S237" s="19"/>
       <c r="T237" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="238" spans="1:20" s="2" customFormat="1">
@@ -28563,14 +28560,14 @@
       </c>
       <c r="B238" s="19"/>
       <c r="C238" s="27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D238" s="28" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E238" s="29"/>
       <c r="F238" s="30" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G238" s="31" t="s">
         <v>21</v>
@@ -28609,7 +28606,7 @@
       <c r="R238" s="26"/>
       <c r="S238" s="19"/>
       <c r="T238" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="239" spans="1:20" s="2" customFormat="1">
@@ -28618,14 +28615,14 @@
       </c>
       <c r="B239" s="19"/>
       <c r="C239" s="27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D239" s="28" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E239" s="29"/>
       <c r="F239" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G239" s="31" t="s">
         <v>39</v>
@@ -28664,7 +28661,7 @@
       <c r="R239" s="26"/>
       <c r="S239" s="19"/>
       <c r="T239" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="240" spans="1:20" s="2" customFormat="1">
@@ -28676,11 +28673,11 @@
         <v>172</v>
       </c>
       <c r="D240" s="34" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E240" s="35"/>
       <c r="F240" s="36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G240" s="37" t="s">
         <v>39</v>
@@ -28719,7 +28716,7 @@
       <c r="R240" s="32"/>
       <c r="S240" s="19"/>
       <c r="T240" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="242" spans="6:6">

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECB4ECE-18E5-4976-AC03-9737BF982073}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FA035C-349D-4298-B369-C3386313060C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="765">
   <si>
     <t>DAFTAR PENDUDUK RT 06 - RW 14</t>
   </si>
@@ -2315,6 +2315,18 @@
   </si>
   <si>
     <t>WIDURI NURSYAHRANI</t>
+  </si>
+  <si>
+    <t>Belum Tamat SD/sederajat</t>
+  </si>
+  <si>
+    <t>SLTP/Sederajat</t>
+  </si>
+  <si>
+    <t>SLTA/Sederajat</t>
+  </si>
+  <si>
+    <t>Tamat SD/Sederajat</t>
   </si>
 </sst>
 </file>
@@ -2999,51 +3011,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3074,8 +3041,53 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3735,108 +3747,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="18.75">
-      <c r="A1" s="147"/>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
+      <c r="A1" s="149"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="18.75">
-      <c r="A2" s="147"/>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
+      <c r="A2" s="149"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="142" t="s">
+      <c r="A4" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="142" t="s">
+      <c r="B4" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="142" t="s">
+      <c r="C4" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="142" t="s">
+      <c r="E4" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="142" t="s">
+      <c r="F4" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="142" t="s">
+      <c r="G4" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="142" t="s">
+      <c r="H4" s="150" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="142" t="s">
+      <c r="I4" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="142" t="s">
+      <c r="J4" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="142" t="s">
+      <c r="K4" s="150" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="142" t="s">
+      <c r="L4" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="148" t="s">
+      <c r="M4" s="152" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="142" t="s">
+      <c r="N4" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="142" t="s">
+      <c r="O4" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="142" t="s">
+      <c r="P4" s="150" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="143"/>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="149"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
+      <c r="A5" s="151"/>
+      <c r="B5" s="151"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
+      <c r="L5" s="151"/>
+      <c r="M5" s="153"/>
+      <c r="N5" s="151"/>
+      <c r="O5" s="151"/>
+      <c r="P5" s="151"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="14" t="s">
@@ -3890,7 +3902,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1">
-      <c r="A7" s="135" t="s">
+      <c r="A7" s="145" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="23" t="s">
@@ -3933,7 +3945,7 @@
       <c r="N7" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O7" s="135" t="s">
+      <c r="O7" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P7" s="19" t="s">
@@ -3941,7 +3953,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1">
-      <c r="A8" s="136"/>
+      <c r="A8" s="146"/>
       <c r="B8" s="29"/>
       <c r="C8" s="30" t="s">
         <v>38</v>
@@ -3980,13 +3992,13 @@
       <c r="N8" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O8" s="136"/>
+      <c r="O8" s="146"/>
       <c r="P8" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1">
-      <c r="A9" s="136"/>
+      <c r="A9" s="146"/>
       <c r="B9" s="29"/>
       <c r="C9" s="30" t="s">
         <v>43</v>
@@ -4025,13 +4037,13 @@
       <c r="N9" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O9" s="136"/>
+      <c r="O9" s="146"/>
       <c r="P9" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1">
-      <c r="A10" s="136"/>
+      <c r="A10" s="146"/>
       <c r="B10" s="29"/>
       <c r="C10" s="30" t="s">
         <v>47</v>
@@ -4065,18 +4077,18 @@
         <v>27</v>
       </c>
       <c r="M10" s="29" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N10" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O10" s="136"/>
+      <c r="O10" s="146"/>
       <c r="P10" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1">
-      <c r="A11" s="137"/>
+      <c r="A11" s="147"/>
       <c r="B11" s="35"/>
       <c r="C11" s="36" t="s">
         <v>51</v>
@@ -4115,13 +4127,13 @@
       <c r="N11" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O11" s="137"/>
+      <c r="O11" s="147"/>
       <c r="P11" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1">
-      <c r="A12" s="135" t="s">
+      <c r="A12" s="145" t="s">
         <v>54</v>
       </c>
       <c r="B12" s="38" t="s">
@@ -4164,7 +4176,7 @@
       <c r="N12" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O12" s="135" t="s">
+      <c r="O12" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P12" s="46" t="s">
@@ -4172,7 +4184,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1">
-      <c r="A13" s="137"/>
+      <c r="A13" s="147"/>
       <c r="B13" s="35"/>
       <c r="C13" s="36" t="s">
         <v>56</v>
@@ -4211,7 +4223,7 @@
       <c r="N13" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O13" s="137"/>
+      <c r="O13" s="147"/>
       <c r="P13" s="46" t="s">
         <v>31</v>
       </c>
@@ -4239,7 +4251,7 @@
       <c r="P14" s="133"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1">
-      <c r="A15" s="135" t="s">
+      <c r="A15" s="145" t="s">
         <v>59</v>
       </c>
       <c r="B15" s="39" t="s">
@@ -4282,7 +4294,7 @@
       <c r="N15" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="O15" s="135" t="s">
+      <c r="O15" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P15" s="19" t="s">
@@ -4290,7 +4302,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1">
-      <c r="A16" s="136"/>
+      <c r="A16" s="146"/>
       <c r="B16" s="29"/>
       <c r="C16" s="29" t="s">
         <v>710</v>
@@ -4329,13 +4341,13 @@
       <c r="N16" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O16" s="136"/>
+      <c r="O16" s="146"/>
       <c r="P16" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1">
-      <c r="A17" s="136"/>
+      <c r="A17" s="146"/>
       <c r="B17" s="91"/>
       <c r="C17" s="91" t="s">
         <v>711</v>
@@ -4374,13 +4386,13 @@
       <c r="N17" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O17" s="136"/>
+      <c r="O17" s="146"/>
       <c r="P17" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1">
-      <c r="A18" s="136"/>
+      <c r="A18" s="146"/>
       <c r="B18" s="127"/>
       <c r="C18" s="127" t="s">
         <v>742</v>
@@ -4419,13 +4431,13 @@
       <c r="N18" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="O18" s="136"/>
+      <c r="O18" s="146"/>
       <c r="P18" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1">
-      <c r="A19" s="137"/>
+      <c r="A19" s="147"/>
       <c r="B19" s="26"/>
       <c r="C19" s="134" t="s">
         <v>743</v>
@@ -4464,13 +4476,13 @@
       <c r="N19" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O19" s="137"/>
+      <c r="O19" s="147"/>
       <c r="P19" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="145" t="s">
         <v>64</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -4513,7 +4525,7 @@
       <c r="N20" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O20" s="135" t="s">
+      <c r="O20" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P20" s="19" t="s">
@@ -4521,7 +4533,7 @@
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1">
-      <c r="A21" s="136"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
         <v>66</v>
@@ -4560,13 +4572,13 @@
       <c r="N21" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O21" s="136"/>
+      <c r="O21" s="146"/>
       <c r="P21" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1">
-      <c r="A22" s="136"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29" t="s">
         <v>67</v>
@@ -4605,13 +4617,13 @@
       <c r="N22" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O22" s="136"/>
+      <c r="O22" s="146"/>
       <c r="P22" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1">
-      <c r="A23" s="137"/>
+      <c r="A23" s="147"/>
       <c r="B23" s="35"/>
       <c r="C23" s="35" t="s">
         <v>69</v>
@@ -4645,18 +4657,18 @@
         <v>27</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N23" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O23" s="137"/>
+      <c r="O23" s="147"/>
       <c r="P23" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1">
-      <c r="A24" s="135" t="s">
+      <c r="A24" s="145" t="s">
         <v>70</v>
       </c>
       <c r="B24" s="38" t="s">
@@ -4699,7 +4711,7 @@
       <c r="N24" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O24" s="135" t="s">
+      <c r="O24" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P24" s="19" t="s">
@@ -4707,7 +4719,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1">
-      <c r="A25" s="136"/>
+      <c r="A25" s="146"/>
       <c r="B25" s="29"/>
       <c r="C25" s="29" t="s">
         <v>72</v>
@@ -4746,13 +4758,13 @@
       <c r="N25" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O25" s="136"/>
+      <c r="O25" s="146"/>
       <c r="P25" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1">
-      <c r="A26" s="136"/>
+      <c r="A26" s="146"/>
       <c r="B26" s="35"/>
       <c r="C26" s="35" t="s">
         <v>73</v>
@@ -4786,18 +4798,18 @@
         <v>27</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>49</v>
+        <v>764</v>
       </c>
       <c r="N26" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O26" s="136"/>
+      <c r="O26" s="146"/>
       <c r="P26" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1">
-      <c r="A27" s="137"/>
+      <c r="A27" s="147"/>
       <c r="B27" s="35"/>
       <c r="C27" s="35" t="s">
         <v>712</v>
@@ -4836,13 +4848,13 @@
       <c r="N27" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O27" s="137"/>
+      <c r="O27" s="147"/>
       <c r="P27" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1">
-      <c r="A28" s="135" t="s">
+      <c r="A28" s="145" t="s">
         <v>74</v>
       </c>
       <c r="B28" s="38" t="s">
@@ -4885,7 +4897,7 @@
       <c r="N28" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O28" s="135" t="s">
+      <c r="O28" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P28" s="19" t="s">
@@ -4893,7 +4905,7 @@
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1">
-      <c r="A29" s="136"/>
+      <c r="A29" s="146"/>
       <c r="B29" s="29"/>
       <c r="C29" s="29" t="s">
         <v>78</v>
@@ -4932,13 +4944,13 @@
       <c r="N29" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O29" s="136"/>
+      <c r="O29" s="146"/>
       <c r="P29" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1">
-      <c r="A30" s="136"/>
+      <c r="A30" s="146"/>
       <c r="B30" s="29"/>
       <c r="C30" s="29" t="s">
         <v>80</v>
@@ -4972,18 +4984,18 @@
         <v>27</v>
       </c>
       <c r="M30" s="29" t="s">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="N30" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O30" s="136"/>
+      <c r="O30" s="146"/>
       <c r="P30" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1">
-      <c r="A31" s="136"/>
+      <c r="A31" s="146"/>
       <c r="B31" s="29"/>
       <c r="C31" s="29" t="s">
         <v>81</v>
@@ -5016,19 +5028,19 @@
       <c r="L31" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M31" s="29" t="s">
-        <v>61</v>
+      <c r="M31" s="35" t="s">
+        <v>98</v>
       </c>
       <c r="N31" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O31" s="136"/>
+      <c r="O31" s="146"/>
       <c r="P31" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1">
-      <c r="A32" s="137"/>
+      <c r="A32" s="147"/>
       <c r="B32" s="35"/>
       <c r="C32" s="35" t="s">
         <v>82</v>
@@ -5062,18 +5074,18 @@
         <v>27</v>
       </c>
       <c r="M32" s="35" t="s">
-        <v>83</v>
+        <v>764</v>
       </c>
       <c r="N32" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O32" s="137"/>
+      <c r="O32" s="147"/>
       <c r="P32" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1">
-      <c r="A33" s="135" t="s">
+      <c r="A33" s="145" t="s">
         <v>84</v>
       </c>
       <c r="B33" s="38" t="s">
@@ -5116,7 +5128,7 @@
       <c r="N33" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O33" s="135" t="s">
+      <c r="O33" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P33" s="19" t="s">
@@ -5124,7 +5136,7 @@
       </c>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1">
-      <c r="A34" s="136"/>
+      <c r="A34" s="146"/>
       <c r="B34" s="29"/>
       <c r="C34" s="29" t="s">
         <v>88</v>
@@ -5163,13 +5175,13 @@
       <c r="N34" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O34" s="136"/>
+      <c r="O34" s="146"/>
       <c r="P34" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1">
-      <c r="A35" s="136"/>
+      <c r="A35" s="146"/>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
         <v>90</v>
@@ -5208,13 +5220,13 @@
       <c r="N35" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O35" s="136"/>
+      <c r="O35" s="146"/>
       <c r="P35" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1">
-      <c r="A36" s="136"/>
+      <c r="A36" s="146"/>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
         <v>92</v>
@@ -5248,18 +5260,18 @@
         <v>27</v>
       </c>
       <c r="M36" s="29" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N36" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O36" s="136"/>
+      <c r="O36" s="146"/>
       <c r="P36" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1">
-      <c r="A37" s="137"/>
+      <c r="A37" s="147"/>
       <c r="B37" s="35"/>
       <c r="C37" s="35" t="s">
         <v>94</v>
@@ -5292,19 +5304,19 @@
       <c r="L37" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M37" s="29" t="s">
-        <v>61</v>
+      <c r="M37" s="35" t="s">
+        <v>761</v>
       </c>
       <c r="N37" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O37" s="137"/>
+      <c r="O37" s="147"/>
       <c r="P37" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1">
-      <c r="A38" s="135" t="s">
+      <c r="A38" s="145" t="s">
         <v>95</v>
       </c>
       <c r="B38" s="38" t="s">
@@ -5347,7 +5359,7 @@
       <c r="N38" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="O38" s="135" t="s">
+      <c r="O38" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P38" s="46" t="s">
@@ -5355,7 +5367,7 @@
       </c>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1">
-      <c r="A39" s="136"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
         <v>705</v>
@@ -5394,13 +5406,13 @@
       <c r="N39" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O39" s="136"/>
+      <c r="O39" s="146"/>
       <c r="P39" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1">
-      <c r="A40" s="136"/>
+      <c r="A40" s="146"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
         <v>706</v>
@@ -5434,18 +5446,18 @@
         <v>27</v>
       </c>
       <c r="M40" s="29" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N40" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O40" s="136"/>
+      <c r="O40" s="146"/>
       <c r="P40" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1">
-      <c r="A41" s="135" t="s">
+      <c r="A41" s="145" t="s">
         <v>103</v>
       </c>
       <c r="B41" s="38" t="s">
@@ -5488,7 +5500,7 @@
       <c r="N41" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O41" s="135" t="s">
+      <c r="O41" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P41" s="19" t="s">
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1">
-      <c r="A42" s="136"/>
+      <c r="A42" s="146"/>
       <c r="B42" s="29"/>
       <c r="C42" s="29" t="s">
         <v>106</v>
@@ -5535,13 +5547,13 @@
       <c r="N42" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O42" s="136"/>
+      <c r="O42" s="146"/>
       <c r="P42" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1">
-      <c r="A43" s="136"/>
+      <c r="A43" s="146"/>
       <c r="B43" s="29"/>
       <c r="C43" s="29" t="s">
         <v>107</v>
@@ -5575,18 +5587,18 @@
         <v>27</v>
       </c>
       <c r="M43" s="29" t="s">
-        <v>61</v>
+        <v>721</v>
       </c>
       <c r="N43" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O43" s="136"/>
+      <c r="O43" s="146"/>
       <c r="P43" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1">
-      <c r="A44" s="137"/>
+      <c r="A44" s="147"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35" t="s">
         <v>108</v>
@@ -5625,13 +5637,13 @@
       <c r="N44" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O44" s="137"/>
+      <c r="O44" s="147"/>
       <c r="P44" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1">
-      <c r="A45" s="135" t="s">
+      <c r="A45" s="145" t="s">
         <v>109</v>
       </c>
       <c r="B45" s="38" t="s">
@@ -5674,7 +5686,7 @@
       <c r="N45" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O45" s="135" t="s">
+      <c r="O45" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P45" s="19" t="s">
@@ -5682,7 +5694,7 @@
       </c>
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1">
-      <c r="A46" s="136"/>
+      <c r="A46" s="146"/>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
         <v>113</v>
@@ -5721,13 +5733,13 @@
       <c r="N46" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O46" s="136"/>
+      <c r="O46" s="146"/>
       <c r="P46" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1">
-      <c r="A47" s="136"/>
+      <c r="A47" s="146"/>
       <c r="B47" s="29"/>
       <c r="C47" s="29" t="s">
         <v>114</v>
@@ -5761,18 +5773,18 @@
         <v>27</v>
       </c>
       <c r="M47" s="29" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N47" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O47" s="136"/>
+      <c r="O47" s="146"/>
       <c r="P47" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:16" s="2" customFormat="1">
-      <c r="A48" s="137"/>
+      <c r="A48" s="147"/>
       <c r="B48" s="35"/>
       <c r="C48" s="35" t="s">
         <v>115</v>
@@ -5806,18 +5818,18 @@
         <v>27</v>
       </c>
       <c r="M48" s="29" t="s">
-        <v>49</v>
+        <v>762</v>
       </c>
       <c r="N48" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O48" s="137"/>
+      <c r="O48" s="147"/>
       <c r="P48" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:16" s="2" customFormat="1">
-      <c r="A49" s="135" t="s">
+      <c r="A49" s="145" t="s">
         <v>116</v>
       </c>
       <c r="B49" s="38" t="s">
@@ -5860,7 +5872,7 @@
       <c r="N49" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O49" s="135" t="s">
+      <c r="O49" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P49" s="46" t="s">
@@ -5868,7 +5880,7 @@
       </c>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1">
-      <c r="A50" s="136"/>
+      <c r="A50" s="146"/>
       <c r="B50" s="29"/>
       <c r="C50" s="29" t="s">
         <v>118</v>
@@ -5907,13 +5919,13 @@
       <c r="N50" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O50" s="136"/>
+      <c r="O50" s="146"/>
       <c r="P50" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1">
-      <c r="A51" s="136"/>
+      <c r="A51" s="146"/>
       <c r="B51" s="29"/>
       <c r="C51" s="29" t="s">
         <v>120</v>
@@ -5952,13 +5964,13 @@
       <c r="N51" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O51" s="136"/>
+      <c r="O51" s="146"/>
       <c r="P51" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1">
-      <c r="A52" s="136"/>
+      <c r="A52" s="146"/>
       <c r="B52" s="29"/>
       <c r="C52" s="29" t="s">
         <v>121</v>
@@ -5997,13 +6009,13 @@
       <c r="N52" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O52" s="136"/>
+      <c r="O52" s="146"/>
       <c r="P52" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1">
-      <c r="A53" s="137"/>
+      <c r="A53" s="147"/>
       <c r="B53" s="35"/>
       <c r="C53" s="35" t="s">
         <v>122</v>
@@ -6042,13 +6054,13 @@
       <c r="N53" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O53" s="137"/>
+      <c r="O53" s="147"/>
       <c r="P53" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1">
-      <c r="A54" s="135" t="s">
+      <c r="A54" s="145" t="s">
         <v>123</v>
       </c>
       <c r="B54" s="38" t="s">
@@ -6091,7 +6103,7 @@
       <c r="N54" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O54" s="135" t="s">
+      <c r="O54" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P54" s="19" t="s">
@@ -6099,7 +6111,7 @@
       </c>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1">
-      <c r="A55" s="136"/>
+      <c r="A55" s="146"/>
       <c r="B55" s="29"/>
       <c r="C55" s="29" t="s">
         <v>127</v>
@@ -6138,13 +6150,13 @@
       <c r="N55" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O55" s="136"/>
+      <c r="O55" s="146"/>
       <c r="P55" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1">
-      <c r="A56" s="136"/>
+      <c r="A56" s="146"/>
       <c r="B56" s="29"/>
       <c r="C56" s="29" t="s">
         <v>129</v>
@@ -6183,13 +6195,13 @@
       <c r="N56" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O56" s="136"/>
+      <c r="O56" s="146"/>
       <c r="P56" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1">
-      <c r="A57" s="137"/>
+      <c r="A57" s="147"/>
       <c r="B57" s="35"/>
       <c r="C57" s="35" t="s">
         <v>130</v>
@@ -6223,18 +6235,18 @@
         <v>27</v>
       </c>
       <c r="M57" s="29" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N57" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O57" s="137"/>
+      <c r="O57" s="147"/>
       <c r="P57" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="158" t="s">
         <v>131</v>
       </c>
       <c r="B58" s="38" t="s">
@@ -6277,7 +6289,7 @@
       <c r="N58" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O58" s="135" t="s">
+      <c r="O58" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P58" s="19" t="s">
@@ -6285,7 +6297,7 @@
       </c>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1">
-      <c r="A59" s="145"/>
+      <c r="A59" s="159"/>
       <c r="B59" s="29"/>
       <c r="C59" s="29" t="s">
         <v>134</v>
@@ -6324,13 +6336,13 @@
       <c r="N59" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O59" s="136"/>
+      <c r="O59" s="146"/>
       <c r="P59" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1">
-      <c r="A60" s="145"/>
+      <c r="A60" s="159"/>
       <c r="B60" s="29"/>
       <c r="C60" s="29" t="s">
         <v>135</v>
@@ -6369,13 +6381,13 @@
       <c r="N60" s="91" t="s">
         <v>731</v>
       </c>
-      <c r="O60" s="136"/>
+      <c r="O60" s="146"/>
       <c r="P60" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1">
-      <c r="A61" s="145"/>
+      <c r="A61" s="159"/>
       <c r="B61" s="29"/>
       <c r="C61" s="29" t="s">
         <v>136</v>
@@ -6414,13 +6426,13 @@
       <c r="N61" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O61" s="136"/>
+      <c r="O61" s="146"/>
       <c r="P61" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1">
-      <c r="A62" s="146"/>
+      <c r="A62" s="160"/>
       <c r="B62" s="35"/>
       <c r="C62" s="35" t="s">
         <v>137</v>
@@ -6459,13 +6471,13 @@
       <c r="N62" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O62" s="137"/>
+      <c r="O62" s="147"/>
       <c r="P62" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1">
-      <c r="A63" s="135" t="s">
+      <c r="A63" s="145" t="s">
         <v>138</v>
       </c>
       <c r="B63" s="38" t="s">
@@ -6508,7 +6520,7 @@
       <c r="N63" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O63" s="135" t="s">
+      <c r="O63" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P63" s="46" t="s">
@@ -6516,7 +6528,7 @@
       </c>
     </row>
     <row r="64" spans="1:16" s="2" customFormat="1">
-      <c r="A64" s="136"/>
+      <c r="A64" s="146"/>
       <c r="B64" s="29"/>
       <c r="C64" s="29" t="s">
         <v>140</v>
@@ -6555,13 +6567,13 @@
       <c r="N64" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O64" s="136"/>
+      <c r="O64" s="146"/>
       <c r="P64" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1">
-      <c r="A65" s="136"/>
+      <c r="A65" s="146"/>
       <c r="B65" s="29"/>
       <c r="C65" s="29" t="s">
         <v>141</v>
@@ -6600,13 +6612,13 @@
       <c r="N65" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O65" s="136"/>
+      <c r="O65" s="146"/>
       <c r="P65" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:16" s="2" customFormat="1">
-      <c r="A66" s="136"/>
+      <c r="A66" s="146"/>
       <c r="B66" s="29"/>
       <c r="C66" s="29" t="s">
         <v>142</v>
@@ -6640,18 +6652,18 @@
         <v>27</v>
       </c>
       <c r="M66" s="29" t="s">
-        <v>91</v>
+        <v>763</v>
       </c>
       <c r="N66" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O66" s="136"/>
+      <c r="O66" s="146"/>
       <c r="P66" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1">
-      <c r="A67" s="137"/>
+      <c r="A67" s="147"/>
       <c r="B67" s="35"/>
       <c r="C67" s="35" t="s">
         <v>143</v>
@@ -6685,18 +6697,18 @@
         <v>27</v>
       </c>
       <c r="M67" s="35" t="s">
-        <v>61</v>
+        <v>761</v>
       </c>
       <c r="N67" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O67" s="137"/>
+      <c r="O67" s="147"/>
       <c r="P67" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:16" s="2" customFormat="1">
-      <c r="A68" s="144" t="s">
+      <c r="A68" s="158" t="s">
         <v>144</v>
       </c>
       <c r="B68" s="38" t="s">
@@ -6739,7 +6751,7 @@
       <c r="N68" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O68" s="135" t="s">
+      <c r="O68" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P68" s="19" t="s">
@@ -6747,7 +6759,7 @@
       </c>
     </row>
     <row r="69" spans="1:16" s="2" customFormat="1">
-      <c r="A69" s="145"/>
+      <c r="A69" s="159"/>
       <c r="B69" s="29"/>
       <c r="C69" s="29" t="s">
         <v>146</v>
@@ -6786,13 +6798,13 @@
       <c r="N69" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O69" s="136"/>
+      <c r="O69" s="146"/>
       <c r="P69" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="70" spans="1:16" s="2" customFormat="1">
-      <c r="A70" s="145"/>
+      <c r="A70" s="159"/>
       <c r="B70" s="29"/>
       <c r="C70" s="29" t="s">
         <v>147</v>
@@ -6831,13 +6843,13 @@
       <c r="N70" s="91" t="s">
         <v>731</v>
       </c>
-      <c r="O70" s="136"/>
+      <c r="O70" s="146"/>
       <c r="P70" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:16" s="2" customFormat="1">
-      <c r="A71" s="146"/>
+      <c r="A71" s="160"/>
       <c r="B71" s="35"/>
       <c r="C71" s="35" t="s">
         <v>148</v>
@@ -6871,18 +6883,18 @@
         <v>27</v>
       </c>
       <c r="M71" s="29" t="s">
-        <v>49</v>
+        <v>762</v>
       </c>
       <c r="N71" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O71" s="137"/>
+      <c r="O71" s="147"/>
       <c r="P71" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:16" s="2" customFormat="1">
-      <c r="A72" s="144" t="s">
+      <c r="A72" s="158" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="38" t="s">
@@ -6925,7 +6937,7 @@
       <c r="N72" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O72" s="135" t="s">
+      <c r="O72" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P72" s="19" t="s">
@@ -6933,7 +6945,7 @@
       </c>
     </row>
     <row r="73" spans="1:16" s="2" customFormat="1">
-      <c r="A73" s="145"/>
+      <c r="A73" s="159"/>
       <c r="B73" s="29"/>
       <c r="C73" s="29" t="s">
         <v>151</v>
@@ -6972,13 +6984,13 @@
       <c r="N73" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O73" s="136"/>
+      <c r="O73" s="146"/>
       <c r="P73" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:16" s="2" customFormat="1">
-      <c r="A74" s="145"/>
+      <c r="A74" s="159"/>
       <c r="B74" s="29"/>
       <c r="C74" s="29" t="s">
         <v>152</v>
@@ -7011,19 +7023,19 @@
       <c r="L74" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M74" s="29" t="s">
-        <v>49</v>
+      <c r="M74" s="35" t="s">
+        <v>764</v>
       </c>
       <c r="N74" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O74" s="136"/>
+      <c r="O74" s="146"/>
       <c r="P74" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:16" s="2" customFormat="1">
-      <c r="A75" s="146"/>
+      <c r="A75" s="160"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35" t="s">
         <v>153</v>
@@ -7056,19 +7068,19 @@
       <c r="L75" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M75" s="35" t="s">
-        <v>61</v>
+      <c r="M75" s="29" t="s">
+        <v>721</v>
       </c>
       <c r="N75" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O75" s="137"/>
+      <c r="O75" s="147"/>
       <c r="P75" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:16" s="2" customFormat="1">
-      <c r="A76" s="140" t="s">
+      <c r="A76" s="155" t="s">
         <v>154</v>
       </c>
       <c r="B76" s="93" t="s">
@@ -7111,7 +7123,7 @@
       <c r="N76" s="25" t="s">
         <v>739</v>
       </c>
-      <c r="O76" s="140" t="s">
+      <c r="O76" s="155" t="s">
         <v>30</v>
       </c>
       <c r="P76" s="46" t="s">
@@ -7119,7 +7131,7 @@
       </c>
     </row>
     <row r="77" spans="1:16" s="2" customFormat="1">
-      <c r="A77" s="139"/>
+      <c r="A77" s="157"/>
       <c r="B77" s="94"/>
       <c r="C77" s="95" t="s">
         <v>694</v>
@@ -7158,13 +7170,13 @@
       <c r="N77" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O77" s="139"/>
+      <c r="O77" s="157"/>
       <c r="P77" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:16" s="2" customFormat="1">
-      <c r="A78" s="135" t="s">
+      <c r="A78" s="145" t="s">
         <v>156</v>
       </c>
       <c r="B78" s="38" t="s">
@@ -7207,7 +7219,7 @@
       <c r="N78" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O78" s="135" t="s">
+      <c r="O78" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P78" s="19" t="s">
@@ -7215,7 +7227,7 @@
       </c>
     </row>
     <row r="79" spans="1:16" s="2" customFormat="1">
-      <c r="A79" s="136"/>
+      <c r="A79" s="146"/>
       <c r="B79" s="29"/>
       <c r="C79" s="29" t="s">
         <v>159</v>
@@ -7254,13 +7266,13 @@
       <c r="N79" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O79" s="136"/>
+      <c r="O79" s="146"/>
       <c r="P79" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:16" s="2" customFormat="1">
-      <c r="A80" s="136"/>
+      <c r="A80" s="146"/>
       <c r="B80" s="29"/>
       <c r="C80" s="29" t="s">
         <v>161</v>
@@ -7299,13 +7311,13 @@
       <c r="N80" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O80" s="136"/>
+      <c r="O80" s="146"/>
       <c r="P80" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:16" s="2" customFormat="1">
-      <c r="A81" s="137"/>
+      <c r="A81" s="147"/>
       <c r="B81" s="35"/>
       <c r="C81" s="35" t="s">
         <v>163</v>
@@ -7344,13 +7356,13 @@
       <c r="N81" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="O81" s="137"/>
+      <c r="O81" s="147"/>
       <c r="P81" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:16" s="2" customFormat="1">
-      <c r="A82" s="144" t="s">
+      <c r="A82" s="158" t="s">
         <v>164</v>
       </c>
       <c r="B82" s="38" t="s">
@@ -7393,7 +7405,7 @@
       <c r="N82" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O82" s="135" t="s">
+      <c r="O82" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P82" s="19" t="s">
@@ -7401,7 +7413,7 @@
       </c>
     </row>
     <row r="83" spans="1:16" s="2" customFormat="1">
-      <c r="A83" s="145"/>
+      <c r="A83" s="159"/>
       <c r="B83" s="29"/>
       <c r="C83" s="29" t="s">
         <v>166</v>
@@ -7440,13 +7452,13 @@
       <c r="N83" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O83" s="136"/>
+      <c r="O83" s="146"/>
       <c r="P83" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:16" s="2" customFormat="1">
-      <c r="A84" s="145"/>
+      <c r="A84" s="159"/>
       <c r="B84" s="29"/>
       <c r="C84" s="29" t="s">
         <v>168</v>
@@ -7485,13 +7497,13 @@
       <c r="N84" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O84" s="136"/>
+      <c r="O84" s="146"/>
       <c r="P84" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="2" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A85" s="146"/>
+      <c r="A85" s="160"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35" t="s">
         <v>169</v>
@@ -7525,18 +7537,18 @@
         <v>27</v>
       </c>
       <c r="M85" s="35" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="N85" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O85" s="137"/>
+      <c r="O85" s="147"/>
       <c r="P85" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="86" spans="1:16" s="2" customFormat="1">
-      <c r="A86" s="135" t="s">
+      <c r="A86" s="145" t="s">
         <v>170</v>
       </c>
       <c r="B86" s="38" t="s">
@@ -7579,7 +7591,7 @@
       <c r="N86" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O86" s="135" t="s">
+      <c r="O86" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P86" s="19" t="s">
@@ -7587,7 +7599,7 @@
       </c>
     </row>
     <row r="87" spans="1:16" s="2" customFormat="1">
-      <c r="A87" s="136"/>
+      <c r="A87" s="146"/>
       <c r="B87" s="29"/>
       <c r="C87" s="29" t="s">
         <v>281</v>
@@ -7626,13 +7638,13 @@
       <c r="N87" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O87" s="136"/>
+      <c r="O87" s="146"/>
       <c r="P87" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="88" spans="1:16" s="2" customFormat="1">
-      <c r="A88" s="136"/>
+      <c r="A88" s="146"/>
       <c r="B88" s="29"/>
       <c r="C88" s="29" t="s">
         <v>283</v>
@@ -7666,18 +7678,18 @@
         <v>27</v>
       </c>
       <c r="M88" s="29" t="s">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="N88" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O88" s="136"/>
+      <c r="O88" s="146"/>
       <c r="P88" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:16" s="2" customFormat="1">
-      <c r="A89" s="136"/>
+      <c r="A89" s="146"/>
       <c r="B89" s="29"/>
       <c r="C89" s="29" t="s">
         <v>284</v>
@@ -7711,18 +7723,18 @@
         <v>27</v>
       </c>
       <c r="M89" s="29" t="s">
-        <v>61</v>
+        <v>721</v>
       </c>
       <c r="N89" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O89" s="136"/>
+      <c r="O89" s="146"/>
       <c r="P89" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:16" s="2" customFormat="1">
-      <c r="A90" s="137"/>
+      <c r="A90" s="147"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
         <v>285</v>
@@ -7761,13 +7773,13 @@
       <c r="N90" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O90" s="137"/>
+      <c r="O90" s="147"/>
       <c r="P90" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="91" spans="1:16" s="2" customFormat="1">
-      <c r="A91" s="135" t="s">
+      <c r="A91" s="145" t="s">
         <v>171</v>
       </c>
       <c r="B91" s="38" t="s">
@@ -7810,7 +7822,7 @@
       <c r="N91" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O91" s="135" t="s">
+      <c r="O91" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P91" s="46" t="s">
@@ -7818,7 +7830,7 @@
       </c>
     </row>
     <row r="92" spans="1:16" s="2" customFormat="1">
-      <c r="A92" s="136"/>
+      <c r="A92" s="146"/>
       <c r="B92" s="29"/>
       <c r="C92" s="29" t="s">
         <v>708</v>
@@ -7857,13 +7869,13 @@
       <c r="N92" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O92" s="136"/>
+      <c r="O92" s="146"/>
       <c r="P92" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="93" spans="1:16" s="2" customFormat="1">
-      <c r="A93" s="136"/>
+      <c r="A93" s="146"/>
       <c r="B93" s="91"/>
       <c r="C93" s="91" t="s">
         <v>709</v>
@@ -7902,13 +7914,13 @@
       <c r="N93" s="91" t="s">
         <v>731</v>
       </c>
-      <c r="O93" s="136"/>
+      <c r="O93" s="146"/>
       <c r="P93" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="94" spans="1:16" s="2" customFormat="1">
-      <c r="A94" s="135" t="s">
+      <c r="A94" s="145" t="s">
         <v>176</v>
       </c>
       <c r="B94" s="38" t="s">
@@ -7951,7 +7963,7 @@
       <c r="N94" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O94" s="135" t="s">
+      <c r="O94" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P94" s="19" t="s">
@@ -7959,7 +7971,7 @@
       </c>
     </row>
     <row r="95" spans="1:16" s="2" customFormat="1">
-      <c r="A95" s="136"/>
+      <c r="A95" s="146"/>
       <c r="B95" s="29"/>
       <c r="C95" s="29" t="s">
         <v>178</v>
@@ -7998,13 +8010,13 @@
       <c r="N95" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O95" s="136"/>
+      <c r="O95" s="146"/>
       <c r="P95" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:16" s="2" customFormat="1">
-      <c r="A96" s="136"/>
+      <c r="A96" s="146"/>
       <c r="B96" s="29"/>
       <c r="C96" s="29" t="s">
         <v>179</v>
@@ -8043,13 +8055,13 @@
       <c r="N96" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O96" s="136"/>
+      <c r="O96" s="146"/>
       <c r="P96" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="97" spans="1:16" s="2" customFormat="1">
-      <c r="A97" s="137"/>
+      <c r="A97" s="147"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
         <v>180</v>
@@ -8082,19 +8094,19 @@
       <c r="L97" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M97" s="35" t="s">
-        <v>61</v>
+      <c r="M97" s="29" t="s">
+        <v>721</v>
       </c>
       <c r="N97" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O97" s="137"/>
+      <c r="O97" s="147"/>
       <c r="P97" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:16" s="2" customFormat="1">
-      <c r="A98" s="141" t="s">
+      <c r="A98" s="154" t="s">
         <v>181</v>
       </c>
       <c r="B98" s="38" t="s">
@@ -8137,7 +8149,7 @@
       <c r="N98" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="O98" s="135" t="s">
+      <c r="O98" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P98" s="19" t="s">
@@ -8145,7 +8157,7 @@
       </c>
     </row>
     <row r="99" spans="1:16" s="2" customFormat="1">
-      <c r="A99" s="141"/>
+      <c r="A99" s="154"/>
       <c r="B99" s="29"/>
       <c r="C99" s="29" t="s">
         <v>183</v>
@@ -8184,13 +8196,13 @@
       <c r="N99" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O99" s="136"/>
+      <c r="O99" s="146"/>
       <c r="P99" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="100" spans="1:16" s="2" customFormat="1">
-      <c r="A100" s="141"/>
+      <c r="A100" s="154"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
         <v>184</v>
@@ -8229,13 +8241,13 @@
       <c r="N100" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="O100" s="136"/>
+      <c r="O100" s="146"/>
       <c r="P100" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A101" s="140" t="s">
+      <c r="A101" s="155" t="s">
         <v>185</v>
       </c>
       <c r="B101" s="99" t="s">
@@ -8278,7 +8290,7 @@
       <c r="N101" s="32" t="s">
         <v>737</v>
       </c>
-      <c r="O101" s="138" t="s">
+      <c r="O101" s="156" t="s">
         <v>36</v>
       </c>
       <c r="P101" s="19" t="s">
@@ -8286,7 +8298,7 @@
       </c>
     </row>
     <row r="102" spans="1:16" s="2" customFormat="1">
-      <c r="A102" s="138"/>
+      <c r="A102" s="156"/>
       <c r="B102" s="99"/>
       <c r="C102" s="32" t="s">
         <v>188</v>
@@ -8325,13 +8337,13 @@
       <c r="N102" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O102" s="138"/>
+      <c r="O102" s="156"/>
       <c r="P102" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="103" spans="1:16" s="2" customFormat="1">
-      <c r="A103" s="138"/>
+      <c r="A103" s="156"/>
       <c r="B103" s="99"/>
       <c r="C103" s="32" t="s">
         <v>190</v>
@@ -8370,13 +8382,13 @@
       <c r="N103" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O103" s="138"/>
+      <c r="O103" s="156"/>
       <c r="P103" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="104" spans="1:16" s="2" customFormat="1">
-      <c r="A104" s="138"/>
+      <c r="A104" s="156"/>
       <c r="B104" s="99"/>
       <c r="C104" s="32" t="s">
         <v>191</v>
@@ -8415,13 +8427,13 @@
       <c r="N104" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O104" s="138"/>
+      <c r="O104" s="156"/>
       <c r="P104" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="105" spans="1:16" s="2" customFormat="1">
-      <c r="A105" s="138"/>
+      <c r="A105" s="156"/>
       <c r="B105" s="99"/>
       <c r="C105" s="32" t="s">
         <v>192</v>
@@ -8455,18 +8467,18 @@
         <v>27</v>
       </c>
       <c r="M105" s="29" t="s">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="N105" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O105" s="138"/>
+      <c r="O105" s="156"/>
       <c r="P105" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="106" spans="1:16" s="84" customFormat="1">
-      <c r="A106" s="139"/>
+      <c r="A106" s="157"/>
       <c r="B106" s="101"/>
       <c r="C106" s="102" t="s">
         <v>193</v>
@@ -8499,19 +8511,19 @@
       <c r="L106" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M106" s="29" t="s">
-        <v>61</v>
+      <c r="M106" s="35" t="s">
+        <v>98</v>
       </c>
       <c r="N106" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O106" s="139"/>
+      <c r="O106" s="157"/>
       <c r="P106" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="107" spans="1:16" s="2" customFormat="1">
-      <c r="A107" s="135" t="s">
+      <c r="A107" s="145" t="s">
         <v>194</v>
       </c>
       <c r="B107" s="38" t="s">
@@ -8554,7 +8566,7 @@
       <c r="N107" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O107" s="135" t="s">
+      <c r="O107" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P107" s="19" t="s">
@@ -8562,7 +8574,7 @@
       </c>
     </row>
     <row r="108" spans="1:16" s="2" customFormat="1">
-      <c r="A108" s="136"/>
+      <c r="A108" s="146"/>
       <c r="B108" s="29"/>
       <c r="C108" s="29" t="s">
         <v>196</v>
@@ -8601,13 +8613,13 @@
       <c r="N108" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O108" s="136"/>
+      <c r="O108" s="146"/>
       <c r="P108" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:16" s="2" customFormat="1">
-      <c r="A109" s="136"/>
+      <c r="A109" s="146"/>
       <c r="B109" s="29"/>
       <c r="C109" s="29" t="s">
         <v>197</v>
@@ -8646,13 +8658,13 @@
       <c r="N109" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O109" s="136"/>
+      <c r="O109" s="146"/>
       <c r="P109" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="110" spans="1:16" s="2" customFormat="1">
-      <c r="A110" s="136"/>
+      <c r="A110" s="146"/>
       <c r="B110" s="29"/>
       <c r="C110" s="29" t="s">
         <v>198</v>
@@ -8686,18 +8698,18 @@
         <v>27</v>
       </c>
       <c r="M110" s="29" t="s">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="N110" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O110" s="136"/>
+      <c r="O110" s="146"/>
       <c r="P110" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="111" spans="1:16" s="2" customFormat="1">
-      <c r="A111" s="136"/>
+      <c r="A111" s="146"/>
       <c r="B111" s="29"/>
       <c r="C111" s="29" t="s">
         <v>199</v>
@@ -8731,18 +8743,18 @@
         <v>27</v>
       </c>
       <c r="M111" s="29" t="s">
-        <v>61</v>
+        <v>721</v>
       </c>
       <c r="N111" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O111" s="136"/>
+      <c r="O111" s="146"/>
       <c r="P111" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="112" spans="1:16" s="2" customFormat="1">
-      <c r="A112" s="137"/>
+      <c r="A112" s="147"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
         <v>200</v>
@@ -8776,18 +8788,18 @@
         <v>27</v>
       </c>
       <c r="M112" s="35" t="s">
-        <v>83</v>
+        <v>764</v>
       </c>
       <c r="N112" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O112" s="137"/>
+      <c r="O112" s="147"/>
       <c r="P112" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="113" spans="1:16" s="2" customFormat="1">
-      <c r="A113" s="135" t="s">
+      <c r="A113" s="145" t="s">
         <v>201</v>
       </c>
       <c r="B113" s="39" t="s">
@@ -8830,7 +8842,7 @@
       <c r="N113" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O113" s="135" t="s">
+      <c r="O113" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P113" s="19" t="s">
@@ -8838,7 +8850,7 @@
       </c>
     </row>
     <row r="114" spans="1:16" s="2" customFormat="1">
-      <c r="A114" s="136"/>
+      <c r="A114" s="146"/>
       <c r="B114" s="29"/>
       <c r="C114" s="30" t="s">
         <v>205</v>
@@ -8877,13 +8889,13 @@
       <c r="N114" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O114" s="136"/>
+      <c r="O114" s="146"/>
       <c r="P114" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="115" spans="1:16" s="2" customFormat="1">
-      <c r="A115" s="136"/>
+      <c r="A115" s="146"/>
       <c r="B115" s="29"/>
       <c r="C115" s="30" t="s">
         <v>206</v>
@@ -8916,19 +8928,19 @@
       <c r="L115" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="M115" s="29" t="s">
-        <v>49</v>
+      <c r="M115" s="35" t="s">
+        <v>764</v>
       </c>
       <c r="N115" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O115" s="136"/>
+      <c r="O115" s="146"/>
       <c r="P115" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="116" spans="1:16" s="2" customFormat="1">
-      <c r="A116" s="137"/>
+      <c r="A116" s="147"/>
       <c r="B116" s="35"/>
       <c r="C116" s="36" t="s">
         <v>207</v>
@@ -8961,19 +8973,19 @@
       <c r="L116" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M116" s="29" t="s">
-        <v>61</v>
+      <c r="M116" s="35" t="s">
+        <v>761</v>
       </c>
       <c r="N116" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O116" s="137"/>
+      <c r="O116" s="147"/>
       <c r="P116" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="117" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A117" s="140" t="s">
+      <c r="A117" s="155" t="s">
         <v>208</v>
       </c>
       <c r="B117" s="99" t="s">
@@ -9016,7 +9028,7 @@
       <c r="N117" s="32" t="s">
         <v>738</v>
       </c>
-      <c r="O117" s="135" t="s">
+      <c r="O117" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P117" s="46" t="s">
@@ -9024,7 +9036,7 @@
       </c>
     </row>
     <row r="118" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A118" s="138"/>
+      <c r="A118" s="156"/>
       <c r="B118" s="99"/>
       <c r="C118" s="32" t="s">
         <v>210</v>
@@ -9063,13 +9075,13 @@
       <c r="N118" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O118" s="136"/>
+      <c r="O118" s="146"/>
       <c r="P118" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A119" s="138"/>
+      <c r="A119" s="156"/>
       <c r="B119" s="99"/>
       <c r="C119" s="32" t="s">
         <v>211</v>
@@ -9102,19 +9114,19 @@
       <c r="L119" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M119" s="29" t="s">
-        <v>49</v>
+      <c r="M119" s="35" t="s">
+        <v>764</v>
       </c>
       <c r="N119" s="32" t="s">
         <v>741</v>
       </c>
-      <c r="O119" s="136"/>
+      <c r="O119" s="146"/>
       <c r="P119" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="120" spans="1:16" s="84" customFormat="1">
-      <c r="A120" s="139"/>
+      <c r="A120" s="157"/>
       <c r="B120" s="101"/>
       <c r="C120" s="102" t="s">
         <v>212</v>
@@ -9153,13 +9165,13 @@
       <c r="N120" s="102" t="s">
         <v>731</v>
       </c>
-      <c r="O120" s="137"/>
+      <c r="O120" s="147"/>
       <c r="P120" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="121" spans="1:16" s="2" customFormat="1">
-      <c r="A121" s="135" t="s">
+      <c r="A121" s="145" t="s">
         <v>213</v>
       </c>
       <c r="B121" s="38" t="s">
@@ -9202,7 +9214,7 @@
       <c r="N121" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O121" s="135" t="s">
+      <c r="O121" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P121" s="19" t="s">
@@ -9210,7 +9222,7 @@
       </c>
     </row>
     <row r="122" spans="1:16" s="2" customFormat="1">
-      <c r="A122" s="136"/>
+      <c r="A122" s="146"/>
       <c r="B122" s="29"/>
       <c r="C122" s="30" t="s">
         <v>216</v>
@@ -9249,13 +9261,13 @@
       <c r="N122" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O122" s="136"/>
+      <c r="O122" s="146"/>
       <c r="P122" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:16" s="2" customFormat="1">
-      <c r="A123" s="137"/>
+      <c r="A123" s="147"/>
       <c r="B123" s="35"/>
       <c r="C123" s="36" t="s">
         <v>218</v>
@@ -9289,18 +9301,18 @@
         <v>27</v>
       </c>
       <c r="M123" s="35" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N123" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O123" s="137"/>
+      <c r="O123" s="147"/>
       <c r="P123" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="124" spans="1:16" s="2" customFormat="1">
-      <c r="A124" s="135" t="s">
+      <c r="A124" s="145" t="s">
         <v>219</v>
       </c>
       <c r="B124" s="38" t="s">
@@ -9343,7 +9355,7 @@
       <c r="N124" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O124" s="135" t="s">
+      <c r="O124" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P124" s="19" t="s">
@@ -9351,7 +9363,7 @@
       </c>
     </row>
     <row r="125" spans="1:16" s="2" customFormat="1">
-      <c r="A125" s="136"/>
+      <c r="A125" s="146"/>
       <c r="B125" s="29"/>
       <c r="C125" s="29" t="s">
         <v>222</v>
@@ -9390,13 +9402,13 @@
       <c r="N125" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O125" s="136"/>
+      <c r="O125" s="146"/>
       <c r="P125" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="126" spans="1:16" s="2" customFormat="1">
-      <c r="A126" s="137"/>
+      <c r="A126" s="147"/>
       <c r="B126" s="35"/>
       <c r="C126" s="35" t="s">
         <v>223</v>
@@ -9429,19 +9441,19 @@
       <c r="L126" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M126" s="35" t="s">
-        <v>61</v>
+      <c r="M126" s="29" t="s">
+        <v>721</v>
       </c>
       <c r="N126" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O126" s="137"/>
+      <c r="O126" s="147"/>
       <c r="P126" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="127" spans="1:16" s="2" customFormat="1">
-      <c r="A127" s="135" t="s">
+      <c r="A127" s="145" t="s">
         <v>496</v>
       </c>
       <c r="B127" s="127" t="s">
@@ -9484,7 +9496,7 @@
       <c r="N127" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O127" s="135" t="s">
+      <c r="O127" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P127" s="19" t="s">
@@ -9492,7 +9504,7 @@
       </c>
     </row>
     <row r="128" spans="1:16" s="2" customFormat="1">
-      <c r="A128" s="136"/>
+      <c r="A128" s="146"/>
       <c r="B128" s="26"/>
       <c r="C128" s="26" t="s">
         <v>525</v>
@@ -9525,19 +9537,19 @@
       <c r="L128" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="M128" s="29" t="s">
-        <v>49</v>
+      <c r="M128" s="35" t="s">
+        <v>764</v>
       </c>
       <c r="N128" s="32" t="s">
         <v>741</v>
       </c>
-      <c r="O128" s="136"/>
+      <c r="O128" s="146"/>
       <c r="P128" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:16" s="2" customFormat="1">
-      <c r="A129" s="137"/>
+      <c r="A129" s="147"/>
       <c r="B129" s="26"/>
       <c r="C129" s="26" t="s">
         <v>527</v>
@@ -9570,13 +9582,13 @@
       <c r="L129" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="M129" s="91" t="s">
-        <v>61</v>
+      <c r="M129" s="35" t="s">
+        <v>761</v>
       </c>
       <c r="N129" s="32" t="s">
         <v>741</v>
       </c>
-      <c r="O129" s="137"/>
+      <c r="O129" s="147"/>
       <c r="P129" s="19" t="s">
         <v>37</v>
       </c>
@@ -9604,7 +9616,7 @@
       <c r="P130" s="68"/>
     </row>
     <row r="131" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A131" s="140" t="s">
+      <c r="A131" s="155" t="s">
         <v>224</v>
       </c>
       <c r="B131" s="39" t="s">
@@ -9647,7 +9659,7 @@
       <c r="N131" s="20" t="s">
         <v>740</v>
       </c>
-      <c r="O131" s="135" t="s">
+      <c r="O131" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P131" s="19" t="s">
@@ -9655,7 +9667,7 @@
       </c>
     </row>
     <row r="132" spans="1:16" s="84" customFormat="1">
-      <c r="A132" s="139"/>
+      <c r="A132" s="157"/>
       <c r="B132" s="101"/>
       <c r="C132" s="102" t="s">
         <v>227</v>
@@ -9694,13 +9706,13 @@
       <c r="N132" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="O132" s="137"/>
+      <c r="O132" s="147"/>
       <c r="P132" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="133" spans="1:16" s="2" customFormat="1">
-      <c r="A133" s="135" t="s">
+      <c r="A133" s="145" t="s">
         <v>228</v>
       </c>
       <c r="B133" s="128" t="s">
@@ -9743,7 +9755,7 @@
       <c r="N133" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="O133" s="135" t="s">
+      <c r="O133" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P133" s="19" t="s">
@@ -9751,7 +9763,7 @@
       </c>
     </row>
     <row r="134" spans="1:16" s="2" customFormat="1">
-      <c r="A134" s="136"/>
+      <c r="A134" s="146"/>
       <c r="B134" s="29"/>
       <c r="C134" s="30" t="s">
         <v>733</v>
@@ -9790,13 +9802,13 @@
       <c r="N134" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O134" s="136"/>
+      <c r="O134" s="146"/>
       <c r="P134" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="135" spans="1:16" s="2" customFormat="1">
-      <c r="A135" s="136"/>
+      <c r="A135" s="146"/>
       <c r="B135" s="91"/>
       <c r="C135" s="36" t="s">
         <v>734</v>
@@ -9835,13 +9847,13 @@
       <c r="N135" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O135" s="136"/>
+      <c r="O135" s="146"/>
       <c r="P135" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="136" spans="1:16" s="2" customFormat="1">
-      <c r="A136" s="136"/>
+      <c r="A136" s="146"/>
       <c r="B136" s="91"/>
       <c r="C136" s="36" t="s">
         <v>735</v>
@@ -9874,19 +9886,19 @@
       <c r="L136" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="M136" s="29" t="s">
-        <v>49</v>
+      <c r="M136" s="35" t="s">
+        <v>764</v>
       </c>
       <c r="N136" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O136" s="136"/>
+      <c r="O136" s="146"/>
       <c r="P136" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="137" spans="1:16" s="2" customFormat="1">
-      <c r="A137" s="137"/>
+      <c r="A137" s="147"/>
       <c r="B137" s="35"/>
       <c r="C137" s="36" t="s">
         <v>736</v>
@@ -9925,7 +9937,7 @@
       <c r="N137" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O137" s="137"/>
+      <c r="O137" s="147"/>
       <c r="P137" s="19" t="s">
         <v>37</v>
       </c>
@@ -9934,10 +9946,10 @@
       <c r="A138" s="120" t="s">
         <v>518</v>
       </c>
-      <c r="B138" s="150" t="s">
+      <c r="B138" s="135" t="s">
         <v>756</v>
       </c>
-      <c r="C138" s="150" t="s">
+      <c r="C138" s="135" t="s">
         <v>756</v>
       </c>
       <c r="D138" s="123" t="s">
@@ -9946,13 +9958,13 @@
       <c r="E138" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F138" s="151" t="s">
+      <c r="F138" s="136" t="s">
         <v>101</v>
       </c>
-      <c r="G138" s="158">
+      <c r="G138" s="143">
         <v>39103</v>
       </c>
-      <c r="H138" s="159">
+      <c r="H138" s="144">
         <f t="shared" ca="1" si="3"/>
         <v>19</v>
       </c>
@@ -9982,13 +9994,13 @@
       </c>
     </row>
     <row r="139" spans="1:16" s="2" customFormat="1">
-      <c r="A139" s="160" t="s">
+      <c r="A139" s="148" t="s">
         <v>528</v>
       </c>
-      <c r="B139" s="152" t="s">
+      <c r="B139" s="137" t="s">
         <v>752</v>
       </c>
-      <c r="C139" s="155" t="s">
+      <c r="C139" s="140" t="s">
         <v>752</v>
       </c>
       <c r="D139" s="121" t="s">
@@ -9997,10 +10009,10 @@
       <c r="E139" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F139" s="151" t="s">
+      <c r="F139" s="136" t="s">
         <v>215</v>
       </c>
-      <c r="G139" s="158">
+      <c r="G139" s="143">
         <v>36197</v>
       </c>
       <c r="H139" s="58">
@@ -10025,7 +10037,7 @@
       <c r="N139" s="126" t="s">
         <v>737</v>
       </c>
-      <c r="O139" s="135" t="s">
+      <c r="O139" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P139" s="46" t="s">
@@ -10033,9 +10045,9 @@
       </c>
     </row>
     <row r="140" spans="1:16" s="2" customFormat="1">
-      <c r="A140" s="160"/>
-      <c r="B140" s="153"/>
-      <c r="C140" s="156" t="s">
+      <c r="A140" s="148"/>
+      <c r="B140" s="138"/>
+      <c r="C140" s="141" t="s">
         <v>753</v>
       </c>
       <c r="D140" s="122" t="s">
@@ -10044,10 +10056,10 @@
       <c r="E140" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F140" s="151" t="s">
+      <c r="F140" s="136" t="s">
         <v>215</v>
       </c>
-      <c r="G140" s="158">
+      <c r="G140" s="143">
         <v>36708</v>
       </c>
       <c r="H140" s="58">
@@ -10072,15 +10084,15 @@
       <c r="N140" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O140" s="136"/>
+      <c r="O140" s="146"/>
       <c r="P140" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:16" s="2" customFormat="1">
-      <c r="A141" s="160"/>
-      <c r="B141" s="154"/>
-      <c r="C141" s="157" t="s">
+      <c r="A141" s="148"/>
+      <c r="B141" s="139"/>
+      <c r="C141" s="142" t="s">
         <v>754</v>
       </c>
       <c r="D141" s="97" t="s">
@@ -10089,10 +10101,10 @@
       <c r="E141" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="151" t="s">
+      <c r="F141" s="136" t="s">
         <v>755</v>
       </c>
-      <c r="G141" s="158">
+      <c r="G141" s="143">
         <v>45621</v>
       </c>
       <c r="H141" s="58">
@@ -10117,7 +10129,7 @@
       <c r="N141" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O141" s="137"/>
+      <c r="O141" s="147"/>
       <c r="P141" s="46" t="s">
         <v>31</v>
       </c>
@@ -10166,7 +10178,7 @@
       <c r="N142" s="20" t="s">
         <v>740</v>
       </c>
-      <c r="O142" s="136" t="s">
+      <c r="O142" s="146" t="s">
         <v>36</v>
       </c>
       <c r="P142" s="19" t="s">
@@ -10213,7 +10225,7 @@
       <c r="N143" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O143" s="136"/>
+      <c r="O143" s="146"/>
       <c r="P143" s="19" t="s">
         <v>37</v>
       </c>
@@ -10258,7 +10270,7 @@
       <c r="N144" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O144" s="136"/>
+      <c r="O144" s="146"/>
       <c r="P144" s="19" t="s">
         <v>37</v>
       </c>
@@ -10303,7 +10315,7 @@
       <c r="N145" s="126" t="s">
         <v>737</v>
       </c>
-      <c r="O145" s="136"/>
+      <c r="O145" s="146"/>
       <c r="P145" s="19" t="s">
         <v>37</v>
       </c>
@@ -10348,7 +10360,7 @@
       <c r="N146" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O146" s="136"/>
+      <c r="O146" s="146"/>
       <c r="P146" s="19" t="s">
         <v>37</v>
       </c>
@@ -10393,7 +10405,7 @@
       <c r="N147" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O147" s="136"/>
+      <c r="O147" s="146"/>
       <c r="P147" s="19" t="s">
         <v>37</v>
       </c>
@@ -10433,18 +10445,18 @@
         <v>27</v>
       </c>
       <c r="M148" s="29" t="s">
-        <v>49</v>
+        <v>762</v>
       </c>
       <c r="N148" s="126" t="s">
         <v>741</v>
       </c>
-      <c r="O148" s="137"/>
+      <c r="O148" s="147"/>
       <c r="P148" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="149" spans="1:16" s="2" customFormat="1">
-      <c r="A149" s="135" t="s">
+      <c r="A149" s="145" t="s">
         <v>233</v>
       </c>
       <c r="B149" s="38" t="s">
@@ -10487,7 +10499,7 @@
       <c r="N149" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O149" s="135" t="s">
+      <c r="O149" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P149" s="19" t="s">
@@ -10495,7 +10507,7 @@
       </c>
     </row>
     <row r="150" spans="1:16" s="2" customFormat="1">
-      <c r="A150" s="136"/>
+      <c r="A150" s="146"/>
       <c r="B150" s="29"/>
       <c r="C150" s="29" t="s">
         <v>235</v>
@@ -10534,13 +10546,13 @@
       <c r="N150" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O150" s="136"/>
+      <c r="O150" s="146"/>
       <c r="P150" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="151" spans="1:16" s="2" customFormat="1">
-      <c r="A151" s="137"/>
+      <c r="A151" s="147"/>
       <c r="B151" s="35"/>
       <c r="C151" s="35" t="s">
         <v>237</v>
@@ -10574,12 +10586,12 @@
         <v>27</v>
       </c>
       <c r="M151" s="35" t="s">
-        <v>91</v>
+        <v>763</v>
       </c>
       <c r="N151" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O151" s="136"/>
+      <c r="O151" s="146"/>
       <c r="P151" s="19" t="s">
         <v>37</v>
       </c>
@@ -10625,7 +10637,7 @@
       <c r="P152" s="68"/>
     </row>
     <row r="153" spans="1:16" s="2" customFormat="1">
-      <c r="A153" s="135" t="s">
+      <c r="A153" s="145" t="s">
         <v>239</v>
       </c>
       <c r="B153" s="38" t="s">
@@ -10668,7 +10680,7 @@
       <c r="N153" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O153" s="135" t="s">
+      <c r="O153" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P153" s="19" t="s">
@@ -10676,7 +10688,7 @@
       </c>
     </row>
     <row r="154" spans="1:16" s="2" customFormat="1">
-      <c r="A154" s="136"/>
+      <c r="A154" s="146"/>
       <c r="B154" s="29"/>
       <c r="C154" s="29" t="s">
         <v>241</v>
@@ -10715,13 +10727,13 @@
       <c r="N154" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O154" s="136"/>
+      <c r="O154" s="146"/>
       <c r="P154" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="155" spans="1:16" s="2" customFormat="1">
-      <c r="A155" s="136"/>
+      <c r="A155" s="146"/>
       <c r="B155" s="29"/>
       <c r="C155" s="29" t="s">
         <v>242</v>
@@ -10755,18 +10767,18 @@
         <v>27</v>
       </c>
       <c r="M155" s="29" t="s">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="N155" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O155" s="136"/>
+      <c r="O155" s="146"/>
       <c r="P155" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="156" spans="1:16" s="2" customFormat="1">
-      <c r="A156" s="136"/>
+      <c r="A156" s="146"/>
       <c r="B156" s="35"/>
       <c r="C156" s="35" t="s">
         <v>243</v>
@@ -10799,19 +10811,19 @@
       <c r="L156" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M156" s="35" t="s">
-        <v>61</v>
+      <c r="M156" s="29" t="s">
+        <v>721</v>
       </c>
       <c r="N156" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O156" s="136"/>
+      <c r="O156" s="146"/>
       <c r="P156" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="157" spans="1:16" s="2" customFormat="1">
-      <c r="A157" s="136"/>
+      <c r="A157" s="146"/>
       <c r="B157" s="26"/>
       <c r="C157" s="38" t="s">
         <v>229</v>
@@ -10850,13 +10862,13 @@
       <c r="N157" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="O157" s="136"/>
+      <c r="O157" s="146"/>
       <c r="P157" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="158" spans="1:16" s="2" customFormat="1">
-      <c r="A158" s="136"/>
+      <c r="A158" s="146"/>
       <c r="B158" s="26"/>
       <c r="C158" s="30" t="s">
         <v>230</v>
@@ -10895,13 +10907,13 @@
       <c r="N158" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O158" s="136"/>
+      <c r="O158" s="146"/>
       <c r="P158" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="159" spans="1:16" s="2" customFormat="1">
-      <c r="A159" s="136"/>
+      <c r="A159" s="146"/>
       <c r="B159" s="26"/>
       <c r="C159" s="36" t="s">
         <v>231</v>
@@ -10935,13 +10947,13 @@
       <c r="N159" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O159" s="136"/>
+      <c r="O159" s="146"/>
       <c r="P159" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="160" spans="1:16" s="2" customFormat="1">
-      <c r="A160" s="137"/>
+      <c r="A160" s="147"/>
       <c r="B160" s="26"/>
       <c r="C160" s="36" t="s">
         <v>232</v>
@@ -10980,13 +10992,13 @@
       <c r="N160" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O160" s="137"/>
+      <c r="O160" s="147"/>
       <c r="P160" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="161" spans="1:16" s="2" customFormat="1">
-      <c r="A161" s="135" t="s">
+      <c r="A161" s="145" t="s">
         <v>244</v>
       </c>
       <c r="B161" s="39" t="s">
@@ -11029,7 +11041,7 @@
       <c r="N161" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O161" s="135" t="s">
+      <c r="O161" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P161" s="19" t="s">
@@ -11037,7 +11049,7 @@
       </c>
     </row>
     <row r="162" spans="1:16" s="2" customFormat="1">
-      <c r="A162" s="136"/>
+      <c r="A162" s="146"/>
       <c r="B162" s="29"/>
       <c r="C162" s="30" t="s">
         <v>246</v>
@@ -11076,13 +11088,13 @@
       <c r="N162" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O162" s="136"/>
+      <c r="O162" s="146"/>
       <c r="P162" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="163" spans="1:16" s="2" customFormat="1">
-      <c r="A163" s="136"/>
+      <c r="A163" s="146"/>
       <c r="B163" s="29"/>
       <c r="C163" s="30" t="s">
         <v>247</v>
@@ -11121,13 +11133,13 @@
       <c r="N163" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O163" s="136"/>
+      <c r="O163" s="146"/>
       <c r="P163" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="164" spans="1:16" s="2" customFormat="1">
-      <c r="A164" s="137"/>
+      <c r="A164" s="147"/>
       <c r="B164" s="35"/>
       <c r="C164" s="36" t="s">
         <v>249</v>
@@ -11166,13 +11178,13 @@
       <c r="N164" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O164" s="137"/>
+      <c r="O164" s="147"/>
       <c r="P164" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="165" spans="1:16" s="2" customFormat="1">
-      <c r="A165" s="135" t="s">
+      <c r="A165" s="145" t="s">
         <v>251</v>
       </c>
       <c r="B165" s="39" t="s">
@@ -11215,7 +11227,7 @@
       <c r="N165" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O165" s="141" t="s">
+      <c r="O165" s="154" t="s">
         <v>36</v>
       </c>
       <c r="P165" s="19" t="s">
@@ -11223,7 +11235,7 @@
       </c>
     </row>
     <row r="166" spans="1:16" s="2" customFormat="1">
-      <c r="A166" s="136"/>
+      <c r="A166" s="146"/>
       <c r="B166" s="29"/>
       <c r="C166" s="30" t="s">
         <v>715</v>
@@ -11262,13 +11274,13 @@
       <c r="N166" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O166" s="141"/>
+      <c r="O166" s="154"/>
       <c r="P166" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="167" spans="1:16" s="2" customFormat="1">
-      <c r="A167" s="137"/>
+      <c r="A167" s="147"/>
       <c r="B167" s="35"/>
       <c r="C167" s="36" t="s">
         <v>716</v>
@@ -11307,13 +11319,13 @@
       <c r="N167" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O167" s="141"/>
+      <c r="O167" s="154"/>
       <c r="P167" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="168" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A168" s="140" t="s">
+      <c r="A168" s="155" t="s">
         <v>252</v>
       </c>
       <c r="B168" s="99" t="s">
@@ -11356,7 +11368,7 @@
       <c r="N168" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O168" s="135" t="s">
+      <c r="O168" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P168" s="19" t="s">
@@ -11364,7 +11376,7 @@
       </c>
     </row>
     <row r="169" spans="1:16" s="2" customFormat="1">
-      <c r="A169" s="138"/>
+      <c r="A169" s="156"/>
       <c r="B169" s="32"/>
       <c r="C169" s="106" t="s">
         <v>698</v>
@@ -11403,13 +11415,13 @@
       <c r="N169" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O169" s="137"/>
+      <c r="O169" s="147"/>
       <c r="P169" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="170" spans="1:16" s="2" customFormat="1">
-      <c r="A170" s="135" t="s">
+      <c r="A170" s="145" t="s">
         <v>257</v>
       </c>
       <c r="B170" s="39" t="s">
@@ -11452,7 +11464,7 @@
       <c r="N170" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O170" s="135" t="s">
+      <c r="O170" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P170" s="19" t="s">
@@ -11460,7 +11472,7 @@
       </c>
     </row>
     <row r="171" spans="1:16" s="2" customFormat="1">
-      <c r="A171" s="136"/>
+      <c r="A171" s="146"/>
       <c r="B171" s="29"/>
       <c r="C171" s="30" t="s">
         <v>261</v>
@@ -11499,13 +11511,13 @@
       <c r="N171" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O171" s="136"/>
+      <c r="O171" s="146"/>
       <c r="P171" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="172" spans="1:16" s="2" customFormat="1">
-      <c r="A172" s="136"/>
+      <c r="A172" s="146"/>
       <c r="B172" s="29"/>
       <c r="C172" s="30" t="s">
         <v>262</v>
@@ -11544,13 +11556,13 @@
       <c r="N172" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O172" s="136"/>
+      <c r="O172" s="146"/>
       <c r="P172" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="173" spans="1:16" s="2" customFormat="1">
-      <c r="A173" s="137"/>
+      <c r="A173" s="147"/>
       <c r="B173" s="35"/>
       <c r="C173" s="36" t="s">
         <v>263</v>
@@ -11584,18 +11596,18 @@
         <v>27</v>
       </c>
       <c r="M173" s="35" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="N173" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O173" s="136"/>
+      <c r="O173" s="146"/>
       <c r="P173" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="174" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A174" s="140" t="s">
+      <c r="A174" s="155" t="s">
         <v>264</v>
       </c>
       <c r="B174" s="99" t="s">
@@ -11638,7 +11650,7 @@
       <c r="N174" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="O174" s="136" t="s">
+      <c r="O174" s="146" t="s">
         <v>30</v>
       </c>
       <c r="P174" s="19" t="s">
@@ -11646,7 +11658,7 @@
       </c>
     </row>
     <row r="175" spans="1:16" s="2" customFormat="1">
-      <c r="A175" s="138"/>
+      <c r="A175" s="156"/>
       <c r="B175" s="32"/>
       <c r="C175" s="106" t="s">
         <v>254</v>
@@ -11685,13 +11697,13 @@
       <c r="N175" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O175" s="136"/>
+      <c r="O175" s="146"/>
       <c r="P175" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="176" spans="1:16" s="2" customFormat="1">
-      <c r="A176" s="138"/>
+      <c r="A176" s="156"/>
       <c r="B176" s="32"/>
       <c r="C176" s="106" t="s">
         <v>255</v>
@@ -11730,13 +11742,13 @@
       <c r="N176" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O176" s="136"/>
+      <c r="O176" s="146"/>
       <c r="P176" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="177" spans="1:16" s="84" customFormat="1">
-      <c r="A177" s="139"/>
+      <c r="A177" s="157"/>
       <c r="B177" s="101"/>
       <c r="C177" s="102" t="s">
         <v>256</v>
@@ -11769,19 +11781,19 @@
       <c r="L177" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="M177" s="35" t="s">
-        <v>61</v>
+      <c r="M177" s="29" t="s">
+        <v>721</v>
       </c>
       <c r="N177" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O177" s="137"/>
+      <c r="O177" s="147"/>
       <c r="P177" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="178" spans="1:16" s="84" customFormat="1" ht="15" customHeight="1">
-      <c r="A178" s="140" t="s">
+      <c r="A178" s="155" t="s">
         <v>265</v>
       </c>
       <c r="B178" s="93" t="s">
@@ -11824,7 +11836,7 @@
       <c r="N178" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O178" s="140" t="s">
+      <c r="O178" s="155" t="s">
         <v>30</v>
       </c>
       <c r="P178" s="19" t="s">
@@ -11832,7 +11844,7 @@
       </c>
     </row>
     <row r="179" spans="1:16" s="84" customFormat="1">
-      <c r="A179" s="138"/>
+      <c r="A179" s="156"/>
       <c r="B179" s="101"/>
       <c r="C179" s="102" t="s">
         <v>758</v>
@@ -11871,13 +11883,13 @@
       <c r="N179" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O179" s="138"/>
+      <c r="O179" s="156"/>
       <c r="P179" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="180" spans="1:16" s="84" customFormat="1">
-      <c r="A180" s="138"/>
+      <c r="A180" s="156"/>
       <c r="B180" s="101"/>
       <c r="C180" s="102" t="s">
         <v>759</v>
@@ -11916,13 +11928,13 @@
       <c r="N180" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O180" s="138"/>
+      <c r="O180" s="156"/>
       <c r="P180" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="181" spans="1:16" s="84" customFormat="1">
-      <c r="A181" s="138"/>
+      <c r="A181" s="156"/>
       <c r="B181" s="101"/>
       <c r="C181" s="102" t="s">
         <v>760</v>
@@ -11956,18 +11968,18 @@
         <v>27</v>
       </c>
       <c r="M181" s="29" t="s">
-        <v>91</v>
+        <v>762</v>
       </c>
       <c r="N181" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O181" s="139"/>
+      <c r="O181" s="157"/>
       <c r="P181" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="182" spans="1:16" s="2" customFormat="1">
-      <c r="A182" s="135" t="s">
+      <c r="A182" s="145" t="s">
         <v>266</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -12010,7 +12022,7 @@
       <c r="N182" s="19" t="s">
         <v>738</v>
       </c>
-      <c r="O182" s="135" t="s">
+      <c r="O182" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P182" s="19" t="s">
@@ -12018,7 +12030,7 @@
       </c>
     </row>
     <row r="183" spans="1:16" s="2" customFormat="1">
-      <c r="A183" s="136"/>
+      <c r="A183" s="146"/>
       <c r="B183" s="29"/>
       <c r="C183" s="29" t="s">
         <v>269</v>
@@ -12057,13 +12069,13 @@
       <c r="N183" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="O183" s="136"/>
+      <c r="O183" s="146"/>
       <c r="P183" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="184" spans="1:16" s="2" customFormat="1">
-      <c r="A184" s="136"/>
+      <c r="A184" s="146"/>
       <c r="B184" s="29"/>
       <c r="C184" s="29" t="s">
         <v>270</v>
@@ -12097,18 +12109,18 @@
         <v>27</v>
       </c>
       <c r="M184" s="29" t="s">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="N184" s="19" t="s">
         <v>741</v>
       </c>
-      <c r="O184" s="136"/>
+      <c r="O184" s="146"/>
       <c r="P184" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="185" spans="1:16" s="2" customFormat="1">
-      <c r="A185" s="137"/>
+      <c r="A185" s="147"/>
       <c r="B185" s="35"/>
       <c r="C185" s="35" t="s">
         <v>272</v>
@@ -12142,18 +12154,18 @@
         <v>27</v>
       </c>
       <c r="M185" s="35" t="s">
-        <v>83</v>
+        <v>764</v>
       </c>
       <c r="N185" s="19" t="s">
         <v>741</v>
       </c>
-      <c r="O185" s="137"/>
+      <c r="O185" s="147"/>
       <c r="P185" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="186" spans="1:16" s="2" customFormat="1">
-      <c r="A186" s="135" t="s">
+      <c r="A186" s="145" t="s">
         <v>273</v>
       </c>
       <c r="B186" s="38" t="s">
@@ -12196,7 +12208,7 @@
       <c r="N186" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O186" s="135" t="s">
+      <c r="O186" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P186" s="19" t="s">
@@ -12204,7 +12216,7 @@
       </c>
     </row>
     <row r="187" spans="1:16" s="2" customFormat="1">
-      <c r="A187" s="136"/>
+      <c r="A187" s="146"/>
       <c r="B187" s="29"/>
       <c r="C187" s="29" t="s">
         <v>275</v>
@@ -12243,13 +12255,13 @@
       <c r="N187" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O187" s="136"/>
+      <c r="O187" s="146"/>
       <c r="P187" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="188" spans="1:16" s="2" customFormat="1">
-      <c r="A188" s="136"/>
+      <c r="A188" s="146"/>
       <c r="B188" s="29"/>
       <c r="C188" s="29" t="s">
         <v>276</v>
@@ -12283,18 +12295,18 @@
         <v>27</v>
       </c>
       <c r="M188" s="29" t="s">
-        <v>91</v>
+        <v>763</v>
       </c>
       <c r="N188" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O188" s="136"/>
+      <c r="O188" s="146"/>
       <c r="P188" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="189" spans="1:16" s="2" customFormat="1">
-      <c r="A189" s="136"/>
+      <c r="A189" s="146"/>
       <c r="B189" s="29"/>
       <c r="C189" s="29" t="s">
         <v>277</v>
@@ -12328,18 +12340,18 @@
         <v>27</v>
       </c>
       <c r="M189" s="29" t="s">
-        <v>49</v>
+        <v>763</v>
       </c>
       <c r="N189" s="29" t="s">
-        <v>741</v>
-      </c>
-      <c r="O189" s="136"/>
+        <v>738</v>
+      </c>
+      <c r="O189" s="146"/>
       <c r="P189" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="190" spans="1:16" s="2" customFormat="1">
-      <c r="A190" s="137"/>
+      <c r="A190" s="147"/>
       <c r="B190" s="35"/>
       <c r="C190" s="35" t="s">
         <v>278</v>
@@ -12373,12 +12385,12 @@
         <v>27</v>
       </c>
       <c r="M190" s="35" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="N190" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O190" s="137"/>
+      <c r="O190" s="147"/>
       <c r="P190" s="19" t="s">
         <v>37</v>
       </c>
@@ -12428,7 +12440,7 @@
       <c r="P192" s="133"/>
     </row>
     <row r="193" spans="1:16" s="2" customFormat="1">
-      <c r="A193" s="135" t="s">
+      <c r="A193" s="145" t="s">
         <v>605</v>
       </c>
       <c r="B193" s="38" t="s">
@@ -12471,7 +12483,7 @@
       <c r="N193" s="19" t="s">
         <v>738</v>
       </c>
-      <c r="O193" s="135" t="s">
+      <c r="O193" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P193" s="46" t="s">
@@ -12479,7 +12491,7 @@
       </c>
     </row>
     <row r="194" spans="1:16" s="2" customFormat="1">
-      <c r="A194" s="136"/>
+      <c r="A194" s="146"/>
       <c r="B194" s="29"/>
       <c r="C194" s="29" t="s">
         <v>703</v>
@@ -12518,13 +12530,13 @@
       <c r="N194" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="O194" s="136"/>
+      <c r="O194" s="146"/>
       <c r="P194" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="195" spans="1:16" s="2" customFormat="1">
-      <c r="A195" s="135" t="s">
+      <c r="A195" s="145" t="s">
         <v>288</v>
       </c>
       <c r="B195" s="38" t="s">
@@ -12567,7 +12579,7 @@
       <c r="N195" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O195" s="135" t="s">
+      <c r="O195" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P195" s="19" t="s">
@@ -12575,7 +12587,7 @@
       </c>
     </row>
     <row r="196" spans="1:16" s="2" customFormat="1">
-      <c r="A196" s="136"/>
+      <c r="A196" s="146"/>
       <c r="B196" s="29"/>
       <c r="C196" s="29" t="s">
         <v>291</v>
@@ -12614,13 +12626,13 @@
       <c r="N196" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O196" s="136"/>
+      <c r="O196" s="146"/>
       <c r="P196" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="197" spans="1:16" s="2" customFormat="1">
-      <c r="A197" s="136"/>
+      <c r="A197" s="146"/>
       <c r="B197" s="29"/>
       <c r="C197" s="29" t="s">
         <v>293</v>
@@ -12659,13 +12671,13 @@
       <c r="N197" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O197" s="136"/>
+      <c r="O197" s="146"/>
       <c r="P197" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="198" spans="1:16" s="2" customFormat="1">
-      <c r="A198" s="137"/>
+      <c r="A198" s="147"/>
       <c r="B198" s="35"/>
       <c r="C198" s="35" t="s">
         <v>294</v>
@@ -12704,7 +12716,7 @@
       <c r="N198" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="O198" s="137"/>
+      <c r="O198" s="147"/>
       <c r="P198" s="19" t="s">
         <v>37</v>
       </c>
@@ -12753,7 +12765,7 @@
       <c r="N199" s="26" t="s">
         <v>740</v>
       </c>
-      <c r="O199" s="135" t="s">
+      <c r="O199" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P199" s="19" t="s">
@@ -12800,7 +12812,7 @@
       <c r="N200" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O200" s="136"/>
+      <c r="O200" s="146"/>
       <c r="P200" s="19" t="s">
         <v>37</v>
       </c>
@@ -12845,7 +12857,7 @@
       <c r="N201" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O201" s="136"/>
+      <c r="O201" s="146"/>
       <c r="P201" s="19" t="s">
         <v>37</v>
       </c>
@@ -12890,13 +12902,13 @@
       <c r="N202" s="26" t="s">
         <v>741</v>
       </c>
-      <c r="O202" s="137"/>
+      <c r="O202" s="147"/>
       <c r="P202" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="203" spans="1:16" s="2" customFormat="1">
-      <c r="A203" s="135" t="s">
+      <c r="A203" s="145" t="s">
         <v>295</v>
       </c>
       <c r="B203" s="38" t="s">
@@ -12939,7 +12951,7 @@
       <c r="N203" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O203" s="135" t="s">
+      <c r="O203" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P203" s="46" t="s">
@@ -12947,7 +12959,7 @@
       </c>
     </row>
     <row r="204" spans="1:16" s="2" customFormat="1">
-      <c r="A204" s="136"/>
+      <c r="A204" s="146"/>
       <c r="B204" s="29"/>
       <c r="C204" s="29" t="s">
         <v>724</v>
@@ -12986,13 +12998,13 @@
       <c r="N204" s="29" t="s">
         <v>726</v>
       </c>
-      <c r="O204" s="136"/>
+      <c r="O204" s="146"/>
       <c r="P204" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="205" spans="1:16" s="2" customFormat="1">
-      <c r="A205" s="135" t="s">
+      <c r="A205" s="145" t="s">
         <v>301</v>
       </c>
       <c r="B205" s="38" t="s">
@@ -13035,7 +13047,7 @@
       <c r="N205" s="25" t="s">
         <v>739</v>
       </c>
-      <c r="O205" s="135" t="s">
+      <c r="O205" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P205" s="19" t="s">
@@ -13043,7 +13055,7 @@
       </c>
     </row>
     <row r="206" spans="1:16" s="2" customFormat="1">
-      <c r="A206" s="136"/>
+      <c r="A206" s="146"/>
       <c r="B206" s="29"/>
       <c r="C206" s="29" t="s">
         <v>303</v>
@@ -13082,13 +13094,13 @@
       <c r="N206" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O206" s="136"/>
+      <c r="O206" s="146"/>
       <c r="P206" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="207" spans="1:16" s="2" customFormat="1">
-      <c r="A207" s="137"/>
+      <c r="A207" s="147"/>
       <c r="B207" s="35"/>
       <c r="C207" s="35" t="s">
         <v>304</v>
@@ -13127,7 +13139,7 @@
       <c r="N207" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O207" s="137"/>
+      <c r="O207" s="147"/>
       <c r="P207" s="19" t="s">
         <v>37</v>
       </c>
@@ -13182,7 +13194,7 @@
       </c>
     </row>
     <row r="209" spans="1:16" s="2" customFormat="1">
-      <c r="A209" s="135" t="s">
+      <c r="A209" s="145" t="s">
         <v>306</v>
       </c>
       <c r="B209" s="39" t="s">
@@ -13225,7 +13237,7 @@
       <c r="N209" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="O209" s="135" t="s">
+      <c r="O209" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P209" s="46" t="s">
@@ -13233,7 +13245,7 @@
       </c>
     </row>
     <row r="210" spans="1:16" s="2" customFormat="1">
-      <c r="A210" s="136"/>
+      <c r="A210" s="146"/>
       <c r="B210" s="29"/>
       <c r="C210" s="30" t="s">
         <v>309</v>
@@ -13272,13 +13284,13 @@
       <c r="N210" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="O210" s="136"/>
+      <c r="O210" s="146"/>
       <c r="P210" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="211" spans="1:16" s="2" customFormat="1">
-      <c r="A211" s="136"/>
+      <c r="A211" s="146"/>
       <c r="B211" s="29"/>
       <c r="C211" s="30" t="s">
         <v>311</v>
@@ -13312,18 +13324,18 @@
         <v>27</v>
       </c>
       <c r="M211" s="35" t="s">
-        <v>61</v>
+        <v>761</v>
       </c>
       <c r="N211" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O211" s="136"/>
+      <c r="O211" s="146"/>
       <c r="P211" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="212" spans="1:16" s="2" customFormat="1">
-      <c r="A212" s="136"/>
+      <c r="A212" s="146"/>
       <c r="B212" s="29"/>
       <c r="C212" s="30" t="s">
         <v>312</v>
@@ -13357,18 +13369,18 @@
         <v>27</v>
       </c>
       <c r="M212" s="35" t="s">
-        <v>61</v>
+        <v>761</v>
       </c>
       <c r="N212" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O212" s="136"/>
+      <c r="O212" s="146"/>
       <c r="P212" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="213" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A213" s="140" t="s">
+      <c r="A213" s="155" t="s">
         <v>313</v>
       </c>
       <c r="B213" s="39" t="s">
@@ -13411,7 +13423,7 @@
       <c r="N213" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="O213" s="135" t="s">
+      <c r="O213" s="145" t="s">
         <v>30</v>
       </c>
       <c r="P213" s="19" t="s">
@@ -13419,7 +13431,7 @@
       </c>
     </row>
     <row r="214" spans="1:16" s="2" customFormat="1">
-      <c r="A214" s="138"/>
+      <c r="A214" s="156"/>
       <c r="B214" s="29"/>
       <c r="C214" s="30" t="s">
         <v>315</v>
@@ -13458,13 +13470,13 @@
       <c r="N214" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O214" s="136"/>
+      <c r="O214" s="146"/>
       <c r="P214" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="215" spans="1:16" s="2" customFormat="1">
-      <c r="A215" s="138"/>
+      <c r="A215" s="156"/>
       <c r="B215" s="29"/>
       <c r="C215" s="30" t="s">
         <v>316</v>
@@ -13503,13 +13515,13 @@
       <c r="N215" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O215" s="136"/>
+      <c r="O215" s="146"/>
       <c r="P215" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="216" spans="1:16" s="2" customFormat="1">
-      <c r="A216" s="139"/>
+      <c r="A216" s="157"/>
       <c r="B216" s="35"/>
       <c r="C216" s="36" t="s">
         <v>318</v>
@@ -13543,16 +13555,16 @@
         <v>27</v>
       </c>
       <c r="M216" s="35" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="N216" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O216" s="137"/>
+      <c r="O216" s="147"/>
       <c r="P216" s="19"/>
     </row>
     <row r="217" spans="1:16" s="2" customFormat="1">
-      <c r="A217" s="135" t="s">
+      <c r="A217" s="145" t="s">
         <v>319</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -13595,7 +13607,7 @@
       <c r="N217" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O217" s="135" t="s">
+      <c r="O217" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P217" s="19" t="s">
@@ -13603,7 +13615,7 @@
       </c>
     </row>
     <row r="218" spans="1:16" s="2" customFormat="1">
-      <c r="A218" s="136"/>
+      <c r="A218" s="146"/>
       <c r="B218" s="29"/>
       <c r="C218" s="29" t="s">
         <v>322</v>
@@ -13642,13 +13654,13 @@
       <c r="N218" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="O218" s="136"/>
+      <c r="O218" s="146"/>
       <c r="P218" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="219" spans="1:16" s="2" customFormat="1">
-      <c r="A219" s="136"/>
+      <c r="A219" s="146"/>
       <c r="B219" s="29"/>
       <c r="C219" s="29" t="s">
         <v>324</v>
@@ -13687,13 +13699,13 @@
       <c r="N219" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O219" s="136"/>
+      <c r="O219" s="146"/>
       <c r="P219" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="220" spans="1:16" s="2" customFormat="1">
-      <c r="A220" s="137"/>
+      <c r="A220" s="147"/>
       <c r="B220" s="35"/>
       <c r="C220" s="36" t="s">
         <v>325</v>
@@ -13732,13 +13744,13 @@
       <c r="N220" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O220" s="137"/>
+      <c r="O220" s="147"/>
       <c r="P220" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="221" spans="1:16" s="2" customFormat="1">
-      <c r="A221" s="135" t="s">
+      <c r="A221" s="145" t="s">
         <v>326</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -13781,7 +13793,7 @@
       <c r="N221" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O221" s="135" t="s">
+      <c r="O221" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P221" s="46" t="s">
@@ -13789,7 +13801,7 @@
       </c>
     </row>
     <row r="222" spans="1:16" s="2" customFormat="1">
-      <c r="A222" s="136"/>
+      <c r="A222" s="146"/>
       <c r="B222" s="29"/>
       <c r="C222" s="30" t="s">
         <v>328</v>
@@ -13828,13 +13840,13 @@
       <c r="N222" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O222" s="136"/>
+      <c r="O222" s="146"/>
       <c r="P222" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="223" spans="1:16" s="2" customFormat="1">
-      <c r="A223" s="136"/>
+      <c r="A223" s="146"/>
       <c r="B223" s="29"/>
       <c r="C223" s="30" t="s">
         <v>699</v>
@@ -13873,13 +13885,13 @@
       <c r="N223" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O223" s="136"/>
+      <c r="O223" s="146"/>
       <c r="P223" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="224" spans="1:16" s="2" customFormat="1">
-      <c r="A224" s="136"/>
+      <c r="A224" s="146"/>
       <c r="B224" s="29"/>
       <c r="C224" s="30" t="s">
         <v>700</v>
@@ -13918,7 +13930,7 @@
       <c r="N224" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O224" s="136"/>
+      <c r="O224" s="146"/>
       <c r="P224" s="46" t="s">
         <v>31</v>
       </c>
@@ -13948,7 +13960,7 @@
       </c>
     </row>
     <row r="226" spans="1:253" s="2" customFormat="1">
-      <c r="A226" s="135" t="s">
+      <c r="A226" s="145" t="s">
         <v>330</v>
       </c>
       <c r="B226" s="38" t="s">
@@ -13991,7 +14003,7 @@
       <c r="N226" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O226" s="135" t="s">
+      <c r="O226" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P226" s="19" t="s">
@@ -13999,7 +14011,7 @@
       </c>
     </row>
     <row r="227" spans="1:253" s="2" customFormat="1">
-      <c r="A227" s="136"/>
+      <c r="A227" s="146"/>
       <c r="B227" s="29"/>
       <c r="C227" s="29" t="s">
         <v>332</v>
@@ -14038,13 +14050,13 @@
       <c r="N227" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O227" s="136"/>
+      <c r="O227" s="146"/>
       <c r="P227" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="228" spans="1:253" s="2" customFormat="1">
-      <c r="A228" s="136"/>
+      <c r="A228" s="146"/>
       <c r="B228" s="35"/>
       <c r="C228" s="35" t="s">
         <v>334</v>
@@ -14078,18 +14090,18 @@
         <v>27</v>
       </c>
       <c r="M228" s="35" t="s">
-        <v>91</v>
+        <v>763</v>
       </c>
       <c r="N228" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="O228" s="136"/>
+      <c r="O228" s="146"/>
       <c r="P228" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="229" spans="1:253" s="2" customFormat="1">
-      <c r="A229" s="136"/>
+      <c r="A229" s="146"/>
       <c r="B229" s="29"/>
       <c r="C229" s="29" t="s">
         <v>333</v>
@@ -14128,13 +14140,13 @@
       <c r="N229" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="O229" s="136"/>
+      <c r="O229" s="146"/>
       <c r="P229" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="230" spans="1:253" s="2" customFormat="1">
-      <c r="A230" s="136"/>
+      <c r="A230" s="146"/>
       <c r="B230" s="91"/>
       <c r="C230" s="91" t="s">
         <v>722</v>
@@ -14173,13 +14185,13 @@
       <c r="N230" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O230" s="136"/>
+      <c r="O230" s="146"/>
       <c r="P230" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="231" spans="1:253" s="2" customFormat="1">
-      <c r="A231" s="141" t="s">
+      <c r="A231" s="154" t="s">
         <v>335</v>
       </c>
       <c r="B231" s="39" t="s">
@@ -14222,7 +14234,7 @@
       <c r="N231" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O231" s="141" t="s">
+      <c r="O231" s="154" t="s">
         <v>36</v>
       </c>
       <c r="P231" s="46" t="s">
@@ -14230,7 +14242,7 @@
       </c>
     </row>
     <row r="232" spans="1:253" s="2" customFormat="1">
-      <c r="A232" s="141"/>
+      <c r="A232" s="154"/>
       <c r="B232" s="29"/>
       <c r="C232" s="30" t="s">
         <v>337</v>
@@ -14269,13 +14281,13 @@
       <c r="N232" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O232" s="141"/>
+      <c r="O232" s="154"/>
       <c r="P232" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="233" spans="1:253" s="2" customFormat="1">
-      <c r="A233" s="141"/>
+      <c r="A233" s="154"/>
       <c r="B233" s="29"/>
       <c r="C233" s="30" t="s">
         <v>338</v>
@@ -14314,13 +14326,13 @@
       <c r="N233" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O233" s="141"/>
+      <c r="O233" s="154"/>
       <c r="P233" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="234" spans="1:253" s="2" customFormat="1">
-      <c r="A234" s="141"/>
+      <c r="A234" s="154"/>
       <c r="B234" s="29"/>
       <c r="C234" s="30" t="s">
         <v>339</v>
@@ -14353,19 +14365,19 @@
       <c r="L234" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M234" s="29" t="s">
-        <v>61</v>
+      <c r="M234" s="35" t="s">
+        <v>98</v>
       </c>
       <c r="N234" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O234" s="136"/>
+      <c r="O234" s="146"/>
       <c r="P234" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="235" spans="1:253" s="2" customFormat="1">
-      <c r="A235" s="141"/>
+      <c r="A235" s="154"/>
       <c r="B235" s="29"/>
       <c r="C235" s="30" t="s">
         <v>340</v>
@@ -14398,19 +14410,19 @@
       <c r="L235" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M235" s="29" t="s">
-        <v>61</v>
+      <c r="M235" s="35" t="s">
+        <v>98</v>
       </c>
       <c r="N235" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="O235" s="136"/>
+      <c r="O235" s="146"/>
       <c r="P235" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="236" spans="1:253" s="2" customFormat="1">
-      <c r="A236" s="141"/>
+      <c r="A236" s="154"/>
       <c r="B236" s="29"/>
       <c r="C236" s="30" t="s">
         <v>341</v>
@@ -14449,13 +14461,13 @@
       <c r="N236" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="O236" s="136"/>
+      <c r="O236" s="146"/>
       <c r="P236" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="237" spans="1:253" s="2" customFormat="1">
-      <c r="A237" s="141"/>
+      <c r="A237" s="154"/>
       <c r="B237" s="35"/>
       <c r="C237" s="36" t="s">
         <v>342</v>
@@ -14489,12 +14501,12 @@
         <v>27</v>
       </c>
       <c r="M237" s="35" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="N237" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O237" s="137"/>
+      <c r="O237" s="147"/>
       <c r="P237" s="46" t="s">
         <v>31</v>
       </c>
@@ -15270,25 +15282,84 @@
   </sheetData>
   <autoFilter ref="A4:P240" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="126">
-    <mergeCell ref="O139:O141"/>
-    <mergeCell ref="A139:A141"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O91:O93"/>
+    <mergeCell ref="O94:O97"/>
+    <mergeCell ref="O98:O100"/>
+    <mergeCell ref="O49:O53"/>
+    <mergeCell ref="O54:O57"/>
+    <mergeCell ref="O58:O62"/>
+    <mergeCell ref="O63:O67"/>
+    <mergeCell ref="O68:O71"/>
+    <mergeCell ref="O142:O148"/>
+    <mergeCell ref="O213:O216"/>
+    <mergeCell ref="O101:O106"/>
+    <mergeCell ref="O117:O120"/>
+    <mergeCell ref="O131:O132"/>
+    <mergeCell ref="O153:O160"/>
+    <mergeCell ref="O168:O169"/>
+    <mergeCell ref="A153:A160"/>
+    <mergeCell ref="O127:O129"/>
+    <mergeCell ref="A127:A129"/>
+    <mergeCell ref="O174:O177"/>
+    <mergeCell ref="O199:O202"/>
+    <mergeCell ref="O178:O181"/>
+    <mergeCell ref="O107:O112"/>
+    <mergeCell ref="O221:O224"/>
+    <mergeCell ref="O226:O230"/>
+    <mergeCell ref="O231:O237"/>
+    <mergeCell ref="P4:P5"/>
+    <mergeCell ref="O193:O194"/>
+    <mergeCell ref="O195:O198"/>
+    <mergeCell ref="O203:O204"/>
+    <mergeCell ref="O205:O207"/>
+    <mergeCell ref="O209:O212"/>
+    <mergeCell ref="O217:O220"/>
+    <mergeCell ref="O161:O164"/>
+    <mergeCell ref="O165:O167"/>
+    <mergeCell ref="O170:O173"/>
+    <mergeCell ref="O182:O185"/>
+    <mergeCell ref="O186:O190"/>
+    <mergeCell ref="O113:O116"/>
+    <mergeCell ref="O121:O123"/>
+    <mergeCell ref="O124:O126"/>
+    <mergeCell ref="O133:O137"/>
+    <mergeCell ref="O149:O151"/>
+    <mergeCell ref="O78:O81"/>
+    <mergeCell ref="O82:O85"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="O7:O11"/>
+    <mergeCell ref="O15:O19"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A62"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="O28:O32"/>
+    <mergeCell ref="O33:O37"/>
+    <mergeCell ref="O38:O40"/>
+    <mergeCell ref="O41:O44"/>
+    <mergeCell ref="O45:O48"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="O20:O23"/>
+    <mergeCell ref="A213:A216"/>
+    <mergeCell ref="A217:A220"/>
+    <mergeCell ref="A221:A224"/>
+    <mergeCell ref="A113:A116"/>
+    <mergeCell ref="A117:A120"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A91:A93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="A174:A177"/>
     <mergeCell ref="A226:A230"/>
     <mergeCell ref="A231:A237"/>
     <mergeCell ref="B4:B5"/>
@@ -15313,89 +15384,30 @@
     <mergeCell ref="A107:A112"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A213:A216"/>
-    <mergeCell ref="A217:A220"/>
-    <mergeCell ref="A221:A224"/>
-    <mergeCell ref="A113:A116"/>
-    <mergeCell ref="A117:A120"/>
-    <mergeCell ref="A121:A123"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A91:A93"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="O139:O141"/>
+    <mergeCell ref="A139:A141"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="O72:O75"/>
     <mergeCell ref="O76:O77"/>
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="O86:O90"/>
     <mergeCell ref="O24:O27"/>
-    <mergeCell ref="O15:O19"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A62"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="O28:O32"/>
-    <mergeCell ref="O33:O37"/>
-    <mergeCell ref="O38:O40"/>
-    <mergeCell ref="O41:O44"/>
-    <mergeCell ref="O45:O48"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A33:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="O221:O224"/>
-    <mergeCell ref="O226:O230"/>
-    <mergeCell ref="O231:O237"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="O193:O194"/>
-    <mergeCell ref="O195:O198"/>
-    <mergeCell ref="O203:O204"/>
-    <mergeCell ref="O205:O207"/>
-    <mergeCell ref="O209:O212"/>
-    <mergeCell ref="O217:O220"/>
-    <mergeCell ref="O161:O164"/>
-    <mergeCell ref="O165:O167"/>
-    <mergeCell ref="O170:O173"/>
-    <mergeCell ref="O182:O185"/>
-    <mergeCell ref="O186:O190"/>
-    <mergeCell ref="O113:O116"/>
-    <mergeCell ref="O121:O123"/>
-    <mergeCell ref="O124:O126"/>
-    <mergeCell ref="O133:O137"/>
-    <mergeCell ref="O149:O151"/>
-    <mergeCell ref="O78:O81"/>
-    <mergeCell ref="O82:O85"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="O7:O11"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="O142:O148"/>
-    <mergeCell ref="O213:O216"/>
-    <mergeCell ref="O101:O106"/>
-    <mergeCell ref="O117:O120"/>
-    <mergeCell ref="O131:O132"/>
-    <mergeCell ref="O153:O160"/>
-    <mergeCell ref="O168:O169"/>
-    <mergeCell ref="A153:A160"/>
-    <mergeCell ref="O127:O129"/>
-    <mergeCell ref="A127:A129"/>
-    <mergeCell ref="O174:O177"/>
-    <mergeCell ref="O199:O202"/>
-    <mergeCell ref="O178:O181"/>
-    <mergeCell ref="O107:O112"/>
-    <mergeCell ref="O20:O23"/>
-    <mergeCell ref="O91:O93"/>
-    <mergeCell ref="O94:O97"/>
-    <mergeCell ref="O98:O100"/>
-    <mergeCell ref="O49:O53"/>
-    <mergeCell ref="O54:O57"/>
-    <mergeCell ref="O58:O62"/>
-    <mergeCell ref="O63:O67"/>
-    <mergeCell ref="O68:O71"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15748031496062992" right="0.23622047244094491" top="0.19685039370078741" bottom="0.23622047244094491" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FA035C-349D-4298-B369-C3386313060C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184ABF8C-C25E-42A5-9F42-68653E452146}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="763">
   <si>
     <t>DAFTAR PENDUDUK RT 06 - RW 14</t>
   </si>
@@ -2192,12 +2192,6 @@
   </si>
   <si>
     <t>TIDAK/BELUM SEKOLAH</t>
-  </si>
-  <si>
-    <t>SLTA/SEDERAJAT</t>
-  </si>
-  <si>
-    <t>SLTP/SEDERAJAT</t>
   </si>
   <si>
     <t>SITA PUSPA TRIANA</t>
@@ -3889,10 +3883,10 @@
         <v>27</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O6" s="18" t="s">
         <v>30</v>
@@ -3940,10 +3934,10 @@
         <v>27</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O7" s="145" t="s">
         <v>36</v>
@@ -3987,10 +3981,10 @@
         <v>27</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O8" s="146"/>
       <c r="P8" s="19" t="s">
@@ -4035,7 +4029,7 @@
         <v>155</v>
       </c>
       <c r="N9" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O9" s="146"/>
       <c r="P9" s="19" t="s">
@@ -4077,10 +4071,10 @@
         <v>27</v>
       </c>
       <c r="M10" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N10" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O10" s="146"/>
       <c r="P10" s="19" t="s">
@@ -4122,10 +4116,10 @@
         <v>27</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O11" s="147"/>
       <c r="P11" s="19" t="s">
@@ -4171,10 +4165,10 @@
         <v>27</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N12" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O12" s="145" t="s">
         <v>30</v>
@@ -4218,10 +4212,10 @@
         <v>27</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N13" s="35" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O13" s="147"/>
       <c r="P13" s="46" t="s">
@@ -4292,7 +4286,7 @@
         <v>98</v>
       </c>
       <c r="N15" s="25" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O15" s="145" t="s">
         <v>30</v>
@@ -4339,7 +4333,7 @@
         <v>98</v>
       </c>
       <c r="N16" s="35" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O16" s="146"/>
       <c r="P16" s="19" t="s">
@@ -4381,10 +4375,10 @@
         <v>27</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N17" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O17" s="146"/>
       <c r="P17" s="19" t="s">
@@ -4395,7 +4389,7 @@
       <c r="A18" s="146"/>
       <c r="B18" s="127"/>
       <c r="C18" s="127" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D18" s="116" t="s">
         <v>21</v>
@@ -4426,10 +4420,10 @@
         <v>27</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N18" s="35" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O18" s="146"/>
       <c r="P18" s="19" t="s">
@@ -4440,7 +4434,7 @@
       <c r="A19" s="147"/>
       <c r="B19" s="26"/>
       <c r="C19" s="134" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D19" s="116" t="s">
         <v>39</v>
@@ -4471,10 +4465,10 @@
         <v>27</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N19" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O19" s="147"/>
       <c r="P19" s="19" t="s">
@@ -4520,10 +4514,10 @@
         <v>27</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N20" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O20" s="145" t="s">
         <v>36</v>
@@ -4567,10 +4561,10 @@
         <v>27</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O21" s="146"/>
       <c r="P21" s="19" t="s">
@@ -4615,7 +4609,7 @@
         <v>155</v>
       </c>
       <c r="N22" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O22" s="146"/>
       <c r="P22" s="19" t="s">
@@ -4657,10 +4651,10 @@
         <v>27</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N23" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O23" s="147"/>
       <c r="P23" s="19" t="s">
@@ -4706,10 +4700,10 @@
         <v>27</v>
       </c>
       <c r="M24" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N24" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O24" s="145" t="s">
         <v>36</v>
@@ -4753,10 +4747,10 @@
         <v>27</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N25" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O25" s="146"/>
       <c r="P25" s="19" t="s">
@@ -4798,10 +4792,10 @@
         <v>27</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N26" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O26" s="146"/>
       <c r="P26" s="19" t="s">
@@ -4846,7 +4840,7 @@
         <v>719</v>
       </c>
       <c r="N27" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O27" s="147"/>
       <c r="P27" s="19" t="s">
@@ -4892,10 +4886,10 @@
         <v>77</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N28" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O28" s="145" t="s">
         <v>36</v>
@@ -4939,10 +4933,10 @@
         <v>27</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N29" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O29" s="146"/>
       <c r="P29" s="19" t="s">
@@ -4984,10 +4978,10 @@
         <v>27</v>
       </c>
       <c r="M30" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N30" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O30" s="146"/>
       <c r="P30" s="19" t="s">
@@ -5032,7 +5026,7 @@
         <v>98</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O31" s="146"/>
       <c r="P31" s="19" t="s">
@@ -5074,10 +5068,10 @@
         <v>27</v>
       </c>
       <c r="M32" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N32" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O32" s="147"/>
       <c r="P32" s="19" t="s">
@@ -5123,10 +5117,10 @@
         <v>87</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N33" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O33" s="145" t="s">
         <v>36</v>
@@ -5170,10 +5164,10 @@
         <v>89</v>
       </c>
       <c r="M34" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N34" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O34" s="146"/>
       <c r="P34" s="19" t="s">
@@ -5218,7 +5212,7 @@
         <v>155</v>
       </c>
       <c r="N35" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O35" s="146"/>
       <c r="P35" s="19" t="s">
@@ -5260,10 +5254,10 @@
         <v>27</v>
       </c>
       <c r="M36" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N36" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O36" s="146"/>
       <c r="P36" s="19" t="s">
@@ -5305,10 +5299,10 @@
         <v>27</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="N37" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O37" s="147"/>
       <c r="P37" s="19" t="s">
@@ -5357,7 +5351,7 @@
         <v>98</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O38" s="145" t="s">
         <v>30</v>
@@ -5401,10 +5395,10 @@
         <v>27</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N39" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O39" s="146"/>
       <c r="P39" s="46" t="s">
@@ -5446,10 +5440,10 @@
         <v>27</v>
       </c>
       <c r="M40" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N40" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O40" s="146"/>
       <c r="P40" s="46" t="s">
@@ -5498,7 +5492,7 @@
         <v>155</v>
       </c>
       <c r="N41" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O41" s="145" t="s">
         <v>36</v>
@@ -5545,7 +5539,7 @@
         <v>155</v>
       </c>
       <c r="N42" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O42" s="146"/>
       <c r="P42" s="19" t="s">
@@ -5587,10 +5581,10 @@
         <v>27</v>
       </c>
       <c r="M43" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N43" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O43" s="146"/>
       <c r="P43" s="19" t="s">
@@ -5635,7 +5629,7 @@
         <v>719</v>
       </c>
       <c r="N44" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O44" s="147"/>
       <c r="P44" s="19" t="s">
@@ -5681,10 +5675,10 @@
         <v>112</v>
       </c>
       <c r="M45" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N45" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O45" s="145" t="s">
         <v>36</v>
@@ -5728,10 +5722,10 @@
         <v>27</v>
       </c>
       <c r="M46" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N46" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O46" s="146"/>
       <c r="P46" s="19" t="s">
@@ -5773,10 +5767,10 @@
         <v>27</v>
       </c>
       <c r="M47" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N47" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O47" s="146"/>
       <c r="P47" s="19" t="s">
@@ -5818,10 +5812,10 @@
         <v>27</v>
       </c>
       <c r="M48" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N48" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O48" s="147"/>
       <c r="P48" s="19" t="s">
@@ -5867,10 +5861,10 @@
         <v>27</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O49" s="145" t="s">
         <v>30</v>
@@ -5914,10 +5908,10 @@
         <v>27</v>
       </c>
       <c r="M50" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N50" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O50" s="146"/>
       <c r="P50" s="46" t="s">
@@ -5962,7 +5956,7 @@
         <v>719</v>
       </c>
       <c r="N51" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O51" s="146"/>
       <c r="P51" s="46" t="s">
@@ -6007,7 +6001,7 @@
         <v>719</v>
       </c>
       <c r="N52" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O52" s="146"/>
       <c r="P52" s="46" t="s">
@@ -6052,7 +6046,7 @@
         <v>719</v>
       </c>
       <c r="N53" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O53" s="147"/>
       <c r="P53" s="46" t="s">
@@ -6101,7 +6095,7 @@
         <v>126</v>
       </c>
       <c r="N54" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O54" s="145" t="s">
         <v>36</v>
@@ -6145,10 +6139,10 @@
         <v>27</v>
       </c>
       <c r="M55" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N55" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O55" s="146"/>
       <c r="P55" s="19" t="s">
@@ -6193,7 +6187,7 @@
         <v>204</v>
       </c>
       <c r="N56" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O56" s="146"/>
       <c r="P56" s="19" t="s">
@@ -6235,10 +6229,10 @@
         <v>27</v>
       </c>
       <c r="M57" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N57" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O57" s="147"/>
       <c r="P57" s="19" t="s">
@@ -6284,10 +6278,10 @@
         <v>112</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N58" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O58" s="145" t="s">
         <v>36</v>
@@ -6331,10 +6325,10 @@
         <v>112</v>
       </c>
       <c r="M59" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N59" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O59" s="146"/>
       <c r="P59" s="19" t="s">
@@ -6379,7 +6373,7 @@
         <v>204</v>
       </c>
       <c r="N60" s="91" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O60" s="146"/>
       <c r="P60" s="19" t="s">
@@ -6421,10 +6415,10 @@
         <v>27</v>
       </c>
       <c r="M61" s="91" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="N61" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O61" s="146"/>
       <c r="P61" s="19" t="s">
@@ -6469,7 +6463,7 @@
         <v>719</v>
       </c>
       <c r="N62" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O62" s="147"/>
       <c r="P62" s="19" t="s">
@@ -6515,10 +6509,10 @@
         <v>27</v>
       </c>
       <c r="M63" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N63" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O63" s="145" t="s">
         <v>30</v>
@@ -6562,10 +6556,10 @@
         <v>27</v>
       </c>
       <c r="M64" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N64" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O64" s="146"/>
       <c r="P64" s="46" t="s">
@@ -6607,10 +6601,10 @@
         <v>27</v>
       </c>
       <c r="M65" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N65" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O65" s="146"/>
       <c r="P65" s="46" t="s">
@@ -6652,10 +6646,10 @@
         <v>27</v>
       </c>
       <c r="M66" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N66" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O66" s="146"/>
       <c r="P66" s="46" t="s">
@@ -6697,10 +6691,10 @@
         <v>27</v>
       </c>
       <c r="M67" s="35" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="N67" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O67" s="147"/>
       <c r="P67" s="46" t="s">
@@ -6746,10 +6740,10 @@
         <v>27</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N68" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O68" s="145" t="s">
         <v>36</v>
@@ -6793,10 +6787,10 @@
         <v>27</v>
       </c>
       <c r="M69" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N69" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O69" s="146"/>
       <c r="P69" s="19" t="s">
@@ -6841,7 +6835,7 @@
         <v>155</v>
       </c>
       <c r="N70" s="91" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O70" s="146"/>
       <c r="P70" s="19" t="s">
@@ -6883,10 +6877,10 @@
         <v>27</v>
       </c>
       <c r="M71" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N71" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O71" s="147"/>
       <c r="P71" s="19" t="s">
@@ -6932,10 +6926,10 @@
         <v>27</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O72" s="145" t="s">
         <v>36</v>
@@ -6979,10 +6973,10 @@
         <v>27</v>
       </c>
       <c r="M73" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N73" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O73" s="146"/>
       <c r="P73" s="19" t="s">
@@ -7024,10 +7018,10 @@
         <v>27</v>
       </c>
       <c r="M74" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N74" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O74" s="146"/>
       <c r="P74" s="19" t="s">
@@ -7069,10 +7063,10 @@
         <v>27</v>
       </c>
       <c r="M75" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N75" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O75" s="147"/>
       <c r="P75" s="19" t="s">
@@ -7118,10 +7112,10 @@
         <v>27</v>
       </c>
       <c r="M76" s="50" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N76" s="25" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O76" s="155" t="s">
         <v>30</v>
@@ -7165,10 +7159,10 @@
         <v>27</v>
       </c>
       <c r="M77" s="50" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N77" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O77" s="157"/>
       <c r="P77" s="46" t="s">
@@ -7214,10 +7208,10 @@
         <v>112</v>
       </c>
       <c r="M78" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N78" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O78" s="145" t="s">
         <v>36</v>
@@ -7261,10 +7255,10 @@
         <v>112</v>
       </c>
       <c r="M79" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N79" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O79" s="146"/>
       <c r="P79" s="19" t="s">
@@ -7309,7 +7303,7 @@
         <v>162</v>
       </c>
       <c r="N80" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O80" s="146"/>
       <c r="P80" s="19" t="s">
@@ -7351,10 +7345,10 @@
         <v>27</v>
       </c>
       <c r="M81" s="35" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N81" s="35" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O81" s="147"/>
       <c r="P81" s="19" t="s">
@@ -7400,10 +7394,10 @@
         <v>27</v>
       </c>
       <c r="M82" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N82" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O82" s="145" t="s">
         <v>36</v>
@@ -7447,10 +7441,10 @@
         <v>27</v>
       </c>
       <c r="M83" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N83" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O83" s="146"/>
       <c r="P83" s="19" t="s">
@@ -7492,10 +7486,10 @@
         <v>27</v>
       </c>
       <c r="M84" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N84" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O84" s="146"/>
       <c r="P84" s="19" t="s">
@@ -7540,7 +7534,7 @@
         <v>98</v>
       </c>
       <c r="N85" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O85" s="147"/>
       <c r="P85" s="19" t="s">
@@ -7586,10 +7580,10 @@
         <v>27</v>
       </c>
       <c r="M86" s="25" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N86" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O86" s="145" t="s">
         <v>30</v>
@@ -7633,10 +7627,10 @@
         <v>87</v>
       </c>
       <c r="M87" s="29" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N87" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O87" s="146"/>
       <c r="P87" s="19" t="s">
@@ -7678,10 +7672,10 @@
         <v>27</v>
       </c>
       <c r="M88" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N88" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O88" s="146"/>
       <c r="P88" s="19" t="s">
@@ -7723,10 +7717,10 @@
         <v>27</v>
       </c>
       <c r="M89" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N89" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O89" s="146"/>
       <c r="P89" s="19" t="s">
@@ -7771,7 +7765,7 @@
         <v>719</v>
       </c>
       <c r="N90" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O90" s="147"/>
       <c r="P90" s="19" t="s">
@@ -7817,10 +7811,10 @@
         <v>27</v>
       </c>
       <c r="M91" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N91" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O91" s="145" t="s">
         <v>30</v>
@@ -7864,10 +7858,10 @@
         <v>27</v>
       </c>
       <c r="M92" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N92" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O92" s="146"/>
       <c r="P92" s="46" t="s">
@@ -7912,7 +7906,7 @@
         <v>719</v>
       </c>
       <c r="N93" s="91" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O93" s="146"/>
       <c r="P93" s="46" t="s">
@@ -7958,10 +7952,10 @@
         <v>27</v>
       </c>
       <c r="M94" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N94" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O94" s="145" t="s">
         <v>36</v>
@@ -8005,10 +7999,10 @@
         <v>27</v>
       </c>
       <c r="M95" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N95" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O95" s="146"/>
       <c r="P95" s="19" t="s">
@@ -8050,10 +8044,10 @@
         <v>27</v>
       </c>
       <c r="M96" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N96" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O96" s="146"/>
       <c r="P96" s="19" t="s">
@@ -8095,10 +8089,10 @@
         <v>27</v>
       </c>
       <c r="M97" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N97" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O97" s="147"/>
       <c r="P97" s="19" t="s">
@@ -8144,10 +8138,10 @@
         <v>27</v>
       </c>
       <c r="M98" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N98" s="25" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O98" s="145" t="s">
         <v>30</v>
@@ -8191,10 +8185,10 @@
         <v>27</v>
       </c>
       <c r="M99" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N99" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O99" s="146"/>
       <c r="P99" s="19" t="s">
@@ -8236,10 +8230,10 @@
         <v>27</v>
       </c>
       <c r="M100" s="35" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N100" s="35" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O100" s="146"/>
       <c r="P100" s="19" t="s">
@@ -8285,10 +8279,10 @@
         <v>27</v>
       </c>
       <c r="M101" s="35" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N101" s="32" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O101" s="156" t="s">
         <v>36</v>
@@ -8335,7 +8329,7 @@
         <v>189</v>
       </c>
       <c r="N102" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O102" s="156"/>
       <c r="P102" s="19" t="s">
@@ -8377,10 +8371,10 @@
         <v>27</v>
       </c>
       <c r="M103" s="35" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N103" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O103" s="156"/>
       <c r="P103" s="19" t="s">
@@ -8422,10 +8416,10 @@
         <v>27</v>
       </c>
       <c r="M104" s="35" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N104" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O104" s="156"/>
       <c r="P104" s="19" t="s">
@@ -8467,10 +8461,10 @@
         <v>27</v>
       </c>
       <c r="M105" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N105" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O105" s="156"/>
       <c r="P105" s="19" t="s">
@@ -8515,7 +8509,7 @@
         <v>98</v>
       </c>
       <c r="N106" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O106" s="157"/>
       <c r="P106" s="19" t="s">
@@ -8561,10 +8555,10 @@
         <v>27</v>
       </c>
       <c r="M107" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N107" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O107" s="145" t="s">
         <v>36</v>
@@ -8608,10 +8602,10 @@
         <v>27</v>
       </c>
       <c r="M108" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N108" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O108" s="146"/>
       <c r="P108" s="19" t="s">
@@ -8653,10 +8647,10 @@
         <v>27</v>
       </c>
       <c r="M109" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N109" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O109" s="146"/>
       <c r="P109" s="19" t="s">
@@ -8698,10 +8692,10 @@
         <v>27</v>
       </c>
       <c r="M110" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N110" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O110" s="146"/>
       <c r="P110" s="19" t="s">
@@ -8743,10 +8737,10 @@
         <v>27</v>
       </c>
       <c r="M111" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N111" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O111" s="146"/>
       <c r="P111" s="19" t="s">
@@ -8788,10 +8782,10 @@
         <v>27</v>
       </c>
       <c r="M112" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N112" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O112" s="147"/>
       <c r="P112" s="19" t="s">
@@ -8840,7 +8834,7 @@
         <v>204</v>
       </c>
       <c r="N113" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O113" s="145" t="s">
         <v>36</v>
@@ -8887,7 +8881,7 @@
         <v>155</v>
       </c>
       <c r="N114" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O114" s="146"/>
       <c r="P114" s="19" t="s">
@@ -8929,10 +8923,10 @@
         <v>112</v>
       </c>
       <c r="M115" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N115" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O115" s="146"/>
       <c r="P115" s="19" t="s">
@@ -8974,10 +8968,10 @@
         <v>27</v>
       </c>
       <c r="M116" s="35" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="N116" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O116" s="147"/>
       <c r="P116" s="19" t="s">
@@ -9023,10 +9017,10 @@
         <v>27</v>
       </c>
       <c r="M117" s="25" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N117" s="32" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O117" s="145" t="s">
         <v>30</v>
@@ -9070,10 +9064,10 @@
         <v>27</v>
       </c>
       <c r="M118" s="25" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N118" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O118" s="146"/>
       <c r="P118" s="46" t="s">
@@ -9115,10 +9109,10 @@
         <v>27</v>
       </c>
       <c r="M119" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N119" s="32" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O119" s="146"/>
       <c r="P119" s="46" t="s">
@@ -9163,7 +9157,7 @@
         <v>719</v>
       </c>
       <c r="N120" s="102" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O120" s="147"/>
       <c r="P120" s="46" t="s">
@@ -9209,10 +9203,10 @@
         <v>27</v>
       </c>
       <c r="M121" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N121" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O121" s="145" t="s">
         <v>36</v>
@@ -9256,10 +9250,10 @@
         <v>112</v>
       </c>
       <c r="M122" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N122" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O122" s="146"/>
       <c r="P122" s="19" t="s">
@@ -9301,10 +9295,10 @@
         <v>27</v>
       </c>
       <c r="M123" s="35" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N123" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O123" s="147"/>
       <c r="P123" s="19" t="s">
@@ -9350,10 +9344,10 @@
         <v>27</v>
       </c>
       <c r="M124" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N124" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O124" s="145" t="s">
         <v>36</v>
@@ -9397,10 +9391,10 @@
         <v>27</v>
       </c>
       <c r="M125" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N125" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O125" s="146"/>
       <c r="P125" s="19" t="s">
@@ -9442,10 +9436,10 @@
         <v>27</v>
       </c>
       <c r="M126" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N126" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O126" s="147"/>
       <c r="P126" s="19" t="s">
@@ -9491,10 +9485,10 @@
         <v>27</v>
       </c>
       <c r="M127" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N127" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O127" s="145" t="s">
         <v>30</v>
@@ -9538,10 +9532,10 @@
         <v>27</v>
       </c>
       <c r="M128" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N128" s="32" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O128" s="146"/>
       <c r="P128" s="19" t="s">
@@ -9583,10 +9577,10 @@
         <v>27</v>
       </c>
       <c r="M129" s="35" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="N129" s="32" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O129" s="147"/>
       <c r="P129" s="19" t="s">
@@ -9654,10 +9648,10 @@
         <v>27</v>
       </c>
       <c r="M131" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N131" s="20" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O131" s="145" t="s">
         <v>30</v>
@@ -9701,10 +9695,10 @@
         <v>27</v>
       </c>
       <c r="M132" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N132" s="35" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O132" s="147"/>
       <c r="P132" s="19" t="s">
@@ -9716,10 +9710,10 @@
         <v>228</v>
       </c>
       <c r="B133" s="128" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C133" s="128" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D133" s="24" t="s">
         <v>21</v>
@@ -9753,7 +9747,7 @@
         <v>98</v>
       </c>
       <c r="N133" s="35" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O133" s="145" t="s">
         <v>30</v>
@@ -9766,7 +9760,7 @@
       <c r="A134" s="146"/>
       <c r="B134" s="29"/>
       <c r="C134" s="30" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D134" s="31" t="s">
         <v>39</v>
@@ -9797,10 +9791,10 @@
         <v>27</v>
       </c>
       <c r="M134" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N134" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O134" s="146"/>
       <c r="P134" s="19" t="s">
@@ -9811,7 +9805,7 @@
       <c r="A135" s="146"/>
       <c r="B135" s="91"/>
       <c r="C135" s="36" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D135" s="97" t="s">
         <v>39</v>
@@ -9842,10 +9836,10 @@
         <v>27</v>
       </c>
       <c r="M135" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N135" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O135" s="146"/>
       <c r="P135" s="19" t="s">
@@ -9856,7 +9850,7 @@
       <c r="A136" s="146"/>
       <c r="B136" s="91"/>
       <c r="C136" s="36" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D136" s="117" t="s">
         <v>21</v>
@@ -9887,10 +9881,10 @@
         <v>27</v>
       </c>
       <c r="M136" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N136" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O136" s="146"/>
       <c r="P136" s="19" t="s">
@@ -9901,7 +9895,7 @@
       <c r="A137" s="147"/>
       <c r="B137" s="35"/>
       <c r="C137" s="36" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D137" s="37" t="s">
         <v>21</v>
@@ -9935,7 +9929,7 @@
         <v>719</v>
       </c>
       <c r="N137" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O137" s="147"/>
       <c r="P137" s="19" t="s">
@@ -9947,10 +9941,10 @@
         <v>518</v>
       </c>
       <c r="B138" s="135" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C138" s="135" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D138" s="123" t="s">
         <v>21</v>
@@ -9981,10 +9975,10 @@
         <v>27</v>
       </c>
       <c r="M138" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N138" s="126" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O138" s="120" t="s">
         <v>30</v>
@@ -9998,10 +9992,10 @@
         <v>528</v>
       </c>
       <c r="B139" s="137" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C139" s="140" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D139" s="121" t="s">
         <v>21</v>
@@ -10032,10 +10026,10 @@
         <v>27</v>
       </c>
       <c r="M139" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N139" s="126" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O139" s="145" t="s">
         <v>30</v>
@@ -10048,7 +10042,7 @@
       <c r="A140" s="148"/>
       <c r="B140" s="138"/>
       <c r="C140" s="141" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D140" s="122" t="s">
         <v>39</v>
@@ -10079,10 +10073,10 @@
         <v>27</v>
       </c>
       <c r="M140" s="25" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N140" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O140" s="146"/>
       <c r="P140" s="46" t="s">
@@ -10093,7 +10087,7 @@
       <c r="A141" s="148"/>
       <c r="B141" s="139"/>
       <c r="C141" s="142" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D141" s="97" t="s">
         <v>39</v>
@@ -10102,7 +10096,7 @@
         <v>44</v>
       </c>
       <c r="F141" s="136" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G141" s="143">
         <v>45621</v>
@@ -10127,7 +10121,7 @@
         <v>719</v>
       </c>
       <c r="N141" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O141" s="147"/>
       <c r="P141" s="46" t="s">
@@ -10139,10 +10133,10 @@
         <v>540</v>
       </c>
       <c r="B142" s="127" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C142" s="127" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D142" s="117" t="s">
         <v>21</v>
@@ -10173,10 +10167,10 @@
         <v>27</v>
       </c>
       <c r="M142" s="25" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N142" s="20" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O142" s="146" t="s">
         <v>36</v>
@@ -10189,7 +10183,7 @@
       <c r="A143" s="116"/>
       <c r="B143" s="26"/>
       <c r="C143" s="134" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D143" s="118" t="s">
         <v>39</v>
@@ -10220,10 +10214,10 @@
         <v>27</v>
       </c>
       <c r="M143" s="25" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N143" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O143" s="146"/>
       <c r="P143" s="19" t="s">
@@ -10234,7 +10228,7 @@
       <c r="A144" s="116"/>
       <c r="B144" s="26"/>
       <c r="C144" s="134" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D144" s="97" t="s">
         <v>39</v>
@@ -10268,7 +10262,7 @@
         <v>719</v>
       </c>
       <c r="N144" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O144" s="146"/>
       <c r="P144" s="19" t="s">
@@ -10279,7 +10273,7 @@
       <c r="A145" s="116"/>
       <c r="B145" s="26"/>
       <c r="C145" s="134" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D145" s="117" t="s">
         <v>21</v>
@@ -10313,7 +10307,7 @@
         <v>98</v>
       </c>
       <c r="N145" s="126" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O145" s="146"/>
       <c r="P145" s="19" t="s">
@@ -10324,7 +10318,7 @@
       <c r="A146" s="116"/>
       <c r="B146" s="26"/>
       <c r="C146" s="134" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D146" s="118" t="s">
         <v>39</v>
@@ -10333,7 +10327,7 @@
         <v>40</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G146" s="124">
         <v>27706</v>
@@ -10358,7 +10352,7 @@
         <v>98</v>
       </c>
       <c r="N146" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O146" s="146"/>
       <c r="P146" s="19" t="s">
@@ -10369,7 +10363,7 @@
       <c r="A147" s="116"/>
       <c r="B147" s="26"/>
       <c r="C147" s="134" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D147" s="117" t="s">
         <v>21</v>
@@ -10400,10 +10394,10 @@
         <v>27</v>
       </c>
       <c r="M147" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N147" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O147" s="146"/>
       <c r="P147" s="19" t="s">
@@ -10414,7 +10408,7 @@
       <c r="A148" s="116"/>
       <c r="B148" s="26"/>
       <c r="C148" s="134" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D148" s="117" t="s">
         <v>21</v>
@@ -10445,10 +10439,10 @@
         <v>27</v>
       </c>
       <c r="M148" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N148" s="126" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O148" s="147"/>
       <c r="P148" s="19" t="s">
@@ -10494,10 +10488,10 @@
         <v>27</v>
       </c>
       <c r="M149" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N149" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O149" s="145" t="s">
         <v>36</v>
@@ -10544,7 +10538,7 @@
         <v>126</v>
       </c>
       <c r="N150" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O150" s="146"/>
       <c r="P150" s="19" t="s">
@@ -10586,10 +10580,10 @@
         <v>27</v>
       </c>
       <c r="M151" s="35" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N151" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O151" s="146"/>
       <c r="P151" s="19" t="s">
@@ -10675,10 +10669,10 @@
         <v>27</v>
       </c>
       <c r="M153" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N153" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O153" s="145" t="s">
         <v>36</v>
@@ -10722,10 +10716,10 @@
         <v>27</v>
       </c>
       <c r="M154" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N154" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O154" s="146"/>
       <c r="P154" s="19" t="s">
@@ -10767,10 +10761,10 @@
         <v>27</v>
       </c>
       <c r="M155" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N155" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O155" s="146"/>
       <c r="P155" s="19" t="s">
@@ -10812,10 +10806,10 @@
         <v>27</v>
       </c>
       <c r="M156" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N156" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O156" s="146"/>
       <c r="P156" s="19" t="s">
@@ -10857,10 +10851,10 @@
         <v>27</v>
       </c>
       <c r="M157" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N157" s="35" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O157" s="146"/>
       <c r="P157" s="19" t="s">
@@ -10902,10 +10896,10 @@
         <v>27</v>
       </c>
       <c r="M158" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N158" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O158" s="146"/>
       <c r="P158" s="19" t="s">
@@ -10945,7 +10939,7 @@
         <v>719</v>
       </c>
       <c r="N159" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O159" s="146"/>
       <c r="P159" s="19" t="s">
@@ -10990,7 +10984,7 @@
         <v>719</v>
       </c>
       <c r="N160" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O160" s="147"/>
       <c r="P160" s="19" t="s">
@@ -11036,10 +11030,10 @@
         <v>27</v>
       </c>
       <c r="M161" s="29" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N161" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O161" s="145" t="s">
         <v>36</v>
@@ -11083,10 +11077,10 @@
         <v>27</v>
       </c>
       <c r="M162" s="29" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N162" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O162" s="146"/>
       <c r="P162" s="19" t="s">
@@ -11128,10 +11122,10 @@
         <v>27</v>
       </c>
       <c r="M163" s="29" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N163" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O163" s="146"/>
       <c r="P163" s="19" t="s">
@@ -11176,7 +11170,7 @@
         <v>718</v>
       </c>
       <c r="N164" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O164" s="147"/>
       <c r="P164" s="19" t="s">
@@ -11222,10 +11216,10 @@
         <v>27</v>
       </c>
       <c r="M165" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N165" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O165" s="154" t="s">
         <v>36</v>
@@ -11269,10 +11263,10 @@
         <v>27</v>
       </c>
       <c r="M166" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N166" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O166" s="154"/>
       <c r="P166" s="19" t="s">
@@ -11317,7 +11311,7 @@
         <v>719</v>
       </c>
       <c r="N167" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O167" s="154"/>
       <c r="P167" s="19" t="s">
@@ -11363,10 +11357,10 @@
         <v>27</v>
       </c>
       <c r="M168" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N168" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O168" s="145" t="s">
         <v>30</v>
@@ -11410,10 +11404,10 @@
         <v>27</v>
       </c>
       <c r="M169" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N169" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O169" s="147"/>
       <c r="P169" s="19" t="s">
@@ -11462,7 +11456,7 @@
         <v>126</v>
       </c>
       <c r="N170" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O170" s="145" t="s">
         <v>36</v>
@@ -11509,7 +11503,7 @@
         <v>126</v>
       </c>
       <c r="N171" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O171" s="146"/>
       <c r="P171" s="19" t="s">
@@ -11551,10 +11545,10 @@
         <v>27</v>
       </c>
       <c r="M172" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N172" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O172" s="146"/>
       <c r="P172" s="19" t="s">
@@ -11599,7 +11593,7 @@
         <v>98</v>
       </c>
       <c r="N173" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O173" s="146"/>
       <c r="P173" s="19" t="s">
@@ -11648,7 +11642,7 @@
         <v>98</v>
       </c>
       <c r="N174" s="25" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O174" s="146" t="s">
         <v>30</v>
@@ -11692,10 +11686,10 @@
         <v>27</v>
       </c>
       <c r="M175" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N175" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O175" s="146"/>
       <c r="P175" s="19" t="s">
@@ -11737,10 +11731,10 @@
         <v>27</v>
       </c>
       <c r="M176" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N176" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O176" s="146"/>
       <c r="P176" s="19" t="s">
@@ -11782,10 +11776,10 @@
         <v>27</v>
       </c>
       <c r="M177" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N177" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O177" s="147"/>
       <c r="P177" s="19" t="s">
@@ -11831,10 +11825,10 @@
         <v>27</v>
       </c>
       <c r="M178" s="25" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N178" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O178" s="155" t="s">
         <v>30</v>
@@ -11847,7 +11841,7 @@
       <c r="A179" s="156"/>
       <c r="B179" s="101"/>
       <c r="C179" s="102" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D179" s="31" t="s">
         <v>39</v>
@@ -11878,10 +11872,10 @@
         <v>27</v>
       </c>
       <c r="M179" s="25" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N179" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O179" s="156"/>
       <c r="P179" s="19" t="s">
@@ -11892,7 +11886,7 @@
       <c r="A180" s="156"/>
       <c r="B180" s="101"/>
       <c r="C180" s="102" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D180" s="118" t="s">
         <v>39</v>
@@ -11923,10 +11917,10 @@
         <v>27</v>
       </c>
       <c r="M180" s="25" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N180" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O180" s="156"/>
       <c r="P180" s="19" t="s">
@@ -11937,7 +11931,7 @@
       <c r="A181" s="156"/>
       <c r="B181" s="101"/>
       <c r="C181" s="102" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D181" s="86" t="s">
         <v>39</v>
@@ -11968,10 +11962,10 @@
         <v>27</v>
       </c>
       <c r="M181" s="29" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="N181" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O181" s="157"/>
       <c r="P181" s="19" t="s">
@@ -12020,7 +12014,7 @@
         <v>204</v>
       </c>
       <c r="N182" s="19" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O182" s="145" t="s">
         <v>36</v>
@@ -12064,10 +12058,10 @@
         <v>27</v>
       </c>
       <c r="M183" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N183" s="19" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O183" s="146"/>
       <c r="P183" s="19" t="s">
@@ -12109,10 +12103,10 @@
         <v>27</v>
       </c>
       <c r="M184" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N184" s="19" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O184" s="146"/>
       <c r="P184" s="19" t="s">
@@ -12126,7 +12120,7 @@
         <v>272</v>
       </c>
       <c r="D185" s="37" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E185" s="35" t="s">
         <v>44</v>
@@ -12154,10 +12148,10 @@
         <v>27</v>
       </c>
       <c r="M185" s="35" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N185" s="19" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O185" s="147"/>
       <c r="P185" s="19" t="s">
@@ -12203,10 +12197,10 @@
         <v>27</v>
       </c>
       <c r="M186" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N186" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O186" s="145" t="s">
         <v>36</v>
@@ -12250,10 +12244,10 @@
         <v>27</v>
       </c>
       <c r="M187" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N187" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O187" s="146"/>
       <c r="P187" s="19" t="s">
@@ -12295,10 +12289,10 @@
         <v>27</v>
       </c>
       <c r="M188" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N188" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O188" s="146"/>
       <c r="P188" s="19" t="s">
@@ -12340,10 +12334,10 @@
         <v>27</v>
       </c>
       <c r="M189" s="29" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N189" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O189" s="146"/>
       <c r="P189" s="19" t="s">
@@ -12388,7 +12382,7 @@
         <v>98</v>
       </c>
       <c r="N190" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O190" s="147"/>
       <c r="P190" s="19" t="s">
@@ -12481,7 +12475,7 @@
         <v>204</v>
       </c>
       <c r="N193" s="19" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O193" s="145" t="s">
         <v>30</v>
@@ -12525,10 +12519,10 @@
         <v>27</v>
       </c>
       <c r="M194" s="29" t="s">
-        <v>248</v>
+        <v>761</v>
       </c>
       <c r="N194" s="19" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O194" s="146"/>
       <c r="P194" s="46" t="s">
@@ -12574,10 +12568,10 @@
         <v>27</v>
       </c>
       <c r="M195" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N195" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O195" s="145" t="s">
         <v>36</v>
@@ -12621,10 +12615,10 @@
         <v>112</v>
       </c>
       <c r="M196" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N196" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O196" s="146"/>
       <c r="P196" s="19" t="s">
@@ -12669,7 +12663,7 @@
         <v>155</v>
       </c>
       <c r="N197" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O197" s="146"/>
       <c r="P197" s="19" t="s">
@@ -12711,10 +12705,10 @@
         <v>27</v>
       </c>
       <c r="M198" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N198" s="35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O198" s="147"/>
       <c r="P198" s="19" t="s">
@@ -12726,10 +12720,10 @@
         <v>624</v>
       </c>
       <c r="B199" s="127" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C199" s="127" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D199" s="117" t="s">
         <v>21</v>
@@ -12763,7 +12757,7 @@
         <v>98</v>
       </c>
       <c r="N199" s="26" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O199" s="145" t="s">
         <v>30</v>
@@ -12776,7 +12770,7 @@
       <c r="A200" s="116"/>
       <c r="B200" s="26"/>
       <c r="C200" s="26" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D200" s="118" t="s">
         <v>39</v>
@@ -12807,10 +12801,10 @@
         <v>27</v>
       </c>
       <c r="M200" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N200" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O200" s="146"/>
       <c r="P200" s="19" t="s">
@@ -12821,7 +12815,7 @@
       <c r="A201" s="116"/>
       <c r="B201" s="26"/>
       <c r="C201" s="26" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D201" s="118" t="s">
         <v>39</v>
@@ -12852,10 +12846,10 @@
         <v>27</v>
       </c>
       <c r="M201" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N201" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O201" s="146"/>
       <c r="P201" s="19" t="s">
@@ -12866,7 +12860,7 @@
       <c r="A202" s="116"/>
       <c r="B202" s="26"/>
       <c r="C202" s="26" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D202" s="119" t="s">
         <v>39</v>
@@ -12897,10 +12891,10 @@
         <v>27</v>
       </c>
       <c r="M202" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N202" s="26" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O202" s="147"/>
       <c r="P202" s="19" t="s">
@@ -12912,10 +12906,10 @@
         <v>295</v>
       </c>
       <c r="B203" s="38" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C203" s="38" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D203" s="24" t="s">
         <v>21</v>
@@ -12946,10 +12940,10 @@
         <v>27</v>
       </c>
       <c r="M203" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N203" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O203" s="145" t="s">
         <v>30</v>
@@ -12962,7 +12956,7 @@
       <c r="A204" s="146"/>
       <c r="B204" s="29"/>
       <c r="C204" s="29" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D204" s="31" t="s">
         <v>39</v>
@@ -12971,7 +12965,7 @@
         <v>40</v>
       </c>
       <c r="F204" s="29" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G204" s="54">
         <v>20531</v>
@@ -12996,7 +12990,7 @@
         <v>155</v>
       </c>
       <c r="N204" s="29" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="O204" s="146"/>
       <c r="P204" s="46" t="s">
@@ -13042,10 +13036,10 @@
         <v>27</v>
       </c>
       <c r="M205" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N205" s="25" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O205" s="145" t="s">
         <v>36</v>
@@ -13089,10 +13083,10 @@
         <v>27</v>
       </c>
       <c r="M206" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N206" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O206" s="146"/>
       <c r="P206" s="19" t="s">
@@ -13134,10 +13128,10 @@
         <v>27</v>
       </c>
       <c r="M207" s="35" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N207" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O207" s="147"/>
       <c r="P207" s="19" t="s">
@@ -13184,7 +13178,7 @@
         <v>98</v>
       </c>
       <c r="N208" s="35" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O208" s="87" t="s">
         <v>36</v>
@@ -13324,10 +13318,10 @@
         <v>27</v>
       </c>
       <c r="M211" s="35" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="N211" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O211" s="146"/>
       <c r="P211" s="46" t="s">
@@ -13369,10 +13363,10 @@
         <v>27</v>
       </c>
       <c r="M212" s="35" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="N212" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O212" s="146"/>
       <c r="P212" s="46" t="s">
@@ -13421,7 +13415,7 @@
         <v>98</v>
       </c>
       <c r="N213" s="25" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="O213" s="145" t="s">
         <v>30</v>
@@ -13465,10 +13459,10 @@
         <v>27</v>
       </c>
       <c r="M214" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N214" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O214" s="146"/>
       <c r="P214" s="19" t="s">
@@ -13510,10 +13504,10 @@
         <v>27</v>
       </c>
       <c r="M215" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N215" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O215" s="146"/>
       <c r="P215" s="19" t="s">
@@ -13558,7 +13552,7 @@
         <v>98</v>
       </c>
       <c r="N216" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O216" s="147"/>
       <c r="P216" s="19"/>
@@ -13605,7 +13599,7 @@
         <v>204</v>
       </c>
       <c r="N217" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O217" s="145" t="s">
         <v>36</v>
@@ -13697,7 +13691,7 @@
         <v>719</v>
       </c>
       <c r="N219" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O219" s="146"/>
       <c r="P219" s="19" t="s">
@@ -13742,7 +13736,7 @@
         <v>98</v>
       </c>
       <c r="N220" s="35" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O220" s="147"/>
       <c r="P220" s="19" t="s">
@@ -13788,10 +13782,10 @@
         <v>27</v>
       </c>
       <c r="M221" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N221" s="25" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O221" s="145" t="s">
         <v>36</v>
@@ -13835,10 +13829,10 @@
         <v>27</v>
       </c>
       <c r="M222" s="29" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="N222" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O222" s="146"/>
       <c r="P222" s="46" t="s">
@@ -13880,10 +13874,10 @@
         <v>27</v>
       </c>
       <c r="M223" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N223" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O223" s="146"/>
       <c r="P223" s="46" t="s">
@@ -13928,7 +13922,7 @@
         <v>719</v>
       </c>
       <c r="N224" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O224" s="146"/>
       <c r="P224" s="46" t="s">
@@ -13998,10 +13992,10 @@
         <v>27</v>
       </c>
       <c r="M226" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N226" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O226" s="145" t="s">
         <v>36</v>
@@ -14045,10 +14039,10 @@
         <v>27</v>
       </c>
       <c r="M227" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N227" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O227" s="146"/>
       <c r="P227" s="19" t="s">
@@ -14090,10 +14084,10 @@
         <v>27</v>
       </c>
       <c r="M228" s="35" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N228" s="35" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O228" s="146"/>
       <c r="P228" s="19" t="s">
@@ -14138,7 +14132,7 @@
         <v>204</v>
       </c>
       <c r="N229" s="29" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="O229" s="146"/>
       <c r="P229" s="19" t="s">
@@ -14149,7 +14143,7 @@
       <c r="A230" s="146"/>
       <c r="B230" s="91"/>
       <c r="C230" s="91" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D230" s="97" t="s">
         <v>39</v>
@@ -14183,7 +14177,7 @@
         <v>155</v>
       </c>
       <c r="N230" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O230" s="146"/>
       <c r="P230" s="19" t="s">
@@ -14229,10 +14223,10 @@
         <v>27</v>
       </c>
       <c r="M231" s="25" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N231" s="25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="O231" s="154" t="s">
         <v>36</v>
@@ -14276,10 +14270,10 @@
         <v>27</v>
       </c>
       <c r="M232" s="29" t="s">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="N232" s="29" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O232" s="154"/>
       <c r="P232" s="46" t="s">
@@ -14324,7 +14318,7 @@
         <v>98</v>
       </c>
       <c r="N233" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O233" s="154"/>
       <c r="P233" s="46" t="s">
@@ -14369,7 +14363,7 @@
         <v>98</v>
       </c>
       <c r="N234" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O234" s="146"/>
       <c r="P234" s="46" t="s">
@@ -14414,7 +14408,7 @@
         <v>98</v>
       </c>
       <c r="N235" s="29" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="O235" s="146"/>
       <c r="P235" s="46" t="s">
@@ -14459,7 +14453,7 @@
         <v>719</v>
       </c>
       <c r="N236" s="29" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="O236" s="146"/>
       <c r="P236" s="46" t="s">
@@ -14504,7 +14498,7 @@
         <v>98</v>
       </c>
       <c r="N237" s="35" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="O237" s="147"/>
       <c r="P237" s="46" t="s">

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184ABF8C-C25E-42A5-9F42-68653E452146}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A434036-948D-457D-A7AB-6F65CD4F9AE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4103,8 +4103,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>72</v>
       </c>
-      <c r="I11" s="35" t="s">
-        <v>53</v>
+      <c r="I11" s="25" t="s">
+        <v>695</v>
       </c>
       <c r="J11" s="35" t="s">
         <v>25</v>
@@ -4282,8 +4282,8 @@
       <c r="L15" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="25" t="s">
-        <v>98</v>
+      <c r="M15" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N15" s="25" t="s">
         <v>738</v>
@@ -4329,8 +4329,8 @@
       <c r="L16" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="25" t="s">
-        <v>98</v>
+      <c r="M16" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N16" s="35" t="s">
         <v>737</v>
@@ -5023,7 +5023,7 @@
         <v>27</v>
       </c>
       <c r="M31" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N31" s="29" t="s">
         <v>739</v>
@@ -5347,8 +5347,8 @@
       <c r="L38" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="M38" s="25" t="s">
-        <v>98</v>
+      <c r="M38" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N38" s="25" t="s">
         <v>738</v>
@@ -7531,7 +7531,7 @@
         <v>27</v>
       </c>
       <c r="M85" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N85" s="35" t="s">
         <v>739</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="M106" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N106" s="29" t="s">
         <v>739</v>
@@ -9743,8 +9743,8 @@
       <c r="L133" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="M133" s="32" t="s">
-        <v>98</v>
+      <c r="M133" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N133" s="35" t="s">
         <v>736</v>
@@ -10303,8 +10303,8 @@
       <c r="L145" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="M145" s="32" t="s">
-        <v>98</v>
+      <c r="M145" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N145" s="126" t="s">
         <v>735</v>
@@ -10348,8 +10348,8 @@
       <c r="L146" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="M146" s="32" t="s">
-        <v>98</v>
+      <c r="M146" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N146" s="29" t="s">
         <v>737</v>
@@ -11590,7 +11590,7 @@
         <v>27</v>
       </c>
       <c r="M173" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N173" s="35" t="s">
         <v>739</v>
@@ -11638,8 +11638,8 @@
       <c r="L174" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="M174" s="32" t="s">
-        <v>98</v>
+      <c r="M174" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N174" s="25" t="s">
         <v>738</v>
@@ -12379,7 +12379,7 @@
         <v>27</v>
       </c>
       <c r="M190" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N190" s="35" t="s">
         <v>739</v>
@@ -12754,7 +12754,7 @@
         <v>27</v>
       </c>
       <c r="M199" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N199" s="26" t="s">
         <v>738</v>
@@ -13024,7 +13024,7 @@
         <v>64</v>
       </c>
       <c r="I205" s="25" t="s">
-        <v>53</v>
+        <v>695</v>
       </c>
       <c r="J205" s="25" t="s">
         <v>25</v>
@@ -13162,8 +13162,8 @@
         <f t="shared" ca="1" si="3"/>
         <v>68</v>
       </c>
-      <c r="I208" s="35" t="s">
-        <v>24</v>
+      <c r="I208" s="25" t="s">
+        <v>695</v>
       </c>
       <c r="J208" s="35" t="s">
         <v>25</v>
@@ -13175,7 +13175,7 @@
         <v>27</v>
       </c>
       <c r="M208" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N208" s="35" t="s">
         <v>737</v>
@@ -13411,8 +13411,8 @@
       <c r="L213" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="M213" s="25" t="s">
-        <v>98</v>
+      <c r="M213" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N213" s="25" t="s">
         <v>738</v>
@@ -13549,7 +13549,7 @@
         <v>27</v>
       </c>
       <c r="M216" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N216" s="35" t="s">
         <v>739</v>
@@ -13720,8 +13720,8 @@
         <f t="shared" ca="1" si="3"/>
         <v>59</v>
       </c>
-      <c r="I220" s="35" t="s">
-        <v>53</v>
+      <c r="I220" s="26" t="s">
+        <v>713</v>
       </c>
       <c r="J220" s="35" t="s">
         <v>25</v>
@@ -13733,7 +13733,7 @@
         <v>27</v>
       </c>
       <c r="M220" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N220" s="35" t="s">
         <v>737</v>
@@ -14314,8 +14314,8 @@
       <c r="L233" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M233" s="29" t="s">
-        <v>98</v>
+      <c r="M233" s="35" t="s">
+        <v>762</v>
       </c>
       <c r="N233" s="29" t="s">
         <v>739</v>
@@ -14360,7 +14360,7 @@
         <v>27</v>
       </c>
       <c r="M234" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N234" s="29" t="s">
         <v>739</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="M235" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N235" s="29" t="s">
         <v>739</v>
@@ -14482,8 +14482,8 @@
         <f ca="1">INT((TODAY()-G237)/365)</f>
         <v>71</v>
       </c>
-      <c r="I237" s="35" t="s">
-        <v>53</v>
+      <c r="I237" s="25" t="s">
+        <v>695</v>
       </c>
       <c r="J237" s="35" t="s">
         <v>25</v>
@@ -14495,7 +14495,7 @@
         <v>27</v>
       </c>
       <c r="M237" s="35" t="s">
-        <v>98</v>
+        <v>762</v>
       </c>
       <c r="N237" s="35" t="s">
         <v>737</v>

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A434036-948D-457D-A7AB-6F65CD4F9AE5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2762271B-1E31-403E-9CAE-5A1010664AE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5904" uniqueCount="763">
   <si>
     <t>DAFTAR PENDUDUK RT 06 - RW 14</t>
   </si>
@@ -3044,35 +3044,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3082,6 +3070,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3741,108 +3741,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="18.75">
-      <c r="A1" s="149"/>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="149"/>
-      <c r="P1" s="149"/>
+      <c r="A1" s="158"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="18.75">
-      <c r="A2" s="149"/>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
-      <c r="M2" s="149"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="149"/>
-      <c r="P2" s="149"/>
+      <c r="A2" s="158"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="158"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="150" t="s">
+      <c r="A4" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="152" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="150" t="s">
+      <c r="C4" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="150" t="s">
+      <c r="D4" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="150" t="s">
+      <c r="E4" s="152" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="150" t="s">
+      <c r="F4" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="150" t="s">
+      <c r="G4" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="150" t="s">
+      <c r="H4" s="152" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="150" t="s">
+      <c r="I4" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="150" t="s">
+      <c r="J4" s="152" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="150" t="s">
+      <c r="K4" s="152" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="150" t="s">
+      <c r="L4" s="152" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="152" t="s">
+      <c r="M4" s="159" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="150" t="s">
+      <c r="N4" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="150" t="s">
+      <c r="O4" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="150" t="s">
+      <c r="P4" s="152" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="151"/>
-      <c r="B5" s="151"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="151"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="151"/>
-      <c r="L5" s="151"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="151"/>
-      <c r="O5" s="151"/>
-      <c r="P5" s="151"/>
+      <c r="A5" s="153"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="153"/>
+      <c r="I5" s="153"/>
+      <c r="J5" s="153"/>
+      <c r="K5" s="153"/>
+      <c r="L5" s="153"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="153"/>
+      <c r="O5" s="153"/>
+      <c r="P5" s="153"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="14" t="s">
@@ -6240,7 +6240,7 @@
       </c>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1">
-      <c r="A58" s="158" t="s">
+      <c r="A58" s="154" t="s">
         <v>131</v>
       </c>
       <c r="B58" s="38" t="s">
@@ -6291,7 +6291,7 @@
       </c>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1">
-      <c r="A59" s="159"/>
+      <c r="A59" s="155"/>
       <c r="B59" s="29"/>
       <c r="C59" s="29" t="s">
         <v>134</v>
@@ -6336,7 +6336,7 @@
       </c>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1">
-      <c r="A60" s="159"/>
+      <c r="A60" s="155"/>
       <c r="B60" s="29"/>
       <c r="C60" s="29" t="s">
         <v>135</v>
@@ -6381,7 +6381,7 @@
       </c>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1">
-      <c r="A61" s="159"/>
+      <c r="A61" s="155"/>
       <c r="B61" s="29"/>
       <c r="C61" s="29" t="s">
         <v>136</v>
@@ -6426,7 +6426,7 @@
       </c>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1">
-      <c r="A62" s="160"/>
+      <c r="A62" s="156"/>
       <c r="B62" s="35"/>
       <c r="C62" s="35" t="s">
         <v>137</v>
@@ -6702,7 +6702,7 @@
       </c>
     </row>
     <row r="68" spans="1:16" s="2" customFormat="1">
-      <c r="A68" s="158" t="s">
+      <c r="A68" s="154" t="s">
         <v>144</v>
       </c>
       <c r="B68" s="38" t="s">
@@ -6753,7 +6753,7 @@
       </c>
     </row>
     <row r="69" spans="1:16" s="2" customFormat="1">
-      <c r="A69" s="159"/>
+      <c r="A69" s="155"/>
       <c r="B69" s="29"/>
       <c r="C69" s="29" t="s">
         <v>146</v>
@@ -6798,7 +6798,7 @@
       </c>
     </row>
     <row r="70" spans="1:16" s="2" customFormat="1">
-      <c r="A70" s="159"/>
+      <c r="A70" s="155"/>
       <c r="B70" s="29"/>
       <c r="C70" s="29" t="s">
         <v>147</v>
@@ -6843,7 +6843,7 @@
       </c>
     </row>
     <row r="71" spans="1:16" s="2" customFormat="1">
-      <c r="A71" s="160"/>
+      <c r="A71" s="156"/>
       <c r="B71" s="35"/>
       <c r="C71" s="35" t="s">
         <v>148</v>
@@ -6888,7 +6888,7 @@
       </c>
     </row>
     <row r="72" spans="1:16" s="2" customFormat="1">
-      <c r="A72" s="158" t="s">
+      <c r="A72" s="154" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="38" t="s">
@@ -6939,7 +6939,7 @@
       </c>
     </row>
     <row r="73" spans="1:16" s="2" customFormat="1">
-      <c r="A73" s="159"/>
+      <c r="A73" s="155"/>
       <c r="B73" s="29"/>
       <c r="C73" s="29" t="s">
         <v>151</v>
@@ -6984,7 +6984,7 @@
       </c>
     </row>
     <row r="74" spans="1:16" s="2" customFormat="1">
-      <c r="A74" s="159"/>
+      <c r="A74" s="155"/>
       <c r="B74" s="29"/>
       <c r="C74" s="29" t="s">
         <v>152</v>
@@ -7029,7 +7029,7 @@
       </c>
     </row>
     <row r="75" spans="1:16" s="2" customFormat="1">
-      <c r="A75" s="160"/>
+      <c r="A75" s="156"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35" t="s">
         <v>153</v>
@@ -7074,7 +7074,7 @@
       </c>
     </row>
     <row r="76" spans="1:16" s="2" customFormat="1">
-      <c r="A76" s="155" t="s">
+      <c r="A76" s="150" t="s">
         <v>154</v>
       </c>
       <c r="B76" s="93" t="s">
@@ -7117,7 +7117,7 @@
       <c r="N76" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O76" s="155" t="s">
+      <c r="O76" s="150" t="s">
         <v>30</v>
       </c>
       <c r="P76" s="46" t="s">
@@ -7125,7 +7125,7 @@
       </c>
     </row>
     <row r="77" spans="1:16" s="2" customFormat="1">
-      <c r="A77" s="157"/>
+      <c r="A77" s="149"/>
       <c r="B77" s="94"/>
       <c r="C77" s="95" t="s">
         <v>694</v>
@@ -7164,7 +7164,7 @@
       <c r="N77" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O77" s="157"/>
+      <c r="O77" s="149"/>
       <c r="P77" s="46" t="s">
         <v>31</v>
       </c>
@@ -7356,7 +7356,7 @@
       </c>
     </row>
     <row r="82" spans="1:16" s="2" customFormat="1">
-      <c r="A82" s="158" t="s">
+      <c r="A82" s="154" t="s">
         <v>164</v>
       </c>
       <c r="B82" s="38" t="s">
@@ -7407,7 +7407,7 @@
       </c>
     </row>
     <row r="83" spans="1:16" s="2" customFormat="1">
-      <c r="A83" s="159"/>
+      <c r="A83" s="155"/>
       <c r="B83" s="29"/>
       <c r="C83" s="29" t="s">
         <v>166</v>
@@ -7452,7 +7452,7 @@
       </c>
     </row>
     <row r="84" spans="1:16" s="2" customFormat="1">
-      <c r="A84" s="159"/>
+      <c r="A84" s="155"/>
       <c r="B84" s="29"/>
       <c r="C84" s="29" t="s">
         <v>168</v>
@@ -7497,7 +7497,7 @@
       </c>
     </row>
     <row r="85" spans="1:16" s="2" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A85" s="160"/>
+      <c r="A85" s="156"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35" t="s">
         <v>169</v>
@@ -8100,7 +8100,7 @@
       </c>
     </row>
     <row r="98" spans="1:16" s="2" customFormat="1">
-      <c r="A98" s="154" t="s">
+      <c r="A98" s="151" t="s">
         <v>181</v>
       </c>
       <c r="B98" s="38" t="s">
@@ -8151,7 +8151,7 @@
       </c>
     </row>
     <row r="99" spans="1:16" s="2" customFormat="1">
-      <c r="A99" s="154"/>
+      <c r="A99" s="151"/>
       <c r="B99" s="29"/>
       <c r="C99" s="29" t="s">
         <v>183</v>
@@ -8196,7 +8196,7 @@
       </c>
     </row>
     <row r="100" spans="1:16" s="2" customFormat="1">
-      <c r="A100" s="154"/>
+      <c r="A100" s="151"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
         <v>184</v>
@@ -8241,7 +8241,7 @@
       </c>
     </row>
     <row r="101" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A101" s="155" t="s">
+      <c r="A101" s="150" t="s">
         <v>185</v>
       </c>
       <c r="B101" s="99" t="s">
@@ -8284,7 +8284,7 @@
       <c r="N101" s="32" t="s">
         <v>735</v>
       </c>
-      <c r="O101" s="156" t="s">
+      <c r="O101" s="148" t="s">
         <v>36</v>
       </c>
       <c r="P101" s="19" t="s">
@@ -8292,7 +8292,7 @@
       </c>
     </row>
     <row r="102" spans="1:16" s="2" customFormat="1">
-      <c r="A102" s="156"/>
+      <c r="A102" s="148"/>
       <c r="B102" s="99"/>
       <c r="C102" s="32" t="s">
         <v>188</v>
@@ -8331,13 +8331,13 @@
       <c r="N102" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O102" s="156"/>
+      <c r="O102" s="148"/>
       <c r="P102" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="103" spans="1:16" s="2" customFormat="1">
-      <c r="A103" s="156"/>
+      <c r="A103" s="148"/>
       <c r="B103" s="99"/>
       <c r="C103" s="32" t="s">
         <v>190</v>
@@ -8376,13 +8376,13 @@
       <c r="N103" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O103" s="156"/>
+      <c r="O103" s="148"/>
       <c r="P103" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="104" spans="1:16" s="2" customFormat="1">
-      <c r="A104" s="156"/>
+      <c r="A104" s="148"/>
       <c r="B104" s="99"/>
       <c r="C104" s="32" t="s">
         <v>191</v>
@@ -8421,13 +8421,13 @@
       <c r="N104" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O104" s="156"/>
+      <c r="O104" s="148"/>
       <c r="P104" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="105" spans="1:16" s="2" customFormat="1">
-      <c r="A105" s="156"/>
+      <c r="A105" s="148"/>
       <c r="B105" s="99"/>
       <c r="C105" s="32" t="s">
         <v>192</v>
@@ -8466,13 +8466,13 @@
       <c r="N105" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O105" s="156"/>
+      <c r="O105" s="148"/>
       <c r="P105" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="106" spans="1:16" s="84" customFormat="1">
-      <c r="A106" s="157"/>
+      <c r="A106" s="149"/>
       <c r="B106" s="101"/>
       <c r="C106" s="102" t="s">
         <v>193</v>
@@ -8511,7 +8511,7 @@
       <c r="N106" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O106" s="157"/>
+      <c r="O106" s="149"/>
       <c r="P106" s="19" t="s">
         <v>37</v>
       </c>
@@ -8979,7 +8979,7 @@
       </c>
     </row>
     <row r="117" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A117" s="155" t="s">
+      <c r="A117" s="150" t="s">
         <v>208</v>
       </c>
       <c r="B117" s="99" t="s">
@@ -9030,7 +9030,7 @@
       </c>
     </row>
     <row r="118" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A118" s="156"/>
+      <c r="A118" s="148"/>
       <c r="B118" s="99"/>
       <c r="C118" s="32" t="s">
         <v>210</v>
@@ -9075,7 +9075,7 @@
       </c>
     </row>
     <row r="119" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A119" s="156"/>
+      <c r="A119" s="148"/>
       <c r="B119" s="99"/>
       <c r="C119" s="32" t="s">
         <v>211</v>
@@ -9120,7 +9120,7 @@
       </c>
     </row>
     <row r="120" spans="1:16" s="84" customFormat="1">
-      <c r="A120" s="157"/>
+      <c r="A120" s="149"/>
       <c r="B120" s="101"/>
       <c r="C120" s="102" t="s">
         <v>212</v>
@@ -9610,7 +9610,7 @@
       <c r="P130" s="68"/>
     </row>
     <row r="131" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A131" s="155" t="s">
+      <c r="A131" s="150" t="s">
         <v>224</v>
       </c>
       <c r="B131" s="39" t="s">
@@ -9661,7 +9661,7 @@
       </c>
     </row>
     <row r="132" spans="1:16" s="84" customFormat="1">
-      <c r="A132" s="157"/>
+      <c r="A132" s="149"/>
       <c r="B132" s="101"/>
       <c r="C132" s="102" t="s">
         <v>227</v>
@@ -9988,7 +9988,7 @@
       </c>
     </row>
     <row r="139" spans="1:16" s="2" customFormat="1">
-      <c r="A139" s="148" t="s">
+      <c r="A139" s="157" t="s">
         <v>528</v>
       </c>
       <c r="B139" s="137" t="s">
@@ -10039,7 +10039,7 @@
       </c>
     </row>
     <row r="140" spans="1:16" s="2" customFormat="1">
-      <c r="A140" s="148"/>
+      <c r="A140" s="157"/>
       <c r="B140" s="138"/>
       <c r="C140" s="141" t="s">
         <v>751</v>
@@ -10084,7 +10084,7 @@
       </c>
     </row>
     <row r="141" spans="1:16" s="2" customFormat="1">
-      <c r="A141" s="148"/>
+      <c r="A141" s="157"/>
       <c r="B141" s="139"/>
       <c r="C141" s="142" t="s">
         <v>752</v>
@@ -11221,7 +11221,7 @@
       <c r="N165" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O165" s="154" t="s">
+      <c r="O165" s="151" t="s">
         <v>36</v>
       </c>
       <c r="P165" s="19" t="s">
@@ -11268,7 +11268,7 @@
       <c r="N166" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O166" s="154"/>
+      <c r="O166" s="151"/>
       <c r="P166" s="19" t="s">
         <v>37</v>
       </c>
@@ -11313,13 +11313,13 @@
       <c r="N167" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O167" s="154"/>
+      <c r="O167" s="151"/>
       <c r="P167" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="168" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A168" s="155" t="s">
+      <c r="A168" s="150" t="s">
         <v>252</v>
       </c>
       <c r="B168" s="99" t="s">
@@ -11370,7 +11370,7 @@
       </c>
     </row>
     <row r="169" spans="1:16" s="2" customFormat="1">
-      <c r="A169" s="156"/>
+      <c r="A169" s="148"/>
       <c r="B169" s="32"/>
       <c r="C169" s="106" t="s">
         <v>698</v>
@@ -11601,7 +11601,7 @@
       </c>
     </row>
     <row r="174" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A174" s="155" t="s">
+      <c r="A174" s="150" t="s">
         <v>264</v>
       </c>
       <c r="B174" s="99" t="s">
@@ -11652,7 +11652,7 @@
       </c>
     </row>
     <row r="175" spans="1:16" s="2" customFormat="1">
-      <c r="A175" s="156"/>
+      <c r="A175" s="148"/>
       <c r="B175" s="32"/>
       <c r="C175" s="106" t="s">
         <v>254</v>
@@ -11697,7 +11697,7 @@
       </c>
     </row>
     <row r="176" spans="1:16" s="2" customFormat="1">
-      <c r="A176" s="156"/>
+      <c r="A176" s="148"/>
       <c r="B176" s="32"/>
       <c r="C176" s="106" t="s">
         <v>255</v>
@@ -11742,7 +11742,7 @@
       </c>
     </row>
     <row r="177" spans="1:16" s="84" customFormat="1">
-      <c r="A177" s="157"/>
+      <c r="A177" s="149"/>
       <c r="B177" s="101"/>
       <c r="C177" s="102" t="s">
         <v>256</v>
@@ -11787,7 +11787,7 @@
       </c>
     </row>
     <row r="178" spans="1:16" s="84" customFormat="1" ht="15" customHeight="1">
-      <c r="A178" s="155" t="s">
+      <c r="A178" s="150" t="s">
         <v>265</v>
       </c>
       <c r="B178" s="93" t="s">
@@ -11830,7 +11830,7 @@
       <c r="N178" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O178" s="155" t="s">
+      <c r="O178" s="150" t="s">
         <v>30</v>
       </c>
       <c r="P178" s="19" t="s">
@@ -11838,7 +11838,7 @@
       </c>
     </row>
     <row r="179" spans="1:16" s="84" customFormat="1">
-      <c r="A179" s="156"/>
+      <c r="A179" s="148"/>
       <c r="B179" s="101"/>
       <c r="C179" s="102" t="s">
         <v>756</v>
@@ -11877,13 +11877,13 @@
       <c r="N179" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O179" s="156"/>
+      <c r="O179" s="148"/>
       <c r="P179" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="180" spans="1:16" s="84" customFormat="1">
-      <c r="A180" s="156"/>
+      <c r="A180" s="148"/>
       <c r="B180" s="101"/>
       <c r="C180" s="102" t="s">
         <v>757</v>
@@ -11922,13 +11922,13 @@
       <c r="N180" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O180" s="156"/>
+      <c r="O180" s="148"/>
       <c r="P180" s="19" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="181" spans="1:16" s="84" customFormat="1">
-      <c r="A181" s="156"/>
+      <c r="A181" s="148"/>
       <c r="B181" s="101"/>
       <c r="C181" s="102" t="s">
         <v>758</v>
@@ -11967,7 +11967,7 @@
       <c r="N181" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O181" s="157"/>
+      <c r="O181" s="149"/>
       <c r="P181" s="19" t="s">
         <v>31</v>
       </c>
@@ -13374,7 +13374,7 @@
       </c>
     </row>
     <row r="213" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A213" s="155" t="s">
+      <c r="A213" s="150" t="s">
         <v>313</v>
       </c>
       <c r="B213" s="39" t="s">
@@ -13425,7 +13425,7 @@
       </c>
     </row>
     <row r="214" spans="1:16" s="2" customFormat="1">
-      <c r="A214" s="156"/>
+      <c r="A214" s="148"/>
       <c r="B214" s="29"/>
       <c r="C214" s="30" t="s">
         <v>315</v>
@@ -13470,7 +13470,7 @@
       </c>
     </row>
     <row r="215" spans="1:16" s="2" customFormat="1">
-      <c r="A215" s="156"/>
+      <c r="A215" s="148"/>
       <c r="B215" s="29"/>
       <c r="C215" s="30" t="s">
         <v>316</v>
@@ -13515,7 +13515,7 @@
       </c>
     </row>
     <row r="216" spans="1:16" s="2" customFormat="1">
-      <c r="A216" s="157"/>
+      <c r="A216" s="149"/>
       <c r="B216" s="35"/>
       <c r="C216" s="36" t="s">
         <v>318</v>
@@ -13949,9 +13949,7 @@
       <c r="O225" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="P225" s="46" t="s">
-        <v>31</v>
-      </c>
+      <c r="P225" s="46"/>
     </row>
     <row r="226" spans="1:253" s="2" customFormat="1">
       <c r="A226" s="145" t="s">
@@ -14185,7 +14183,7 @@
       </c>
     </row>
     <row r="231" spans="1:253" s="2" customFormat="1">
-      <c r="A231" s="154" t="s">
+      <c r="A231" s="151" t="s">
         <v>335</v>
       </c>
       <c r="B231" s="39" t="s">
@@ -14228,7 +14226,7 @@
       <c r="N231" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O231" s="154" t="s">
+      <c r="O231" s="151" t="s">
         <v>36</v>
       </c>
       <c r="P231" s="46" t="s">
@@ -14236,7 +14234,7 @@
       </c>
     </row>
     <row r="232" spans="1:253" s="2" customFormat="1">
-      <c r="A232" s="154"/>
+      <c r="A232" s="151"/>
       <c r="B232" s="29"/>
       <c r="C232" s="30" t="s">
         <v>337</v>
@@ -14275,13 +14273,13 @@
       <c r="N232" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O232" s="154"/>
+      <c r="O232" s="151"/>
       <c r="P232" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="233" spans="1:253" s="2" customFormat="1">
-      <c r="A233" s="154"/>
+      <c r="A233" s="151"/>
       <c r="B233" s="29"/>
       <c r="C233" s="30" t="s">
         <v>338</v>
@@ -14320,13 +14318,13 @@
       <c r="N233" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O233" s="154"/>
+      <c r="O233" s="151"/>
       <c r="P233" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="234" spans="1:253" s="2" customFormat="1">
-      <c r="A234" s="154"/>
+      <c r="A234" s="151"/>
       <c r="B234" s="29"/>
       <c r="C234" s="30" t="s">
         <v>339</v>
@@ -14371,7 +14369,7 @@
       </c>
     </row>
     <row r="235" spans="1:253" s="2" customFormat="1">
-      <c r="A235" s="154"/>
+      <c r="A235" s="151"/>
       <c r="B235" s="29"/>
       <c r="C235" s="30" t="s">
         <v>340</v>
@@ -14416,7 +14414,7 @@
       </c>
     </row>
     <row r="236" spans="1:253" s="2" customFormat="1">
-      <c r="A236" s="154"/>
+      <c r="A236" s="151"/>
       <c r="B236" s="29"/>
       <c r="C236" s="30" t="s">
         <v>341</v>
@@ -14461,7 +14459,7 @@
       </c>
     </row>
     <row r="237" spans="1:253" s="2" customFormat="1">
-      <c r="A237" s="154"/>
+      <c r="A237" s="151"/>
       <c r="B237" s="35"/>
       <c r="C237" s="36" t="s">
         <v>342</v>
@@ -14506,10 +14504,6 @@
       </c>
     </row>
     <row r="238" spans="1:253">
-      <c r="D238" s="4">
-        <f>COUNTA(D6:D237)</f>
-        <v>226</v>
-      </c>
       <c r="E238" s="111"/>
       <c r="F238" s="112"/>
     </row>
@@ -15276,28 +15270,81 @@
   </sheetData>
   <autoFilter ref="A4:P240" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="126">
-    <mergeCell ref="O91:O93"/>
-    <mergeCell ref="O94:O97"/>
-    <mergeCell ref="O98:O100"/>
-    <mergeCell ref="O49:O53"/>
-    <mergeCell ref="O54:O57"/>
-    <mergeCell ref="O58:O62"/>
-    <mergeCell ref="O63:O67"/>
-    <mergeCell ref="O68:O71"/>
-    <mergeCell ref="O142:O148"/>
-    <mergeCell ref="O213:O216"/>
-    <mergeCell ref="O101:O106"/>
-    <mergeCell ref="O117:O120"/>
-    <mergeCell ref="O131:O132"/>
-    <mergeCell ref="O153:O160"/>
-    <mergeCell ref="O168:O169"/>
-    <mergeCell ref="A153:A160"/>
-    <mergeCell ref="O127:O129"/>
-    <mergeCell ref="A127:A129"/>
-    <mergeCell ref="O174:O177"/>
-    <mergeCell ref="O199:O202"/>
-    <mergeCell ref="O178:O181"/>
-    <mergeCell ref="O107:O112"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="A226:A230"/>
+    <mergeCell ref="A231:A237"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="A195:A198"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="A205:A207"/>
+    <mergeCell ref="A209:A212"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="A186:A190"/>
+    <mergeCell ref="A124:A126"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="A133:A137"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A161:A164"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="A101:A106"/>
+    <mergeCell ref="A107:A112"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A217:A220"/>
+    <mergeCell ref="A221:A224"/>
+    <mergeCell ref="A113:A116"/>
+    <mergeCell ref="A117:A120"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A91:A93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A86:A90"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="A139:A141"/>
+    <mergeCell ref="O15:O19"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A58:A62"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="O28:O32"/>
+    <mergeCell ref="O33:O37"/>
+    <mergeCell ref="O38:O40"/>
+    <mergeCell ref="O41:O44"/>
+    <mergeCell ref="O45:O48"/>
+    <mergeCell ref="A28:A32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="O20:O23"/>
+    <mergeCell ref="O24:O27"/>
     <mergeCell ref="O221:O224"/>
     <mergeCell ref="O226:O230"/>
     <mergeCell ref="O231:O237"/>
@@ -15322,86 +15369,33 @@
     <mergeCell ref="O82:O85"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="O7:O11"/>
-    <mergeCell ref="O15:O19"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="A58:A62"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="O28:O32"/>
-    <mergeCell ref="O33:O37"/>
-    <mergeCell ref="O38:O40"/>
-    <mergeCell ref="O41:O44"/>
-    <mergeCell ref="O45:O48"/>
-    <mergeCell ref="A28:A32"/>
-    <mergeCell ref="A33:A37"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="O20:O23"/>
+    <mergeCell ref="O213:O216"/>
+    <mergeCell ref="O101:O106"/>
+    <mergeCell ref="O117:O120"/>
+    <mergeCell ref="O131:O132"/>
+    <mergeCell ref="O153:O160"/>
+    <mergeCell ref="O168:O169"/>
+    <mergeCell ref="A153:A160"/>
+    <mergeCell ref="O127:O129"/>
+    <mergeCell ref="A127:A129"/>
+    <mergeCell ref="O174:O177"/>
+    <mergeCell ref="O199:O202"/>
+    <mergeCell ref="O178:O181"/>
+    <mergeCell ref="O107:O112"/>
     <mergeCell ref="A213:A216"/>
-    <mergeCell ref="A217:A220"/>
-    <mergeCell ref="A221:A224"/>
-    <mergeCell ref="A113:A116"/>
-    <mergeCell ref="A117:A120"/>
-    <mergeCell ref="A121:A123"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A91:A93"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A86:A90"/>
-    <mergeCell ref="A174:A177"/>
-    <mergeCell ref="A226:A230"/>
-    <mergeCell ref="A231:A237"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="A195:A198"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="A205:A207"/>
-    <mergeCell ref="A209:A212"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A178:A181"/>
-    <mergeCell ref="A182:A185"/>
-    <mergeCell ref="A186:A190"/>
-    <mergeCell ref="A124:A126"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="A133:A137"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A161:A164"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="A101:A106"/>
-    <mergeCell ref="A107:A112"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A27"/>
     <mergeCell ref="O139:O141"/>
-    <mergeCell ref="A139:A141"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O91:O93"/>
+    <mergeCell ref="O94:O97"/>
+    <mergeCell ref="O98:O100"/>
+    <mergeCell ref="O49:O53"/>
+    <mergeCell ref="O54:O57"/>
+    <mergeCell ref="O58:O62"/>
+    <mergeCell ref="O63:O67"/>
+    <mergeCell ref="O68:O71"/>
+    <mergeCell ref="O142:O148"/>
     <mergeCell ref="O72:O75"/>
     <mergeCell ref="O76:O77"/>
-    <mergeCell ref="O12:O13"/>
     <mergeCell ref="O86:O90"/>
-    <mergeCell ref="O24:O27"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15748031496062992" right="0.23622047244094491" top="0.19685039370078741" bottom="0.23622047244094491" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2762271B-1E31-403E-9CAE-5A1010664AE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4D934E-632B-4BA1-B03F-0158C22C301E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5904" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5906" uniqueCount="762">
   <si>
     <t>DAFTAR PENDUDUK RT 06 - RW 14</t>
   </si>
@@ -2297,9 +2297,6 @@
   </si>
   <si>
     <t>RIFQIU ATTAUFIQI</t>
-  </si>
-  <si>
-    <t>p</t>
   </si>
   <si>
     <t>ERNY NURLAENY</t>
@@ -2859,9 +2856,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3082,6 +3076,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3741,108 +3738,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="18.75">
-      <c r="A1" s="158"/>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
+      <c r="A1" s="157"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="18.75">
-      <c r="A2" s="158"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
+      <c r="A2" s="157"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="151" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="152" t="s">
+      <c r="C4" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="152" t="s">
+      <c r="D4" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="152" t="s">
+      <c r="E4" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="152" t="s">
+      <c r="F4" s="151" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="152" t="s">
+      <c r="G4" s="151" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="152" t="s">
+      <c r="H4" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="152" t="s">
+      <c r="I4" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="152" t="s">
+      <c r="J4" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="152" t="s">
+      <c r="K4" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="152" t="s">
+      <c r="L4" s="151" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="159" t="s">
+      <c r="M4" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="152" t="s">
+      <c r="N4" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="152" t="s">
+      <c r="O4" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="152" t="s">
+      <c r="P4" s="151" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="153"/>
-      <c r="B5" s="153"/>
-      <c r="C5" s="153"/>
-      <c r="D5" s="153"/>
-      <c r="E5" s="153"/>
-      <c r="F5" s="153"/>
-      <c r="G5" s="153"/>
-      <c r="H5" s="153"/>
-      <c r="I5" s="153"/>
-      <c r="J5" s="153"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="153"/>
-      <c r="M5" s="160"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="153"/>
+      <c r="A5" s="152"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="14" t="s">
@@ -3883,7 +3880,7 @@
         <v>27</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N6" s="19" t="s">
         <v>735</v>
@@ -3896,7 +3893,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="144" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="23" t="s">
@@ -3934,12 +3931,12 @@
         <v>27</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N7" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O7" s="145" t="s">
+      <c r="O7" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P7" s="19" t="s">
@@ -3947,7 +3944,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1">
-      <c r="A8" s="146"/>
+      <c r="A8" s="145"/>
       <c r="B8" s="29"/>
       <c r="C8" s="30" t="s">
         <v>38</v>
@@ -3981,18 +3978,18 @@
         <v>27</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N8" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O8" s="146"/>
+      <c r="O8" s="145"/>
       <c r="P8" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1">
-      <c r="A9" s="146"/>
+      <c r="A9" s="145"/>
       <c r="B9" s="29"/>
       <c r="C9" s="30" t="s">
         <v>43</v>
@@ -4031,13 +4028,13 @@
       <c r="N9" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O9" s="146"/>
+      <c r="O9" s="145"/>
       <c r="P9" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1">
-      <c r="A10" s="146"/>
+      <c r="A10" s="145"/>
       <c r="B10" s="29"/>
       <c r="C10" s="30" t="s">
         <v>47</v>
@@ -4071,18 +4068,18 @@
         <v>27</v>
       </c>
       <c r="M10" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N10" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O10" s="146"/>
+      <c r="O10" s="145"/>
       <c r="P10" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1">
-      <c r="A11" s="147"/>
+      <c r="A11" s="146"/>
       <c r="B11" s="35"/>
       <c r="C11" s="36" t="s">
         <v>51</v>
@@ -4116,18 +4113,18 @@
         <v>27</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N11" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="O11" s="147"/>
+      <c r="O11" s="146"/>
       <c r="P11" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1">
-      <c r="A12" s="145" t="s">
+      <c r="A12" s="144" t="s">
         <v>54</v>
       </c>
       <c r="B12" s="38" t="s">
@@ -4165,12 +4162,12 @@
         <v>27</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N12" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O12" s="145" t="s">
+      <c r="O12" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P12" s="46" t="s">
@@ -4178,7 +4175,7 @@
       </c>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1">
-      <c r="A13" s="147"/>
+      <c r="A13" s="146"/>
       <c r="B13" s="35"/>
       <c r="C13" s="36" t="s">
         <v>56</v>
@@ -4212,40 +4209,40 @@
         <v>27</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N13" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="O13" s="147"/>
+      <c r="O13" s="146"/>
       <c r="P13" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="89"/>
       <c r="D14" s="66"/>
       <c r="E14" s="68"/>
       <c r="F14" s="67"/>
       <c r="G14" s="82"/>
-      <c r="H14" s="92"/>
+      <c r="H14" s="91"/>
       <c r="I14" s="68"/>
       <c r="J14" s="68"/>
       <c r="K14" s="68"/>
       <c r="L14" s="66"/>
       <c r="M14" s="68"/>
       <c r="N14" s="68"/>
-      <c r="O14" s="90" t="s">
+      <c r="O14" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="P14" s="133"/>
+      <c r="P14" s="132"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="144" t="s">
         <v>59</v>
       </c>
       <c r="B15" s="39" t="s">
@@ -4283,12 +4280,12 @@
         <v>27</v>
       </c>
       <c r="M15" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N15" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O15" s="145" t="s">
+      <c r="O15" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P15" s="19" t="s">
@@ -4296,7 +4293,7 @@
       </c>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1">
-      <c r="A16" s="146"/>
+      <c r="A16" s="145"/>
       <c r="B16" s="29"/>
       <c r="C16" s="29" t="s">
         <v>710</v>
@@ -4330,20 +4327,20 @@
         <v>27</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N16" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="O16" s="146"/>
+      <c r="O16" s="145"/>
       <c r="P16" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1">
-      <c r="A17" s="146"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91" t="s">
+      <c r="A17" s="145"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90" t="s">
         <v>711</v>
       </c>
       <c r="D17" s="31" t="s">
@@ -4375,23 +4372,23 @@
         <v>27</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N17" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O17" s="146"/>
+      <c r="O17" s="145"/>
       <c r="P17" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1">
-      <c r="A18" s="146"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="127" t="s">
+      <c r="A18" s="145"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="126" t="s">
         <v>740</v>
       </c>
-      <c r="D18" s="116" t="s">
+      <c r="D18" s="115" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="25" t="s">
@@ -4400,7 +4397,7 @@
       <c r="F18" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="124">
+      <c r="G18" s="123">
         <v>33579</v>
       </c>
       <c r="H18" s="58">
@@ -4416,27 +4413,27 @@
       <c r="K18" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="117" t="s">
+      <c r="L18" s="116" t="s">
         <v>27</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N18" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="O18" s="146"/>
+      <c r="O18" s="145"/>
       <c r="P18" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1">
-      <c r="A19" s="147"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="26"/>
-      <c r="C19" s="134" t="s">
+      <c r="C19" s="133" t="s">
         <v>741</v>
       </c>
-      <c r="D19" s="116" t="s">
+      <c r="D19" s="115" t="s">
         <v>39</v>
       </c>
       <c r="E19" s="29" t="s">
@@ -4445,7 +4442,7 @@
       <c r="F19" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="124">
+      <c r="G19" s="123">
         <v>35097</v>
       </c>
       <c r="H19" s="58">
@@ -4461,22 +4458,22 @@
       <c r="K19" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="118" t="s">
+      <c r="L19" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N19" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O19" s="147"/>
+      <c r="O19" s="146"/>
       <c r="P19" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1">
-      <c r="A20" s="145" t="s">
+      <c r="A20" s="144" t="s">
         <v>64</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -4514,12 +4511,12 @@
         <v>27</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N20" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O20" s="145" t="s">
+      <c r="O20" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P20" s="19" t="s">
@@ -4527,7 +4524,7 @@
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1">
-      <c r="A21" s="146"/>
+      <c r="A21" s="145"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29" t="s">
         <v>66</v>
@@ -4561,18 +4558,18 @@
         <v>27</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N21" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O21" s="146"/>
+      <c r="O21" s="145"/>
       <c r="P21" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1">
-      <c r="A22" s="146"/>
+      <c r="A22" s="145"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29" t="s">
         <v>67</v>
@@ -4611,13 +4608,13 @@
       <c r="N22" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O22" s="146"/>
+      <c r="O22" s="145"/>
       <c r="P22" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1">
-      <c r="A23" s="147"/>
+      <c r="A23" s="146"/>
       <c r="B23" s="35"/>
       <c r="C23" s="35" t="s">
         <v>69</v>
@@ -4651,18 +4648,18 @@
         <v>27</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N23" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O23" s="147"/>
+      <c r="O23" s="146"/>
       <c r="P23" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1">
-      <c r="A24" s="145" t="s">
+      <c r="A24" s="144" t="s">
         <v>70</v>
       </c>
       <c r="B24" s="38" t="s">
@@ -4696,16 +4693,16 @@
       <c r="K24" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="L24" s="119" t="s">
+      <c r="L24" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M24" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N24" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O24" s="145" t="s">
+      <c r="O24" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P24" s="19" t="s">
@@ -4713,7 +4710,7 @@
       </c>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1">
-      <c r="A25" s="146"/>
+      <c r="A25" s="145"/>
       <c r="B25" s="29"/>
       <c r="C25" s="29" t="s">
         <v>72</v>
@@ -4743,27 +4740,27 @@
       <c r="K25" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L25" s="119" t="s">
+      <c r="L25" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N25" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O25" s="146"/>
+      <c r="O25" s="145"/>
       <c r="P25" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1">
-      <c r="A26" s="146"/>
+      <c r="A26" s="145"/>
       <c r="B26" s="35"/>
       <c r="C26" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="119" t="s">
+      <c r="D26" s="118" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="35" t="s">
@@ -4788,22 +4785,22 @@
       <c r="K26" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L26" s="119" t="s">
+      <c r="L26" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N26" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O26" s="146"/>
+      <c r="O26" s="145"/>
       <c r="P26" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1">
-      <c r="A27" s="147"/>
+      <c r="A27" s="146"/>
       <c r="B27" s="35"/>
       <c r="C27" s="35" t="s">
         <v>712</v>
@@ -4833,7 +4830,7 @@
       <c r="K27" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L27" s="119" t="s">
+      <c r="L27" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M27" s="35" t="s">
@@ -4842,13 +4839,13 @@
       <c r="N27" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O27" s="147"/>
+      <c r="O27" s="146"/>
       <c r="P27" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1">
-      <c r="A28" s="145" t="s">
+      <c r="A28" s="144" t="s">
         <v>74</v>
       </c>
       <c r="B28" s="38" t="s">
@@ -4886,12 +4883,12 @@
         <v>77</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N28" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O28" s="145" t="s">
+      <c r="O28" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P28" s="19" t="s">
@@ -4899,7 +4896,7 @@
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1">
-      <c r="A29" s="146"/>
+      <c r="A29" s="145"/>
       <c r="B29" s="29"/>
       <c r="C29" s="29" t="s">
         <v>78</v>
@@ -4933,18 +4930,18 @@
         <v>27</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N29" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O29" s="146"/>
+      <c r="O29" s="145"/>
       <c r="P29" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1">
-      <c r="A30" s="146"/>
+      <c r="A30" s="145"/>
       <c r="B30" s="29"/>
       <c r="C30" s="29" t="s">
         <v>80</v>
@@ -4978,18 +4975,18 @@
         <v>27</v>
       </c>
       <c r="M30" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N30" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O30" s="146"/>
+      <c r="O30" s="145"/>
       <c r="P30" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1">
-      <c r="A31" s="146"/>
+      <c r="A31" s="145"/>
       <c r="B31" s="29"/>
       <c r="C31" s="29" t="s">
         <v>81</v>
@@ -5023,18 +5020,18 @@
         <v>27</v>
       </c>
       <c r="M31" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N31" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O31" s="146"/>
+      <c r="O31" s="145"/>
       <c r="P31" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1">
-      <c r="A32" s="147"/>
+      <c r="A32" s="146"/>
       <c r="B32" s="35"/>
       <c r="C32" s="35" t="s">
         <v>82</v>
@@ -5068,18 +5065,18 @@
         <v>27</v>
       </c>
       <c r="M32" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N32" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O32" s="147"/>
+      <c r="O32" s="146"/>
       <c r="P32" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1">
-      <c r="A33" s="145" t="s">
+      <c r="A33" s="144" t="s">
         <v>84</v>
       </c>
       <c r="B33" s="38" t="s">
@@ -5117,12 +5114,12 @@
         <v>87</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N33" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O33" s="145" t="s">
+      <c r="O33" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P33" s="19" t="s">
@@ -5130,7 +5127,7 @@
       </c>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1">
-      <c r="A34" s="146"/>
+      <c r="A34" s="145"/>
       <c r="B34" s="29"/>
       <c r="C34" s="29" t="s">
         <v>88</v>
@@ -5164,18 +5161,18 @@
         <v>89</v>
       </c>
       <c r="M34" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N34" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O34" s="146"/>
+      <c r="O34" s="145"/>
       <c r="P34" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1">
-      <c r="A35" s="146"/>
+      <c r="A35" s="145"/>
       <c r="B35" s="29"/>
       <c r="C35" s="29" t="s">
         <v>90</v>
@@ -5214,13 +5211,13 @@
       <c r="N35" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O35" s="146"/>
+      <c r="O35" s="145"/>
       <c r="P35" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1">
-      <c r="A36" s="146"/>
+      <c r="A36" s="145"/>
       <c r="B36" s="29"/>
       <c r="C36" s="29" t="s">
         <v>92</v>
@@ -5254,18 +5251,18 @@
         <v>27</v>
       </c>
       <c r="M36" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N36" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O36" s="146"/>
+      <c r="O36" s="145"/>
       <c r="P36" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1">
-      <c r="A37" s="147"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="35"/>
       <c r="C37" s="35" t="s">
         <v>94</v>
@@ -5299,18 +5296,18 @@
         <v>27</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N37" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O37" s="147"/>
+      <c r="O37" s="146"/>
       <c r="P37" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1">
-      <c r="A38" s="145" t="s">
+      <c r="A38" s="144" t="s">
         <v>95</v>
       </c>
       <c r="B38" s="38" t="s">
@@ -5348,12 +5345,12 @@
         <v>27</v>
       </c>
       <c r="M38" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N38" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O38" s="145" t="s">
+      <c r="O38" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P38" s="46" t="s">
@@ -5361,7 +5358,7 @@
       </c>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1">
-      <c r="A39" s="146"/>
+      <c r="A39" s="145"/>
       <c r="B39" s="29"/>
       <c r="C39" s="29" t="s">
         <v>705</v>
@@ -5395,18 +5392,18 @@
         <v>27</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N39" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O39" s="146"/>
+      <c r="O39" s="145"/>
       <c r="P39" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1">
-      <c r="A40" s="146"/>
+      <c r="A40" s="145"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29" t="s">
         <v>706</v>
@@ -5440,18 +5437,18 @@
         <v>27</v>
       </c>
       <c r="M40" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N40" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O40" s="146"/>
+      <c r="O40" s="145"/>
       <c r="P40" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1">
-      <c r="A41" s="145" t="s">
+      <c r="A41" s="144" t="s">
         <v>103</v>
       </c>
       <c r="B41" s="38" t="s">
@@ -5494,7 +5491,7 @@
       <c r="N41" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O41" s="145" t="s">
+      <c r="O41" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P41" s="19" t="s">
@@ -5502,7 +5499,7 @@
       </c>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1">
-      <c r="A42" s="146"/>
+      <c r="A42" s="145"/>
       <c r="B42" s="29"/>
       <c r="C42" s="29" t="s">
         <v>106</v>
@@ -5541,13 +5538,13 @@
       <c r="N42" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O42" s="146"/>
+      <c r="O42" s="145"/>
       <c r="P42" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1">
-      <c r="A43" s="146"/>
+      <c r="A43" s="145"/>
       <c r="B43" s="29"/>
       <c r="C43" s="29" t="s">
         <v>107</v>
@@ -5581,18 +5578,18 @@
         <v>27</v>
       </c>
       <c r="M43" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N43" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O43" s="146"/>
+      <c r="O43" s="145"/>
       <c r="P43" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1">
-      <c r="A44" s="147"/>
+      <c r="A44" s="146"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35" t="s">
         <v>108</v>
@@ -5631,13 +5628,13 @@
       <c r="N44" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O44" s="147"/>
+      <c r="O44" s="146"/>
       <c r="P44" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1">
-      <c r="A45" s="145" t="s">
+      <c r="A45" s="144" t="s">
         <v>109</v>
       </c>
       <c r="B45" s="38" t="s">
@@ -5675,12 +5672,12 @@
         <v>112</v>
       </c>
       <c r="M45" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N45" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O45" s="145" t="s">
+      <c r="O45" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P45" s="19" t="s">
@@ -5688,7 +5685,7 @@
       </c>
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1">
-      <c r="A46" s="146"/>
+      <c r="A46" s="145"/>
       <c r="B46" s="29"/>
       <c r="C46" s="29" t="s">
         <v>113</v>
@@ -5722,18 +5719,18 @@
         <v>27</v>
       </c>
       <c r="M46" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N46" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O46" s="146"/>
+      <c r="O46" s="145"/>
       <c r="P46" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1">
-      <c r="A47" s="146"/>
+      <c r="A47" s="145"/>
       <c r="B47" s="29"/>
       <c r="C47" s="29" t="s">
         <v>114</v>
@@ -5767,18 +5764,18 @@
         <v>27</v>
       </c>
       <c r="M47" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N47" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O47" s="146"/>
+      <c r="O47" s="145"/>
       <c r="P47" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:16" s="2" customFormat="1">
-      <c r="A48" s="147"/>
+      <c r="A48" s="146"/>
       <c r="B48" s="35"/>
       <c r="C48" s="35" t="s">
         <v>115</v>
@@ -5812,18 +5809,18 @@
         <v>27</v>
       </c>
       <c r="M48" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N48" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O48" s="147"/>
+      <c r="O48" s="146"/>
       <c r="P48" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:16" s="2" customFormat="1">
-      <c r="A49" s="145" t="s">
+      <c r="A49" s="144" t="s">
         <v>116</v>
       </c>
       <c r="B49" s="38" t="s">
@@ -5861,12 +5858,12 @@
         <v>27</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N49" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O49" s="145" t="s">
+      <c r="O49" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P49" s="46" t="s">
@@ -5874,7 +5871,7 @@
       </c>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1">
-      <c r="A50" s="146"/>
+      <c r="A50" s="145"/>
       <c r="B50" s="29"/>
       <c r="C50" s="29" t="s">
         <v>118</v>
@@ -5908,18 +5905,18 @@
         <v>27</v>
       </c>
       <c r="M50" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N50" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O50" s="146"/>
+      <c r="O50" s="145"/>
       <c r="P50" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1">
-      <c r="A51" s="146"/>
+      <c r="A51" s="145"/>
       <c r="B51" s="29"/>
       <c r="C51" s="29" t="s">
         <v>120</v>
@@ -5958,13 +5955,13 @@
       <c r="N51" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O51" s="146"/>
+      <c r="O51" s="145"/>
       <c r="P51" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1">
-      <c r="A52" s="146"/>
+      <c r="A52" s="145"/>
       <c r="B52" s="29"/>
       <c r="C52" s="29" t="s">
         <v>121</v>
@@ -6003,13 +6000,13 @@
       <c r="N52" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O52" s="146"/>
+      <c r="O52" s="145"/>
       <c r="P52" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1">
-      <c r="A53" s="147"/>
+      <c r="A53" s="146"/>
       <c r="B53" s="35"/>
       <c r="C53" s="35" t="s">
         <v>122</v>
@@ -6048,13 +6045,13 @@
       <c r="N53" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O53" s="147"/>
+      <c r="O53" s="146"/>
       <c r="P53" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1">
-      <c r="A54" s="145" t="s">
+      <c r="A54" s="144" t="s">
         <v>123</v>
       </c>
       <c r="B54" s="38" t="s">
@@ -6097,7 +6094,7 @@
       <c r="N54" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O54" s="145" t="s">
+      <c r="O54" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P54" s="19" t="s">
@@ -6105,7 +6102,7 @@
       </c>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1">
-      <c r="A55" s="146"/>
+      <c r="A55" s="145"/>
       <c r="B55" s="29"/>
       <c r="C55" s="29" t="s">
         <v>127</v>
@@ -6139,18 +6136,18 @@
         <v>27</v>
       </c>
       <c r="M55" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N55" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O55" s="146"/>
+      <c r="O55" s="145"/>
       <c r="P55" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1">
-      <c r="A56" s="146"/>
+      <c r="A56" s="145"/>
       <c r="B56" s="29"/>
       <c r="C56" s="29" t="s">
         <v>129</v>
@@ -6189,13 +6186,13 @@
       <c r="N56" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O56" s="146"/>
+      <c r="O56" s="145"/>
       <c r="P56" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1">
-      <c r="A57" s="147"/>
+      <c r="A57" s="146"/>
       <c r="B57" s="35"/>
       <c r="C57" s="35" t="s">
         <v>130</v>
@@ -6229,18 +6226,18 @@
         <v>27</v>
       </c>
       <c r="M57" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N57" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O57" s="147"/>
+      <c r="O57" s="146"/>
       <c r="P57" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1">
-      <c r="A58" s="154" t="s">
+      <c r="A58" s="153" t="s">
         <v>131</v>
       </c>
       <c r="B58" s="38" t="s">
@@ -6278,12 +6275,12 @@
         <v>112</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N58" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O58" s="145" t="s">
+      <c r="O58" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P58" s="19" t="s">
@@ -6291,7 +6288,7 @@
       </c>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1">
-      <c r="A59" s="155"/>
+      <c r="A59" s="154"/>
       <c r="B59" s="29"/>
       <c r="C59" s="29" t="s">
         <v>134</v>
@@ -6325,18 +6322,18 @@
         <v>112</v>
       </c>
       <c r="M59" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N59" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O59" s="146"/>
+      <c r="O59" s="145"/>
       <c r="P59" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1">
-      <c r="A60" s="155"/>
+      <c r="A60" s="154"/>
       <c r="B60" s="29"/>
       <c r="C60" s="29" t="s">
         <v>135</v>
@@ -6372,16 +6369,16 @@
       <c r="M60" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="N60" s="91" t="s">
+      <c r="N60" s="90" t="s">
         <v>729</v>
       </c>
-      <c r="O60" s="146"/>
+      <c r="O60" s="145"/>
       <c r="P60" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1">
-      <c r="A61" s="155"/>
+      <c r="A61" s="154"/>
       <c r="B61" s="29"/>
       <c r="C61" s="29" t="s">
         <v>136</v>
@@ -6414,19 +6411,19 @@
       <c r="L61" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="M61" s="91" t="s">
+      <c r="M61" s="90" t="s">
         <v>729</v>
       </c>
       <c r="N61" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O61" s="146"/>
+      <c r="O61" s="145"/>
       <c r="P61" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1">
-      <c r="A62" s="156"/>
+      <c r="A62" s="155"/>
       <c r="B62" s="35"/>
       <c r="C62" s="35" t="s">
         <v>137</v>
@@ -6465,13 +6462,13 @@
       <c r="N62" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O62" s="147"/>
+      <c r="O62" s="146"/>
       <c r="P62" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1">
-      <c r="A63" s="145" t="s">
+      <c r="A63" s="144" t="s">
         <v>138</v>
       </c>
       <c r="B63" s="38" t="s">
@@ -6509,12 +6506,12 @@
         <v>27</v>
       </c>
       <c r="M63" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N63" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O63" s="145" t="s">
+      <c r="O63" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P63" s="46" t="s">
@@ -6522,7 +6519,7 @@
       </c>
     </row>
     <row r="64" spans="1:16" s="2" customFormat="1">
-      <c r="A64" s="146"/>
+      <c r="A64" s="145"/>
       <c r="B64" s="29"/>
       <c r="C64" s="29" t="s">
         <v>140</v>
@@ -6556,18 +6553,18 @@
         <v>27</v>
       </c>
       <c r="M64" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N64" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O64" s="146"/>
+      <c r="O64" s="145"/>
       <c r="P64" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1">
-      <c r="A65" s="146"/>
+      <c r="A65" s="145"/>
       <c r="B65" s="29"/>
       <c r="C65" s="29" t="s">
         <v>141</v>
@@ -6601,18 +6598,18 @@
         <v>27</v>
       </c>
       <c r="M65" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N65" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O65" s="146"/>
+      <c r="O65" s="145"/>
       <c r="P65" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="66" spans="1:16" s="2" customFormat="1">
-      <c r="A66" s="146"/>
+      <c r="A66" s="145"/>
       <c r="B66" s="29"/>
       <c r="C66" s="29" t="s">
         <v>142</v>
@@ -6646,18 +6643,18 @@
         <v>27</v>
       </c>
       <c r="M66" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N66" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O66" s="146"/>
+      <c r="O66" s="145"/>
       <c r="P66" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1">
-      <c r="A67" s="147"/>
+      <c r="A67" s="146"/>
       <c r="B67" s="35"/>
       <c r="C67" s="35" t="s">
         <v>143</v>
@@ -6691,18 +6688,18 @@
         <v>27</v>
       </c>
       <c r="M67" s="35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N67" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O67" s="147"/>
+      <c r="O67" s="146"/>
       <c r="P67" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:16" s="2" customFormat="1">
-      <c r="A68" s="154" t="s">
+      <c r="A68" s="153" t="s">
         <v>144</v>
       </c>
       <c r="B68" s="38" t="s">
@@ -6740,12 +6737,12 @@
         <v>27</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N68" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O68" s="145" t="s">
+      <c r="O68" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P68" s="19" t="s">
@@ -6753,7 +6750,7 @@
       </c>
     </row>
     <row r="69" spans="1:16" s="2" customFormat="1">
-      <c r="A69" s="155"/>
+      <c r="A69" s="154"/>
       <c r="B69" s="29"/>
       <c r="C69" s="29" t="s">
         <v>146</v>
@@ -6787,18 +6784,18 @@
         <v>27</v>
       </c>
       <c r="M69" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N69" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O69" s="146"/>
+      <c r="O69" s="145"/>
       <c r="P69" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="70" spans="1:16" s="2" customFormat="1">
-      <c r="A70" s="155"/>
+      <c r="A70" s="154"/>
       <c r="B70" s="29"/>
       <c r="C70" s="29" t="s">
         <v>147</v>
@@ -6834,16 +6831,16 @@
       <c r="M70" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="N70" s="91" t="s">
+      <c r="N70" s="90" t="s">
         <v>729</v>
       </c>
-      <c r="O70" s="146"/>
+      <c r="O70" s="145"/>
       <c r="P70" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:16" s="2" customFormat="1">
-      <c r="A71" s="156"/>
+      <c r="A71" s="155"/>
       <c r="B71" s="35"/>
       <c r="C71" s="35" t="s">
         <v>148</v>
@@ -6877,18 +6874,18 @@
         <v>27</v>
       </c>
       <c r="M71" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N71" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O71" s="147"/>
+      <c r="O71" s="146"/>
       <c r="P71" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:16" s="2" customFormat="1">
-      <c r="A72" s="154" t="s">
+      <c r="A72" s="153" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="38" t="s">
@@ -6926,12 +6923,12 @@
         <v>27</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N72" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O72" s="145" t="s">
+      <c r="O72" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P72" s="19" t="s">
@@ -6939,7 +6936,7 @@
       </c>
     </row>
     <row r="73" spans="1:16" s="2" customFormat="1">
-      <c r="A73" s="155"/>
+      <c r="A73" s="154"/>
       <c r="B73" s="29"/>
       <c r="C73" s="29" t="s">
         <v>151</v>
@@ -6973,18 +6970,18 @@
         <v>27</v>
       </c>
       <c r="M73" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N73" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O73" s="146"/>
+      <c r="O73" s="145"/>
       <c r="P73" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:16" s="2" customFormat="1">
-      <c r="A74" s="155"/>
+      <c r="A74" s="154"/>
       <c r="B74" s="29"/>
       <c r="C74" s="29" t="s">
         <v>152</v>
@@ -7018,18 +7015,18 @@
         <v>27</v>
       </c>
       <c r="M74" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N74" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O74" s="146"/>
+      <c r="O74" s="145"/>
       <c r="P74" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:16" s="2" customFormat="1">
-      <c r="A75" s="156"/>
+      <c r="A75" s="155"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35" t="s">
         <v>153</v>
@@ -7063,24 +7060,24 @@
         <v>27</v>
       </c>
       <c r="M75" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N75" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O75" s="147"/>
+      <c r="O75" s="146"/>
       <c r="P75" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:16" s="2" customFormat="1">
-      <c r="A76" s="150" t="s">
+      <c r="A76" s="149" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="93" t="s">
+      <c r="B76" s="92" t="s">
         <v>693</v>
       </c>
-      <c r="C76" s="93" t="s">
+      <c r="C76" s="92" t="s">
         <v>693</v>
       </c>
       <c r="D76" s="24" t="s">
@@ -7112,12 +7109,12 @@
         <v>27</v>
       </c>
       <c r="M76" s="50" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N76" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O76" s="150" t="s">
+      <c r="O76" s="149" t="s">
         <v>30</v>
       </c>
       <c r="P76" s="46" t="s">
@@ -7125,9 +7122,9 @@
       </c>
     </row>
     <row r="77" spans="1:16" s="2" customFormat="1">
-      <c r="A77" s="149"/>
-      <c r="B77" s="94"/>
-      <c r="C77" s="95" t="s">
+      <c r="A77" s="148"/>
+      <c r="B77" s="93"/>
+      <c r="C77" s="94" t="s">
         <v>694</v>
       </c>
       <c r="D77" s="31" t="s">
@@ -7159,18 +7156,18 @@
         <v>27</v>
       </c>
       <c r="M77" s="50" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N77" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O77" s="149"/>
+      <c r="O77" s="148"/>
       <c r="P77" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:16" s="2" customFormat="1">
-      <c r="A78" s="145" t="s">
+      <c r="A78" s="144" t="s">
         <v>156</v>
       </c>
       <c r="B78" s="38" t="s">
@@ -7208,12 +7205,12 @@
         <v>112</v>
       </c>
       <c r="M78" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N78" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O78" s="145" t="s">
+      <c r="O78" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P78" s="19" t="s">
@@ -7221,7 +7218,7 @@
       </c>
     </row>
     <row r="79" spans="1:16" s="2" customFormat="1">
-      <c r="A79" s="146"/>
+      <c r="A79" s="145"/>
       <c r="B79" s="29"/>
       <c r="C79" s="29" t="s">
         <v>159</v>
@@ -7255,18 +7252,18 @@
         <v>112</v>
       </c>
       <c r="M79" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N79" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O79" s="146"/>
+      <c r="O79" s="145"/>
       <c r="P79" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:16" s="2" customFormat="1">
-      <c r="A80" s="146"/>
+      <c r="A80" s="145"/>
       <c r="B80" s="29"/>
       <c r="C80" s="29" t="s">
         <v>161</v>
@@ -7305,13 +7302,13 @@
       <c r="N80" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O80" s="146"/>
+      <c r="O80" s="145"/>
       <c r="P80" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:16" s="2" customFormat="1">
-      <c r="A81" s="147"/>
+      <c r="A81" s="146"/>
       <c r="B81" s="35"/>
       <c r="C81" s="35" t="s">
         <v>163</v>
@@ -7345,18 +7342,18 @@
         <v>27</v>
       </c>
       <c r="M81" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N81" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="O81" s="147"/>
+      <c r="O81" s="146"/>
       <c r="P81" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:16" s="2" customFormat="1">
-      <c r="A82" s="154" t="s">
+      <c r="A82" s="153" t="s">
         <v>164</v>
       </c>
       <c r="B82" s="38" t="s">
@@ -7394,12 +7391,12 @@
         <v>27</v>
       </c>
       <c r="M82" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N82" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O82" s="145" t="s">
+      <c r="O82" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P82" s="19" t="s">
@@ -7407,7 +7404,7 @@
       </c>
     </row>
     <row r="83" spans="1:16" s="2" customFormat="1">
-      <c r="A83" s="155"/>
+      <c r="A83" s="154"/>
       <c r="B83" s="29"/>
       <c r="C83" s="29" t="s">
         <v>166</v>
@@ -7441,18 +7438,18 @@
         <v>27</v>
       </c>
       <c r="M83" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N83" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O83" s="146"/>
+      <c r="O83" s="145"/>
       <c r="P83" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="84" spans="1:16" s="2" customFormat="1">
-      <c r="A84" s="155"/>
+      <c r="A84" s="154"/>
       <c r="B84" s="29"/>
       <c r="C84" s="29" t="s">
         <v>168</v>
@@ -7486,18 +7483,18 @@
         <v>27</v>
       </c>
       <c r="M84" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N84" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O84" s="146"/>
+      <c r="O84" s="145"/>
       <c r="P84" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="85" spans="1:16" s="2" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A85" s="156"/>
+      <c r="A85" s="155"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35" t="s">
         <v>169</v>
@@ -7531,18 +7528,18 @@
         <v>27</v>
       </c>
       <c r="M85" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N85" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O85" s="147"/>
+      <c r="O85" s="146"/>
       <c r="P85" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="86" spans="1:16" s="2" customFormat="1">
-      <c r="A86" s="145" t="s">
+      <c r="A86" s="144" t="s">
         <v>170</v>
       </c>
       <c r="B86" s="38" t="s">
@@ -7551,7 +7548,7 @@
       <c r="C86" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="D86" s="117" t="s">
+      <c r="D86" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E86" s="25" t="s">
@@ -7576,16 +7573,16 @@
       <c r="K86" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="L86" s="117" t="s">
+      <c r="L86" s="116" t="s">
         <v>27</v>
       </c>
       <c r="M86" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N86" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O86" s="145" t="s">
+      <c r="O86" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P86" s="19" t="s">
@@ -7593,12 +7590,12 @@
       </c>
     </row>
     <row r="87" spans="1:16" s="2" customFormat="1">
-      <c r="A87" s="146"/>
+      <c r="A87" s="145"/>
       <c r="B87" s="29"/>
       <c r="C87" s="29" t="s">
         <v>281</v>
       </c>
-      <c r="D87" s="118" t="s">
+      <c r="D87" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E87" s="29" t="s">
@@ -7623,27 +7620,27 @@
       <c r="K87" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L87" s="118" t="s">
+      <c r="L87" s="117" t="s">
         <v>87</v>
       </c>
       <c r="M87" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N87" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O87" s="146"/>
+      <c r="O87" s="145"/>
       <c r="P87" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="88" spans="1:16" s="2" customFormat="1">
-      <c r="A88" s="146"/>
+      <c r="A88" s="145"/>
       <c r="B88" s="29"/>
       <c r="C88" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="D88" s="118" t="s">
+      <c r="D88" s="117" t="s">
         <v>21</v>
       </c>
       <c r="E88" s="29" t="s">
@@ -7668,27 +7665,27 @@
       <c r="K88" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L88" s="118" t="s">
+      <c r="L88" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M88" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N88" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O88" s="146"/>
+      <c r="O88" s="145"/>
       <c r="P88" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="89" spans="1:16" s="2" customFormat="1">
-      <c r="A89" s="146"/>
+      <c r="A89" s="145"/>
       <c r="B89" s="29"/>
       <c r="C89" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="D89" s="118" t="s">
+      <c r="D89" s="117" t="s">
         <v>21</v>
       </c>
       <c r="E89" s="29" t="s">
@@ -7713,27 +7710,27 @@
       <c r="K89" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L89" s="118" t="s">
+      <c r="L89" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M89" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N89" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O89" s="146"/>
+      <c r="O89" s="145"/>
       <c r="P89" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:16" s="2" customFormat="1">
-      <c r="A90" s="147"/>
+      <c r="A90" s="146"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="D90" s="119" t="s">
+      <c r="D90" s="118" t="s">
         <v>21</v>
       </c>
       <c r="E90" s="35" t="s">
@@ -7758,7 +7755,7 @@
       <c r="K90" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L90" s="119" t="s">
+      <c r="L90" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M90" s="35" t="s">
@@ -7767,13 +7764,13 @@
       <c r="N90" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O90" s="147"/>
+      <c r="O90" s="146"/>
       <c r="P90" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="91" spans="1:16" s="2" customFormat="1">
-      <c r="A91" s="145" t="s">
+      <c r="A91" s="144" t="s">
         <v>171</v>
       </c>
       <c r="B91" s="38" t="s">
@@ -7811,12 +7808,12 @@
         <v>27</v>
       </c>
       <c r="M91" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N91" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O91" s="145" t="s">
+      <c r="O91" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P91" s="46" t="s">
@@ -7824,7 +7821,7 @@
       </c>
     </row>
     <row r="92" spans="1:16" s="2" customFormat="1">
-      <c r="A92" s="146"/>
+      <c r="A92" s="145"/>
       <c r="B92" s="29"/>
       <c r="C92" s="29" t="s">
         <v>708</v>
@@ -7854,27 +7851,27 @@
       <c r="K92" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L92" s="117" t="s">
+      <c r="L92" s="116" t="s">
         <v>27</v>
       </c>
       <c r="M92" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N92" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O92" s="146"/>
+      <c r="O92" s="145"/>
       <c r="P92" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="93" spans="1:16" s="2" customFormat="1">
-      <c r="A93" s="146"/>
-      <c r="B93" s="91"/>
-      <c r="C93" s="91" t="s">
+      <c r="A93" s="145"/>
+      <c r="B93" s="90"/>
+      <c r="C93" s="90" t="s">
         <v>709</v>
       </c>
-      <c r="D93" s="97" t="s">
+      <c r="D93" s="96" t="s">
         <v>39</v>
       </c>
       <c r="E93" s="29" t="s">
@@ -7883,14 +7880,14 @@
       <c r="F93" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="G93" s="98">
+      <c r="G93" s="97">
         <v>44412</v>
       </c>
-      <c r="H93" s="104">
+      <c r="H93" s="103">
         <f t="shared" ca="1" si="3"/>
         <v>5</v>
       </c>
-      <c r="I93" s="91" t="s">
+      <c r="I93" s="90" t="s">
         <v>45</v>
       </c>
       <c r="J93" s="29" t="s">
@@ -7899,22 +7896,22 @@
       <c r="K93" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L93" s="117" t="s">
-        <v>27</v>
-      </c>
-      <c r="M93" s="91" t="s">
+      <c r="L93" s="116" t="s">
+        <v>27</v>
+      </c>
+      <c r="M93" s="90" t="s">
         <v>719</v>
       </c>
-      <c r="N93" s="91" t="s">
+      <c r="N93" s="90" t="s">
         <v>729</v>
       </c>
-      <c r="O93" s="146"/>
+      <c r="O93" s="145"/>
       <c r="P93" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="94" spans="1:16" s="2" customFormat="1">
-      <c r="A94" s="145" t="s">
+      <c r="A94" s="144" t="s">
         <v>176</v>
       </c>
       <c r="B94" s="38" t="s">
@@ -7952,12 +7949,12 @@
         <v>27</v>
       </c>
       <c r="M94" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N94" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O94" s="145" t="s">
+      <c r="O94" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P94" s="19" t="s">
@@ -7965,7 +7962,7 @@
       </c>
     </row>
     <row r="95" spans="1:16" s="2" customFormat="1">
-      <c r="A95" s="146"/>
+      <c r="A95" s="145"/>
       <c r="B95" s="29"/>
       <c r="C95" s="29" t="s">
         <v>178</v>
@@ -7999,18 +7996,18 @@
         <v>27</v>
       </c>
       <c r="M95" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N95" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O95" s="146"/>
+      <c r="O95" s="145"/>
       <c r="P95" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:16" s="2" customFormat="1">
-      <c r="A96" s="146"/>
+      <c r="A96" s="145"/>
       <c r="B96" s="29"/>
       <c r="C96" s="29" t="s">
         <v>179</v>
@@ -8044,18 +8041,18 @@
         <v>27</v>
       </c>
       <c r="M96" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N96" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O96" s="146"/>
+      <c r="O96" s="145"/>
       <c r="P96" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="97" spans="1:16" s="2" customFormat="1">
-      <c r="A97" s="147"/>
+      <c r="A97" s="146"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
         <v>180</v>
@@ -8089,18 +8086,18 @@
         <v>27</v>
       </c>
       <c r="M97" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N97" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O97" s="147"/>
+      <c r="O97" s="146"/>
       <c r="P97" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:16" s="2" customFormat="1">
-      <c r="A98" s="151" t="s">
+      <c r="A98" s="150" t="s">
         <v>181</v>
       </c>
       <c r="B98" s="38" t="s">
@@ -8138,12 +8135,12 @@
         <v>27</v>
       </c>
       <c r="M98" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N98" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O98" s="145" t="s">
+      <c r="O98" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P98" s="19" t="s">
@@ -8151,7 +8148,7 @@
       </c>
     </row>
     <row r="99" spans="1:16" s="2" customFormat="1">
-      <c r="A99" s="151"/>
+      <c r="A99" s="150"/>
       <c r="B99" s="29"/>
       <c r="C99" s="29" t="s">
         <v>183</v>
@@ -8185,18 +8182,18 @@
         <v>27</v>
       </c>
       <c r="M99" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N99" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O99" s="146"/>
+      <c r="O99" s="145"/>
       <c r="P99" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="100" spans="1:16" s="2" customFormat="1">
-      <c r="A100" s="151"/>
+      <c r="A100" s="150"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
         <v>184</v>
@@ -8230,24 +8227,24 @@
         <v>27</v>
       </c>
       <c r="M100" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N100" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="O100" s="146"/>
+      <c r="O100" s="145"/>
       <c r="P100" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A101" s="150" t="s">
+      <c r="A101" s="149" t="s">
         <v>185</v>
       </c>
-      <c r="B101" s="99" t="s">
+      <c r="B101" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="C101" s="99" t="s">
+      <c r="C101" s="98" t="s">
         <v>186</v>
       </c>
       <c r="D101" s="24" t="s">
@@ -8256,7 +8253,7 @@
       <c r="E101" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F101" s="100" t="s">
+      <c r="F101" s="99" t="s">
         <v>187</v>
       </c>
       <c r="G101" s="57">
@@ -8279,12 +8276,12 @@
         <v>27</v>
       </c>
       <c r="M101" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N101" s="32" t="s">
         <v>735</v>
       </c>
-      <c r="O101" s="148" t="s">
+      <c r="O101" s="147" t="s">
         <v>36</v>
       </c>
       <c r="P101" s="19" t="s">
@@ -8292,8 +8289,8 @@
       </c>
     </row>
     <row r="102" spans="1:16" s="2" customFormat="1">
-      <c r="A102" s="148"/>
-      <c r="B102" s="99"/>
+      <c r="A102" s="147"/>
+      <c r="B102" s="98"/>
       <c r="C102" s="32" t="s">
         <v>188</v>
       </c>
@@ -8303,7 +8300,7 @@
       <c r="E102" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F102" s="100" t="s">
+      <c r="F102" s="99" t="s">
         <v>48</v>
       </c>
       <c r="G102" s="57">
@@ -8331,14 +8328,14 @@
       <c r="N102" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O102" s="148"/>
+      <c r="O102" s="147"/>
       <c r="P102" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="103" spans="1:16" s="2" customFormat="1">
-      <c r="A103" s="148"/>
-      <c r="B103" s="99"/>
+      <c r="A103" s="147"/>
+      <c r="B103" s="98"/>
       <c r="C103" s="32" t="s">
         <v>190</v>
       </c>
@@ -8348,7 +8345,7 @@
       <c r="E103" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F103" s="100" t="s">
+      <c r="F103" s="99" t="s">
         <v>23</v>
       </c>
       <c r="G103" s="57">
@@ -8371,29 +8368,29 @@
         <v>27</v>
       </c>
       <c r="M103" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N103" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O103" s="148"/>
+      <c r="O103" s="147"/>
       <c r="P103" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="104" spans="1:16" s="2" customFormat="1">
-      <c r="A104" s="148"/>
-      <c r="B104" s="99"/>
+      <c r="A104" s="147"/>
+      <c r="B104" s="98"/>
       <c r="C104" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="D104" s="97" t="s">
+      <c r="D104" s="96" t="s">
         <v>21</v>
       </c>
       <c r="E104" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F104" s="100" t="s">
+      <c r="F104" s="99" t="s">
         <v>48</v>
       </c>
       <c r="G104" s="57">
@@ -8416,29 +8413,29 @@
         <v>27</v>
       </c>
       <c r="M104" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N104" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O104" s="148"/>
+      <c r="O104" s="147"/>
       <c r="P104" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="105" spans="1:16" s="2" customFormat="1">
-      <c r="A105" s="148"/>
-      <c r="B105" s="99"/>
+      <c r="A105" s="147"/>
+      <c r="B105" s="98"/>
       <c r="C105" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="D105" s="97" t="s">
+      <c r="D105" s="96" t="s">
         <v>21</v>
       </c>
       <c r="E105" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F105" s="100" t="s">
+      <c r="F105" s="99" t="s">
         <v>48</v>
       </c>
       <c r="G105" s="57">
@@ -8461,20 +8458,20 @@
         <v>27</v>
       </c>
       <c r="M105" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N105" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O105" s="148"/>
+      <c r="O105" s="147"/>
       <c r="P105" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="106" spans="1:16" s="84" customFormat="1">
-      <c r="A106" s="149"/>
-      <c r="B106" s="101"/>
-      <c r="C106" s="102" t="s">
+      <c r="A106" s="148"/>
+      <c r="B106" s="100"/>
+      <c r="C106" s="101" t="s">
         <v>193</v>
       </c>
       <c r="D106" s="37" t="s">
@@ -8483,7 +8480,7 @@
       <c r="E106" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F106" s="102" t="s">
+      <c r="F106" s="101" t="s">
         <v>23</v>
       </c>
       <c r="G106" s="57">
@@ -8506,18 +8503,18 @@
         <v>27</v>
       </c>
       <c r="M106" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N106" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O106" s="149"/>
+      <c r="O106" s="148"/>
       <c r="P106" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="107" spans="1:16" s="2" customFormat="1">
-      <c r="A107" s="145" t="s">
+      <c r="A107" s="144" t="s">
         <v>194</v>
       </c>
       <c r="B107" s="38" t="s">
@@ -8555,12 +8552,12 @@
         <v>27</v>
       </c>
       <c r="M107" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N107" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O107" s="145" t="s">
+      <c r="O107" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P107" s="19" t="s">
@@ -8568,7 +8565,7 @@
       </c>
     </row>
     <row r="108" spans="1:16" s="2" customFormat="1">
-      <c r="A108" s="146"/>
+      <c r="A108" s="145"/>
       <c r="B108" s="29"/>
       <c r="C108" s="29" t="s">
         <v>196</v>
@@ -8602,18 +8599,18 @@
         <v>27</v>
       </c>
       <c r="M108" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N108" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O108" s="146"/>
+      <c r="O108" s="145"/>
       <c r="P108" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:16" s="2" customFormat="1">
-      <c r="A109" s="146"/>
+      <c r="A109" s="145"/>
       <c r="B109" s="29"/>
       <c r="C109" s="29" t="s">
         <v>197</v>
@@ -8647,18 +8644,18 @@
         <v>27</v>
       </c>
       <c r="M109" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N109" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O109" s="146"/>
+      <c r="O109" s="145"/>
       <c r="P109" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="110" spans="1:16" s="2" customFormat="1">
-      <c r="A110" s="146"/>
+      <c r="A110" s="145"/>
       <c r="B110" s="29"/>
       <c r="C110" s="29" t="s">
         <v>198</v>
@@ -8692,18 +8689,18 @@
         <v>27</v>
       </c>
       <c r="M110" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N110" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O110" s="146"/>
+      <c r="O110" s="145"/>
       <c r="P110" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="111" spans="1:16" s="2" customFormat="1">
-      <c r="A111" s="146"/>
+      <c r="A111" s="145"/>
       <c r="B111" s="29"/>
       <c r="C111" s="29" t="s">
         <v>199</v>
@@ -8737,18 +8734,18 @@
         <v>27</v>
       </c>
       <c r="M111" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N111" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O111" s="146"/>
+      <c r="O111" s="145"/>
       <c r="P111" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="112" spans="1:16" s="2" customFormat="1">
-      <c r="A112" s="147"/>
+      <c r="A112" s="146"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
         <v>200</v>
@@ -8782,18 +8779,18 @@
         <v>27</v>
       </c>
       <c r="M112" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N112" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O112" s="147"/>
+      <c r="O112" s="146"/>
       <c r="P112" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="113" spans="1:16" s="2" customFormat="1">
-      <c r="A113" s="145" t="s">
+      <c r="A113" s="144" t="s">
         <v>201</v>
       </c>
       <c r="B113" s="39" t="s">
@@ -8836,7 +8833,7 @@
       <c r="N113" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O113" s="145" t="s">
+      <c r="O113" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P113" s="19" t="s">
@@ -8844,7 +8841,7 @@
       </c>
     </row>
     <row r="114" spans="1:16" s="2" customFormat="1">
-      <c r="A114" s="146"/>
+      <c r="A114" s="145"/>
       <c r="B114" s="29"/>
       <c r="C114" s="30" t="s">
         <v>205</v>
@@ -8883,13 +8880,13 @@
       <c r="N114" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O114" s="146"/>
+      <c r="O114" s="145"/>
       <c r="P114" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="115" spans="1:16" s="2" customFormat="1">
-      <c r="A115" s="146"/>
+      <c r="A115" s="145"/>
       <c r="B115" s="29"/>
       <c r="C115" s="30" t="s">
         <v>206</v>
@@ -8923,18 +8920,18 @@
         <v>112</v>
       </c>
       <c r="M115" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N115" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O115" s="146"/>
+      <c r="O115" s="145"/>
       <c r="P115" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="116" spans="1:16" s="2" customFormat="1">
-      <c r="A116" s="147"/>
+      <c r="A116" s="146"/>
       <c r="B116" s="35"/>
       <c r="C116" s="36" t="s">
         <v>207</v>
@@ -8968,24 +8965,24 @@
         <v>27</v>
       </c>
       <c r="M116" s="35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N116" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O116" s="147"/>
+      <c r="O116" s="146"/>
       <c r="P116" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="117" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A117" s="150" t="s">
+      <c r="A117" s="149" t="s">
         <v>208</v>
       </c>
-      <c r="B117" s="99" t="s">
+      <c r="B117" s="98" t="s">
         <v>209</v>
       </c>
-      <c r="C117" s="99" t="s">
+      <c r="C117" s="98" t="s">
         <v>209</v>
       </c>
       <c r="D117" s="24" t="s">
@@ -9017,12 +9014,12 @@
         <v>27</v>
       </c>
       <c r="M117" s="25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N117" s="32" t="s">
         <v>736</v>
       </c>
-      <c r="O117" s="145" t="s">
+      <c r="O117" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P117" s="46" t="s">
@@ -9030,12 +9027,12 @@
       </c>
     </row>
     <row r="118" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A118" s="148"/>
-      <c r="B118" s="99"/>
+      <c r="A118" s="147"/>
+      <c r="B118" s="98"/>
       <c r="C118" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="D118" s="103" t="s">
+      <c r="D118" s="102" t="s">
         <v>39</v>
       </c>
       <c r="E118" s="29" t="s">
@@ -9064,23 +9061,23 @@
         <v>27</v>
       </c>
       <c r="M118" s="25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N118" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O118" s="146"/>
+      <c r="O118" s="145"/>
       <c r="P118" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A119" s="148"/>
-      <c r="B119" s="99"/>
+      <c r="A119" s="147"/>
+      <c r="B119" s="98"/>
       <c r="C119" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="D119" s="103" t="s">
+      <c r="D119" s="102" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="35" t="s">
@@ -9109,20 +9106,20 @@
         <v>27</v>
       </c>
       <c r="M119" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N119" s="32" t="s">
         <v>739</v>
       </c>
-      <c r="O119" s="146"/>
+      <c r="O119" s="145"/>
       <c r="P119" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="120" spans="1:16" s="84" customFormat="1">
-      <c r="A120" s="149"/>
-      <c r="B120" s="101"/>
-      <c r="C120" s="102" t="s">
+      <c r="A120" s="148"/>
+      <c r="B120" s="100"/>
+      <c r="C120" s="101" t="s">
         <v>212</v>
       </c>
       <c r="D120" s="31" t="s">
@@ -9131,7 +9128,7 @@
       <c r="E120" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F120" s="102" t="s">
+      <c r="F120" s="101" t="s">
         <v>23</v>
       </c>
       <c r="G120" s="57">
@@ -9153,19 +9150,19 @@
       <c r="L120" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="M120" s="102" t="s">
+      <c r="M120" s="101" t="s">
         <v>719</v>
       </c>
-      <c r="N120" s="102" t="s">
+      <c r="N120" s="101" t="s">
         <v>729</v>
       </c>
-      <c r="O120" s="147"/>
+      <c r="O120" s="146"/>
       <c r="P120" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="121" spans="1:16" s="2" customFormat="1">
-      <c r="A121" s="145" t="s">
+      <c r="A121" s="144" t="s">
         <v>213</v>
       </c>
       <c r="B121" s="38" t="s">
@@ -9203,12 +9200,12 @@
         <v>27</v>
       </c>
       <c r="M121" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N121" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O121" s="145" t="s">
+      <c r="O121" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P121" s="19" t="s">
@@ -9216,7 +9213,7 @@
       </c>
     </row>
     <row r="122" spans="1:16" s="2" customFormat="1">
-      <c r="A122" s="146"/>
+      <c r="A122" s="145"/>
       <c r="B122" s="29"/>
       <c r="C122" s="30" t="s">
         <v>216</v>
@@ -9250,18 +9247,18 @@
         <v>112</v>
       </c>
       <c r="M122" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N122" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O122" s="146"/>
+      <c r="O122" s="145"/>
       <c r="P122" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="123" spans="1:16" s="2" customFormat="1">
-      <c r="A123" s="147"/>
+      <c r="A123" s="146"/>
       <c r="B123" s="35"/>
       <c r="C123" s="36" t="s">
         <v>218</v>
@@ -9295,18 +9292,18 @@
         <v>27</v>
       </c>
       <c r="M123" s="35" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N123" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O123" s="147"/>
+      <c r="O123" s="146"/>
       <c r="P123" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="124" spans="1:16" s="2" customFormat="1">
-      <c r="A124" s="145" t="s">
+      <c r="A124" s="144" t="s">
         <v>219</v>
       </c>
       <c r="B124" s="38" t="s">
@@ -9344,12 +9341,12 @@
         <v>27</v>
       </c>
       <c r="M124" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N124" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O124" s="145" t="s">
+      <c r="O124" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P124" s="19" t="s">
@@ -9357,7 +9354,7 @@
       </c>
     </row>
     <row r="125" spans="1:16" s="2" customFormat="1">
-      <c r="A125" s="146"/>
+      <c r="A125" s="145"/>
       <c r="B125" s="29"/>
       <c r="C125" s="29" t="s">
         <v>222</v>
@@ -9391,18 +9388,18 @@
         <v>27</v>
       </c>
       <c r="M125" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N125" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O125" s="146"/>
+      <c r="O125" s="145"/>
       <c r="P125" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="126" spans="1:16" s="2" customFormat="1">
-      <c r="A126" s="147"/>
+      <c r="A126" s="146"/>
       <c r="B126" s="35"/>
       <c r="C126" s="35" t="s">
         <v>223</v>
@@ -9436,27 +9433,27 @@
         <v>27</v>
       </c>
       <c r="M126" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N126" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O126" s="147"/>
+      <c r="O126" s="146"/>
       <c r="P126" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="127" spans="1:16" s="2" customFormat="1">
-      <c r="A127" s="145" t="s">
+      <c r="A127" s="144" t="s">
         <v>496</v>
       </c>
-      <c r="B127" s="127" t="s">
+      <c r="B127" s="126" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="127" t="s">
+      <c r="C127" s="126" t="s">
         <v>523</v>
       </c>
-      <c r="D127" s="119" t="s">
+      <c r="D127" s="118" t="s">
         <v>39</v>
       </c>
       <c r="E127" s="25" t="s">
@@ -9481,16 +9478,16 @@
       <c r="K127" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L127" s="119" t="s">
+      <c r="L127" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M127" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N127" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O127" s="145" t="s">
+      <c r="O127" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P127" s="19" t="s">
@@ -9498,12 +9495,12 @@
       </c>
     </row>
     <row r="128" spans="1:16" s="2" customFormat="1">
-      <c r="A128" s="146"/>
+      <c r="A128" s="145"/>
       <c r="B128" s="26"/>
       <c r="C128" s="26" t="s">
         <v>525</v>
       </c>
-      <c r="D128" s="117" t="s">
+      <c r="D128" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E128" s="35" t="s">
@@ -9528,30 +9525,30 @@
       <c r="K128" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L128" s="119" t="s">
+      <c r="L128" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M128" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N128" s="32" t="s">
         <v>739</v>
       </c>
-      <c r="O128" s="146"/>
+      <c r="O128" s="145"/>
       <c r="P128" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:16" s="2" customFormat="1">
-      <c r="A129" s="147"/>
+      <c r="A129" s="146"/>
       <c r="B129" s="26"/>
       <c r="C129" s="26" t="s">
         <v>527</v>
       </c>
-      <c r="D129" s="97" t="s">
+      <c r="D129" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="E129" s="91" t="s">
+      <c r="E129" s="90" t="s">
         <v>44</v>
       </c>
       <c r="F129" s="26" t="s">
@@ -9573,16 +9570,16 @@
       <c r="K129" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L129" s="119" t="s">
+      <c r="L129" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M129" s="35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N129" s="32" t="s">
         <v>739</v>
       </c>
-      <c r="O129" s="147"/>
+      <c r="O129" s="146"/>
       <c r="P129" s="19" t="s">
         <v>37</v>
       </c>
@@ -9596,21 +9593,21 @@
       <c r="D130" s="66"/>
       <c r="E130" s="68"/>
       <c r="F130" s="68"/>
-      <c r="G130" s="129"/>
-      <c r="H130" s="92"/>
-      <c r="I130" s="96"/>
-      <c r="J130" s="130"/>
-      <c r="K130" s="130"/>
-      <c r="L130" s="131"/>
+      <c r="G130" s="128"/>
+      <c r="H130" s="91"/>
+      <c r="I130" s="95"/>
+      <c r="J130" s="129"/>
+      <c r="K130" s="129"/>
+      <c r="L130" s="130"/>
       <c r="M130" s="66"/>
-      <c r="N130" s="96"/>
+      <c r="N130" s="95"/>
       <c r="O130" s="72" t="s">
         <v>58</v>
       </c>
       <c r="P130" s="68"/>
     </row>
     <row r="131" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A131" s="150" t="s">
+      <c r="A131" s="149" t="s">
         <v>224</v>
       </c>
       <c r="B131" s="39" t="s">
@@ -9648,12 +9645,12 @@
         <v>27</v>
       </c>
       <c r="M131" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N131" s="20" t="s">
         <v>738</v>
       </c>
-      <c r="O131" s="145" t="s">
+      <c r="O131" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P131" s="19" t="s">
@@ -9661,9 +9658,9 @@
       </c>
     </row>
     <row r="132" spans="1:16" s="84" customFormat="1">
-      <c r="A132" s="149"/>
-      <c r="B132" s="101"/>
-      <c r="C132" s="102" t="s">
+      <c r="A132" s="148"/>
+      <c r="B132" s="100"/>
+      <c r="C132" s="101" t="s">
         <v>227</v>
       </c>
       <c r="D132" s="31" t="s">
@@ -9672,7 +9669,7 @@
       <c r="E132" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F132" s="102" t="s">
+      <c r="F132" s="101" t="s">
         <v>23</v>
       </c>
       <c r="G132" s="57">
@@ -9695,24 +9692,24 @@
         <v>27</v>
       </c>
       <c r="M132" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N132" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="O132" s="147"/>
+      <c r="O132" s="146"/>
       <c r="P132" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="133" spans="1:16" s="2" customFormat="1">
-      <c r="A133" s="145" t="s">
+      <c r="A133" s="144" t="s">
         <v>228</v>
       </c>
-      <c r="B133" s="128" t="s">
+      <c r="B133" s="127" t="s">
         <v>730</v>
       </c>
-      <c r="C133" s="128" t="s">
+      <c r="C133" s="127" t="s">
         <v>730</v>
       </c>
       <c r="D133" s="24" t="s">
@@ -9744,12 +9741,12 @@
         <v>27</v>
       </c>
       <c r="M133" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N133" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="O133" s="145" t="s">
+      <c r="O133" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P133" s="19" t="s">
@@ -9757,7 +9754,7 @@
       </c>
     </row>
     <row r="134" spans="1:16" s="2" customFormat="1">
-      <c r="A134" s="146"/>
+      <c r="A134" s="145"/>
       <c r="B134" s="29"/>
       <c r="C134" s="30" t="s">
         <v>731</v>
@@ -9791,23 +9788,23 @@
         <v>27</v>
       </c>
       <c r="M134" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N134" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O134" s="146"/>
+      <c r="O134" s="145"/>
       <c r="P134" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="135" spans="1:16" s="2" customFormat="1">
-      <c r="A135" s="146"/>
-      <c r="B135" s="91"/>
+      <c r="A135" s="145"/>
+      <c r="B135" s="90"/>
       <c r="C135" s="36" t="s">
         <v>732</v>
       </c>
-      <c r="D135" s="97" t="s">
+      <c r="D135" s="96" t="s">
         <v>39</v>
       </c>
       <c r="E135" s="35" t="s">
@@ -9816,10 +9813,10 @@
       <c r="F135" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G135" s="98">
+      <c r="G135" s="97">
         <v>39543</v>
       </c>
-      <c r="H135" s="104">
+      <c r="H135" s="103">
         <f t="shared" ca="1" si="3"/>
         <v>18</v>
       </c>
@@ -9832,27 +9829,27 @@
       <c r="K135" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L135" s="118" t="s">
+      <c r="L135" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M135" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N135" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O135" s="146"/>
+      <c r="O135" s="145"/>
       <c r="P135" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="136" spans="1:16" s="2" customFormat="1">
-      <c r="A136" s="146"/>
-      <c r="B136" s="91"/>
+      <c r="A136" s="145"/>
+      <c r="B136" s="90"/>
       <c r="C136" s="36" t="s">
         <v>733</v>
       </c>
-      <c r="D136" s="117" t="s">
+      <c r="D136" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E136" s="35" t="s">
@@ -9861,10 +9858,10 @@
       <c r="F136" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G136" s="98">
+      <c r="G136" s="97">
         <v>42258</v>
       </c>
-      <c r="H136" s="104">
+      <c r="H136" s="103">
         <f t="shared" ca="1" si="3"/>
         <v>11</v>
       </c>
@@ -9877,22 +9874,22 @@
       <c r="K136" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L136" s="118" t="s">
+      <c r="L136" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M136" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N136" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O136" s="146"/>
+      <c r="O136" s="145"/>
       <c r="P136" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="137" spans="1:16" s="2" customFormat="1">
-      <c r="A137" s="147"/>
+      <c r="A137" s="146"/>
       <c r="B137" s="35"/>
       <c r="C137" s="36" t="s">
         <v>734</v>
@@ -9931,34 +9928,34 @@
       <c r="N137" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O137" s="147"/>
+      <c r="O137" s="146"/>
       <c r="P137" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="138" spans="1:16" s="2" customFormat="1">
-      <c r="A138" s="120" t="s">
+      <c r="A138" s="119" t="s">
         <v>518</v>
       </c>
-      <c r="B138" s="135" t="s">
+      <c r="B138" s="134" t="s">
         <v>754</v>
       </c>
-      <c r="C138" s="135" t="s">
+      <c r="C138" s="134" t="s">
         <v>754</v>
       </c>
-      <c r="D138" s="123" t="s">
+      <c r="D138" s="122" t="s">
         <v>21</v>
       </c>
       <c r="E138" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F138" s="136" t="s">
+      <c r="F138" s="135" t="s">
         <v>101</v>
       </c>
-      <c r="G138" s="143">
+      <c r="G138" s="142">
         <v>39103</v>
       </c>
-      <c r="H138" s="144">
+      <c r="H138" s="143">
         <f t="shared" ca="1" si="3"/>
         <v>19</v>
       </c>
@@ -9971,16 +9968,16 @@
       <c r="K138" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L138" s="123" t="s">
+      <c r="L138" s="122" t="s">
         <v>27</v>
       </c>
       <c r="M138" s="25" t="s">
-        <v>761</v>
-      </c>
-      <c r="N138" s="126" t="s">
+        <v>760</v>
+      </c>
+      <c r="N138" s="125" t="s">
         <v>735</v>
       </c>
-      <c r="O138" s="120" t="s">
+      <c r="O138" s="119" t="s">
         <v>30</v>
       </c>
       <c r="P138" s="46" t="s">
@@ -9988,25 +9985,25 @@
       </c>
     </row>
     <row r="139" spans="1:16" s="2" customFormat="1">
-      <c r="A139" s="157" t="s">
+      <c r="A139" s="156" t="s">
         <v>528</v>
       </c>
-      <c r="B139" s="137" t="s">
+      <c r="B139" s="136" t="s">
         <v>750</v>
       </c>
-      <c r="C139" s="140" t="s">
+      <c r="C139" s="139" t="s">
         <v>750</v>
       </c>
-      <c r="D139" s="121" t="s">
+      <c r="D139" s="120" t="s">
         <v>21</v>
       </c>
       <c r="E139" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F139" s="136" t="s">
+      <c r="F139" s="135" t="s">
         <v>215</v>
       </c>
-      <c r="G139" s="143">
+      <c r="G139" s="142">
         <v>36197</v>
       </c>
       <c r="H139" s="58">
@@ -10022,16 +10019,16 @@
       <c r="K139" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="L139" s="121" t="s">
+      <c r="L139" s="120" t="s">
         <v>27</v>
       </c>
       <c r="M139" s="29" t="s">
-        <v>761</v>
-      </c>
-      <c r="N139" s="126" t="s">
+        <v>760</v>
+      </c>
+      <c r="N139" s="125" t="s">
         <v>735</v>
       </c>
-      <c r="O139" s="145" t="s">
+      <c r="O139" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P139" s="46" t="s">
@@ -10039,21 +10036,21 @@
       </c>
     </row>
     <row r="140" spans="1:16" s="2" customFormat="1">
-      <c r="A140" s="157"/>
-      <c r="B140" s="138"/>
-      <c r="C140" s="141" t="s">
+      <c r="A140" s="156"/>
+      <c r="B140" s="137"/>
+      <c r="C140" s="140" t="s">
         <v>751</v>
       </c>
-      <c r="D140" s="122" t="s">
+      <c r="D140" s="121" t="s">
         <v>39</v>
       </c>
       <c r="E140" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F140" s="136" t="s">
+      <c r="F140" s="135" t="s">
         <v>215</v>
       </c>
-      <c r="G140" s="143">
+      <c r="G140" s="142">
         <v>36708</v>
       </c>
       <c r="H140" s="58">
@@ -10069,36 +10066,36 @@
       <c r="K140" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L140" s="122" t="s">
+      <c r="L140" s="121" t="s">
         <v>27</v>
       </c>
       <c r="M140" s="25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N140" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O140" s="146"/>
+      <c r="O140" s="145"/>
       <c r="P140" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:16" s="2" customFormat="1">
-      <c r="A141" s="157"/>
-      <c r="B141" s="139"/>
-      <c r="C141" s="142" t="s">
+      <c r="A141" s="156"/>
+      <c r="B141" s="138"/>
+      <c r="C141" s="141" t="s">
         <v>752</v>
       </c>
-      <c r="D141" s="97" t="s">
+      <c r="D141" s="96" t="s">
         <v>39</v>
       </c>
       <c r="E141" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="136" t="s">
+      <c r="F141" s="135" t="s">
         <v>753</v>
       </c>
-      <c r="G141" s="143">
+      <c r="G141" s="142">
         <v>45621</v>
       </c>
       <c r="H141" s="58">
@@ -10114,7 +10111,7 @@
       <c r="K141" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L141" s="122" t="s">
+      <c r="L141" s="121" t="s">
         <v>27</v>
       </c>
       <c r="M141" s="35" t="s">
@@ -10123,22 +10120,22 @@
       <c r="N141" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O141" s="147"/>
+      <c r="O141" s="146"/>
       <c r="P141" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="142" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A142" s="116" t="s">
+      <c r="A142" s="115" t="s">
         <v>540</v>
       </c>
-      <c r="B142" s="127" t="s">
+      <c r="B142" s="126" t="s">
         <v>742</v>
       </c>
-      <c r="C142" s="127" t="s">
+      <c r="C142" s="126" t="s">
         <v>742</v>
       </c>
-      <c r="D142" s="117" t="s">
+      <c r="D142" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E142" s="25" t="s">
@@ -10147,7 +10144,7 @@
       <c r="F142" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G142" s="124">
+      <c r="G142" s="123">
         <v>33231</v>
       </c>
       <c r="H142" s="58">
@@ -10163,16 +10160,16 @@
       <c r="K142" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L142" s="119" t="s">
+      <c r="L142" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M142" s="25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N142" s="20" t="s">
         <v>738</v>
       </c>
-      <c r="O142" s="146" t="s">
+      <c r="O142" s="145" t="s">
         <v>36</v>
       </c>
       <c r="P142" s="19" t="s">
@@ -10180,12 +10177,12 @@
       </c>
     </row>
     <row r="143" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A143" s="116"/>
+      <c r="A143" s="115"/>
       <c r="B143" s="26"/>
-      <c r="C143" s="134" t="s">
+      <c r="C143" s="133" t="s">
         <v>743</v>
       </c>
-      <c r="D143" s="118" t="s">
+      <c r="D143" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E143" s="29" t="s">
@@ -10194,7 +10191,7 @@
       <c r="F143" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G143" s="124">
+      <c r="G143" s="123">
         <v>34979</v>
       </c>
       <c r="H143" s="58">
@@ -10210,27 +10207,27 @@
       <c r="K143" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L143" s="119" t="s">
+      <c r="L143" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M143" s="25" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N143" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O143" s="146"/>
+      <c r="O143" s="145"/>
       <c r="P143" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="144" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A144" s="116"/>
+      <c r="A144" s="115"/>
       <c r="B144" s="26"/>
-      <c r="C144" s="134" t="s">
+      <c r="C144" s="133" t="s">
         <v>744</v>
       </c>
-      <c r="D144" s="97" t="s">
+      <c r="D144" s="96" t="s">
         <v>39</v>
       </c>
       <c r="E144" s="35" t="s">
@@ -10239,7 +10236,7 @@
       <c r="F144" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G144" s="124">
+      <c r="G144" s="123">
         <v>43989</v>
       </c>
       <c r="H144" s="58">
@@ -10255,7 +10252,7 @@
       <c r="K144" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L144" s="118" t="s">
+      <c r="L144" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M144" s="35" t="s">
@@ -10264,18 +10261,18 @@
       <c r="N144" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O144" s="146"/>
+      <c r="O144" s="145"/>
       <c r="P144" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="145" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A145" s="116"/>
+      <c r="A145" s="115"/>
       <c r="B145" s="26"/>
-      <c r="C145" s="134" t="s">
+      <c r="C145" s="133" t="s">
         <v>745</v>
       </c>
-      <c r="D145" s="117" t="s">
+      <c r="D145" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E145" s="25" t="s">
@@ -10284,7 +10281,7 @@
       <c r="F145" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="G145" s="124">
+      <c r="G145" s="123">
         <v>23230</v>
       </c>
       <c r="H145" s="58">
@@ -10300,27 +10297,27 @@
       <c r="K145" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L145" s="119" t="s">
+      <c r="L145" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M145" s="35" t="s">
-        <v>762</v>
-      </c>
-      <c r="N145" s="126" t="s">
+        <v>761</v>
+      </c>
+      <c r="N145" s="125" t="s">
         <v>735</v>
       </c>
-      <c r="O145" s="146"/>
+      <c r="O145" s="145"/>
       <c r="P145" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="146" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A146" s="116"/>
+      <c r="A146" s="115"/>
       <c r="B146" s="26"/>
-      <c r="C146" s="134" t="s">
+      <c r="C146" s="133" t="s">
         <v>746</v>
       </c>
-      <c r="D146" s="118" t="s">
+      <c r="D146" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E146" s="29" t="s">
@@ -10329,7 +10326,7 @@
       <c r="F146" s="26" t="s">
         <v>749</v>
       </c>
-      <c r="G146" s="124">
+      <c r="G146" s="123">
         <v>27706</v>
       </c>
       <c r="H146" s="58">
@@ -10345,27 +10342,27 @@
       <c r="K146" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L146" s="119" t="s">
+      <c r="L146" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M146" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N146" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O146" s="146"/>
+      <c r="O146" s="145"/>
       <c r="P146" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="147" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A147" s="116"/>
+      <c r="A147" s="115"/>
       <c r="B147" s="26"/>
-      <c r="C147" s="134" t="s">
+      <c r="C147" s="133" t="s">
         <v>747</v>
       </c>
-      <c r="D147" s="117" t="s">
+      <c r="D147" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E147" s="35" t="s">
@@ -10374,7 +10371,7 @@
       <c r="F147" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="G147" s="124">
+      <c r="G147" s="123">
         <v>36914</v>
       </c>
       <c r="H147" s="58">
@@ -10390,27 +10387,27 @@
       <c r="K147" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L147" s="118" t="s">
+      <c r="L147" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M147" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N147" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O147" s="146"/>
+      <c r="O147" s="145"/>
       <c r="P147" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="148" spans="1:16" s="2" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A148" s="116"/>
+      <c r="A148" s="115"/>
       <c r="B148" s="26"/>
-      <c r="C148" s="134" t="s">
+      <c r="C148" s="133" t="s">
         <v>748</v>
       </c>
-      <c r="D148" s="117" t="s">
+      <c r="D148" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E148" s="35" t="s">
@@ -10419,7 +10416,7 @@
       <c r="F148" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="G148" s="124">
+      <c r="G148" s="123">
         <v>40647</v>
       </c>
       <c r="H148" s="58">
@@ -10435,22 +10432,22 @@
       <c r="K148" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L148" s="118" t="s">
+      <c r="L148" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M148" s="29" t="s">
-        <v>760</v>
-      </c>
-      <c r="N148" s="126" t="s">
+        <v>759</v>
+      </c>
+      <c r="N148" s="125" t="s">
         <v>739</v>
       </c>
-      <c r="O148" s="147"/>
+      <c r="O148" s="146"/>
       <c r="P148" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="149" spans="1:16" s="2" customFormat="1">
-      <c r="A149" s="145" t="s">
+      <c r="A149" s="144" t="s">
         <v>233</v>
       </c>
       <c r="B149" s="38" t="s">
@@ -10488,12 +10485,12 @@
         <v>27</v>
       </c>
       <c r="M149" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N149" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O149" s="145" t="s">
+      <c r="O149" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P149" s="19" t="s">
@@ -10501,7 +10498,7 @@
       </c>
     </row>
     <row r="150" spans="1:16" s="2" customFormat="1">
-      <c r="A150" s="146"/>
+      <c r="A150" s="145"/>
       <c r="B150" s="29"/>
       <c r="C150" s="29" t="s">
         <v>235</v>
@@ -10540,13 +10537,13 @@
       <c r="N150" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O150" s="146"/>
+      <c r="O150" s="145"/>
       <c r="P150" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="151" spans="1:16" s="2" customFormat="1">
-      <c r="A151" s="147"/>
+      <c r="A151" s="146"/>
       <c r="B151" s="35"/>
       <c r="C151" s="35" t="s">
         <v>237</v>
@@ -10580,22 +10577,22 @@
         <v>27</v>
       </c>
       <c r="M151" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N151" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O151" s="146"/>
+      <c r="O151" s="145"/>
       <c r="P151" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="152" spans="1:16" s="2" customFormat="1">
-      <c r="A152" s="105" t="s">
+      <c r="A152" s="104" t="s">
         <v>238</v>
       </c>
       <c r="B152" s="66"/>
-      <c r="C152" s="90"/>
+      <c r="C152" s="89"/>
       <c r="D152" s="66"/>
       <c r="E152" s="66" t="s">
         <v>172</v>
@@ -10625,13 +10622,13 @@
       <c r="N152" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="O152" s="64" t="s">
+      <c r="O152" s="87" t="s">
         <v>58</v>
       </c>
       <c r="P152" s="68"/>
     </row>
     <row r="153" spans="1:16" s="2" customFormat="1">
-      <c r="A153" s="145" t="s">
+      <c r="A153" s="144" t="s">
         <v>239</v>
       </c>
       <c r="B153" s="38" t="s">
@@ -10669,12 +10666,12 @@
         <v>27</v>
       </c>
       <c r="M153" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N153" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O153" s="145" t="s">
+      <c r="O153" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P153" s="19" t="s">
@@ -10682,7 +10679,7 @@
       </c>
     </row>
     <row r="154" spans="1:16" s="2" customFormat="1">
-      <c r="A154" s="146"/>
+      <c r="A154" s="145"/>
       <c r="B154" s="29"/>
       <c r="C154" s="29" t="s">
         <v>241</v>
@@ -10716,18 +10713,18 @@
         <v>27</v>
       </c>
       <c r="M154" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N154" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O154" s="146"/>
+      <c r="O154" s="145"/>
       <c r="P154" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="155" spans="1:16" s="2" customFormat="1">
-      <c r="A155" s="146"/>
+      <c r="A155" s="145"/>
       <c r="B155" s="29"/>
       <c r="C155" s="29" t="s">
         <v>242</v>
@@ -10761,18 +10758,18 @@
         <v>27</v>
       </c>
       <c r="M155" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N155" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O155" s="146"/>
+      <c r="O155" s="145"/>
       <c r="P155" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="156" spans="1:16" s="2" customFormat="1">
-      <c r="A156" s="146"/>
+      <c r="A156" s="145"/>
       <c r="B156" s="35"/>
       <c r="C156" s="35" t="s">
         <v>243</v>
@@ -10806,23 +10803,23 @@
         <v>27</v>
       </c>
       <c r="M156" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N156" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O156" s="146"/>
+      <c r="O156" s="145"/>
       <c r="P156" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="157" spans="1:16" s="2" customFormat="1">
-      <c r="A157" s="146"/>
+      <c r="A157" s="145"/>
       <c r="B157" s="26"/>
       <c r="C157" s="38" t="s">
         <v>229</v>
       </c>
-      <c r="D157" s="117" t="s">
+      <c r="D157" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E157" s="25" t="s">
@@ -10847,27 +10844,27 @@
       <c r="K157" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="L157" s="117" t="s">
+      <c r="L157" s="116" t="s">
         <v>27</v>
       </c>
       <c r="M157" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N157" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="O157" s="146"/>
+      <c r="O157" s="145"/>
       <c r="P157" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="158" spans="1:16" s="2" customFormat="1">
-      <c r="A158" s="146"/>
+      <c r="A158" s="145"/>
       <c r="B158" s="26"/>
       <c r="C158" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="D158" s="118" t="s">
+      <c r="D158" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E158" s="29" t="s">
@@ -10892,27 +10889,27 @@
       <c r="K158" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L158" s="118" t="s">
+      <c r="L158" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M158" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N158" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O158" s="146"/>
+      <c r="O158" s="145"/>
       <c r="P158" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="159" spans="1:16" s="2" customFormat="1">
-      <c r="A159" s="146"/>
+      <c r="A159" s="145"/>
       <c r="B159" s="26"/>
       <c r="C159" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="D159" s="97" t="s">
+      <c r="D159" s="96" t="s">
         <v>39</v>
       </c>
       <c r="E159" s="35" t="s">
@@ -10921,8 +10918,8 @@
       <c r="F159" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G159" s="98"/>
-      <c r="H159" s="104"/>
+      <c r="G159" s="97"/>
+      <c r="H159" s="103"/>
       <c r="I159" s="35" t="s">
         <v>45</v>
       </c>
@@ -10932,7 +10929,7 @@
       <c r="K159" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L159" s="118" t="s">
+      <c r="L159" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M159" s="35" t="s">
@@ -10941,18 +10938,18 @@
       <c r="N159" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O159" s="146"/>
+      <c r="O159" s="145"/>
       <c r="P159" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="160" spans="1:16" s="2" customFormat="1">
-      <c r="A160" s="147"/>
+      <c r="A160" s="146"/>
       <c r="B160" s="26"/>
       <c r="C160" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="D160" s="119" t="s">
+      <c r="D160" s="118" t="s">
         <v>21</v>
       </c>
       <c r="E160" s="35" t="s">
@@ -10977,7 +10974,7 @@
       <c r="K160" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L160" s="119" t="s">
+      <c r="L160" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M160" s="35" t="s">
@@ -10986,13 +10983,13 @@
       <c r="N160" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O160" s="147"/>
+      <c r="O160" s="146"/>
       <c r="P160" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="161" spans="1:16" s="2" customFormat="1">
-      <c r="A161" s="145" t="s">
+      <c r="A161" s="144" t="s">
         <v>244</v>
       </c>
       <c r="B161" s="39" t="s">
@@ -11030,12 +11027,12 @@
         <v>27</v>
       </c>
       <c r="M161" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N161" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O161" s="145" t="s">
+      <c r="O161" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P161" s="19" t="s">
@@ -11043,7 +11040,7 @@
       </c>
     </row>
     <row r="162" spans="1:16" s="2" customFormat="1">
-      <c r="A162" s="146"/>
+      <c r="A162" s="145"/>
       <c r="B162" s="29"/>
       <c r="C162" s="30" t="s">
         <v>246</v>
@@ -11077,18 +11074,18 @@
         <v>27</v>
       </c>
       <c r="M162" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N162" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O162" s="146"/>
+      <c r="O162" s="145"/>
       <c r="P162" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="163" spans="1:16" s="2" customFormat="1">
-      <c r="A163" s="146"/>
+      <c r="A163" s="145"/>
       <c r="B163" s="29"/>
       <c r="C163" s="30" t="s">
         <v>247</v>
@@ -11122,18 +11119,18 @@
         <v>27</v>
       </c>
       <c r="M163" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N163" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O163" s="146"/>
+      <c r="O163" s="145"/>
       <c r="P163" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="164" spans="1:16" s="2" customFormat="1">
-      <c r="A164" s="147"/>
+      <c r="A164" s="146"/>
       <c r="B164" s="35"/>
       <c r="C164" s="36" t="s">
         <v>249</v>
@@ -11172,13 +11169,13 @@
       <c r="N164" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O164" s="147"/>
+      <c r="O164" s="146"/>
       <c r="P164" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="165" spans="1:16" s="2" customFormat="1">
-      <c r="A165" s="145" t="s">
+      <c r="A165" s="144" t="s">
         <v>251</v>
       </c>
       <c r="B165" s="39" t="s">
@@ -11216,12 +11213,12 @@
         <v>27</v>
       </c>
       <c r="M165" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N165" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O165" s="151" t="s">
+      <c r="O165" s="150" t="s">
         <v>36</v>
       </c>
       <c r="P165" s="19" t="s">
@@ -11229,7 +11226,7 @@
       </c>
     </row>
     <row r="166" spans="1:16" s="2" customFormat="1">
-      <c r="A166" s="146"/>
+      <c r="A166" s="145"/>
       <c r="B166" s="29"/>
       <c r="C166" s="30" t="s">
         <v>715</v>
@@ -11263,18 +11260,18 @@
         <v>27</v>
       </c>
       <c r="M166" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N166" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O166" s="151"/>
+      <c r="O166" s="150"/>
       <c r="P166" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="167" spans="1:16" s="2" customFormat="1">
-      <c r="A167" s="147"/>
+      <c r="A167" s="146"/>
       <c r="B167" s="35"/>
       <c r="C167" s="36" t="s">
         <v>716</v>
@@ -11313,19 +11310,19 @@
       <c r="N167" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O167" s="151"/>
+      <c r="O167" s="150"/>
       <c r="P167" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="168" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A168" s="150" t="s">
+      <c r="A168" s="149" t="s">
         <v>252</v>
       </c>
-      <c r="B168" s="99" t="s">
+      <c r="B168" s="98" t="s">
         <v>697</v>
       </c>
-      <c r="C168" s="99" t="s">
+      <c r="C168" s="98" t="s">
         <v>697</v>
       </c>
       <c r="D168" s="24" t="s">
@@ -11357,22 +11354,22 @@
         <v>27</v>
       </c>
       <c r="M168" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N168" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O168" s="145" t="s">
+      <c r="O168" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="P168" s="19" t="s">
+      <c r="P168" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="169" spans="1:16" s="2" customFormat="1">
-      <c r="A169" s="148"/>
+      <c r="A169" s="147"/>
       <c r="B169" s="32"/>
-      <c r="C169" s="106" t="s">
+      <c r="C169" s="105" t="s">
         <v>698</v>
       </c>
       <c r="D169" s="31" t="s">
@@ -11404,18 +11401,18 @@
         <v>27</v>
       </c>
       <c r="M169" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N169" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O169" s="147"/>
-      <c r="P169" s="19" t="s">
+      <c r="O169" s="146"/>
+      <c r="P169" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="170" spans="1:16" s="2" customFormat="1">
-      <c r="A170" s="145" t="s">
+      <c r="A170" s="144" t="s">
         <v>257</v>
       </c>
       <c r="B170" s="39" t="s">
@@ -11458,7 +11455,7 @@
       <c r="N170" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O170" s="145" t="s">
+      <c r="O170" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P170" s="19" t="s">
@@ -11466,7 +11463,7 @@
       </c>
     </row>
     <row r="171" spans="1:16" s="2" customFormat="1">
-      <c r="A171" s="146"/>
+      <c r="A171" s="145"/>
       <c r="B171" s="29"/>
       <c r="C171" s="30" t="s">
         <v>261</v>
@@ -11505,13 +11502,13 @@
       <c r="N171" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O171" s="146"/>
+      <c r="O171" s="145"/>
       <c r="P171" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="172" spans="1:16" s="2" customFormat="1">
-      <c r="A172" s="146"/>
+      <c r="A172" s="145"/>
       <c r="B172" s="29"/>
       <c r="C172" s="30" t="s">
         <v>262</v>
@@ -11545,18 +11542,18 @@
         <v>27</v>
       </c>
       <c r="M172" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N172" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O172" s="146"/>
+      <c r="O172" s="145"/>
       <c r="P172" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="173" spans="1:16" s="2" customFormat="1">
-      <c r="A173" s="147"/>
+      <c r="A173" s="146"/>
       <c r="B173" s="35"/>
       <c r="C173" s="36" t="s">
         <v>263</v>
@@ -11590,27 +11587,27 @@
         <v>27</v>
       </c>
       <c r="M173" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N173" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O173" s="146"/>
+      <c r="O173" s="145"/>
       <c r="P173" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="174" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A174" s="150" t="s">
+      <c r="A174" s="149" t="s">
         <v>264</v>
       </c>
-      <c r="B174" s="99" t="s">
+      <c r="B174" s="98" t="s">
         <v>253</v>
       </c>
-      <c r="C174" s="99" t="s">
+      <c r="C174" s="98" t="s">
         <v>253</v>
       </c>
-      <c r="D174" s="117" t="s">
+      <c r="D174" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E174" s="25" t="s">
@@ -11635,29 +11632,29 @@
       <c r="K174" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L174" s="119" t="s">
+      <c r="L174" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M174" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N174" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O174" s="146" t="s">
+      <c r="O174" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="P174" s="19" t="s">
+      <c r="P174" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="175" spans="1:16" s="2" customFormat="1">
-      <c r="A175" s="148"/>
+      <c r="A175" s="147"/>
       <c r="B175" s="32"/>
-      <c r="C175" s="106" t="s">
+      <c r="C175" s="105" t="s">
         <v>254</v>
       </c>
-      <c r="D175" s="118" t="s">
+      <c r="D175" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E175" s="29" t="s">
@@ -11682,27 +11679,27 @@
       <c r="K175" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L175" s="119" t="s">
+      <c r="L175" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M175" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N175" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O175" s="146"/>
-      <c r="P175" s="19" t="s">
+      <c r="O175" s="145"/>
+      <c r="P175" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="176" spans="1:16" s="2" customFormat="1">
-      <c r="A176" s="148"/>
+      <c r="A176" s="147"/>
       <c r="B176" s="32"/>
-      <c r="C176" s="106" t="s">
+      <c r="C176" s="105" t="s">
         <v>255</v>
       </c>
-      <c r="D176" s="118" t="s">
+      <c r="D176" s="117" t="s">
         <v>21</v>
       </c>
       <c r="E176" s="29" t="s">
@@ -11727,27 +11724,27 @@
       <c r="K176" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L176" s="119" t="s">
+      <c r="L176" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M176" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N176" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O176" s="146"/>
-      <c r="P176" s="19" t="s">
+      <c r="O176" s="145"/>
+      <c r="P176" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="177" spans="1:16" s="84" customFormat="1">
-      <c r="A177" s="149"/>
-      <c r="B177" s="101"/>
-      <c r="C177" s="102" t="s">
+      <c r="A177" s="148"/>
+      <c r="B177" s="100"/>
+      <c r="C177" s="101" t="s">
         <v>256</v>
       </c>
-      <c r="D177" s="119" t="s">
+      <c r="D177" s="118" t="s">
         <v>21</v>
       </c>
       <c r="E177" s="35" t="s">
@@ -11772,28 +11769,28 @@
       <c r="K177" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L177" s="119" t="s">
+      <c r="L177" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M177" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N177" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O177" s="147"/>
-      <c r="P177" s="19" t="s">
+      <c r="O177" s="146"/>
+      <c r="P177" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="178" spans="1:16" s="84" customFormat="1" ht="15" customHeight="1">
-      <c r="A178" s="150" t="s">
+      <c r="A178" s="149" t="s">
         <v>265</v>
       </c>
-      <c r="B178" s="93" t="s">
+      <c r="B178" s="92" t="s">
         <v>696</v>
       </c>
-      <c r="C178" s="93" t="s">
+      <c r="C178" s="92" t="s">
         <v>696</v>
       </c>
       <c r="D178" s="24" t="s">
@@ -11802,7 +11799,7 @@
       <c r="E178" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F178" s="102" t="s">
+      <c r="F178" s="101" t="s">
         <v>23</v>
       </c>
       <c r="G178" s="57">
@@ -11821,27 +11818,27 @@
       <c r="K178" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L178" s="101" t="s">
+      <c r="L178" s="100" t="s">
         <v>27</v>
       </c>
       <c r="M178" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N178" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O178" s="150" t="s">
+      <c r="O178" s="149" t="s">
         <v>30</v>
       </c>
-      <c r="P178" s="19" t="s">
+      <c r="P178" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="179" spans="1:16" s="84" customFormat="1">
-      <c r="A179" s="148"/>
-      <c r="B179" s="101"/>
-      <c r="C179" s="102" t="s">
-        <v>756</v>
+      <c r="A179" s="147"/>
+      <c r="B179" s="100"/>
+      <c r="C179" s="101" t="s">
+        <v>755</v>
       </c>
       <c r="D179" s="31" t="s">
         <v>39</v>
@@ -11849,7 +11846,7 @@
       <c r="E179" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F179" s="102" t="s">
+      <c r="F179" s="101" t="s">
         <v>23</v>
       </c>
       <c r="G179" s="57">
@@ -11872,29 +11869,29 @@
         <v>27</v>
       </c>
       <c r="M179" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N179" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O179" s="148"/>
-      <c r="P179" s="19" t="s">
+      <c r="O179" s="147"/>
+      <c r="P179" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="180" spans="1:16" s="84" customFormat="1">
-      <c r="A180" s="148"/>
-      <c r="B180" s="101"/>
-      <c r="C180" s="102" t="s">
-        <v>757</v>
-      </c>
-      <c r="D180" s="118" t="s">
+      <c r="A180" s="147"/>
+      <c r="B180" s="100"/>
+      <c r="C180" s="101" t="s">
+        <v>756</v>
+      </c>
+      <c r="D180" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E180" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F180" s="102" t="s">
+      <c r="F180" s="101" t="s">
         <v>23</v>
       </c>
       <c r="G180" s="57">
@@ -11913,33 +11910,33 @@
       <c r="K180" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L180" s="119" t="s">
+      <c r="L180" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M180" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N180" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O180" s="148"/>
-      <c r="P180" s="19" t="s">
+      <c r="O180" s="147"/>
+      <c r="P180" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="181" spans="1:16" s="84" customFormat="1">
-      <c r="A181" s="148"/>
-      <c r="B181" s="101"/>
-      <c r="C181" s="102" t="s">
-        <v>758</v>
-      </c>
-      <c r="D181" s="86" t="s">
+      <c r="A181" s="147"/>
+      <c r="B181" s="100"/>
+      <c r="C181" s="101" t="s">
+        <v>757</v>
+      </c>
+      <c r="D181" s="85" t="s">
         <v>39</v>
       </c>
       <c r="E181" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F181" s="102" t="s">
+      <c r="F181" s="101" t="s">
         <v>23</v>
       </c>
       <c r="G181" s="57">
@@ -11962,18 +11959,18 @@
         <v>27</v>
       </c>
       <c r="M181" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N181" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O181" s="149"/>
-      <c r="P181" s="19" t="s">
+      <c r="O181" s="148"/>
+      <c r="P181" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="182" spans="1:16" s="2" customFormat="1">
-      <c r="A182" s="145" t="s">
+      <c r="A182" s="144" t="s">
         <v>266</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -12016,7 +12013,7 @@
       <c r="N182" s="19" t="s">
         <v>736</v>
       </c>
-      <c r="O182" s="145" t="s">
+      <c r="O182" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P182" s="19" t="s">
@@ -12024,7 +12021,7 @@
       </c>
     </row>
     <row r="183" spans="1:16" s="2" customFormat="1">
-      <c r="A183" s="146"/>
+      <c r="A183" s="145"/>
       <c r="B183" s="29"/>
       <c r="C183" s="29" t="s">
         <v>269</v>
@@ -12058,18 +12055,18 @@
         <v>27</v>
       </c>
       <c r="M183" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N183" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="O183" s="146"/>
+      <c r="O183" s="145"/>
       <c r="P183" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="184" spans="1:16" s="2" customFormat="1">
-      <c r="A184" s="146"/>
+      <c r="A184" s="145"/>
       <c r="B184" s="29"/>
       <c r="C184" s="29" t="s">
         <v>270</v>
@@ -12103,24 +12100,24 @@
         <v>27</v>
       </c>
       <c r="M184" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N184" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="O184" s="146"/>
+      <c r="O184" s="145"/>
       <c r="P184" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="185" spans="1:16" s="2" customFormat="1">
-      <c r="A185" s="147"/>
+      <c r="A185" s="146"/>
       <c r="B185" s="35"/>
       <c r="C185" s="35" t="s">
         <v>272</v>
       </c>
       <c r="D185" s="37" t="s">
-        <v>755</v>
+        <v>39</v>
       </c>
       <c r="E185" s="35" t="s">
         <v>44</v>
@@ -12148,18 +12145,18 @@
         <v>27</v>
       </c>
       <c r="M185" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N185" s="19" t="s">
         <v>739</v>
       </c>
-      <c r="O185" s="147"/>
+      <c r="O185" s="146"/>
       <c r="P185" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="186" spans="1:16" s="2" customFormat="1">
-      <c r="A186" s="145" t="s">
+      <c r="A186" s="144" t="s">
         <v>273</v>
       </c>
       <c r="B186" s="38" t="s">
@@ -12197,12 +12194,12 @@
         <v>27</v>
       </c>
       <c r="M186" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N186" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O186" s="145" t="s">
+      <c r="O186" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P186" s="19" t="s">
@@ -12210,7 +12207,7 @@
       </c>
     </row>
     <row r="187" spans="1:16" s="2" customFormat="1">
-      <c r="A187" s="146"/>
+      <c r="A187" s="145"/>
       <c r="B187" s="29"/>
       <c r="C187" s="29" t="s">
         <v>275</v>
@@ -12244,18 +12241,18 @@
         <v>27</v>
       </c>
       <c r="M187" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N187" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O187" s="146"/>
+      <c r="O187" s="145"/>
       <c r="P187" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="188" spans="1:16" s="2" customFormat="1">
-      <c r="A188" s="146"/>
+      <c r="A188" s="145"/>
       <c r="B188" s="29"/>
       <c r="C188" s="29" t="s">
         <v>276</v>
@@ -12289,18 +12286,18 @@
         <v>27</v>
       </c>
       <c r="M188" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N188" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O188" s="146"/>
+      <c r="O188" s="145"/>
       <c r="P188" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="189" spans="1:16" s="2" customFormat="1">
-      <c r="A189" s="146"/>
+      <c r="A189" s="145"/>
       <c r="B189" s="29"/>
       <c r="C189" s="29" t="s">
         <v>277</v>
@@ -12334,18 +12331,18 @@
         <v>27</v>
       </c>
       <c r="M189" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N189" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O189" s="146"/>
+      <c r="O189" s="145"/>
       <c r="P189" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="190" spans="1:16" s="2" customFormat="1">
-      <c r="A190" s="147"/>
+      <c r="A190" s="146"/>
       <c r="B190" s="35"/>
       <c r="C190" s="35" t="s">
         <v>278</v>
@@ -12379,62 +12376,62 @@
         <v>27</v>
       </c>
       <c r="M190" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N190" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O190" s="147"/>
+      <c r="O190" s="146"/>
       <c r="P190" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="191" spans="1:16" s="2" customFormat="1">
-      <c r="A191" s="132" t="s">
+      <c r="A191" s="131" t="s">
         <v>279</v>
       </c>
-      <c r="B191" s="107"/>
-      <c r="C191" s="107"/>
-      <c r="D191" s="108"/>
-      <c r="E191" s="109"/>
-      <c r="F191" s="109"/>
-      <c r="G191" s="110"/>
-      <c r="H191" s="115"/>
-      <c r="I191" s="109"/>
-      <c r="J191" s="109"/>
-      <c r="K191" s="109"/>
-      <c r="L191" s="108"/>
-      <c r="M191" s="109"/>
-      <c r="N191" s="109"/>
-      <c r="O191" s="88" t="s">
+      <c r="B191" s="106"/>
+      <c r="C191" s="106"/>
+      <c r="D191" s="107"/>
+      <c r="E191" s="108"/>
+      <c r="F191" s="108"/>
+      <c r="G191" s="109"/>
+      <c r="H191" s="114"/>
+      <c r="I191" s="108"/>
+      <c r="J191" s="108"/>
+      <c r="K191" s="108"/>
+      <c r="L191" s="107"/>
+      <c r="M191" s="108"/>
+      <c r="N191" s="108"/>
+      <c r="O191" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="P191" s="133"/>
+      <c r="P191" s="132"/>
     </row>
     <row r="192" spans="1:16" s="2" customFormat="1">
-      <c r="A192" s="132" t="s">
+      <c r="A192" s="131" t="s">
         <v>287</v>
       </c>
-      <c r="B192" s="107"/>
-      <c r="C192" s="107"/>
-      <c r="D192" s="108"/>
-      <c r="E192" s="109"/>
-      <c r="F192" s="109"/>
-      <c r="G192" s="110"/>
-      <c r="H192" s="115"/>
-      <c r="I192" s="109"/>
-      <c r="J192" s="109"/>
-      <c r="K192" s="109"/>
-      <c r="L192" s="108"/>
-      <c r="M192" s="109"/>
-      <c r="N192" s="132"/>
-      <c r="O192" s="88" t="s">
+      <c r="B192" s="106"/>
+      <c r="C192" s="106"/>
+      <c r="D192" s="107"/>
+      <c r="E192" s="108"/>
+      <c r="F192" s="108"/>
+      <c r="G192" s="109"/>
+      <c r="H192" s="114"/>
+      <c r="I192" s="108"/>
+      <c r="J192" s="108"/>
+      <c r="K192" s="108"/>
+      <c r="L192" s="107"/>
+      <c r="M192" s="108"/>
+      <c r="N192" s="131"/>
+      <c r="O192" s="87" t="s">
         <v>58</v>
       </c>
-      <c r="P192" s="133"/>
+      <c r="P192" s="132"/>
     </row>
     <row r="193" spans="1:16" s="2" customFormat="1">
-      <c r="A193" s="145" t="s">
+      <c r="A193" s="144" t="s">
         <v>605</v>
       </c>
       <c r="B193" s="38" t="s">
@@ -12477,7 +12474,7 @@
       <c r="N193" s="19" t="s">
         <v>736</v>
       </c>
-      <c r="O193" s="145" t="s">
+      <c r="O193" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P193" s="46" t="s">
@@ -12485,7 +12482,7 @@
       </c>
     </row>
     <row r="194" spans="1:16" s="2" customFormat="1">
-      <c r="A194" s="146"/>
+      <c r="A194" s="145"/>
       <c r="B194" s="29"/>
       <c r="C194" s="29" t="s">
         <v>703</v>
@@ -12519,18 +12516,18 @@
         <v>27</v>
       </c>
       <c r="M194" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N194" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="O194" s="146"/>
+      <c r="O194" s="145"/>
       <c r="P194" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="195" spans="1:16" s="2" customFormat="1">
-      <c r="A195" s="145" t="s">
+      <c r="A195" s="144" t="s">
         <v>288</v>
       </c>
       <c r="B195" s="38" t="s">
@@ -12568,12 +12565,12 @@
         <v>27</v>
       </c>
       <c r="M195" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N195" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O195" s="145" t="s">
+      <c r="O195" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P195" s="19" t="s">
@@ -12581,7 +12578,7 @@
       </c>
     </row>
     <row r="196" spans="1:16" s="2" customFormat="1">
-      <c r="A196" s="146"/>
+      <c r="A196" s="145"/>
       <c r="B196" s="29"/>
       <c r="C196" s="29" t="s">
         <v>291</v>
@@ -12615,18 +12612,18 @@
         <v>112</v>
       </c>
       <c r="M196" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N196" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O196" s="146"/>
+      <c r="O196" s="145"/>
       <c r="P196" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="197" spans="1:16" s="2" customFormat="1">
-      <c r="A197" s="146"/>
+      <c r="A197" s="145"/>
       <c r="B197" s="29"/>
       <c r="C197" s="29" t="s">
         <v>293</v>
@@ -12665,13 +12662,13 @@
       <c r="N197" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O197" s="146"/>
+      <c r="O197" s="145"/>
       <c r="P197" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="198" spans="1:16" s="2" customFormat="1">
-      <c r="A198" s="147"/>
+      <c r="A198" s="146"/>
       <c r="B198" s="35"/>
       <c r="C198" s="35" t="s">
         <v>294</v>
@@ -12705,27 +12702,27 @@
         <v>27</v>
       </c>
       <c r="M198" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N198" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="O198" s="147"/>
+      <c r="O198" s="146"/>
       <c r="P198" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="199" spans="1:16" s="2" customFormat="1">
-      <c r="A199" s="116" t="s">
+      <c r="A199" s="115" t="s">
         <v>624</v>
       </c>
-      <c r="B199" s="127" t="s">
+      <c r="B199" s="126" t="s">
         <v>725</v>
       </c>
-      <c r="C199" s="127" t="s">
+      <c r="C199" s="126" t="s">
         <v>725</v>
       </c>
-      <c r="D199" s="117" t="s">
+      <c r="D199" s="116" t="s">
         <v>21</v>
       </c>
       <c r="E199" s="25" t="s">
@@ -12734,10 +12731,10 @@
       <c r="F199" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G199" s="124">
+      <c r="G199" s="123">
         <v>28204</v>
       </c>
-      <c r="H199" s="125">
+      <c r="H199" s="124">
         <f t="shared" ca="1" si="3"/>
         <v>49</v>
       </c>
@@ -12750,16 +12747,16 @@
       <c r="K199" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="L199" s="119" t="s">
+      <c r="L199" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M199" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N199" s="26" t="s">
         <v>738</v>
       </c>
-      <c r="O199" s="145" t="s">
+      <c r="O199" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P199" s="19" t="s">
@@ -12767,12 +12764,12 @@
       </c>
     </row>
     <row r="200" spans="1:16" s="2" customFormat="1">
-      <c r="A200" s="116"/>
+      <c r="A200" s="115"/>
       <c r="B200" s="26"/>
       <c r="C200" s="26" t="s">
         <v>726</v>
       </c>
-      <c r="D200" s="118" t="s">
+      <c r="D200" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E200" s="29" t="s">
@@ -12781,10 +12778,10 @@
       <c r="F200" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G200" s="124">
+      <c r="G200" s="123">
         <v>29381</v>
       </c>
-      <c r="H200" s="125">
+      <c r="H200" s="124">
         <f t="shared" ca="1" si="3"/>
         <v>46</v>
       </c>
@@ -12797,27 +12794,27 @@
       <c r="K200" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L200" s="119" t="s">
+      <c r="L200" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M200" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N200" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O200" s="146"/>
+      <c r="O200" s="145"/>
       <c r="P200" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="201" spans="1:16" s="2" customFormat="1">
-      <c r="A201" s="116"/>
+      <c r="A201" s="115"/>
       <c r="B201" s="26"/>
       <c r="C201" s="26" t="s">
         <v>727</v>
       </c>
-      <c r="D201" s="118" t="s">
+      <c r="D201" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E201" s="29" t="s">
@@ -12826,10 +12823,10 @@
       <c r="F201" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G201" s="124">
+      <c r="G201" s="123">
         <v>36782</v>
       </c>
-      <c r="H201" s="125">
+      <c r="H201" s="124">
         <f t="shared" ca="1" si="3"/>
         <v>26</v>
       </c>
@@ -12842,27 +12839,27 @@
       <c r="K201" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L201" s="119" t="s">
+      <c r="L201" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M201" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N201" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O201" s="146"/>
+      <c r="O201" s="145"/>
       <c r="P201" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="202" spans="1:16" s="2" customFormat="1">
-      <c r="A202" s="116"/>
+      <c r="A202" s="115"/>
       <c r="B202" s="26"/>
       <c r="C202" s="26" t="s">
         <v>728</v>
       </c>
-      <c r="D202" s="119" t="s">
+      <c r="D202" s="118" t="s">
         <v>39</v>
       </c>
       <c r="E202" s="35" t="s">
@@ -12871,10 +12868,10 @@
       <c r="F202" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G202" s="124">
+      <c r="G202" s="123">
         <v>40293</v>
       </c>
-      <c r="H202" s="125">
+      <c r="H202" s="124">
         <f t="shared" ca="1" si="3"/>
         <v>16</v>
       </c>
@@ -12887,22 +12884,22 @@
       <c r="K202" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L202" s="119" t="s">
+      <c r="L202" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M202" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N202" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="O202" s="147"/>
+      <c r="O202" s="146"/>
       <c r="P202" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="203" spans="1:16" s="2" customFormat="1">
-      <c r="A203" s="145" t="s">
+      <c r="A203" s="144" t="s">
         <v>295</v>
       </c>
       <c r="B203" s="38" t="s">
@@ -12940,12 +12937,12 @@
         <v>27</v>
       </c>
       <c r="M203" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N203" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O203" s="145" t="s">
+      <c r="O203" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P203" s="46" t="s">
@@ -12953,7 +12950,7 @@
       </c>
     </row>
     <row r="204" spans="1:16" s="2" customFormat="1">
-      <c r="A204" s="146"/>
+      <c r="A204" s="145"/>
       <c r="B204" s="29"/>
       <c r="C204" s="29" t="s">
         <v>722</v>
@@ -12992,13 +12989,13 @@
       <c r="N204" s="29" t="s">
         <v>724</v>
       </c>
-      <c r="O204" s="146"/>
+      <c r="O204" s="145"/>
       <c r="P204" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="205" spans="1:16" s="2" customFormat="1">
-      <c r="A205" s="145" t="s">
+      <c r="A205" s="144" t="s">
         <v>301</v>
       </c>
       <c r="B205" s="38" t="s">
@@ -13036,12 +13033,12 @@
         <v>27</v>
       </c>
       <c r="M205" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N205" s="25" t="s">
         <v>737</v>
       </c>
-      <c r="O205" s="145" t="s">
+      <c r="O205" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P205" s="19" t="s">
@@ -13049,7 +13046,7 @@
       </c>
     </row>
     <row r="206" spans="1:16" s="2" customFormat="1">
-      <c r="A206" s="146"/>
+      <c r="A206" s="145"/>
       <c r="B206" s="29"/>
       <c r="C206" s="29" t="s">
         <v>303</v>
@@ -13083,18 +13080,18 @@
         <v>27</v>
       </c>
       <c r="M206" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N206" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O206" s="146"/>
+      <c r="O206" s="145"/>
       <c r="P206" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="207" spans="1:16" s="2" customFormat="1">
-      <c r="A207" s="147"/>
+      <c r="A207" s="146"/>
       <c r="B207" s="35"/>
       <c r="C207" s="35" t="s">
         <v>304</v>
@@ -13128,19 +13125,21 @@
         <v>27</v>
       </c>
       <c r="M207" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N207" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O207" s="147"/>
+      <c r="O207" s="146"/>
       <c r="P207" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="208" spans="1:16" s="2" customFormat="1">
-      <c r="A208" s="87"/>
-      <c r="B208" s="36" t="s">
+      <c r="A208" s="86" t="s">
+        <v>649</v>
+      </c>
+      <c r="B208" s="160" t="s">
         <v>305</v>
       </c>
       <c r="C208" s="36" t="s">
@@ -13175,12 +13174,12 @@
         <v>27</v>
       </c>
       <c r="M208" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N208" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="O208" s="87" t="s">
+      <c r="O208" s="86" t="s">
         <v>36</v>
       </c>
       <c r="P208" s="19" t="s">
@@ -13188,7 +13187,7 @@
       </c>
     </row>
     <row r="209" spans="1:16" s="2" customFormat="1">
-      <c r="A209" s="145" t="s">
+      <c r="A209" s="144" t="s">
         <v>306</v>
       </c>
       <c r="B209" s="39" t="s">
@@ -13231,7 +13230,7 @@
       <c r="N209" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="O209" s="145" t="s">
+      <c r="O209" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P209" s="46" t="s">
@@ -13239,7 +13238,7 @@
       </c>
     </row>
     <row r="210" spans="1:16" s="2" customFormat="1">
-      <c r="A210" s="146"/>
+      <c r="A210" s="145"/>
       <c r="B210" s="29"/>
       <c r="C210" s="30" t="s">
         <v>309</v>
@@ -13278,13 +13277,13 @@
       <c r="N210" s="29" t="s">
         <v>310</v>
       </c>
-      <c r="O210" s="146"/>
+      <c r="O210" s="145"/>
       <c r="P210" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="211" spans="1:16" s="2" customFormat="1">
-      <c r="A211" s="146"/>
+      <c r="A211" s="145"/>
       <c r="B211" s="29"/>
       <c r="C211" s="30" t="s">
         <v>311</v>
@@ -13318,18 +13317,18 @@
         <v>27</v>
       </c>
       <c r="M211" s="35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N211" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O211" s="146"/>
+      <c r="O211" s="145"/>
       <c r="P211" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="212" spans="1:16" s="2" customFormat="1">
-      <c r="A212" s="146"/>
+      <c r="A212" s="145"/>
       <c r="B212" s="29"/>
       <c r="C212" s="30" t="s">
         <v>312</v>
@@ -13363,18 +13362,18 @@
         <v>27</v>
       </c>
       <c r="M212" s="35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N212" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O212" s="146"/>
+      <c r="O212" s="145"/>
       <c r="P212" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="213" spans="1:16" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A213" s="150" t="s">
+      <c r="A213" s="149" t="s">
         <v>313</v>
       </c>
       <c r="B213" s="39" t="s">
@@ -13412,12 +13411,12 @@
         <v>27</v>
       </c>
       <c r="M213" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N213" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="O213" s="145" t="s">
+      <c r="O213" s="144" t="s">
         <v>30</v>
       </c>
       <c r="P213" s="19" t="s">
@@ -13425,7 +13424,7 @@
       </c>
     </row>
     <row r="214" spans="1:16" s="2" customFormat="1">
-      <c r="A214" s="148"/>
+      <c r="A214" s="147"/>
       <c r="B214" s="29"/>
       <c r="C214" s="30" t="s">
         <v>315</v>
@@ -13459,18 +13458,18 @@
         <v>27</v>
       </c>
       <c r="M214" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N214" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O214" s="146"/>
+      <c r="O214" s="145"/>
       <c r="P214" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="215" spans="1:16" s="2" customFormat="1">
-      <c r="A215" s="148"/>
+      <c r="A215" s="147"/>
       <c r="B215" s="29"/>
       <c r="C215" s="30" t="s">
         <v>316</v>
@@ -13504,18 +13503,18 @@
         <v>27</v>
       </c>
       <c r="M215" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N215" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O215" s="146"/>
+      <c r="O215" s="145"/>
       <c r="P215" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="216" spans="1:16" s="2" customFormat="1">
-      <c r="A216" s="149"/>
+      <c r="A216" s="148"/>
       <c r="B216" s="35"/>
       <c r="C216" s="36" t="s">
         <v>318</v>
@@ -13549,16 +13548,18 @@
         <v>27</v>
       </c>
       <c r="M216" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N216" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O216" s="147"/>
-      <c r="P216" s="19"/>
+      <c r="O216" s="146"/>
+      <c r="P216" s="19" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="217" spans="1:16" s="2" customFormat="1">
-      <c r="A217" s="145" t="s">
+      <c r="A217" s="144" t="s">
         <v>319</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -13601,7 +13602,7 @@
       <c r="N217" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O217" s="145" t="s">
+      <c r="O217" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P217" s="19" t="s">
@@ -13609,7 +13610,7 @@
       </c>
     </row>
     <row r="218" spans="1:16" s="2" customFormat="1">
-      <c r="A218" s="146"/>
+      <c r="A218" s="145"/>
       <c r="B218" s="29"/>
       <c r="C218" s="29" t="s">
         <v>322</v>
@@ -13648,13 +13649,13 @@
       <c r="N218" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="O218" s="146"/>
+      <c r="O218" s="145"/>
       <c r="P218" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="219" spans="1:16" s="2" customFormat="1">
-      <c r="A219" s="146"/>
+      <c r="A219" s="145"/>
       <c r="B219" s="29"/>
       <c r="C219" s="29" t="s">
         <v>324</v>
@@ -13693,13 +13694,13 @@
       <c r="N219" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O219" s="146"/>
+      <c r="O219" s="145"/>
       <c r="P219" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="220" spans="1:16" s="2" customFormat="1">
-      <c r="A220" s="147"/>
+      <c r="A220" s="146"/>
       <c r="B220" s="35"/>
       <c r="C220" s="36" t="s">
         <v>325</v>
@@ -13733,18 +13734,18 @@
         <v>27</v>
       </c>
       <c r="M220" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N220" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="O220" s="147"/>
+      <c r="O220" s="146"/>
       <c r="P220" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="221" spans="1:16" s="2" customFormat="1">
-      <c r="A221" s="145" t="s">
+      <c r="A221" s="144" t="s">
         <v>326</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -13782,12 +13783,12 @@
         <v>27</v>
       </c>
       <c r="M221" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N221" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="O221" s="145" t="s">
+      <c r="O221" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P221" s="46" t="s">
@@ -13795,12 +13796,12 @@
       </c>
     </row>
     <row r="222" spans="1:16" s="2" customFormat="1">
-      <c r="A222" s="146"/>
+      <c r="A222" s="145"/>
       <c r="B222" s="29"/>
       <c r="C222" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="D222" s="118" t="s">
+      <c r="D222" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E222" s="29" t="s">
@@ -13825,27 +13826,27 @@
       <c r="K222" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L222" s="118" t="s">
+      <c r="L222" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M222" s="29" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N222" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O222" s="146"/>
+      <c r="O222" s="145"/>
       <c r="P222" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="223" spans="1:16" s="2" customFormat="1">
-      <c r="A223" s="146"/>
+      <c r="A223" s="145"/>
       <c r="B223" s="29"/>
       <c r="C223" s="30" t="s">
         <v>699</v>
       </c>
-      <c r="D223" s="118" t="s">
+      <c r="D223" s="117" t="s">
         <v>39</v>
       </c>
       <c r="E223" s="29" t="s">
@@ -13870,22 +13871,22 @@
       <c r="K223" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L223" s="118" t="s">
+      <c r="L223" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M223" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N223" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O223" s="146"/>
+      <c r="O223" s="145"/>
       <c r="P223" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="224" spans="1:16" s="2" customFormat="1">
-      <c r="A224" s="146"/>
+      <c r="A224" s="145"/>
       <c r="B224" s="29"/>
       <c r="C224" s="30" t="s">
         <v>700</v>
@@ -13924,35 +13925,35 @@
       <c r="N224" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O224" s="146"/>
+      <c r="O224" s="145"/>
       <c r="P224" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="225" spans="1:253" s="2" customFormat="1">
-      <c r="A225" s="88" t="s">
+      <c r="A225" s="87" t="s">
         <v>329</v>
       </c>
-      <c r="B225" s="107"/>
-      <c r="C225" s="107"/>
-      <c r="D225" s="108"/>
-      <c r="E225" s="109"/>
-      <c r="F225" s="109"/>
-      <c r="G225" s="110"/>
-      <c r="H225" s="115"/>
-      <c r="I225" s="109"/>
-      <c r="J225" s="109"/>
-      <c r="K225" s="109"/>
-      <c r="L225" s="108"/>
-      <c r="M225" s="109"/>
-      <c r="N225" s="109"/>
-      <c r="O225" s="85" t="s">
+      <c r="B225" s="106"/>
+      <c r="C225" s="106"/>
+      <c r="D225" s="107"/>
+      <c r="E225" s="108"/>
+      <c r="F225" s="108"/>
+      <c r="G225" s="109"/>
+      <c r="H225" s="114"/>
+      <c r="I225" s="108"/>
+      <c r="J225" s="108"/>
+      <c r="K225" s="108"/>
+      <c r="L225" s="107"/>
+      <c r="M225" s="108"/>
+      <c r="N225" s="108"/>
+      <c r="O225" s="87" t="s">
         <v>58</v>
       </c>
       <c r="P225" s="46"/>
     </row>
     <row r="226" spans="1:253" s="2" customFormat="1">
-      <c r="A226" s="145" t="s">
+      <c r="A226" s="144" t="s">
         <v>330</v>
       </c>
       <c r="B226" s="38" t="s">
@@ -13990,12 +13991,12 @@
         <v>27</v>
       </c>
       <c r="M226" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N226" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O226" s="145" t="s">
+      <c r="O226" s="144" t="s">
         <v>36</v>
       </c>
       <c r="P226" s="19" t="s">
@@ -14003,7 +14004,7 @@
       </c>
     </row>
     <row r="227" spans="1:253" s="2" customFormat="1">
-      <c r="A227" s="146"/>
+      <c r="A227" s="145"/>
       <c r="B227" s="29"/>
       <c r="C227" s="29" t="s">
         <v>332</v>
@@ -14037,23 +14038,23 @@
         <v>27</v>
       </c>
       <c r="M227" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N227" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O227" s="146"/>
+      <c r="O227" s="145"/>
       <c r="P227" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="228" spans="1:253" s="2" customFormat="1">
-      <c r="A228" s="146"/>
+      <c r="A228" s="145"/>
       <c r="B228" s="35"/>
       <c r="C228" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="D228" s="119" t="s">
+      <c r="D228" s="118" t="s">
         <v>21</v>
       </c>
       <c r="E228" s="35" t="s">
@@ -14078,22 +14079,22 @@
       <c r="K228" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="L228" s="119" t="s">
+      <c r="L228" s="118" t="s">
         <v>27</v>
       </c>
       <c r="M228" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N228" s="35" t="s">
         <v>739</v>
       </c>
-      <c r="O228" s="146"/>
+      <c r="O228" s="145"/>
       <c r="P228" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="229" spans="1:253" s="2" customFormat="1">
-      <c r="A229" s="146"/>
+      <c r="A229" s="145"/>
       <c r="B229" s="29"/>
       <c r="C229" s="29" t="s">
         <v>333</v>
@@ -14132,18 +14133,18 @@
       <c r="N229" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="O229" s="146"/>
+      <c r="O229" s="145"/>
       <c r="P229" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="230" spans="1:253" s="2" customFormat="1">
-      <c r="A230" s="146"/>
-      <c r="B230" s="91"/>
-      <c r="C230" s="91" t="s">
+      <c r="A230" s="145"/>
+      <c r="B230" s="90"/>
+      <c r="C230" s="90" t="s">
         <v>720</v>
       </c>
-      <c r="D230" s="97" t="s">
+      <c r="D230" s="96" t="s">
         <v>39</v>
       </c>
       <c r="E230" s="29" t="s">
@@ -14152,14 +14153,14 @@
       <c r="F230" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G230" s="98">
+      <c r="G230" s="97">
         <v>36467</v>
       </c>
-      <c r="H230" s="104">
+      <c r="H230" s="103">
         <f t="shared" ca="1" si="3"/>
         <v>26</v>
       </c>
-      <c r="I230" s="91" t="s">
+      <c r="I230" s="90" t="s">
         <v>24</v>
       </c>
       <c r="J230" s="29" t="s">
@@ -14168,7 +14169,7 @@
       <c r="K230" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="L230" s="118" t="s">
+      <c r="L230" s="117" t="s">
         <v>27</v>
       </c>
       <c r="M230" s="25" t="s">
@@ -14177,13 +14178,13 @@
       <c r="N230" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O230" s="146"/>
+      <c r="O230" s="145"/>
       <c r="P230" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="231" spans="1:253" s="2" customFormat="1">
-      <c r="A231" s="151" t="s">
+      <c r="A231" s="150" t="s">
         <v>335</v>
       </c>
       <c r="B231" s="39" t="s">
@@ -14221,12 +14222,12 @@
         <v>27</v>
       </c>
       <c r="M231" s="25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N231" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="O231" s="151" t="s">
+      <c r="O231" s="150" t="s">
         <v>36</v>
       </c>
       <c r="P231" s="46" t="s">
@@ -14234,7 +14235,7 @@
       </c>
     </row>
     <row r="232" spans="1:253" s="2" customFormat="1">
-      <c r="A232" s="151"/>
+      <c r="A232" s="150"/>
       <c r="B232" s="29"/>
       <c r="C232" s="30" t="s">
         <v>337</v>
@@ -14268,18 +14269,18 @@
         <v>27</v>
       </c>
       <c r="M232" s="29" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N232" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="O232" s="151"/>
+      <c r="O232" s="150"/>
       <c r="P232" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="233" spans="1:253" s="2" customFormat="1">
-      <c r="A233" s="151"/>
+      <c r="A233" s="150"/>
       <c r="B233" s="29"/>
       <c r="C233" s="30" t="s">
         <v>338</v>
@@ -14313,18 +14314,18 @@
         <v>27</v>
       </c>
       <c r="M233" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N233" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O233" s="151"/>
+      <c r="O233" s="150"/>
       <c r="P233" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="234" spans="1:253" s="2" customFormat="1">
-      <c r="A234" s="151"/>
+      <c r="A234" s="150"/>
       <c r="B234" s="29"/>
       <c r="C234" s="30" t="s">
         <v>339</v>
@@ -14358,18 +14359,18 @@
         <v>27</v>
       </c>
       <c r="M234" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N234" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O234" s="146"/>
+      <c r="O234" s="145"/>
       <c r="P234" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="235" spans="1:253" s="2" customFormat="1">
-      <c r="A235" s="151"/>
+      <c r="A235" s="150"/>
       <c r="B235" s="29"/>
       <c r="C235" s="30" t="s">
         <v>340</v>
@@ -14403,18 +14404,18 @@
         <v>27</v>
       </c>
       <c r="M235" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N235" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="O235" s="146"/>
+      <c r="O235" s="145"/>
       <c r="P235" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="236" spans="1:253" s="2" customFormat="1">
-      <c r="A236" s="151"/>
+      <c r="A236" s="150"/>
       <c r="B236" s="29"/>
       <c r="C236" s="30" t="s">
         <v>341</v>
@@ -14453,13 +14454,13 @@
       <c r="N236" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="O236" s="146"/>
+      <c r="O236" s="145"/>
       <c r="P236" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="237" spans="1:253" s="2" customFormat="1">
-      <c r="A237" s="151"/>
+      <c r="A237" s="150"/>
       <c r="B237" s="35"/>
       <c r="C237" s="36" t="s">
         <v>342</v>
@@ -14493,27 +14494,27 @@
         <v>27</v>
       </c>
       <c r="M237" s="35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N237" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="O237" s="147"/>
+      <c r="O237" s="146"/>
       <c r="P237" s="46" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="238" spans="1:253">
-      <c r="E238" s="111"/>
-      <c r="F238" s="112"/>
+      <c r="E238" s="110"/>
+      <c r="F238" s="111"/>
     </row>
     <row r="239" spans="1:253" s="4" customFormat="1">
       <c r="B239" s="3"/>
       <c r="C239" s="81"/>
-      <c r="E239" s="113" t="s">
+      <c r="E239" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="F239" s="114">
+      <c r="F239" s="113">
         <f>COUNTIF($D$6:$D$237,"l")</f>
         <v>116</v>
       </c>
@@ -14764,10 +14765,10 @@
     <row r="240" spans="1:253" s="4" customFormat="1">
       <c r="B240" s="3"/>
       <c r="C240" s="81"/>
-      <c r="E240" s="113" t="s">
+      <c r="E240" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="F240" s="114">
+      <c r="F240" s="113">
         <f>COUNTIF($D$6:$D$237,"P")</f>
         <v>110</v>
       </c>
@@ -15016,8 +15017,8 @@
       <c r="IS240" s="3"/>
     </row>
     <row r="241" spans="2:253">
-      <c r="E241" s="111"/>
-      <c r="F241" s="112"/>
+      <c r="E241" s="110"/>
+      <c r="F241" s="111"/>
     </row>
     <row r="242" spans="2:253" s="4" customFormat="1">
       <c r="B242" s="3"/>

--- a/data_warga_rt06.xlsx
+++ b/data_warga_rt06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M.FAHMI ILMAN N\Desktop\WebsitedataRT06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4D934E-632B-4BA1-B03F-0158C22C301E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C0CB89-E56E-43C8-B8C6-C9E1A96E44E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5906" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5897" uniqueCount="762">
   <si>
     <t>DAFTAR PENDUDUK RT 06 - RW 14</t>
   </si>
@@ -10594,34 +10594,16 @@
       <c r="B152" s="66"/>
       <c r="C152" s="89"/>
       <c r="D152" s="66"/>
-      <c r="E152" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="F152" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="G152" s="66" t="s">
-        <v>172</v>
-      </c>
+      <c r="E152" s="66"/>
+      <c r="F152" s="66"/>
+      <c r="G152" s="66"/>
       <c r="H152" s="66"/>
-      <c r="I152" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="J152" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="K152" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="L152" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="M152" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="N152" s="66" t="s">
-        <v>172</v>
-      </c>
+      <c r="I152" s="66"/>
+      <c r="J152" s="66"/>
+      <c r="K152" s="66"/>
+      <c r="L152" s="66"/>
+      <c r="M152" s="66"/>
+      <c r="N152" s="66"/>
       <c r="O152" s="87" t="s">
         <v>58</v>
       </c>
